--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -403,945 +403,1653 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F12"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>enemyBaseHp</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>1스테이지 기준 일반 적 기본 HP</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>적 기본 HP</v>
+      </c>
+      <c r="C4" t="str">
+        <v>enemyBaseHp</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1스테이지 기준 일반 적 기본 HP</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>적 HP 증가율</v>
+      </c>
+      <c r="C5" t="str">
         <v>enemyHpGrowth</v>
       </c>
-      <c r="B3">
+      <c r="D5">
         <v>1.15</v>
       </c>
-      <c r="C3" t="str">
-        <v>스테이지 1개당 적 HP 증가 배율</v>
-      </c>
-      <c r="D3">
+      <c r="E5">
         <v>1.15</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="F5" t="str">
+        <v>적 HP = enemyBaseHp × enemyHpGrowth^(스테이지-1)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>적 기본 공격력</v>
+      </c>
+      <c r="C6" t="str">
         <v>enemyBaseAtk</v>
       </c>
-      <c r="B4">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="str">
         <v>1스테이지 기준 적 기본 공격력</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>적 공격력 증가율</v>
+      </c>
+      <c r="C7" t="str">
+        <v>enemyAtkGrowth</v>
+      </c>
+      <c r="D7">
+        <v>1.12</v>
+      </c>
+      <c r="E7">
+        <v>1.12</v>
+      </c>
+      <c r="F7" t="str">
+        <v>적 공격력 = enemyBaseAtk × enemyAtkGrowth^(스테이지-1)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>스테이지당 처치 필요 수</v>
+      </c>
+      <c r="C8" t="str">
+        <v>killsRequiredPerStage</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>일반 스테이지에서 다음 스테이지로 넘어가기 위한 처치 수 (보스는 1 고정)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>보스 등장 주기</v>
+      </c>
+      <c r="C9" t="str">
+        <v>bossInterval</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" t="str">
+        <v>N스테이지마다 보스 등장 (예: 10 = 10, 20, 30...)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>보스 HP 배율</v>
+      </c>
+      <c r="C10" t="str">
+        <v>bossHpMultiplier</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>보스 HP = 일반 계산값 × 이 배율</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>보스 공격력 배율</v>
+      </c>
+      <c r="C11" t="str">
+        <v>bossAtkMultiplier</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>보스 공격력 = 일반 계산값 × 이 배율</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>보스 보상 배율</v>
+      </c>
+      <c r="C12" t="str">
+        <v>bossRewardMultiplier</v>
+      </c>
+      <c r="D12">
         <v>3</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>enemyAtkGrowth</v>
-      </c>
-      <c r="B5">
-        <v>1.12</v>
-      </c>
-      <c r="C5" t="str">
-        <v>스테이지 1개당 적 공격력 증가 배율</v>
-      </c>
-      <c r="D5">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>killsRequiredPerStage</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="str">
-        <v>일반 스테이지에서 다음 스테이지로 넘어가기 위한 처치 수</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>bossInterval</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>N스테이지마다 보스 등장 (예: 10 = 10, 20, 30...)</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>bossHpMultiplier</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="str">
-        <v>보스 HP = 일반 계산값 × 이 배율</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>bossAtkMultiplier</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="str">
-        <v>보스 공격력 = 일반 계산값 × 이 배율</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>bossRewardMultiplier</v>
-      </c>
-      <c r="B10">
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="C10" t="str">
+      <c r="F12" t="str">
         <v>보스 처치 시 골드/성장에너지/존재력 보상 × 이 배율</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F10"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>goldBaseReward</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>1스테이지 기준 처치당 골드 기본 획득량</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>골드 기본 획득량</v>
+      </c>
+      <c r="C4" t="str">
+        <v>goldBaseReward</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1스테이지 기준 처치당 골드 기본 획득량</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>골드 증가율</v>
+      </c>
+      <c r="C5" t="str">
         <v>goldGrowth</v>
       </c>
-      <c r="B3">
+      <c r="D5">
         <v>1.1</v>
       </c>
-      <c r="C3" t="str">
-        <v>스테이지 1개당 골드 보상 증가 배율</v>
-      </c>
-      <c r="D3">
+      <c r="E5">
         <v>1.1</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="F5" t="str">
+        <v>골드 보상 = goldBaseReward × goldGrowth^(스테이지-1)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>성장에너지 기본 획득량</v>
+      </c>
+      <c r="C6" t="str">
         <v>growthEnergyBaseReward</v>
       </c>
-      <c r="B4">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str">
         <v>1스테이지 기준 처치당 성장에너지 기본 획득량</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>성장에너지 증가율</v>
+      </c>
+      <c r="C7" t="str">
+        <v>growthEnergyGrowth</v>
+      </c>
+      <c r="D7">
+        <v>1.08</v>
+      </c>
+      <c r="E7">
+        <v>1.08</v>
+      </c>
+      <c r="F7" t="str">
+        <v>성장에너지 보상 = growthEnergyBaseReward × growthEnergyGrowth^(스테이지-1)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>존재력 보상 나눔값</v>
+      </c>
+      <c r="C8" t="str">
+        <v>existRewardStageDivisor</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8" t="str">
+        <v>존재력 보상 = max(1, floor(스테이지 / 이 값))</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>존재력 보스 배율</v>
+      </c>
+      <c r="C9" t="str">
+        <v>existRewardBossMultiplier</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>growthEnergyGrowth</v>
-      </c>
-      <c r="B5">
-        <v>1.08</v>
-      </c>
-      <c r="C5" t="str">
-        <v>스테이지 1개당 성장에너지 보상 증가 배율</v>
-      </c>
-      <c r="D5">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>existRewardStageDivisor</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>존재력 보상 = max(1, floor(스테이지 / 이 값))</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>existRewardBossMultiplier</v>
-      </c>
-      <c r="B7">
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="C7" t="str">
+      <c r="F9" t="str">
         <v>보스 처치 시 존재력 보상 × 이 배율</v>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>보스 시간에너지 보상</v>
+      </c>
+      <c r="C10" t="str">
         <v>bossTimeEnergyReward</v>
       </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="str">
         <v>보스 처치 시 지급하는 시간에너지 고정량</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:F17"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>statBaseAtk</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>ATK 레벨 0 기본값</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>statBaseDef</v>
-      </c>
-      <c r="B3">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="C3" t="str">
-        <v>DEF 레벨 0 기본값</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>statBaseAspd</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="str">
+        <v>ATK 기본값</v>
       </c>
       <c r="C4" t="str">
-        <v>ASPD 레벨 0 기본값</v>
+        <v>statBaseAtk</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>ATK 레벨 0 기본값</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DEF 기본값</v>
+      </c>
+      <c r="C5" t="str">
+        <v>statBaseDef</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DEF 레벨 0 기본값</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ASPD 기본값</v>
+      </c>
+      <c r="C6" t="str">
+        <v>statBaseAspd</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>ASPD 레벨 0 기본값</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>CRIT 기본값</v>
+      </c>
+      <c r="C7" t="str">
         <v>statBaseCrit</v>
       </c>
-      <c r="B5">
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
         <v>CRIT(%) 레벨 0 기본값</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CRIT_DMG 기본값</v>
+      </c>
+      <c r="C8" t="str">
         <v>statBaseCritDmg</v>
       </c>
-      <c r="B6">
+      <c r="D8">
         <v>150</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E8">
+        <v>150</v>
+      </c>
+      <c r="F8" t="str">
         <v>CRIT_DMG(%) 레벨 0 기본값</v>
       </c>
-      <c r="D6">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EXIST_GAIN 기본값</v>
+      </c>
+      <c r="C9" t="str">
         <v>statBaseExistGain</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>EXIST_GAIN 배율 레벨 0 기본값</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>statGrowthAtk</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ATK 레벨당 상승치</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>statGrowthDef</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="str">
-        <v>DEF 레벨당 상승치</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>EXIST_GAIN 배율 레벨 0 기본값</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ATK 레벨당 상승치</v>
+      </c>
+      <c r="C10" t="str">
+        <v>statGrowthAtk</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>레벨업 1회당 ATK 상승치</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>DEF 레벨당 상승치</v>
+      </c>
+      <c r="C11" t="str">
+        <v>statGrowthDef</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>레벨업 1회당 DEF 상승치</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ASPD 레벨당 상승치</v>
+      </c>
+      <c r="C12" t="str">
         <v>statGrowthAspd</v>
       </c>
-      <c r="B10">
+      <c r="D12">
         <v>0.05</v>
       </c>
-      <c r="C10" t="str">
-        <v>ASPD 레벨당 상승치</v>
-      </c>
-      <c r="D10">
+      <c r="E12">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+      <c r="F12" t="str">
+        <v>레벨업 1회당 ASPD 상승치</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CRIT 레벨당 상승치</v>
+      </c>
+      <c r="C13" t="str">
         <v>statGrowthCrit</v>
       </c>
-      <c r="B11">
+      <c r="D13">
         <v>0.5</v>
       </c>
-      <c r="C11" t="str">
-        <v>CRIT(%) 레벨당 상승치</v>
-      </c>
-      <c r="D11">
+      <c r="E13">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
+      <c r="F13" t="str">
+        <v>레벨업 1회당 CRIT(%) 상승치</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>CRIT_DMG 레벨당 상승치</v>
+      </c>
+      <c r="C14" t="str">
         <v>statGrowthCritDmg</v>
       </c>
-      <c r="B12">
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="C12" t="str">
-        <v>CRIT_DMG(%) 레벨당 상승치</v>
-      </c>
-      <c r="D12">
+      <c r="E14">
         <v>2</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
+      <c r="F14" t="str">
+        <v>레벨업 1회당 CRIT_DMG(%) 상승치</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>EXIST_GAIN 레벨당 상승치</v>
+      </c>
+      <c r="C15" t="str">
         <v>statGrowthExistGain</v>
       </c>
-      <c r="B13">
+      <c r="D15">
         <v>0.02</v>
       </c>
-      <c r="C13" t="str">
-        <v>EXIST_GAIN 배율 레벨당 상승치</v>
-      </c>
-      <c r="D13">
+      <c r="E15">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
+      <c r="F15" t="str">
+        <v>레벨업 1회당 EXIST_GAIN 배율 상승치</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>스탯 업그레이드 기준 비용</v>
+      </c>
+      <c r="C16" t="str">
         <v>statUpgradeCostBase</v>
       </c>
-      <c r="B14">
+      <c r="D16">
         <v>8</v>
       </c>
-      <c r="C14" t="str">
-        <v>스탯 업그레이드 비용(성장에너지) 기본값 (레벨 0 → 1)</v>
-      </c>
-      <c r="D14">
+      <c r="E16">
         <v>8</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
+      <c r="F16" t="str">
+        <v>스탯 업그레이드 비용(성장에너지) 레벨 0→1 기준값</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="str">
+        <v>스탯 업그레이드 비용 증가율</v>
+      </c>
+      <c r="C17" t="str">
         <v>statUpgradeCostGrowth</v>
       </c>
-      <c r="B15">
+      <c r="D17">
         <v>1.18</v>
       </c>
-      <c r="C15" t="str">
-        <v>스탯 업그레이드 비용 레벨당 증가 배율</v>
-      </c>
-      <c r="D15">
+      <c r="E17">
         <v>1.18</v>
+      </c>
+      <c r="F17" t="str">
+        <v>비용 = statUpgradeCostBase × statUpgradeCostGrowth^현재레벨</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F9"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>equipmentValuePerLevel</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>장비 강화 레벨당 ATK/DEF 상승치 (5부위 공용)</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>장비 레벨당 상승치</v>
+      </c>
+      <c r="C4" t="str">
+        <v>equipmentValuePerLevel</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>장비 강화 레벨당 ATK/DEF 상승치 (5부위 공용)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>장비 강화 기준 비용</v>
+      </c>
+      <c r="C5" t="str">
         <v>equipmentCostBase</v>
       </c>
-      <c r="B3">
+      <c r="D5">
         <v>15</v>
       </c>
-      <c r="C3" t="str">
-        <v>장비 강화 비용(골드) 기본값</v>
-      </c>
-      <c r="D3">
+      <c r="E5">
         <v>15</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="F5" t="str">
+        <v>장비 강화 비용(골드) 레벨 0→1 기준값</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>장비 강화 비용 증가율</v>
+      </c>
+      <c r="C6" t="str">
         <v>equipmentCostGrowth</v>
       </c>
-      <c r="B4">
+      <c r="D6">
         <v>1.22</v>
       </c>
-      <c r="C4" t="str">
-        <v>장비 강화 비용 레벨당 증가 배율</v>
-      </c>
-      <c r="D4">
+      <c r="E6">
         <v>1.22</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="F6" t="str">
+        <v>비용 = equipmentCostBase × equipmentCostGrowth^현재레벨</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>숙련 레벨당 ATK 배율</v>
+      </c>
+      <c r="C7" t="str">
         <v>masteryMultiplierPerLevel</v>
       </c>
-      <c r="B5">
+      <c r="D7">
         <v>0.05</v>
       </c>
-      <c r="C5" t="str">
-        <v>무기 숙련 레벨당 ATK 배율 상승치 (예: 0.05 = +5%)</v>
-      </c>
-      <c r="D5">
+      <c r="E7">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="F7" t="str">
+        <v>무기 숙련 레벨당 ATK 배율 상승치 (0.05 = +5%)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>숙련 기준 비용</v>
+      </c>
+      <c r="C8" t="str">
         <v>masteryCostBase</v>
       </c>
-      <c r="B6">
+      <c r="D8">
         <v>10</v>
       </c>
-      <c r="C6" t="str">
-        <v>무기 숙련 비용(정수/essence) 기본값</v>
-      </c>
-      <c r="D6">
+      <c r="E8">
         <v>10</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+      <c r="F8" t="str">
+        <v>무기 숙련 비용(정수/essence) 레벨 0→1 기준값</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>숙련 비용 증가율</v>
+      </c>
+      <c r="C9" t="str">
         <v>masteryCostGrowth</v>
       </c>
-      <c r="B7">
+      <c r="D9">
         <v>1.25</v>
       </c>
-      <c r="C7" t="str">
-        <v>무기 숙련 비용 레벨당 증가 배율</v>
-      </c>
-      <c r="D7">
+      <c r="E9">
         <v>1.25</v>
+      </c>
+      <c r="F9" t="str">
+        <v>비용 = masteryCostBase × masteryCostGrowth^현재레벨</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F14"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>totalNodes</v>
-      </c>
-      <c r="B2">
-        <v>50</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>존재력 트리 총 노드 개수</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>총 노드 개수</v>
+      </c>
+      <c r="C4" t="str">
+        <v>totalNodes</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4" t="str">
+        <v>존재력 트리 총 노드 개수</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>노드 비용 기준값</v>
+      </c>
+      <c r="C5" t="str">
         <v>nodeCostBase</v>
       </c>
-      <c r="B3">
+      <c r="D5">
         <v>10</v>
       </c>
-      <c r="C3" t="str">
-        <v>노드 해금 비용(존재력) 기본값 (order=1)</v>
-      </c>
-      <c r="D3">
+      <c r="E5">
         <v>10</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="F5" t="str">
+        <v>노드 해금 비용(존재력) order=1 기준값</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>노드 비용 증가율</v>
+      </c>
+      <c r="C6" t="str">
         <v>nodeCostGrowth</v>
       </c>
-      <c r="B4">
+      <c r="D6">
         <v>1.35</v>
       </c>
-      <c r="C4" t="str">
-        <v>노드 해금 비용 order 1당 증가 배율</v>
-      </c>
-      <c r="D4">
+      <c r="E6">
         <v>1.35</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="F6" t="str">
+        <v>비용 = nodeCostBase × nodeCostGrowth^(order-1)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>스탯 효과 기본값</v>
+      </c>
+      <c r="C7" t="str">
         <v>statValueBase</v>
       </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="str">
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="str">
         <v>스탯 지급 노드의 효과값 기본치</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>스탯 효과 티어 증가폭</v>
+      </c>
+      <c r="C8" t="str">
         <v>statValueTierStep</v>
       </c>
-      <c r="B6">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="str">
         <v>10노드(1티어)마다 스탯 효과값에 더해지는 값</v>
       </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>재화 지급 기본값</v>
+      </c>
+      <c r="C9" t="str">
         <v>currencyAmountBase</v>
       </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="str">
         <v>재화 지급 노드의 지급량 기본치</v>
       </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>재화 지급 티어 증가폭</v>
+      </c>
+      <c r="C10" t="str">
         <v>currencyAmountTierStep</v>
       </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="str">
         <v>10노드(1티어)마다 재화 지급량에 더해지는 값</v>
       </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>리버스 필요 노드 수</v>
+      </c>
+      <c r="C11" t="str">
         <v>reverseRequiredNodes</v>
       </c>
-      <c r="B9">
+      <c r="D11">
         <v>15</v>
       </c>
-      <c r="C9" t="str">
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11" t="str">
         <v>리버스 특별 해금이 나타나는 데 필요한 트리 해금 개수</v>
       </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>타임하이스트 필요 노드 수</v>
+      </c>
+      <c r="C12" t="str">
         <v>timeHeistRequiredNodes</v>
       </c>
-      <c r="B10">
+      <c r="D12">
         <v>33</v>
       </c>
-      <c r="C10" t="str">
+      <c r="E12">
+        <v>33</v>
+      </c>
+      <c r="F12" t="str">
         <v>타임 하이스트 특별 해금이 나타나는 데 필요한 트리 해금 개수</v>
       </c>
-      <c r="D10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>리버스 해금 비용</v>
+      </c>
+      <c r="C13" t="str">
         <v>reverseUnlockCost</v>
       </c>
-      <c r="B11">
+      <c r="D13">
         <v>667</v>
       </c>
-      <c r="C11" t="str">
+      <c r="E13">
+        <v>667</v>
+      </c>
+      <c r="F13" t="str">
         <v>리버스 해금에 필요한 존재력</v>
       </c>
-      <c r="D11">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>타임하이스트 해금 비용</v>
+      </c>
+      <c r="C14" t="str">
         <v>timeHeistUnlockCost</v>
       </c>
-      <c r="B12">
+      <c r="D14">
         <v>148142</v>
       </c>
-      <c r="C12" t="str">
+      <c r="E14">
+        <v>148142</v>
+      </c>
+      <c r="F14" t="str">
         <v>타임 하이스트 해금에 필요한 존재력</v>
-      </c>
-      <c r="D12">
-        <v>148142</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F9"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>stageOffset</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>현재 스테이지 + 이 값 = 선취할 미래 스테이지</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>선취 스테이지 오프셋</v>
+      </c>
+      <c r="C4" t="str">
+        <v>stageOffset</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4" t="str">
+        <v>현재 스테이지 + 이 값 = 선취할 미래 스테이지</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>클리어 환산 배수</v>
+      </c>
+      <c r="C5" t="str">
         <v>clearCount</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="str">
         <v>선취 스테이지를 몇 클리어분으로 환산해 보상을 줄지</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>기준 비용</v>
+      </c>
+      <c r="C6" t="str">
         <v>baseCost</v>
       </c>
-      <c r="B4">
+      <c r="D6">
         <v>20</v>
       </c>
-      <c r="C4" t="str">
-        <v>1회차 사용 비용(시간에너지) 기본값</v>
-      </c>
-      <c r="D4">
+      <c r="E6">
         <v>20</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="F6" t="str">
+        <v>1회차 사용 비용(시간에너지) 기준값</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>비용 증가율</v>
+      </c>
+      <c r="C7" t="str">
         <v>costGrowth</v>
       </c>
-      <c r="B5">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="C5" t="str">
-        <v>사용 1회당 비용 증가 배율</v>
-      </c>
-      <c r="D5">
+      <c r="E7">
         <v>2</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="F7" t="str">
+        <v>비용 = baseCost × costGrowth^사용횟수</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>기준 쿨타임(초)</v>
+      </c>
+      <c r="C8" t="str">
         <v>baseCooldownSeconds</v>
       </c>
-      <c r="B6">
+      <c r="D8">
         <v>7200</v>
       </c>
-      <c r="C6" t="str">
-        <v>1회차 사용 후 쿨타임 기본값(초). 7200 = 2시간</v>
-      </c>
-      <c r="D6">
+      <c r="E8">
         <v>7200</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+      <c r="F8" t="str">
+        <v>1회차 사용 후 쿨타임 기준값. 7200 = 2시간</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>쿨타임 증가율</v>
+      </c>
+      <c r="C9" t="str">
         <v>cooldownGrowth</v>
       </c>
-      <c r="B7">
+      <c r="D9">
         <v>1.5</v>
       </c>
-      <c r="C7" t="str">
-        <v>사용 1회당 쿨타임 증가 배율</v>
-      </c>
-      <c r="D7">
+      <c r="E9">
         <v>1.5</v>
+      </c>
+      <c r="F9" t="str">
+        <v>쿨타임 = baseCooldownSeconds × cooldownGrowth^사용횟수</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>번호</v>
+      </c>
+      <c r="B1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="C1" t="str">
         <v>key (수정 금지)</v>
       </c>
-      <c r="B1" t="str">
-        <v>value</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>value (여기만 수정)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>기본값 (참고용)</v>
+      </c>
+      <c r="F1" t="str">
         <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>기본값 (참고용)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>maxHours</v>
-      </c>
-      <c r="B2">
-        <v>8</v>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>//Name</v>
       </c>
       <c r="C2" t="str">
-        <v>오프라인 보상으로 인정하는 최대 시간(시간 단위)</v>
-      </c>
-      <c r="D2">
-        <v>8</v>
+        <v>Key</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Value</v>
+      </c>
+      <c r="E2" t="str">
+        <v>//Default</v>
+      </c>
+      <c r="F2" t="str">
+        <v>//Desc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>int</v>
+      </c>
+      <c r="B3" t="str">
+        <v>string</v>
+      </c>
+      <c r="C3" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" t="str">
+        <v>float</v>
+      </c>
+      <c r="E3" t="str">
+        <v>float</v>
+      </c>
+      <c r="F3" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>최대 인정 시간(시간)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>maxHours</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4" t="str">
+        <v>오프라인 보상으로 인정하는 최대 시간</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>보상 배율</v>
+      </c>
+      <c r="C5" t="str">
         <v>rewardMultiplier</v>
       </c>
-      <c r="B3">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
         <v>오프라인 보상 전체에 곱해지는 배율 (1 = 온라인과 동일 효율)</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="402">
   <si>
     <t>테이블명</t>
   </si>
@@ -1047,6 +1047,12 @@
     <t>Stat</t>
   </si>
   <si>
+    <t>치명타 확률</t>
+  </si>
+  <si>
+    <t>존재력 획득량</t>
+  </si>
+  <si>
     <t>System</t>
   </si>
   <si>
@@ -1059,7 +1065,175 @@
     <t>숙련의 정수</t>
   </si>
   <si>
+    <t>존재력 트리</t>
+  </si>
+  <si>
     <t>EXIST_TREE</t>
+  </si>
+  <si>
+    <t>존재</t>
+  </si>
+  <si>
+    <t>EXIST_ABBR</t>
+  </si>
+  <si>
+    <t>CurrencyAbbr</t>
+  </si>
+  <si>
+    <t>성장</t>
+  </si>
+  <si>
+    <t>GROWTH_ABBR</t>
+  </si>
+  <si>
+    <t>시간</t>
+  </si>
+  <si>
+    <t>TIME_ABBR</t>
+  </si>
+  <si>
+    <t>GOLD_ABBR</t>
+  </si>
+  <si>
+    <t>정수</t>
+  </si>
+  <si>
+    <t>ESSENCE_ABBR</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Tab</t>
+  </si>
+  <si>
+    <t>장비</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>가챠</t>
+  </si>
+  <si>
+    <t>Gacha</t>
+  </si>
+  <si>
+    <t>ExistTree</t>
+  </si>
+  <si>
+    <t>도감</t>
+  </si>
+  <si>
+    <t>Dogam</t>
+  </si>
+  <si>
+    <t>닫기</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>취소</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>확인</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>실행</t>
+  </si>
+  <si>
+    <t>Execute</t>
+  </si>
+  <si>
+    <t>강탈</t>
+  </si>
+  <si>
+    <t>Steal</t>
+  </si>
+  <si>
+    <t>받기</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>해금</t>
+  </si>
+  <si>
+    <t>Unlock</t>
+  </si>
+  <si>
+    <t>강화</t>
+  </si>
+  <si>
+    <t>Enhance</t>
+  </si>
+  <si>
+    <t>수련</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>업그레이드</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>최대로</t>
+  </si>
+  <si>
+    <t>MaxAll</t>
+  </si>
+  <si>
+    <t>뒤로</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>잠김</t>
+  </si>
+  <si>
+    <t>Locked</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>해금됨</t>
+  </si>
+  <si>
+    <t>Unlocked</t>
+  </si>
+  <si>
+    <t>사용 가능</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>효과</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>비용</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1306,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1155,11 +1329,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1178,6 +1367,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3889,7 +4084,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -4015,7 +4210,7 @@
         <v>40004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>240</v>
@@ -4049,7 +4244,7 @@
         <v>40006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>244</v>
@@ -4072,7 +4267,7 @@
         <v>268</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4089,7 +4284,7 @@
         <v>271</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,7 +4383,7 @@
         <v>311</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>252</v>
@@ -4208,7 +4403,7 @@
         <v>222</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -4225,7 +4420,7 @@
         <v>225</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -4236,13 +4431,13 @@
         <v>40017</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>227</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -4259,7 +4454,7 @@
         <v>229</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4276,7 +4471,7 @@
         <v>231</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4287,13 +4482,489 @@
         <v>40020</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7">
+        <v>40021</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7">
+        <v>40022</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>23</v>
+      </c>
+      <c r="B27" s="7">
+        <v>40023</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7">
+        <v>40024</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7">
+        <v>40025</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>26</v>
+      </c>
+      <c r="B30" s="7">
+        <v>40026</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>27</v>
+      </c>
+      <c r="B31" s="7">
+        <v>40027</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>28</v>
+      </c>
+      <c r="B32" s="7">
+        <v>40028</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>29</v>
+      </c>
+      <c r="B33" s="7">
+        <v>40029</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>339</v>
+      <c r="D33" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7">
+        <v>40030</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>31</v>
+      </c>
+      <c r="B35" s="7">
+        <v>40031</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7">
+        <v>40032</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>33</v>
+      </c>
+      <c r="B37" s="7">
+        <v>40033</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>34</v>
+      </c>
+      <c r="B38" s="7">
+        <v>40034</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>35</v>
+      </c>
+      <c r="B39" s="7">
+        <v>40035</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>36</v>
+      </c>
+      <c r="B40" s="7">
+        <v>40036</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>37</v>
+      </c>
+      <c r="B41" s="7">
+        <v>40037</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>38</v>
+      </c>
+      <c r="B42" s="7">
+        <v>40038</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>39</v>
+      </c>
+      <c r="B43" s="7">
+        <v>40039</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>40</v>
+      </c>
+      <c r="B44" s="7">
+        <v>40040</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>41</v>
+      </c>
+      <c r="B45" s="7">
+        <v>40041</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>42</v>
+      </c>
+      <c r="B46" s="7">
+        <v>40042</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>43</v>
+      </c>
+      <c r="B47" s="7">
+        <v>40043</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>44</v>
+      </c>
+      <c r="B48" s="7">
+        <v>40044</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>45</v>
+      </c>
+      <c r="B49" s="7">
+        <v>40045</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>46</v>
+      </c>
+      <c r="B50" s="7">
+        <v>40046</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>47</v>
+      </c>
+      <c r="B51" s="7">
+        <v>40047</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>48</v>
+      </c>
+      <c r="B52" s="7">
+        <v>40048</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="431">
   <si>
     <t>테이블명</t>
   </si>
@@ -597,6 +597,54 @@
     <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
   </si>
   <si>
+    <t>회차 보너스 계수</t>
+  </si>
+  <si>
+    <t>BonusBase</t>
+  </si>
+  <si>
+    <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = floor(BonusBase × 도달스테이지^BonusExponent)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>회차 보너스 지수</t>
+  </si>
+  <si>
+    <t>BonusExponent</t>
+  </si>
+  <si>
+    <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
+  </si>
+  <si>
+    <t>포인트당 스탯 상승률</t>
+  </si>
+  <si>
+    <t>BonusPerPoint</t>
+  </si>
+  <si>
+    <t>누적 보너스 포인트 1당 전 스탯에 곱연산으로 붙는 상승률(%). 전 스탯 보너스율 = 누적 포인트 × 이 값</t>
+  </si>
+  <si>
+    <t>보너스 최소 스테이지</t>
+  </si>
+  <si>
+    <t>MinStageForBonus</t>
+  </si>
+  <si>
+    <t>리버스 시점의 도달 스테이지가 이 값 미만이면 보너스 포인트를 얻지 못함</t>
+  </si>
+  <si>
+    <t>보너스 설명</t>
+  </si>
+  <si>
+    <t>//BonusDescription</t>
+  </si>
+  <si>
+    <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
+  </si>
+  <si>
     <t>CommonTable</t>
   </si>
   <si>
@@ -972,6 +1020,9 @@
     <t>스테이지/스탯/장비/숙련 초기화 + 소비 재화 전액 환급. 존재력 트리는 유지</t>
   </si>
   <si>
+    <t>포인트 = floor(1.0 × 도달스테이지^0.5), 10스테이지 미만이면 0. 전 스탯 보너스율(%) = 누적 포인트 × 1.0</t>
+  </si>
+  <si>
     <t>OfflineMaxHours</t>
   </si>
   <si>
@@ -1234,13 +1285,49 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>회차 보너스</t>
+  </si>
+  <si>
+    <t>RebirthBonus</t>
+  </si>
+  <si>
+    <t>현재 회차</t>
+  </si>
+  <si>
+    <t>CurrentCycle</t>
+  </si>
+  <si>
+    <t>누적 포인트</t>
+  </si>
+  <si>
+    <t>TotalPoints</t>
+  </si>
+  <si>
+    <t>획득 예정 포인트</t>
+  </si>
+  <si>
+    <t>PendingPoints</t>
+  </si>
+  <si>
+    <t>전 스탯 보너스</t>
+  </si>
+  <si>
+    <t>AllStatBonus</t>
+  </si>
+  <si>
+    <t>최고 도달 스테이지</t>
+  </si>
+  <si>
+    <t>MaxStageReached</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1274,8 +1361,30 @@
       <sz val="9"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="7F6000"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="1F3864"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="1F3864"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1303,6 +1412,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="008EA9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="8EA9DB"/>
       </patternFill>
     </fill>
   </fills>
@@ -1348,13 +1477,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1368,11 +1500,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1679,7 +1820,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -3318,287 +3459,387 @@
       <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F90" s="2"/>
+      <c r="C90" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F91" s="2"/>
+      <c r="A91" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="A92" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D92" s="2" t="s">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F92" s="2"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F93" s="2"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F94" s="2"/>
+      <c r="E94" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>197</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="F96" s="2"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>7</v>
+        <v>207</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="F97" s="2"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="F98" s="2"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F99" s="2"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F100" s="2"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="F101" s="2"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D102" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>213</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D103" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F103" s="2"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="D104" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F104" s="2"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="D105" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F105" s="2"/>
     </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F106" s="2"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F107" s="2"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F108" s="2"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F109" s="2"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F110" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F105"/>
+  <autoFilter ref="A1:F110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3608,7 +3849,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -3621,23 +3862,30 @@
     <col min="10" max="10" width="23" customWidth="1"/>
     <col min="11" max="11" width="17.3" customWidth="1"/>
     <col min="12" max="12" width="60" customWidth="1"/>
+    <col min="13" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3674,123 +3922,183 @@
       <c r="L2" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="M2" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="M3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="M4" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>35001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" s="6" t="b">
+        <v>283</v>
+      </c>
+      <c r="D5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="b">
+      <c r="E5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="b">
+      <c r="F5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="6" t="b">
+      <c r="G5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="b">
+      <c r="H5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="6" t="b">
+      <c r="I5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="6" t="b">
+      <c r="J5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="6" t="b">
+      <c r="K5" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
+      </c>
+      <c r="M5" s="12">
+        <v>1</v>
+      </c>
+      <c r="N5" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="12">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L5"/>
+  <autoFilter ref="A4:Q5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3812,13 +4120,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3828,249 +4136,249 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>36001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="6">
+        <v>332</v>
+      </c>
+      <c r="E5" s="7">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>36002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E6" s="6">
+        <v>335</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>36003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E7" s="6">
+        <v>338</v>
+      </c>
+      <c r="E7" s="7">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>36004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E8" s="6">
+        <v>341</v>
+      </c>
+      <c r="E8" s="7">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>36005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="6">
+        <v>344</v>
+      </c>
+      <c r="E9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>36006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E10" s="6">
+        <v>347</v>
+      </c>
+      <c r="E10" s="7">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>36007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E11" s="6">
+        <v>350</v>
+      </c>
+      <c r="E11" s="7">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>8</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>36008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E12" s="6">
+        <v>353</v>
+      </c>
+      <c r="E12" s="7">
         <v>2</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4084,7 +4392,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -4094,11 +4402,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4108,863 +4416,965 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>209</v>
+      <c r="C4" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>40001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>40002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>40003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>40004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>40005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>40006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>40007</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7">
+        <v>40008</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>40009</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <v>40008</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6">
-        <v>40009</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>10</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>40010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>11</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>40011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="7">
         <v>12</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>40012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>13</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>40013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="7">
         <v>14</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>40014</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>15</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>40015</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="7">
         <v>16</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>40016</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="7">
         <v>17</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>40017</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="7">
         <v>18</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>40018</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="7">
         <v>19</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>40019</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="7">
         <v>20</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>40020</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="12">
         <v>21</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="12">
         <v>40021</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>349</v>
+      <c r="C25" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="12">
         <v>22</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="12">
         <v>40022</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>349</v>
+      <c r="C26" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="12">
         <v>23</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="12">
         <v>40023</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>349</v>
+      <c r="C27" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="12">
         <v>24</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="12">
         <v>40024</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>349</v>
+      <c r="C28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="12">
         <v>25</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="12">
         <v>40025</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>349</v>
+      <c r="C29" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="12">
         <v>26</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="12">
         <v>40026</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>358</v>
+      <c r="C30" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="12">
         <v>27</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="12">
         <v>40027</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>358</v>
+      <c r="C31" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="12">
         <v>28</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="12">
         <v>40028</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>358</v>
+      <c r="C32" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="12">
         <v>29</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="12">
         <v>40029</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>358</v>
+      <c r="C33" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="12">
         <v>30</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="12">
         <v>40030</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>358</v>
+      <c r="C34" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="12">
         <v>31</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="12">
         <v>40031</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>368</v>
+      <c r="C35" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="12">
         <v>32</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="12">
         <v>40032</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>368</v>
+      <c r="C36" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="12">
         <v>33</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="12">
         <v>40033</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>368</v>
+      <c r="C37" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="12">
         <v>34</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="12">
         <v>40034</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>368</v>
+      <c r="C38" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39" s="12">
         <v>35</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="12">
         <v>40035</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>368</v>
+      <c r="C39" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="12">
         <v>36</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="12">
         <v>40036</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>368</v>
+      <c r="C40" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41" s="12">
         <v>37</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="12">
         <v>40037</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>368</v>
+      <c r="C41" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42" s="12">
         <v>38</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="12">
         <v>40038</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>368</v>
+      <c r="C42" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43" s="12">
         <v>39</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="12">
         <v>40039</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>368</v>
+      <c r="C43" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="A44" s="12">
         <v>40</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="12">
         <v>40040</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>368</v>
-      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="12">
         <v>41</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="12">
         <v>40041</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>368</v>
+      <c r="C45" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46" s="12">
         <v>42</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="12">
         <v>40042</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>368</v>
+      <c r="C46" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="12">
         <v>43</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="12">
         <v>40043</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>393</v>
+      <c r="C47" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48" s="12">
         <v>44</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="12">
         <v>40044</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>393</v>
+      <c r="C48" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49" s="12">
         <v>45</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="12">
         <v>40045</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>393</v>
+      <c r="C49" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50" s="12">
         <v>46</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="12">
         <v>40046</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>393</v>
+      <c r="E50" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51" s="12">
         <v>47</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="12">
         <v>40047</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>393</v>
+      <c r="C51" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52" s="12">
         <v>48</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="12">
         <v>40048</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>393</v>
+      <c r="C52" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <v>49</v>
+      </c>
+      <c r="B53" s="12">
+        <v>40049</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>50</v>
+      </c>
+      <c r="B54" s="12">
+        <v>40050</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <v>51</v>
+      </c>
+      <c r="B55" s="12">
+        <v>40051</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>52</v>
+      </c>
+      <c r="B56" s="12">
+        <v>40052</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <v>53</v>
+      </c>
+      <c r="B57" s="12">
+        <v>40053</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <v>54</v>
+      </c>
+      <c r="B58" s="12">
+        <v>40054</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4989,86 +5399,86 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5076,13 +5486,13 @@
         <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5090,13 +5500,13 @@
         <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5104,13 +5514,13 @@
         <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5118,13 +5528,13 @@
         <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5132,13 +5542,13 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5146,41 +5556,41 @@
         <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5188,13 +5598,13 @@
         <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5202,13 +5612,13 @@
         <v>127</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5216,13 +5626,13 @@
         <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5230,13 +5640,13 @@
         <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5244,13 +5654,13 @@
         <v>127</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5258,13 +5668,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5272,13 +5682,13 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5286,13 +5696,13 @@
         <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5300,13 +5710,13 @@
         <v>114</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -5339,22 +5749,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5401,970 +5811,970 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>10001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D5" s="6">
+        <v>288</v>
+      </c>
+      <c r="D5" s="7">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F5" s="6">
+        <v>279</v>
+      </c>
+      <c r="F5" s="7">
         <v>20</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>3</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>5</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="7">
         <v>1</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="7">
         <v>0</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="7">
         <v>1.15</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>10002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D6" s="6">
+        <v>289</v>
+      </c>
+      <c r="D6" s="7">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="6">
+        <v>282</v>
+      </c>
+      <c r="F6" s="7">
         <v>350</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>16</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>33</v>
       </c>
-      <c r="J6" s="6">
-        <v>9</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="J6" s="7">
+        <v>9</v>
+      </c>
+      <c r="K6" s="7">
         <v>2</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>5</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="7">
         <v>1.15</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>10003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D7" s="6">
+        <v>290</v>
+      </c>
+      <c r="D7" s="7">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="6">
+        <v>279</v>
+      </c>
+      <c r="F7" s="7">
         <v>80</v>
       </c>
-      <c r="G7" s="6">
-        <v>9</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="7">
+        <v>9</v>
+      </c>
+      <c r="H7" s="7">
         <v>5</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>12</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>4</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="7">
         <v>1</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="7">
         <v>0</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="7">
         <v>1.15</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>10004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="6">
+        <v>291</v>
+      </c>
+      <c r="D8" s="7">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="6">
+        <v>282</v>
+      </c>
+      <c r="F8" s="7">
         <v>1420</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>50</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>1</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>90</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <v>24</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <v>4</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="7">
         <v>5</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="7">
         <v>1.15</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>10005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D9" s="6">
+        <v>292</v>
+      </c>
+      <c r="D9" s="7">
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F9" s="6">
+        <v>279</v>
+      </c>
+      <c r="F9" s="7">
         <v>327</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>28</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>5</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>33</v>
       </c>
-      <c r="J9" s="6">
-        <v>9</v>
-      </c>
-      <c r="K9" s="6">
+      <c r="J9" s="7">
+        <v>9</v>
+      </c>
+      <c r="K9" s="7">
         <v>2</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <v>0</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="7">
         <v>1.15</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>10006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="6">
+        <v>293</v>
+      </c>
+      <c r="D10" s="7">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="6">
+        <v>282</v>
+      </c>
+      <c r="F10" s="7">
         <v>5755</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>160</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>1</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>237</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <v>54</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="7">
         <v>6</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <v>5</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="7">
         <v>1.15</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>10007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D11" s="6">
+        <v>294</v>
+      </c>
+      <c r="D11" s="7">
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F11" s="6">
+        <v>279</v>
+      </c>
+      <c r="F11" s="7">
         <v>1324</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>89</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <v>5</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="7">
         <v>87</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="7">
         <v>20</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="7">
         <v>3</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="7">
         <v>0</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="7">
         <v>1.15</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="7">
         <v>1.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>8</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>10008</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D12" s="7">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F12" s="7">
+        <v>23290</v>
+      </c>
+      <c r="G12" s="7">
+        <v>498</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
+        <v>615</v>
+      </c>
+      <c r="J12" s="7">
+        <v>120</v>
+      </c>
+      <c r="K12" s="7">
+        <v>8</v>
+      </c>
+      <c r="L12" s="7">
+        <v>5</v>
+      </c>
+      <c r="M12" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N12" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" s="7">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="6">
+      <c r="F13" s="7">
+        <v>5357</v>
+      </c>
+      <c r="G13" s="7">
+        <v>279</v>
+      </c>
+      <c r="H13" s="7">
+        <v>5</v>
+      </c>
+      <c r="I13" s="7">
+        <v>226</v>
+      </c>
+      <c r="J13" s="7">
+        <v>43</v>
+      </c>
+      <c r="K13" s="7">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="6">
-        <v>23290</v>
-      </c>
-      <c r="G12" s="6">
-        <v>498</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N13" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10010</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" s="7">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="7">
+        <v>94230</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1548</v>
+      </c>
+      <c r="H14" s="7">
         <v>1</v>
       </c>
-      <c r="I12" s="6">
-        <v>615</v>
-      </c>
-      <c r="J12" s="6">
-        <v>120</v>
-      </c>
-      <c r="K12" s="6">
+      <c r="I14" s="7">
+        <v>1599</v>
+      </c>
+      <c r="J14" s="7">
+        <v>258</v>
+      </c>
+      <c r="K14" s="7">
+        <v>10</v>
+      </c>
+      <c r="L14" s="7">
+        <v>5</v>
+      </c>
+      <c r="M14" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N14" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" s="7">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="7">
+        <v>21673</v>
+      </c>
+      <c r="G15" s="7">
+        <v>867</v>
+      </c>
+      <c r="H15" s="7">
+        <v>5</v>
+      </c>
+      <c r="I15" s="7">
+        <v>586</v>
+      </c>
+      <c r="J15" s="7">
+        <v>93</v>
+      </c>
+      <c r="K15" s="7">
+        <v>5</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N15" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7">
+        <v>10012</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" s="7">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" s="7">
+        <v>381215</v>
+      </c>
+      <c r="G16" s="7">
+        <v>4808</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7">
+        <v>4152</v>
+      </c>
+      <c r="J16" s="7">
+        <v>561</v>
+      </c>
+      <c r="K16" s="7">
+        <v>12</v>
+      </c>
+      <c r="L16" s="7">
+        <v>5</v>
+      </c>
+      <c r="M16" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N16" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7">
+        <v>10013</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D17" s="7">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F17" s="7">
+        <v>87679</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2692</v>
+      </c>
+      <c r="H17" s="7">
+        <v>5</v>
+      </c>
+      <c r="I17" s="7">
+        <v>1522</v>
+      </c>
+      <c r="J17" s="7">
+        <v>202</v>
+      </c>
+      <c r="K17" s="7">
+        <v>6</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N17" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7">
+        <v>10014</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="7">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1542235</v>
+      </c>
+      <c r="G18" s="7">
+        <v>14934</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="I18" s="7">
+        <v>10767</v>
+      </c>
+      <c r="J18" s="7">
+        <v>1212</v>
+      </c>
+      <c r="K18" s="7">
+        <v>14</v>
+      </c>
+      <c r="L18" s="7">
+        <v>5</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N18" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7">
+        <v>10015</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D19" s="7">
         <v>8</v>
       </c>
-      <c r="L12" s="6">
+      <c r="E19" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" s="7">
+        <v>354714</v>
+      </c>
+      <c r="G19" s="7">
+        <v>8363</v>
+      </c>
+      <c r="H19" s="7">
         <v>5</v>
       </c>
-      <c r="M12" s="6">
+      <c r="I19" s="7">
+        <v>3948</v>
+      </c>
+      <c r="J19" s="7">
+        <v>437</v>
+      </c>
+      <c r="K19" s="7">
+        <v>7</v>
+      </c>
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
         <v>1.15</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N19" s="7">
         <v>1.1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6">
-        <v>10009</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D13" s="6">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>16</v>
+      </c>
+      <c r="B20" s="7">
+        <v>10016</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="7">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F20" s="7">
+        <v>6239205</v>
+      </c>
+      <c r="G20" s="7">
+        <v>46384</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1</v>
+      </c>
+      <c r="I20" s="7">
+        <v>27930</v>
+      </c>
+      <c r="J20" s="7">
+        <v>2619</v>
+      </c>
+      <c r="K20" s="7">
+        <v>16</v>
+      </c>
+      <c r="L20" s="7">
         <v>5</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F13" s="6">
-        <v>5357</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="M20" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N20" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7">
+        <v>10017</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="7">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="H13" s="6">
+      <c r="F21" s="7">
+        <v>1435017</v>
+      </c>
+      <c r="G21" s="7">
+        <v>25975</v>
+      </c>
+      <c r="H21" s="7">
         <v>5</v>
       </c>
-      <c r="I13" s="6">
-        <v>226</v>
-      </c>
-      <c r="J13" s="6">
-        <v>43</v>
-      </c>
-      <c r="K13" s="6">
-        <v>4</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="I21" s="7">
+        <v>10242</v>
+      </c>
+      <c r="J21" s="7">
+        <v>943</v>
+      </c>
+      <c r="K21" s="7">
+        <v>8</v>
+      </c>
+      <c r="L21" s="7">
         <v>0</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M21" s="7">
         <v>1.15</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N21" s="7">
         <v>1.1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7">
+        <v>10018</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D22" s="7">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="7">
+        <v>25241070</v>
+      </c>
+      <c r="G22" s="7">
+        <v>144062</v>
+      </c>
+      <c r="H22" s="7">
+        <v>1</v>
+      </c>
+      <c r="I22" s="7">
+        <v>72450</v>
+      </c>
+      <c r="J22" s="7">
+        <v>5658</v>
+      </c>
+      <c r="K22" s="7">
+        <v>18</v>
+      </c>
+      <c r="L22" s="7">
+        <v>5</v>
+      </c>
+      <c r="M22" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N22" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7">
+        <v>10019</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" s="7">
         <v>10</v>
       </c>
-      <c r="B14" s="6">
-        <v>10010</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="E23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F23" s="7">
+        <v>5805446</v>
+      </c>
+      <c r="G23" s="7">
+        <v>80675</v>
+      </c>
+      <c r="H23" s="7">
         <v>5</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="6">
-        <v>94230</v>
-      </c>
-      <c r="G14" s="6">
-        <v>1548</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="I23" s="7">
+        <v>26565</v>
+      </c>
+      <c r="J23" s="7">
+        <v>2037</v>
+      </c>
+      <c r="K23" s="7">
+        <v>9</v>
+      </c>
+      <c r="L23" s="7">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="N23" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7">
+        <v>10020</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D24" s="7">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F24" s="7">
+        <v>102114210</v>
+      </c>
+      <c r="G24" s="7">
+        <v>447440</v>
+      </c>
+      <c r="H24" s="7">
         <v>1</v>
       </c>
-      <c r="I14" s="6">
-        <v>1599</v>
-      </c>
-      <c r="J14" s="6">
-        <v>258</v>
-      </c>
-      <c r="K14" s="6">
-        <v>10</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="I24" s="7">
+        <v>187917</v>
+      </c>
+      <c r="J24" s="7">
+        <v>12219</v>
+      </c>
+      <c r="K24" s="7">
+        <v>20</v>
+      </c>
+      <c r="L24" s="7">
         <v>5</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M24" s="7">
         <v>1.15</v>
       </c>
-      <c r="N14" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6">
-        <v>10011</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="6">
-        <v>6</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F15" s="6">
-        <v>21673</v>
-      </c>
-      <c r="G15" s="6">
-        <v>867</v>
-      </c>
-      <c r="H15" s="6">
-        <v>5</v>
-      </c>
-      <c r="I15" s="6">
-        <v>586</v>
-      </c>
-      <c r="J15" s="6">
-        <v>93</v>
-      </c>
-      <c r="K15" s="6">
-        <v>5</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N15" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6">
-        <v>10012</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D16" s="6">
-        <v>6</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" s="6">
-        <v>381215</v>
-      </c>
-      <c r="G16" s="6">
-        <v>4808</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6">
-        <v>4152</v>
-      </c>
-      <c r="J16" s="6">
-        <v>561</v>
-      </c>
-      <c r="K16" s="6">
-        <v>12</v>
-      </c>
-      <c r="L16" s="6">
-        <v>5</v>
-      </c>
-      <c r="M16" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N16" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6">
-        <v>10013</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" s="6">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F17" s="6">
-        <v>87679</v>
-      </c>
-      <c r="G17" s="6">
-        <v>2692</v>
-      </c>
-      <c r="H17" s="6">
-        <v>5</v>
-      </c>
-      <c r="I17" s="6">
-        <v>1522</v>
-      </c>
-      <c r="J17" s="6">
-        <v>202</v>
-      </c>
-      <c r="K17" s="6">
-        <v>6</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N17" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6">
-        <v>10014</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D18" s="6">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1542235</v>
-      </c>
-      <c r="G18" s="6">
-        <v>14934</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6">
-        <v>10767</v>
-      </c>
-      <c r="J18" s="6">
-        <v>1212</v>
-      </c>
-      <c r="K18" s="6">
-        <v>14</v>
-      </c>
-      <c r="L18" s="6">
-        <v>5</v>
-      </c>
-      <c r="M18" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N18" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6">
-        <v>10015</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D19" s="6">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="6">
-        <v>354714</v>
-      </c>
-      <c r="G19" s="6">
-        <v>8363</v>
-      </c>
-      <c r="H19" s="6">
-        <v>5</v>
-      </c>
-      <c r="I19" s="6">
-        <v>3948</v>
-      </c>
-      <c r="J19" s="6">
-        <v>437</v>
-      </c>
-      <c r="K19" s="6">
-        <v>7</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N19" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6">
-        <v>10016</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D20" s="6">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F20" s="6">
-        <v>6239205</v>
-      </c>
-      <c r="G20" s="6">
-        <v>46384</v>
-      </c>
-      <c r="H20" s="6">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6">
-        <v>27930</v>
-      </c>
-      <c r="J20" s="6">
-        <v>2619</v>
-      </c>
-      <c r="K20" s="6">
-        <v>16</v>
-      </c>
-      <c r="L20" s="6">
-        <v>5</v>
-      </c>
-      <c r="M20" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N20" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6">
-        <v>10017</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D21" s="6">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1435017</v>
-      </c>
-      <c r="G21" s="6">
-        <v>25975</v>
-      </c>
-      <c r="H21" s="6">
-        <v>5</v>
-      </c>
-      <c r="I21" s="6">
-        <v>10242</v>
-      </c>
-      <c r="J21" s="6">
-        <v>943</v>
-      </c>
-      <c r="K21" s="6">
-        <v>8</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N21" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6">
-        <v>10018</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D22" s="6">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F22" s="6">
-        <v>25241070</v>
-      </c>
-      <c r="G22" s="6">
-        <v>144062</v>
-      </c>
-      <c r="H22" s="6">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6">
-        <v>72450</v>
-      </c>
-      <c r="J22" s="6">
-        <v>5658</v>
-      </c>
-      <c r="K22" s="6">
-        <v>18</v>
-      </c>
-      <c r="L22" s="6">
-        <v>5</v>
-      </c>
-      <c r="M22" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N22" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10019</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D23" s="6">
-        <v>10</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="6">
-        <v>5805446</v>
-      </c>
-      <c r="G23" s="6">
-        <v>80675</v>
-      </c>
-      <c r="H23" s="6">
-        <v>5</v>
-      </c>
-      <c r="I23" s="6">
-        <v>26565</v>
-      </c>
-      <c r="J23" s="6">
-        <v>2037</v>
-      </c>
-      <c r="K23" s="6">
-        <v>9</v>
-      </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N23" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10020</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D24" s="6">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F24" s="6">
-        <v>102114210</v>
-      </c>
-      <c r="G24" s="6">
-        <v>447440</v>
-      </c>
-      <c r="H24" s="6">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6">
-        <v>187917</v>
-      </c>
-      <c r="J24" s="6">
-        <v>12219</v>
-      </c>
-      <c r="K24" s="6">
-        <v>20</v>
-      </c>
-      <c r="L24" s="6">
-        <v>5</v>
-      </c>
-      <c r="M24" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="N24" s="6">
+      <c r="N24" s="7">
         <v>1.1</v>
       </c>
     </row>
@@ -6395,21 +6805,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6447,283 +6857,283 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>20001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" s="6">
+        <v>249</v>
+      </c>
+      <c r="E5" s="7">
         <v>40001</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>1</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>8</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>1.18</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>9999</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>20002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" s="6">
+        <v>252</v>
+      </c>
+      <c r="E6" s="7">
         <v>40002</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>1</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>1</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>8</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>1.18</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>9999</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>20003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="6">
+        <v>254</v>
+      </c>
+      <c r="E7" s="7">
         <v>40003</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>1</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>0.05</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>8</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>1.18</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>9999</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>20004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="6">
+        <v>256</v>
+      </c>
+      <c r="E8" s="7">
         <v>40004</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>0.5</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>8</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>1.18</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <v>9999</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>20005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="6">
+        <v>258</v>
+      </c>
+      <c r="E9" s="7">
         <v>40005</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>150</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>8</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>1.18</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <v>9999</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>20006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" s="6">
+        <v>260</v>
+      </c>
+      <c r="E10" s="7">
         <v>40006</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>1</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>0.02</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>8</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>1.18</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <v>9999</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -6756,26 +7166,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6822,301 +7232,301 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>30001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D5" s="6">
+        <v>314</v>
+      </c>
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>1</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>5</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="7">
         <v>0.6</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="7">
         <v>10</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="7">
         <v>1.35</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>30002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="6">
+        <v>316</v>
+      </c>
+      <c r="D6" s="7">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>11</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>11</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>0.6</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>201</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="7">
         <v>1.35</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>30003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D7" s="6">
+        <v>318</v>
+      </c>
+      <c r="D7" s="7">
         <v>3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>21</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>17</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="7">
         <v>0.6</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="7">
         <v>4042</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="7">
         <v>1.35</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>30004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="6">
+        <v>320</v>
+      </c>
+      <c r="D8" s="7">
         <v>4</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>31</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J8" s="6">
+        <v>243</v>
+      </c>
+      <c r="J8" s="7">
         <v>35</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <v>1</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="7">
         <v>81285</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="7">
         <v>1.35</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>30005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D9" s="6">
+        <v>322</v>
+      </c>
+      <c r="D9" s="7">
         <v>5</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>41</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <v>29</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="7">
         <v>0.6</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <v>1634371</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="7">
         <v>1.35</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -7143,18 +7553,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7183,107 +7593,107 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>31001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E5" s="6">
+        <v>284</v>
+      </c>
+      <c r="E5" s="7">
         <v>40007</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>15</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>667</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>31002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E6" s="6">
+        <v>287</v>
+      </c>
+      <c r="E6" s="7">
         <v>40008</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>33</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>148142</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -7311,22 +7721,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7361,226 +7771,226 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>32001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="7">
+        <v>40009</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="H5" s="7">
+        <v>15</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.22</v>
+      </c>
+      <c r="J5" s="7">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>32002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" s="7">
+        <v>40010</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E5" s="6">
-        <v>40009</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="G6" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H6" s="7">
         <v>15</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I6" s="7">
         <v>1.22</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J6" s="7">
         <v>9999</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>32003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" s="7">
+        <v>40011</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G7" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
-        <v>32002</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E6" s="6">
-        <v>40010</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="H7" s="7">
+        <v>15</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.22</v>
+      </c>
+      <c r="J7" s="7">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7">
+        <v>32004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E8" s="7">
+        <v>40012</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H8" s="7">
         <v>15</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I8" s="7">
         <v>1.22</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J8" s="7">
         <v>9999</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6">
-        <v>32003</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" s="6">
-        <v>40011</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G7" s="6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
+        <v>32005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="7">
+        <v>40013</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H9" s="7">
         <v>15</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I9" s="7">
         <v>1.22</v>
       </c>
-      <c r="J7" s="6">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6">
-        <v>32004</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="6">
-        <v>40012</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G8" s="6">
-        <v>2</v>
-      </c>
-      <c r="H8" s="6">
-        <v>15</v>
-      </c>
-      <c r="I8" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="J8" s="6">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
-        <v>32005</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" s="6">
-        <v>40013</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2</v>
-      </c>
-      <c r="H9" s="6">
-        <v>15</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <v>9999</v>
       </c>
     </row>
@@ -7609,17 +8019,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7651,89 +8061,89 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>33001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D5" s="6">
+        <v>327</v>
+      </c>
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>40014</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>0.05</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>10</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>1.25</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>9999</v>
       </c>
     </row>
@@ -7763,16 +8173,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7807,99 +8217,99 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>34001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" s="6">
+        <v>325</v>
+      </c>
+      <c r="D5" s="7">
         <v>20</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>2</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>7200</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>1.5</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>10</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>5</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -603,7 +603,7 @@
     <t>BonusBase</t>
   </si>
   <si>
-    <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = floor(BonusBase × 도달스테이지^BonusExponent)</t>
+    <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
   </si>
   <si>
     <t/>
@@ -618,22 +618,22 @@
     <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
   </si>
   <si>
-    <t>포인트당 스탯 상승률</t>
-  </si>
-  <si>
-    <t>BonusPerPoint</t>
-  </si>
-  <si>
-    <t>누적 보너스 포인트 1당 전 스탯에 곱연산으로 붙는 상승률(%). 전 스탯 보너스율 = 누적 포인트 × 이 값</t>
-  </si>
-  <si>
-    <t>보너스 최소 스테이지</t>
-  </si>
-  <si>
-    <t>MinStageForBonus</t>
-  </si>
-  <si>
-    <t>리버스 시점의 도달 스테이지가 이 값 미만이면 보너스 포인트를 얻지 못함</t>
+    <t>포인트당 환급 증폭률</t>
+  </si>
+  <si>
+    <t>RefundBonusPerPoint</t>
+  </si>
+  <si>
+    <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
+  </si>
+  <si>
+    <t>환급 배율 상한</t>
+  </si>
+  <si>
+    <t>MaxRefundMultiplier</t>
+  </si>
+  <si>
+    <t>환급 배율이 이 값을 넘지 않도록 제한</t>
   </si>
   <si>
     <t>보너스 설명</t>
@@ -1020,7 +1020,7 @@
     <t>스테이지/스탯/장비/숙련 초기화 + 소비 재화 전액 환급. 존재력 트리는 유지</t>
   </si>
   <si>
-    <t>포인트 = floor(1.0 × 도달스테이지^0.5), 10스테이지 미만이면 0. 전 스탯 보너스율(%) = 누적 포인트 × 1.0</t>
+    <t>포인트 = 1.0 × 도달스테이지^0.5 (소수점 유지, 최소 스테이지 제한 없음). 환급 배율 = 1 + (누적 포인트 × 1.0 / 100), 최대 5.0배. 전투 중 재화 획득량/스탯에는 영향 없음</t>
   </si>
   <si>
     <t>OfflineMaxHours</t>
@@ -1311,10 +1311,10 @@
     <t>PendingPoints</t>
   </si>
   <si>
-    <t>전 스탯 보너스</t>
-  </si>
-  <si>
-    <t>AllStatBonus</t>
+    <t>환급 배율</t>
+  </si>
+  <si>
+    <t>RefundMultiplier</t>
   </si>
   <si>
     <t>최고 도달 스테이지</t>
@@ -1327,7 +1327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1367,10 +1367,17 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF7F6000"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="9"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <color rgb="1F3864"/>
@@ -1378,13 +1385,20 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF1F3864"/>
+    </font>
+    <font>
       <b/>
       <color rgb="1F3864"/>
       <sz val="9"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF1F3864"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1421,7 +1435,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
     <fill>
@@ -1431,11 +1455,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="8EA9DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1473,11 +1507,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1487,6 +1536,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1503,14 +1558,26 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3519,22 +3586,22 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="3" t="s">
+      <c r="D93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3862,28 +3929,28 @@
     <col min="10" max="10" width="23" customWidth="1"/>
     <col min="11" max="11" width="17.3" customWidth="1"/>
     <col min="12" max="12" width="60" customWidth="1"/>
-    <col min="13" max="16" width="16" customWidth="1"/>
+    <col min="13" max="15" width="16" customWidth="1"/>
     <col min="17" max="17" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="10"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3922,176 +3989,176 @@
       <c r="L2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="12" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="10" t="s">
+      <c r="P3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>35001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="7" t="b">
+      <c r="D5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="b">
+      <c r="E5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="7" t="b">
+      <c r="F5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="b">
+      <c r="G5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="7" t="b">
+      <c r="H5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="7" t="b">
+      <c r="I5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="7" t="b">
+      <c r="J5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="7" t="b">
+      <c r="K5" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="18">
         <v>1</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="18">
         <v>0.5</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="18">
         <v>1</v>
       </c>
-      <c r="P5" s="12">
-        <v>10</v>
+      <c r="P5" s="5">
+        <v>5</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>330</v>
@@ -4120,13 +4187,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4152,56 +4219,56 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>36001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -4210,7 +4277,7 @@
       <c r="D5" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -4221,10 +4288,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>36002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -4233,7 +4300,7 @@
       <c r="D6" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -4244,10 +4311,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>36003</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -4256,7 +4323,7 @@
       <c r="D7" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -4267,10 +4334,10 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>36004</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -4279,7 +4346,7 @@
       <c r="D8" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -4290,10 +4357,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>36005</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -4302,7 +4369,7 @@
       <c r="D9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -4313,10 +4380,10 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>36006</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -4325,7 +4392,7 @@
       <c r="D10" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="9">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -4336,10 +4403,10 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>36007</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -4348,7 +4415,7 @@
       <c r="D11" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="9">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -4359,10 +4426,10 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>36008</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -4371,7 +4438,7 @@
       <c r="D12" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="9">
         <v>2</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -4402,11 +4469,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4426,44 +4493,44 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>40001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -4477,10 +4544,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>40002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -4494,10 +4561,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>40003</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -4511,10 +4578,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>40004</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -4528,10 +4595,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>40005</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -4545,10 +4612,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>40006</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -4562,10 +4629,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>40007</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -4579,10 +4646,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>40008</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -4596,10 +4663,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="A13" s="9">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
         <v>40009</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -4613,10 +4680,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>40010</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -4630,10 +4697,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="9">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>40011</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -4647,10 +4714,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="9">
         <v>12</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>40012</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -4664,10 +4731,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>13</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>40013</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -4681,10 +4748,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="9">
         <v>14</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>40014</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -4698,10 +4765,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="9">
         <v>15</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>40015</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -4715,10 +4782,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>40016</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -4732,10 +4799,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="9">
         <v>17</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>40017</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -4749,10 +4816,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="9">
         <v>18</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>40018</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -4766,10 +4833,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="9">
         <v>19</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>40019</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -4783,10 +4850,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="9">
         <v>20</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>40020</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -4800,10 +4867,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="A25" s="18">
         <v>21</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="18">
         <v>40021</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -4817,10 +4884,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="18">
         <v>22</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="18">
         <v>40022</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -4834,10 +4901,10 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="A27" s="18">
         <v>23</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="18">
         <v>40023</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -4851,10 +4918,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="A28" s="18">
         <v>24</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="18">
         <v>40024</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -4868,10 +4935,10 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+      <c r="A29" s="18">
         <v>25</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="18">
         <v>40025</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -4885,10 +4952,10 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="A30" s="18">
         <v>26</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="18">
         <v>40026</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -4902,10 +4969,10 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+      <c r="A31" s="18">
         <v>27</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="18">
         <v>40027</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -4919,10 +4986,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="A32" s="18">
         <v>28</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="18">
         <v>40028</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -4936,10 +5003,10 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
+      <c r="A33" s="18">
         <v>29</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="18">
         <v>40029</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -4953,10 +5020,10 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+      <c r="A34" s="18">
         <v>30</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="18">
         <v>40030</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -4970,10 +5037,10 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
+      <c r="A35" s="18">
         <v>31</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="18">
         <v>40031</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -4987,10 +5054,10 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
+      <c r="A36" s="18">
         <v>32</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="18">
         <v>40032</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -5004,10 +5071,10 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
+      <c r="A37" s="18">
         <v>33</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="18">
         <v>40033</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -5021,10 +5088,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
+      <c r="A38" s="18">
         <v>34</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="18">
         <v>40034</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -5038,10 +5105,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
+      <c r="A39" s="18">
         <v>35</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="18">
         <v>40035</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -5055,10 +5122,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
+      <c r="A40" s="18">
         <v>36</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="18">
         <v>40036</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -5072,10 +5139,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
+      <c r="A41" s="18">
         <v>37</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="18">
         <v>40037</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -5089,10 +5156,10 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
+      <c r="A42" s="18">
         <v>38</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="18">
         <v>40038</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -5106,10 +5173,10 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
+      <c r="A43" s="18">
         <v>39</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="18">
         <v>40039</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -5123,10 +5190,10 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
+      <c r="A44" s="18">
         <v>40</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="18">
         <v>40040</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -5140,10 +5207,10 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="12">
+      <c r="A45" s="18">
         <v>41</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="18">
         <v>40041</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -5157,10 +5224,10 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
+      <c r="A46" s="18">
         <v>42</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="18">
         <v>40042</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -5174,10 +5241,10 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
+      <c r="A47" s="18">
         <v>43</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="18">
         <v>40043</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -5191,10 +5258,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
+      <c r="A48" s="18">
         <v>44</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="18">
         <v>40044</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -5208,10 +5275,10 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="12">
+      <c r="A49" s="18">
         <v>45</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="18">
         <v>40045</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -5225,10 +5292,10 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
+      <c r="A50" s="18">
         <v>46</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="18">
         <v>40046</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -5242,10 +5309,10 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
+      <c r="A51" s="18">
         <v>47</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="18">
         <v>40047</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -5259,10 +5326,10 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
+      <c r="A52" s="18">
         <v>48</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="18">
         <v>40048</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -5276,10 +5343,10 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
+      <c r="A53" s="18">
         <v>49</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="18">
         <v>40049</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -5293,10 +5360,10 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="18">
         <v>50</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="18">
         <v>40050</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -5310,10 +5377,10 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="12">
+      <c r="A55" s="18">
         <v>51</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="18">
         <v>40051</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -5327,10 +5394,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
+      <c r="A56" s="18">
         <v>52</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="18">
         <v>40052</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -5344,10 +5411,10 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
+      <c r="A57" s="18">
         <v>53</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B57" s="18">
         <v>40053</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -5361,10 +5428,10 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
+      <c r="A58" s="18">
         <v>54</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="18">
         <v>40054</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -5749,22 +5816,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5811,970 +5878,970 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>10001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>20</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>3</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>5</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>5</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>2</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>1</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>0</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="9">
         <v>1.15</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>10002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>350</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>16</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>1</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>33</v>
       </c>
-      <c r="J6" s="7">
-        <v>9</v>
-      </c>
-      <c r="K6" s="7">
+      <c r="J6" s="9">
+        <v>9</v>
+      </c>
+      <c r="K6" s="9">
         <v>2</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <v>5</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="9">
         <v>1.15</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>10003</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>80</v>
       </c>
-      <c r="G7" s="7">
-        <v>9</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="G7" s="9">
+        <v>9</v>
+      </c>
+      <c r="H7" s="9">
         <v>5</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>12</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>4</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>1</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="9">
         <v>0</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="9">
         <v>1.15</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>10004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="9">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <v>1420</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <v>50</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <v>1</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="9">
         <v>90</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="9">
         <v>24</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="9">
         <v>4</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="9">
         <v>5</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="9">
         <v>1.15</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>10005</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="9">
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="9">
         <v>327</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>28</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <v>5</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="9">
         <v>33</v>
       </c>
-      <c r="J9" s="7">
-        <v>9</v>
-      </c>
-      <c r="K9" s="7">
+      <c r="J9" s="9">
+        <v>9</v>
+      </c>
+      <c r="K9" s="9">
         <v>2</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="9">
         <v>0</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="9">
         <v>1.15</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>10006</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="9">
         <v>5755</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>160</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <v>1</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="9">
         <v>237</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="9">
         <v>54</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="9">
         <v>6</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="9">
         <v>5</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="9">
         <v>1.15</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>10007</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="9">
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="9">
         <v>1324</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="9">
         <v>89</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <v>5</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="9">
         <v>87</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="9">
         <v>20</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="9">
         <v>3</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="9">
         <v>0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="9">
         <v>1.15</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>10008</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="9">
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="9">
         <v>23290</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="9">
         <v>498</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="9">
         <v>1</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="9">
         <v>615</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="9">
         <v>120</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="9">
         <v>8</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="9">
         <v>5</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="9">
         <v>1.15</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="A13" s="9">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
         <v>10009</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="9">
         <v>5</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="9">
         <v>5357</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="9">
         <v>279</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <v>5</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="9">
         <v>226</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="9">
         <v>43</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="9">
         <v>4</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="9">
         <v>0</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="9">
         <v>1.15</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>10010</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="9">
         <v>5</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="9">
         <v>94230</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="9">
         <v>1548</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="9">
         <v>1</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="9">
         <v>1599</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="9">
         <v>258</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="9">
         <v>10</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="9">
         <v>5</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="9">
         <v>1.15</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="9">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>10011</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="9">
         <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="9">
         <v>21673</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <v>867</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <v>5</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="9">
         <v>586</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="9">
         <v>93</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="9">
         <v>5</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="9">
         <v>0</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="9">
         <v>1.15</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="9">
         <v>12</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>10012</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="9">
         <v>381215</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <v>4808</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <v>1</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="9">
         <v>4152</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="9">
         <v>561</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="9">
         <v>12</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="9">
         <v>5</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="9">
         <v>1.15</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>13</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>10013</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="9">
         <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="9">
         <v>87679</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="9">
         <v>2692</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <v>5</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="9">
         <v>1522</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="9">
         <v>202</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="9">
         <v>6</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="9">
         <v>0</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="9">
         <v>1.15</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="9">
         <v>14</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>10014</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="9">
         <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="9">
         <v>1542235</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <v>14934</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <v>1</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="9">
         <v>10767</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="9">
         <v>1212</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="9">
         <v>14</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="9">
         <v>5</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="9">
         <v>1.15</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N18" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="9">
         <v>15</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>10015</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="9">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="9">
         <v>354714</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="9">
         <v>8363</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <v>5</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="9">
         <v>3948</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="9">
         <v>437</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="9">
         <v>7</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="9">
         <v>0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="9">
         <v>1.15</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>10016</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="9">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="9">
         <v>6239205</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="9">
         <v>46384</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <v>1</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="9">
         <v>27930</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="9">
         <v>2619</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="9">
         <v>16</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="9">
         <v>5</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="9">
         <v>1.15</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="9">
         <v>17</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>10017</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="9">
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="9">
         <v>1435017</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="9">
         <v>25975</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="9">
         <v>5</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="9">
         <v>10242</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="9">
         <v>943</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="9">
         <v>8</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="9">
         <v>0</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="9">
         <v>1.15</v>
       </c>
-      <c r="N21" s="7">
+      <c r="N21" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="9">
         <v>18</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>10018</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="9">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="9">
         <v>25241070</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="9">
         <v>144062</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="9">
         <v>1</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="9">
         <v>72450</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="9">
         <v>5658</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="9">
         <v>18</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L22" s="9">
         <v>5</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="9">
         <v>1.15</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="9">
         <v>19</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>10019</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="9">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="9">
         <v>5805446</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="9">
         <v>80675</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <v>5</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="9">
         <v>26565</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="9">
         <v>2037</v>
       </c>
-      <c r="K23" s="7">
-        <v>9</v>
-      </c>
-      <c r="L23" s="7">
+      <c r="K23" s="9">
+        <v>9</v>
+      </c>
+      <c r="L23" s="9">
         <v>0</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="9">
         <v>1.15</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N23" s="9">
         <v>1.1</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="9">
         <v>20</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>10020</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="9">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="9">
         <v>102114210</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="9">
         <v>447440</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <v>1</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="9">
         <v>187917</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="9">
         <v>12219</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="9">
         <v>20</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="9">
         <v>5</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="9">
         <v>1.15</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="9">
         <v>1.1</v>
       </c>
     </row>
@@ -6805,21 +6872,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6857,80 +6924,80 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>20001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -6939,22 +7006,22 @@
       <c r="D5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>40001</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>1</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>1</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>8</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>1.18</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>9999</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -6962,10 +7029,10 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>20002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -6974,22 +7041,22 @@
       <c r="D6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>40002</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>8</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>1.18</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>9999</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -6997,10 +7064,10 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>20003</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -7009,22 +7076,22 @@
       <c r="D7" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>40003</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>1</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>0.05</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>8</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>1.18</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>9999</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -7032,10 +7099,10 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>20004</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -7044,22 +7111,22 @@
       <c r="D8" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <v>40004</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <v>0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <v>0.5</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <v>8</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="9">
         <v>1.18</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="9">
         <v>9999</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -7067,10 +7134,10 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>20005</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -7079,22 +7146,22 @@
       <c r="D9" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <v>40005</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="9">
         <v>150</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>2</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <v>8</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="9">
         <v>1.18</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="9">
         <v>9999</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -7102,10 +7169,10 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>20006</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -7114,22 +7181,22 @@
       <c r="D10" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="9">
         <v>40006</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="9">
         <v>1</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>0.02</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <v>8</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="9">
         <v>1.18</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="9">
         <v>9999</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -7166,26 +7233,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7232,110 +7299,110 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>30001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -7345,16 +7412,16 @@
         <v>249</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>5</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>0.6</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>10</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="9">
         <v>1.35</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -7362,22 +7429,22 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>30002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>11</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -7387,16 +7454,16 @@
         <v>252</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>11</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <v>0.6</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <v>201</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="9">
         <v>1.35</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -7404,22 +7471,22 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>30003</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>21</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -7429,16 +7496,16 @@
         <v>254</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>17</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>0.6</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="9">
         <v>4042</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="9">
         <v>1.35</v>
       </c>
       <c r="N7" s="2" t="s">
@@ -7446,22 +7513,22 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>30004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="9">
         <v>4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <v>31</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -7471,16 +7538,16 @@
       <c r="I8" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="9">
         <v>35</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="9">
         <v>1</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="9">
         <v>81285</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="9">
         <v>1.35</v>
       </c>
       <c r="N8" s="2" t="s">
@@ -7488,22 +7555,22 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>30005</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="9">
         <v>5</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <v>41</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="9">
         <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -7513,16 +7580,16 @@
         <v>260</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="7">
+      <c r="J9" s="9">
         <v>29</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="9">
         <v>0.6</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="9">
         <v>1634371</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="9">
         <v>1.35</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -7553,18 +7620,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7593,62 +7660,62 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>31001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -7657,13 +7724,13 @@
       <c r="D5" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>40007</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>15</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>667</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -7671,10 +7738,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>31002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -7683,13 +7750,13 @@
       <c r="D6" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>40008</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>33</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>148142</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -7721,22 +7788,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7771,74 +7838,74 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>32001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -7847,30 +7914,30 @@
       <c r="D5" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>40009</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>2</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>15</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>1.22</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>9999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>32002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -7879,30 +7946,30 @@
       <c r="D6" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>40010</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>2</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>15</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>1.22</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>9999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>32003</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -7911,30 +7978,30 @@
       <c r="D7" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>40011</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>15</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>1.22</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>9999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>32004</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -7943,30 +8010,30 @@
       <c r="D8" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <v>40012</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <v>2</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <v>15</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="9">
         <v>1.22</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="9">
         <v>9999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>32005</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -7975,22 +8042,22 @@
       <c r="D9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <v>40013</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>2</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <v>15</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="9">
         <v>1.22</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="9">
         <v>9999</v>
       </c>
     </row>
@@ -8019,17 +8086,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -8061,89 +8128,89 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>33001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>40014</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>0.05</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>10</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>1.25</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>9999</v>
       </c>
     </row>
@@ -8173,16 +8240,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -8217,95 +8284,95 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>34001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>20</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>2</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>7200</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>1.5</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>10</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>5</v>
       </c>
       <c r="J5" s="2" t="s">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -28,13 +28,13 @@
     <sheet name="StringTable" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StageTable'!$A$4:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ExistTreeTable'!$A$4:$N$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'FeatureUnlockTable'!$A$4:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MasteryTable'!$A$4:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MasteryTable'!$A$4:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'WeaponTypeTable'!$A$4:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'WeaponGradeTable'!$A$4:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'WeaponUpgradeTable'!$A$4:$G$5</definedName>
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$Q$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1984,25 +1984,29 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>무기 종류</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
+          <t>검/창/활 중 이 숙련이 적용되는 종류</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>EnumDefine/WeaponType</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2012,12 +2016,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>무기ID</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>WeaponId</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2027,10 +2031,14 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>내부 무기 식별자. 지금은 1종(기본 검)뿐이지만 추가 확장 대비</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
+          <t>화면에 표시할 숙련 이름의 StringTable ID</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>StringTable/Id</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2040,29 +2048,25 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>레벨당 배율</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>MultiplierPerLevel</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>화면에 표시할 무기 이름의 StringTable ID</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>StringTable/Id</t>
-        </is>
-      </c>
+          <t>숙련 1레벨당 증가하는 배율 (0.05 = +5%). 장착한 무기 종류의 주 스탯 전체에 곱해진다</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2072,22 +2076,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>레벨당 ATK 배율</t>
+          <t>기준 비용</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AtkMultiplierPerLevel</t>
+          <t>CostBase</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>숙련 1레벨당 증가하는 ATK 배율 (0.05 = +5%)</t>
+          <t>레벨 0→1 숙련 비용(숙련의 정수)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -2100,22 +2104,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>기준 비용</t>
+          <t>비용 증가율</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CostBase</t>
+          <t>CostGrowthRate</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>레벨 0→1 숙련 비용(숙련의 정수)</t>
+          <t>비용 = CostBase × CostGrowthRate^현재레벨</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -2128,22 +2132,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>비용 증가율</t>
+          <t>최대 레벨</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>CostGrowthRate</t>
+          <t>MaxLevel</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>비용 = CostBase × CostGrowthRate^현재레벨</t>
+          <t>레벨 상한. 현재는 실질적 상한 없음을 뜻하는 자리 표시자(9999)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -2151,17 +2155,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MasteryTable</t>
+          <t>WeaponTypeTable</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>최대 레벨</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>MaxLevel</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>레벨 상한. 현재는 실질적 상한 없음을 뜻하는 자리 표시자(9999)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -2184,12 +2188,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2199,7 +2203,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>무기 종류 고유 ID (37000번대)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -2212,25 +2216,29 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>무기 종류</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>무기 종류 고유 ID (37000번대)</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>Sword/Spear/Bow</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>EnumDefine/WeaponType</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2240,27 +2248,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>무기 종류</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sword/Spear/Bow</t>
+          <t>화면에 표시할 종류 이름의 StringTable ID</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>EnumDefine/WeaponType</t>
+          <t>StringTable/Id</t>
         </is>
       </c>
     </row>
@@ -2272,27 +2280,27 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>주 스탯</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>PrimaryStat</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>화면에 표시할 종류 이름의 StringTable ID</t>
+          <t>이 종류의 특성 스탯 (검=ATK, 창=ASPD, 활=CRIT)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>StringTable/Id</t>
+          <t>EnumDefine/StatType</t>
         </is>
       </c>
     </row>
@@ -2304,29 +2312,25 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>주 스탯</t>
+          <t>보유효과 기준 계수</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>PrimaryStat</t>
+          <t>OwnBonusBase</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>이 종류의 특성 스탯 (검=ATK, 창=ASPD, 활=CRIT)</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>EnumDefine/StatType</t>
-        </is>
-      </c>
+          <t>타입당 보유 효과 = 이 값 × 레벨 × 보유개수 × 등급배율 × 단계배율</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2336,12 +2340,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>보유효과 기준 계수</t>
+          <t>장착효과 기준 계수</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>OwnBonusBase</t>
+          <t>EquipBonusBase</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2351,7 +2355,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>타입당 보유 효과 = 이 값 × 레벨 × 보유개수 × 등급배율 × 단계배율</t>
+          <t>장착 효과 = 이 값 × 레벨 × 등급배율 × 단계배율. 보유효과보다 훨씬 큰 값을 넣는다</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -2364,22 +2368,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>장착효과 기준 계수</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EquipBonusBase</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>장착 효과 = 이 값 × 레벨 × 등급배율 × 단계배율. 보유효과보다 훨씬 큰 값을 넣는다</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -2387,27 +2391,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>WeaponTypeTable</t>
+          <t>WeaponGradeTable</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -2420,12 +2424,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2435,7 +2439,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>무기 등급 고유 ID (37010번대)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -2448,25 +2452,29 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>WeaponGrade</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>무기 등급 고유 ID (37010번대)</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
+          <t>Normal/Rare/Epic/Unique/Legendary</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>EnumDefine/WeaponGrade</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2476,27 +2484,27 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>WeaponGrade</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Normal/Rare/Epic/Unique/Legendary</t>
+          <t>화면에 표시할 등급 이름의 StringTable ID</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>EnumDefine/WeaponGrade</t>
+          <t>StringTable/Id</t>
         </is>
       </c>
     </row>
@@ -2508,29 +2516,25 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>등급 배율</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>GradeMultiplier</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>화면에 표시할 등급 이름의 StringTable ID</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>StringTable/Id</t>
-        </is>
-      </c>
+          <t>이 등급의 보유/장착 효과와 레벨업 비용에 곱해지는 배율</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2540,22 +2544,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>등급 배율</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>GradeMultiplier</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>이 등급의 보유/장착 효과와 레벨업 비용에 곱해지는 배율</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -2563,27 +2567,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>WeaponGradeTable</t>
+          <t>WeaponUpgradeTable</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -2596,12 +2600,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2611,7 +2615,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>37021 고정</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -2624,12 +2628,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>기본 레벨 상한</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>BaseMaxLevel</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>37021 고정</t>
+          <t>돌파 전 기본 레벨 상한</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -2652,12 +2656,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>기본 레벨 상한</t>
+          <t>레벨업 비용 기준</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>BaseMaxLevel</t>
+          <t>LevelCostBase</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>돌파 전 기본 레벨 상한</t>
+          <t>골드 비용 = LevelCostBase × LevelCostGrowthRate^(레벨-1) × 등급배율</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -2680,22 +2684,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>레벨업 비용 기준</t>
+          <t>레벨업 비용 증가율</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>LevelCostBase</t>
+          <t>LevelCostGrowthRate</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>골드 비용 = LevelCostBase × LevelCostGrowthRate^(레벨-1) × 등급배율</t>
+          <t>위 공식 참고</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -2708,12 +2712,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>레벨업 비용 증가율</t>
+          <t>단계(Tier)당 스탯 보정</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>LevelCostGrowthRate</t>
+          <t>TierStepBonusPercent</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2723,7 +2727,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>위 공식 참고</t>
+          <t>단계 하나 오를 때마다 등급 배율에 추가로 곱해지는 가산율(%). tier=1 기준 0%, tier=5는 (tier-1)×이 값</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -2736,22 +2740,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>단계(Tier)당 스탯 보정</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TierStepBonusPercent</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>단계 하나 오를 때마다 등급 배율에 추가로 곱해지는 가산율(%). tier=1 기준 0%, tier=5는 (tier-1)×이 값</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -2759,27 +2763,27 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WeaponUpgradeTable</t>
+          <t>WeaponBreakthroughTable</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -2792,12 +2796,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>무기 돌파 단계 고유 ID (37030번대)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -2820,12 +2824,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>돌파 단계</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>BreakthroughStep</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>무기 돌파 단계 고유 ID (37030번대)</t>
+          <t>1~5</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -2848,12 +2852,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>돌파 단계</t>
+          <t>필요 중복 개수</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>BreakthroughStep</t>
+          <t>RequiredDuplicateCount</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2863,7 +2867,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>이 단계를 실행하는 데 소모되는 같은 무기 타입의 추가 보유 개수</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -2876,12 +2880,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>필요 중복 개수</t>
+          <t>레벨 상한 증가량</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>RequiredDuplicateCount</t>
+          <t>LevelCapBonus</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2891,7 +2895,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>이 단계를 실행하는 데 소모되는 같은 무기 타입의 추가 보유 개수</t>
+          <t>이 단계 완료 시 레벨 상한에 더해지는 값</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -2904,22 +2908,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>레벨 상한 증가량</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>LevelCapBonus</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>이 단계 완료 시 레벨 상한에 더해지는 값</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -2927,27 +2931,27 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WeaponBreakthroughTable</t>
+          <t>WeaponFusionTable</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -2960,12 +2964,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2975,7 +2979,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>37041 고정</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -2988,12 +2992,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>합성 필요 개수</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RequiredCount</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3003,7 +3007,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>37041 고정</t>
+          <t>장착 중인 타입은 이 계산에서 항상 1개 제외 (docs/WEAPON_SYSTEM.md 1.3 참고)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -3016,12 +3020,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>합성 필요 개수</t>
+          <t>결과물 레벨</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>RequiredCount</t>
+          <t>ResultLevel</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3031,7 +3035,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>장착 중인 타입은 이 계산에서 항상 1개 제외 (docs/WEAPON_SYSTEM.md 1.3 참고)</t>
+          <t>합성으로 만들어지는 새 무기의 초기 레벨</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -3044,12 +3048,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>결과물 레벨</t>
+          <t>결과물 돌파 횟수</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ResultLevel</t>
+          <t>ResultBreakthroughCount</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3059,7 +3063,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>합성으로 만들어지는 새 무기의 초기 레벨</t>
+          <t>합성으로 만들어지는 새 무기의 초기 돌파 횟수</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -3072,22 +3076,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>결과물 돌파 횟수</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ResultBreakthroughCount</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>합성으로 만들어지는 새 무기의 초기 돌파 횟수</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -3095,27 +3099,27 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WeaponFusionTable</t>
+          <t>GachaTable</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -3128,12 +3132,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3143,7 +3147,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>37100번대</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -3156,12 +3160,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>가챠 레벨</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>GachaLevel</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3169,11 +3173,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>37100번대</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>가챠 레벨</t>
+          <t>필요 누적 뽑기 횟수</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>GachaLevel</t>
+          <t>RequirePullCount</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3197,7 +3197,11 @@
           <t>int</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>이 값 이상 누적 뽑기 시 해당 레벨로 상승</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
@@ -3208,24 +3212,20 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>필요 누적 뽑기 횟수</t>
+          <t>노말 가중치</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>RequirePullCount</t>
+          <t>NormalWeight</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>이 값 이상 누적 뽑기 시 해당 레벨로 상승</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>노말 가중치</t>
+          <t>레어 가중치</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>NormalWeight</t>
+          <t>RareWeight</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>레어 가중치</t>
+          <t>에픽 가중치</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>RareWeight</t>
+          <t>EpicWeight</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>에픽 가중치</t>
+          <t>유니크 가중치</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EpicWeight</t>
+          <t>UniqueWeight</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>유니크 가중치</t>
+          <t>레전드리 가중치</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>UniqueWeight</t>
+          <t>LegendaryWeight</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>레전드리 가중치</t>
+          <t>1단계 가중치</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>LegendaryWeight</t>
+          <t>Tier1Weight</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1단계 가중치</t>
+          <t>2단계 가중치</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tier1Weight</t>
+          <t>Tier2Weight</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>2단계 가중치</t>
+          <t>3단계 가중치</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Tier2Weight</t>
+          <t>Tier3Weight</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>3단계 가중치</t>
+          <t>4단계 가중치</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Tier3Weight</t>
+          <t>Tier4Weight</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>4단계 가중치</t>
+          <t>5단계 가중치</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tier4Weight</t>
+          <t>Tier5Weight</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3452,20 +3452,24 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>5단계 가중치</t>
+          <t>뽑기 1회 비용</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tier5Weight</t>
+          <t>PullCostDiamond</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>다이아 소모량</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3476,22 +3480,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>뽑기 1회 비용</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>PullCostDiamond</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>다이아 소모량</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -3499,27 +3503,27 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GachaTable</t>
+          <t>RelicTable</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -3532,12 +3536,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -3547,7 +3551,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>유물 고유 ID (38000번대)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -3560,25 +3564,29 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RelicGrade</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>유물 고유 ID (38000번대)</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>Normal/Rare/Epic</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>EnumDefine/RelicGrade</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3588,27 +3596,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>RelicGrade</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Normal/Rare/Epic</t>
+          <t>화면에 표시할 유물 이름의 StringTable ID</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>EnumDefine/RelicGrade</t>
+          <t>StringTable/Id</t>
         </is>
       </c>
     </row>
@@ -3620,27 +3628,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>효과 종류</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>EffectType</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>화면에 표시할 유물 이름의 StringTable ID</t>
+          <t>스탯형 또는 특수효과형</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>StringTable/Id</t>
+          <t>EnumDefine/RelicEffectType</t>
         </is>
       </c>
     </row>
@@ -3652,29 +3660,25 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>효과 종류</t>
+          <t>효과 수치</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EffectType</t>
+          <t>EffectValue</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>스탯형 또는 특수효과형</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>EnumDefine/RelicEffectType</t>
-        </is>
-      </c>
+          <t>스탯형이면 가산량, 특수효과형이면 %(GOLD_GAIN, TIMEHEIST_COOLDOWN)</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3684,12 +3688,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>효과 수치</t>
+          <t>뽑기 가중치</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EffectValue</t>
+          <t>GachaWeight</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -3699,7 +3703,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>스탯형이면 가산량, 특수효과형이면 %(GOLD_GAIN, TIMEHEIST_COOLDOWN)</t>
+          <t>등급 내에서의 상대 가중치</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -3712,22 +3716,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>뽑기 가중치</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>GachaWeight</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>등급 내에서의 상대 가중치</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -3735,27 +3739,27 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RelicTable</t>
+          <t>RelicSlotTable</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -3768,12 +3772,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -3783,7 +3787,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>38100번대</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -3796,12 +3800,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>슬롯 번호</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>SlotIndex</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -3811,7 +3815,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>38100번대</t>
+          <t>1~5</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -3824,12 +3828,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>슬롯 번호</t>
+          <t>필요 존재력 해금 수</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>SlotIndex</t>
+          <t>RequireUnlockedCount</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -3839,7 +3843,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>존재력 트리가 이 값 이상 해금되면 이 슬롯이 열림</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -3852,22 +3856,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>필요 존재력 해금 수</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>RequireUnlockedCount</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리가 이 값 이상 해금되면 이 슬롯이 열림</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -3875,27 +3879,27 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RelicSlotTable</t>
+          <t>TimeHeistTable</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -3908,12 +3912,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -3923,7 +3927,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>타임 하이스트 고유 ID (34000번대)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -3936,22 +3940,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>타임 하이스트 고유 ID (34000번대)</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -3964,22 +3968,22 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>기준 비용</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>CostBase</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>1회차 사용 비용(시간에너지)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -3992,22 +3996,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>기준 비용</t>
+          <t>비용 증가율</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>CostBase</t>
+          <t>CostGrowthRate</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>1회차 사용 비용(시간에너지)</t>
+          <t>비용 = CostBase × CostGrowthRate^사용횟수</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -4020,22 +4024,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>비용 증가율</t>
+          <t>기준 쿨타임(초)</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>CostGrowthRate</t>
+          <t>CooldownBase</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>비용 = CostBase × CostGrowthRate^사용횟수</t>
+          <t>1회차 사용 후 쿨타임 기준값(초)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -4048,22 +4052,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>기준 쿨타임(초)</t>
+          <t>쿨타임 증가율</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CooldownBase</t>
+          <t>CooldownGrowthRate</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>1회차 사용 후 쿨타임 기준값(초)</t>
+          <t>쿨타임 = CooldownBase × CooldownGrowthRate^사용횟수</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -4076,22 +4080,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>쿨타임 증가율</t>
+          <t>선취 스테이지 오프셋</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>CooldownGrowthRate</t>
+          <t>TargetStageOffset</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>쿨타임 = CooldownBase × CooldownGrowthRate^사용횟수</t>
+          <t>현재 스테이지 + 이 값 = 선취할 미래 스테이지</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -4104,22 +4108,22 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>선취 스테이지 오프셋</t>
+          <t>보상 배율</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>TargetStageOffset</t>
+          <t>RewardMultiplier</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>현재 스테이지 + 이 값 = 선취할 미래 스테이지</t>
+          <t>선취 스테이지를 몇 클리어분으로 환산해 보상을 줄지</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -4132,22 +4136,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>보상 배율</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>RewardMultiplier</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>선취 스테이지를 몇 클리어분으로 환산해 보상을 줄지</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -4155,27 +4159,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TimeHeistTable</t>
+          <t>RebirthTable</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -4188,12 +4192,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -4203,7 +4207,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>리버스 고유 ID (35000번대)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -4216,22 +4220,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>리버스 고유 ID (35000번대)</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
@@ -4244,22 +4248,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>스테이지 초기화</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>ResetStage</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>실행 시 스테이지를 1로 되돌리는지</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -4272,12 +4276,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>스테이지 초기화</t>
+          <t>스탯 초기화</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ResetStage</t>
+          <t>ResetStats</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -4287,7 +4291,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>실행 시 스테이지를 1로 되돌리는지</t>
+          <t>실행 시 6스탯 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>스탯 초기화</t>
+          <t>장비 초기화</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>ResetStats</t>
+          <t>ResetEquipment</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4315,7 +4319,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>실행 시 6스탯 레벨을 초기화하는지</t>
+          <t>실행 시 장비 강화 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -4328,12 +4332,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>장비 초기화</t>
+          <t>숙련 초기화</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>ResetEquipment</t>
+          <t>ResetMastery</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -4343,7 +4347,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>실행 시 장비 강화 레벨을 초기화하는지</t>
+          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -4356,12 +4360,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>숙련 초기화</t>
+          <t>성장에너지 환급</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>ResetMastery</t>
+          <t>RefundGrowthEnergy</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4371,7 +4375,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
+          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -4384,12 +4388,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>성장에너지 환급</t>
+          <t>골드 환급</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>RefundGrowthEnergy</t>
+          <t>RefundGold</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -4399,7 +4403,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
+          <t>그동안 소비한 골드를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -4412,12 +4416,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>골드 환급</t>
+          <t>숙련의정수 환급</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RefundGold</t>
+          <t>RefundMasteryEssence</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -4427,7 +4431,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 골드를 전액 돌려주는지</t>
+          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -4440,12 +4444,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>숙련의정수 환급</t>
+          <t>존재력트리 유지</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>RefundMasteryEssence</t>
+          <t>KeepExistTree</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -4455,7 +4459,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
+          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -4468,22 +4472,22 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>존재력트리 유지</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>KeepExistTree</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -4496,22 +4500,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>회차 보너스 계수</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>BonusBase</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -4524,12 +4528,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 계수</t>
+          <t>회차 보너스 지수</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>BonusBase</t>
+          <t>BonusExponent</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -4539,7 +4543,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
+          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -4552,12 +4556,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 지수</t>
+          <t>포인트당 환급 증폭률</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>BonusExponent</t>
+          <t>RefundBonusPerPoint</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -4567,7 +4571,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
+          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -4580,12 +4584,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>포인트당 환급 증폭률</t>
+          <t>환급 배율 상한</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>RefundBonusPerPoint</t>
+          <t>MaxRefundMultiplier</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -4595,7 +4599,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
+          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -4608,22 +4612,22 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>환급 배율 상한</t>
+          <t>보너스 설명</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>MaxRefundMultiplier</t>
+          <t>//BonusDescription</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
+          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -4631,27 +4635,27 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>RebirthTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>보너스 설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>//BonusDescription</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -4664,12 +4668,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -4679,7 +4683,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>공용 상수 고유 ID (36000번대)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -4692,22 +4696,22 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>키</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>공용 상수 고유 ID (36000번대)</t>
+          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -4720,12 +4724,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -4735,7 +4739,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -4748,22 +4752,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>값</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>실제 값. 수정 대상</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -4776,22 +4780,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>값 타입</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>ValueType</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>실제 값. 수정 대상</t>
+          <t>Value를 int/float 중 무엇으로 해석할지</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -4804,12 +4808,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>값 타입</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>ValueType</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -4819,7 +4823,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Value를 int/float 중 무엇으로 해석할지</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
@@ -4827,27 +4831,27 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
@@ -4860,12 +4864,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -4875,7 +4879,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -4888,22 +4892,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
+          <t>한국어 표시 문자열</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -4916,12 +4920,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>영문</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -4931,7 +4935,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>한국어 표시 문자열</t>
+          <t>영문/내부 키 표시 문자열</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -4944,12 +4948,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>영문</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>//Category</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -4959,7 +4963,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>영문/내부 키 표시 문자열</t>
+          <t>문자열 용도 분류 (파싱 제외)</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -4967,19 +4971,15 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>#EnumDefine</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>분류</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>//Category</t>
-        </is>
-      </c>
+          <t>enum 그룹</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>문자열 용도 분류 (파싱 제외)</t>
+          <t>enum 값이 속한 그룹 이름</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>enum 그룹</t>
+          <t>한글 라벨</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr"/>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>enum 값이 속한 그룹 이름</t>
+          <t>기획 문서/화면에 쓰는 한글 표기</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>한글 라벨</t>
+          <t>영문 라벨</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>기획 문서/화면에 쓰는 한글 표기</t>
+          <t>코드가 참조하는 영문 값</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>영문 라벨</t>
+          <t>사용처</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
@@ -5059,37 +5059,13 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 영문 값</t>
+          <t>이 enum 그룹을 참조하는 테이블.칼럼 목록</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>#EnumDefine</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>사용처</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr"/>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>이 enum 그룹을 참조하는 테이블.칼럼 목록</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F162"/>
+  <autoFilter ref="A1:F161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7871,7 +7847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9510,8 +9486,123 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>40072</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>검 숙련</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Sword Mastery</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Mastery</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>40073</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>창 숙련</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Spear Mastery</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Mastery</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>40074</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>활 숙련</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Bow Mastery</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Mastery</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>40075</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>다이아</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>DIAMOND</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>40076</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>다이아</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>DIAMOND_ABBR</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyAbbr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E71"/>
+  <autoFilter ref="A4:E76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12808,34 +12899,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9.699999999999999" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="11.6" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="11.6" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="11.6" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="11.6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="n"/>
       <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>EnumDefine/WeaponType</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>StringTable/Id</t>
         </is>
       </c>
+      <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -12850,35 +12943,30 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>무기 종류</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>무기ID</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>레벨당 배율</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>레벨당 ATK 배율</t>
+          <t>기준 비용</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>기준 비용</t>
+          <t>비용 증가율</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>비용 증가율</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>최대 레벨</t>
         </is>
@@ -12897,7 +12985,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -12907,25 +12995,20 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -12944,35 +13027,30 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>WeaponId</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>MultiplierPerLevel</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>AtkMultiplierPerLevel</t>
+          <t>CostBase</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>CostBase</t>
+          <t>CostGrowthRate</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>CostGrowthRate</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>MaxLevel</t>
         </is>
@@ -12983,34 +13061,87 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>33001</v>
+        <v>33002</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>기본 검</t>
+          <t>Sword</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>40072</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>40014</v>
+        <v>0.05</v>
       </c>
       <c r="F5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>33003</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>40073</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>1.25</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>9999</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>33004</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Bow</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40074</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>9999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I5"/>
+  <autoFilter ref="A4:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -28,7 +28,7 @@
     <sheet name="StringTable" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StageTable'!$A$4:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$10</definedName>
@@ -37,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MasteryTable'!$A$4:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'WeaponTypeTable'!$A$4:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'WeaponGradeTable'!$A$4:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'WeaponUpgradeTable'!$A$4:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'WeaponUpgradeTable'!$A$4:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'WeaponBreakthroughTable'!$A$4:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'WeaponFusionTable'!$A$4:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'GachaTable'!$A$4:$P$9</definedName>
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$Q$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,12 +529,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24.3" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="31.69999999999999" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
@@ -2740,22 +2740,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>공통 기본 공격력 보유효과 계수</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>BaseAtkOwnBonusPerLevel</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>종류 불문 모든 무기가 공통으로 갖는 공격력 보유효과 계수. 보유효과 = 이 값 × 등급배율 × 단계배율 × 레벨 × 보유개수, 장착 여부·종류 무관하게 항상 합산</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -2763,27 +2763,27 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WeaponBreakthroughTable</t>
+          <t>WeaponUpgradeTable</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>공통 기본 공격력 장착효과 계수</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>BaseAtkEquipBonusPerLevel</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>종류 불문 모든 무기가 공통으로 갖는 공격력 장착효과 계수. 장착효과 = 이 값 × 등급배율 × 단계배율 × 레벨. 장착한 무기 1개에서만 발생, 종류 무관</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -2791,27 +2791,27 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WeaponBreakthroughTable</t>
+          <t>WeaponUpgradeTable</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>무기 돌파 단계 고유 ID (37030번대)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>돌파 단계</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>BreakthroughStep</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>필요 중복 개수</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>RequiredDuplicateCount</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>이 단계를 실행하는 데 소모되는 같은 무기 타입의 추가 보유 개수</t>
+          <t>무기 돌파 단계 고유 ID (37030번대)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>레벨 상한 증가량</t>
+          <t>돌파 단계</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>LevelCapBonus</t>
+          <t>BreakthroughStep</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>이 단계 완료 시 레벨 상한에 더해지는 값</t>
+          <t>1~5</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -2908,22 +2908,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>필요 중복 개수</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>RequiredDuplicateCount</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>이 단계를 실행하는 데 소모되는 같은 무기 타입의 추가 보유 개수</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -2931,17 +2931,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WeaponFusionTable</t>
+          <t>WeaponBreakthroughTable</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>레벨 상한 증가량</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>LevelCapBonus</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>이 단계 완료 시 레벨 상한에 더해지는 값</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -2959,27 +2959,27 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WeaponFusionTable</t>
+          <t>WeaponBreakthroughTable</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>37041 고정</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>합성 필요 개수</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>RequiredCount</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>장착 중인 타입은 이 계산에서 항상 1개 제외 (docs/WEAPON_SYSTEM.md 1.3 참고)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>결과물 레벨</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ResultLevel</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>합성으로 만들어지는 새 무기의 초기 레벨</t>
+          <t>37041 고정</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>결과물 돌파 횟수</t>
+          <t>합성 필요 개수</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ResultBreakthroughCount</t>
+          <t>RequiredCount</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>합성으로 만들어지는 새 무기의 초기 돌파 횟수</t>
+          <t>장착 중인 타입은 이 계산에서 항상 1개 제외 (docs/WEAPON_SYSTEM.md 1.3 참고)</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -3076,22 +3076,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>결과물 레벨</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>ResultLevel</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>합성으로 만들어지는 새 무기의 초기 레벨</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -3099,17 +3099,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GachaTable</t>
+          <t>WeaponFusionTable</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>결과물 돌파 횟수</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>ResultBreakthroughCount</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>합성으로 만들어지는 새 무기의 초기 돌파 횟수</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -3127,27 +3127,27 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GachaTable</t>
+          <t>WeaponFusionTable</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>37100번대</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>가챠 레벨</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>GachaLevel</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3173,7 +3173,11 @@
           <t>int</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>행 순번(표시용)</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
@@ -3184,12 +3188,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>필요 누적 뽑기 횟수</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>RequirePullCount</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3199,7 +3203,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>이 값 이상 누적 뽑기 시 해당 레벨로 상승</t>
+          <t>37100번대</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -3212,17 +3216,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>노말 가중치</t>
+          <t>가챠 레벨</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>NormalWeight</t>
+          <t>GachaLevel</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -3236,20 +3240,24 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>레어 가중치</t>
+          <t>필요 누적 뽑기 횟수</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>RareWeight</t>
+          <t>RequirePullCount</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>이 값 이상 누적 뽑기 시 해당 레벨로 상승</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
@@ -3260,12 +3268,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>에픽 가중치</t>
+          <t>노말 가중치</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EpicWeight</t>
+          <t>NormalWeight</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3284,12 +3292,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>유니크 가중치</t>
+          <t>레어 가중치</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>UniqueWeight</t>
+          <t>RareWeight</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3308,12 +3316,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>레전드리 가중치</t>
+          <t>에픽 가중치</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>LegendaryWeight</t>
+          <t>EpicWeight</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3332,12 +3340,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1단계 가중치</t>
+          <t>유니크 가중치</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Tier1Weight</t>
+          <t>UniqueWeight</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3356,12 +3364,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>2단계 가중치</t>
+          <t>레전드리 가중치</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tier2Weight</t>
+          <t>LegendaryWeight</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3380,12 +3388,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>3단계 가중치</t>
+          <t>1단계 가중치</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Tier3Weight</t>
+          <t>Tier1Weight</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3404,12 +3412,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>4단계 가중치</t>
+          <t>2단계 가중치</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Tier4Weight</t>
+          <t>Tier2Weight</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3428,12 +3436,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>5단계 가중치</t>
+          <t>3단계 가중치</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tier5Weight</t>
+          <t>Tier3Weight</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3452,24 +3460,20 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>뽑기 1회 비용</t>
+          <t>4단계 가중치</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>PullCostDiamond</t>
+          <t>Tier4Weight</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>다이아 소모량</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3480,40 +3484,36 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>5단계 가중치</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Tier5Weight</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RelicTable</t>
+          <t>GachaTable</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>뽑기 1회 비용</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>PullCostDiamond</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>다이아 소모량</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -3531,27 +3531,27 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RelicTable</t>
+          <t>GachaTable</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>유물 고유 ID (38000번대)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -3564,29 +3564,25 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>RelicGrade</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Normal/Rare/Epic</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>EnumDefine/RelicGrade</t>
-        </is>
-      </c>
+          <t>행 순번(표시용)</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3596,12 +3592,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>이름ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -3611,14 +3607,10 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>화면에 표시할 유물 이름의 StringTable ID</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>StringTable/Id</t>
-        </is>
-      </c>
+          <t>유물 고유 ID (38000번대)</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3628,12 +3620,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>효과 종류</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EffectType</t>
+          <t>RelicGrade</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -3643,12 +3635,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>스탯형 또는 특수효과형</t>
+          <t>Normal/Rare/Epic</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>EnumDefine/RelicEffectType</t>
+          <t>EnumDefine/RelicGrade</t>
         </is>
       </c>
     </row>
@@ -3660,25 +3652,29 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>효과 수치</t>
+          <t>이름ID</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EffectValue</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>스탯형이면 가산량, 특수효과형이면 %(GOLD_GAIN, TIMEHEIST_COOLDOWN)</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
+          <t>화면에 표시할 유물 이름의 StringTable ID</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>StringTable/Id</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3688,25 +3684,29 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>뽑기 가중치</t>
+          <t>효과 종류</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GachaWeight</t>
+          <t>EffectType</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>등급 내에서의 상대 가중치</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>스탯형 또는 특수효과형</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>EnumDefine/RelicEffectType</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3716,22 +3716,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>효과 수치</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>EffectValue</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>스탯형이면 가산량, 특수효과형이면 %(GOLD_GAIN, TIMEHEIST_COOLDOWN)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -3739,27 +3739,27 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RelicSlotTable</t>
+          <t>RelicTable</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>뽑기 가중치</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>GachaWeight</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>등급 내에서의 상대 가중치</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -3767,27 +3767,27 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RelicSlotTable</t>
+          <t>RelicTable</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>38100번대</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>슬롯 번호</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>SlotIndex</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>필요 존재력 해금 수</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>RequireUnlockedCount</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리가 이 값 이상 해금되면 이 슬롯이 열림</t>
+          <t>38100번대</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -3856,22 +3856,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>슬롯 번호</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>SlotIndex</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>1~5</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -3879,17 +3879,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TimeHeistTable</t>
+          <t>RelicSlotTable</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>필요 존재력 해금 수</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>RequireUnlockedCount</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>존재력 트리가 이 값 이상 해금되면 이 슬롯이 열림</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -3907,27 +3907,27 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TimeHeistTable</t>
+          <t>RelicSlotTable</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>타임 하이스트 고유 ID (34000번대)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -3940,22 +3940,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>기준 비용</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>CostBase</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1회차 사용 비용(시간에너지)</t>
+          <t>타임 하이스트 고유 ID (34000번대)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -3996,22 +3996,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>비용 증가율</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>CostGrowthRate</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>비용 = CostBase × CostGrowthRate^사용횟수</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>기준 쿨타임(초)</t>
+          <t>기준 비용</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>CooldownBase</t>
+          <t>CostBase</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1회차 사용 후 쿨타임 기준값(초)</t>
+          <t>1회차 사용 비용(시간에너지)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>쿨타임 증가율</t>
+          <t>비용 증가율</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CooldownGrowthRate</t>
+          <t>CostGrowthRate</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>쿨타임 = CooldownBase × CooldownGrowthRate^사용횟수</t>
+          <t>비용 = CostBase × CostGrowthRate^사용횟수</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>선취 스테이지 오프셋</t>
+          <t>기준 쿨타임(초)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>TargetStageOffset</t>
+          <t>CooldownBase</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>현재 스테이지 + 이 값 = 선취할 미래 스테이지</t>
+          <t>1회차 사용 후 쿨타임 기준값(초)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -4108,12 +4108,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>보상 배율</t>
+          <t>쿨타임 증가율</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>RewardMultiplier</t>
+          <t>CooldownGrowthRate</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>선취 스테이지를 몇 클리어분으로 환산해 보상을 줄지</t>
+          <t>쿨타임 = CooldownBase × CooldownGrowthRate^사용횟수</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -4136,22 +4136,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>선취 스테이지 오프셋</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>TargetStageOffset</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>현재 스테이지 + 이 값 = 선취할 미래 스테이지</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -4159,27 +4159,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RebirthTable</t>
+          <t>TimeHeistTable</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>보상 배율</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>RewardMultiplier</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>선취 스테이지를 몇 클리어분으로 환산해 보상을 줄지</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -4187,27 +4187,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RebirthTable</t>
+          <t>TimeHeistTable</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>리버스 고유 ID (35000번대)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -4220,22 +4220,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
@@ -4248,22 +4248,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>스테이지 초기화</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ResetStage</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>실행 시 스테이지를 1로 되돌리는지</t>
+          <t>리버스 고유 ID (35000번대)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -4276,22 +4276,22 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>스탯 초기화</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ResetStats</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>실행 시 6스탯 레벨을 초기화하는지</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>장비 초기화</t>
+          <t>스테이지 초기화</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>ResetEquipment</t>
+          <t>ResetStage</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>실행 시 장비 강화 레벨을 초기화하는지</t>
+          <t>실행 시 스테이지를 1로 되돌리는지</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>숙련 초기화</t>
+          <t>스탯 초기화</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>ResetMastery</t>
+          <t>ResetStats</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
+          <t>실행 시 6스탯 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>성장에너지 환급</t>
+          <t>장비 초기화</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>RefundGrowthEnergy</t>
+          <t>ResetEquipment</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
+          <t>실행 시 장비 강화 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -4388,12 +4388,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>골드 환급</t>
+          <t>숙련 초기화</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>RefundGold</t>
+          <t>ResetMastery</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 골드를 전액 돌려주는지</t>
+          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>숙련의정수 환급</t>
+          <t>성장에너지 환급</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RefundMasteryEssence</t>
+          <t>RefundGrowthEnergy</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
+          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>존재력트리 유지</t>
+          <t>골드 환급</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>KeepExistTree</t>
+          <t>RefundGold</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
+          <t>그동안 소비한 골드를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -4472,22 +4472,22 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>숙련의정수 환급</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>RefundMasteryEssence</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -4500,22 +4500,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 계수</t>
+          <t>존재력트리 유지</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>BonusBase</t>
+          <t>KeepExistTree</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
+          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -4528,22 +4528,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 지수</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>BonusExponent</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>포인트당 환급 증폭률</t>
+          <t>회차 보너스 계수</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>RefundBonusPerPoint</t>
+          <t>BonusBase</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
+          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>환급 배율 상한</t>
+          <t>회차 보너스 지수</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>MaxRefundMultiplier</t>
+          <t>BonusExponent</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
+          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -4612,22 +4612,22 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>보너스 설명</t>
+          <t>포인트당 환급 증폭률</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>//BonusDescription</t>
+          <t>RefundBonusPerPoint</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
+          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -4635,27 +4635,27 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthTable</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>환급 배율 상한</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>MaxRefundMultiplier</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -4663,27 +4663,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthTable</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>보너스 설명</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//BonusDescription</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>공용 상수 고유 ID (36000번대)</t>
+          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -4696,22 +4696,22 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -4724,22 +4724,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>공용 상수 고유 ID (36000번대)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -4752,22 +4752,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>키</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>실제 값. 수정 대상</t>
+          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>값 타입</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>ValueType</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Value를 int/float 중 무엇으로 해석할지</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -4808,22 +4808,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>값</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>실제 값. 수정 대상</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
@@ -4831,27 +4831,27 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>값 타입</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>ValueType</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>Value를 int/float 중 무엇으로 해석할지</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
@@ -4859,27 +4859,27 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -4892,22 +4892,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>한국어 표시 문자열</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -4920,22 +4920,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>영문</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>영문/내부 키 표시 문자열</t>
+          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>//Category</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>문자열 용도 분류 (파싱 제외)</t>
+          <t>한국어 표시 문자열</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -4971,15 +4971,19 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>enum 그룹</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr"/>
+          <t>영문</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -4987,7 +4991,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>enum 값이 속한 그룹 이름</t>
+          <t>영문/내부 키 표시 문자열</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -4995,15 +4999,19 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>한글 라벨</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr"/>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>//Category</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -5011,7 +5019,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>기획 문서/화면에 쓰는 한글 표기</t>
+          <t>문자열 용도 분류 (파싱 제외)</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -5024,7 +5032,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>영문 라벨</t>
+          <t>enum 그룹</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
@@ -5035,7 +5043,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 영문 값</t>
+          <t>enum 값이 속한 그룹 이름</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -5048,7 +5056,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>사용처</t>
+          <t>한글 라벨</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
@@ -5059,13 +5067,61 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
+          <t>기획 문서/화면에 쓰는 한글 표기</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>영문 라벨</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr"/>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>코드가 참조하는 영문 값</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>사용처</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr"/>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
           <t>이 enum 그룹을 참조하는 테이블.칼럼 목록</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F161"/>
+  <autoFilter ref="A1:F163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5076,7 +5132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5085,7 +5141,9 @@
     <col width="18.3" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24.3" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="31.69999999999999" customWidth="1" min="7" max="7"/>
+    <col width="31.69999999999999" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5096,6 +5154,8 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -5130,6 +5190,16 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
+          <t>공통 기본 공격력 보유효과 계수</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>공통 기본 공격력 장착효과 계수</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
           <t>설명</t>
         </is>
       </c>
@@ -5167,6 +5237,16 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -5203,6 +5283,16 @@
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>BaseAtkOwnBonusPerLevel</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>BaseAtkEquipBonusPerLevel</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>//Description</t>
         </is>
@@ -5227,14 +5317,20 @@
       <c r="F5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>레벨 상한 10, 돌파 1회당 +10 (WeaponBreakthroughTable 참고)</t>
+      <c r="G5" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>레벨 상한 10, 돌파 1회당 +10 (WeaponBreakthroughTable 참고). BaseAtk 계수는 검의 특화 계수와 동일값 — 모든 무기가 검만큼의 기본 공격력은 갖는다는 의미</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G5"/>
+  <autoFilter ref="A4:I5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7847,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8460,12 +8556,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>무기고</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Armory</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -9601,8 +9697,399 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>40077</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>장착</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>40078</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>돌파</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Breakthrough</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>40079</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>합성</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Fuse</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>40080</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>40081</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>유물</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>40082</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>보유 효과</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Own Bonus</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>40083</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>장착 효과</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Equip Bonus</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>40084</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>장착 중</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Equipped</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>40085</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>장착된 무기 없음</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>No Weapon Equipped</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>40086</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>보유 개수</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Owned Count</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>WeaponUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>40088</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>가챠 레벨</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Gacha Level</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>40089</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>다음 레벨까지</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>To Next Level</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>40090</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>1회 뽑기</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Pull x1</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>40091</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>10회 뽑기</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Pull x10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>40092</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>40093</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>중복</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E76"/>
+  <autoFilter ref="A4:E93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$Q$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7943,12 +7943,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20.2" customWidth="1" min="3" max="3"/>
+    <col width="22.1" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
@@ -10088,8 +10088,238 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>40094</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>유물 뽑기</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Pull Relic</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>40095</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>중복 환급</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate Refund</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>40096</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>다음 슬롯</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Next Slot</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>40097</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>활성 슬롯</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Active Slots</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>40098</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>보유 유물</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Owned Relics</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>40099</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>슬롯이 가득 참</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Slots Full</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>40100</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>골드 획득량</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Gold Gain</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>40101</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>타임 하이스트 쿨타임</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Time Heist Cooldown</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>RelicUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>40102</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>활성화</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Activate</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>40103</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>비활성화</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Deactivate</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E93"/>
+  <autoFilter ref="A4:E103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$Q$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7943,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10318,8 +10318,54 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>40104</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>스탯</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>GrowthUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>40105</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>숙련</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Mastery</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>GrowthUi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E103"/>
+  <autoFilter ref="A4:E105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -28,7 +28,7 @@
     <sheet name="StringTable" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StageTable'!$A$4:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$10</definedName>
@@ -44,9 +44,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RelicTable'!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'RelicSlotTable'!$A$4:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$R$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>장비 초기화</t>
+          <t>숙련 초기화</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>ResetEquipment</t>
+          <t>ResetMastery</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>실행 시 장비 강화 레벨을 초기화하는지</t>
+          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -4388,12 +4388,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>숙련 초기화</t>
+          <t>성장에너지 환급</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>ResetMastery</t>
+          <t>RefundGrowthEnergy</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>실행 시 무기 숙련 레벨을 초기화하는지</t>
+          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>성장에너지 환급</t>
+          <t>골드 환급</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RefundGrowthEnergy</t>
+          <t>RefundGold</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 성장에너지를 전액 돌려주는지</t>
+          <t>그동안 소비한 골드를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>골드 환급</t>
+          <t>숙련의정수 환급</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>RefundGold</t>
+          <t>RefundMasteryEssence</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 골드를 전액 돌려주는지</t>
+          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>숙련의정수 환급</t>
+          <t>존재력트리 유지</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RefundMasteryEssence</t>
+          <t>KeepExistTree</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>그동안 소비한 숙련의 정수를 전액 돌려주는지</t>
+          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -4500,22 +4500,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>존재력트리 유지</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>KeepExistTree</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리 해금 상태를 초기화하지 않고 유지하는지</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -4528,22 +4528,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>회차 보너스 계수</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>BonusBase</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 계수</t>
+          <t>회차 보너스 지수</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>BonusBase</t>
+          <t>BonusExponent</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식의 기준 계수. 포인트 = BonusBase × 도달스테이지^BonusExponent (소수점 유지, 최소 스테이지 제한 없음)</t>
+          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 지수</t>
+          <t>다이아 지급 계수</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>BonusExponent</t>
+          <t>DiamondBase</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 포인트 공식에서 도달 스테이지에 적용하는 지수</t>
+          <t>리버스 시 신규 지급되는 다이아 공식의 기준 계수. 지급량 = floor(DiamondBase × 도달스테이지^DiamondExponent). 환급이 아니라 신규 지급이라 rebirthSpent/환급 배율과 무관</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>포인트당 환급 증폭률</t>
+          <t>다이아 지급 지수</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>RefundBonusPerPoint</t>
+          <t>DiamondExponent</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
+          <t>다이아 지급 공식에서 도달 스테이지에 적용하는 지수</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>환급 배율 상한</t>
+          <t>포인트당 환급 증폭률</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>MaxRefundMultiplier</t>
+          <t>RefundBonusPerPoint</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
+          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>보너스 설명</t>
+          <t>환급 배율 상한</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>//BonusDescription</t>
+          <t>MaxRefundMultiplier</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
+          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -4691,27 +4691,27 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthTable</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>보너스 설명</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>//BonusDescription</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>공용 상수 고유 ID (36000번대)</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -4752,22 +4752,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
+          <t>공용 상수 고유 ID (36000번대)</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>키</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -4808,22 +4808,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>실제 값. 수정 대상</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
@@ -4836,22 +4836,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>값 타입</t>
+          <t>값</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>ValueType</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Value를 int/float 중 무엇으로 해석할지</t>
+          <t>실제 값. 수정 대상</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>값 타입</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>ValueType</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>Value를 int/float 중 무엇으로 해석할지</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -4887,27 +4887,27 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -4948,22 +4948,22 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>한국어 표시 문자열</t>
+          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>영문</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>영문/내부 키 표시 문자열</t>
+          <t>한국어 표시 문자열</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>영문</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>//Category</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>문자열 용도 분류 (파싱 제외)</t>
+          <t>영문/내부 키 표시 문자열</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -5027,15 +5027,19 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>enum 그룹</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr"/>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>//Category</t>
+        </is>
+      </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -5043,7 +5047,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>enum 값이 속한 그룹 이름</t>
+          <t>문자열 용도 분류 (파싱 제외)</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>한글 라벨</t>
+          <t>enum 그룹</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
@@ -5067,7 +5071,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>기획 문서/화면에 쓰는 한글 표기</t>
+          <t>enum 값이 속한 그룹 이름</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -5080,7 +5084,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>영문 라벨</t>
+          <t>한글 라벨</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr"/>
@@ -5091,7 +5095,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 영문 값</t>
+          <t>기획 문서/화면에 쓰는 한글 표기</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -5104,7 +5108,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>사용처</t>
+          <t>영문 라벨</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr"/>
@@ -5115,13 +5119,37 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
+          <t>코드가 참조하는 영문 값</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>사용처</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
           <t>이 enum 그룹을 참조하는 테이블.칼럼 목록</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F163"/>
+  <autoFilter ref="A1:F164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7085,7 +7113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7093,18 +7121,19 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="17.3" customWidth="1" min="4" max="4"/>
     <col width="13.5" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="17.3" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="17.3" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="18.3" customWidth="1" min="12" max="12"/>
     <col width="18.3" customWidth="1" min="13" max="13"/>
     <col width="18.3" customWidth="1" min="14" max="14"/>
-    <col width="22.1" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="18.3" customWidth="1" min="15" max="15"/>
+    <col width="22.1" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7125,6 +7154,7 @@
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
       <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -7154,60 +7184,65 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>장비 초기화</t>
+          <t>숙련 초기화</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>숙련 초기화</t>
+          <t>성장에너지 환급</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>성장에너지 환급</t>
+          <t>골드 환급</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>골드 환급</t>
+          <t>숙련의정수 환급</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>숙련의정수 환급</t>
+          <t>존재력트리 유지</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>존재력트리 유지</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>회차 보너스 계수</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>회차 보너스 계수</t>
+          <t>회차 보너스 지수</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>회차 보너스 지수</t>
+          <t>다이아 지급 계수</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
+          <t>다이아 지급 지수</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
           <t>포인트당 환급 증폭률</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>환급 배율 상한</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>보너스 설명</t>
         </is>
@@ -7266,12 +7301,12 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -7295,6 +7330,11 @@
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -7328,60 +7368,65 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>ResetEquipment</t>
+          <t>ResetMastery</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>ResetMastery</t>
+          <t>RefundGrowthEnergy</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>RefundGrowthEnergy</t>
+          <t>RefundGold</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>RefundGold</t>
+          <t>RefundMasteryEssence</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>RefundMasteryEssence</t>
+          <t>KeepExistTree</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>KeepExistTree</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>BonusBase</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>BonusBase</t>
+          <t>BonusExponent</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>BonusExponent</t>
+          <t>DiamondBase</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
+          <t>DiamondExponent</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
           <t>RefundBonusPerPoint</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>MaxRefundMultiplier</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>//BonusDescription</t>
         </is>
@@ -7420,34 +7465,37 @@
       <c r="J5" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="6" t="b">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>스테이지/스탯/숙련 초기화 + 소비 재화 전액 환급 + 다이아 신규 지급. 존재력 트리는 유지</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>스테이지/스탯/장비/숙련 초기화 + 소비 재화 전액 환급. 존재력 트리는 유지</t>
-        </is>
-      </c>
       <c r="M5" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>포인트 = 1.0 × 도달스테이지^0.5 (소수점 유지, 최소 스테이지 제한 없음). 환급 배율 = 1 + (누적 포인트 × 1.0 / 100), 최대 5.0배. 전투 중 재화 획득량/스탯에는 영향 없음</t>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>포인트 = 1.0 × 도달스테이지^0.5 (소수점 유지, 최소 스테이지 제한 없음). 다이아 지급량 = floor(20.0 × 도달스테이지^0.6, 환급과 무관한 신규 지급). 환급 배율 = 1 + (누적 포인트 × 1.0 / 100), 최대 5.0배. 전투 중 재화 획득량/스탯에는 영향 없음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q5"/>
+  <autoFilter ref="A4:R5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7856,7 +7904,7 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -7865,7 +7913,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>게임 시작 시 지급되는 초기 다이아</t>
+          <t>게임 시작 시 지급되는 초기 다이아 — 첫 리버스 전에도 무기 가챠를 1~2회 체험할 수 있는 양</t>
         </is>
       </c>
     </row>
@@ -7943,13 +7991,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22.1" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24.1" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -8230,21 +8278,21 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>40009</v>
+        <v>40015</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>무기</t>
+          <t>존재력</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>EXIST</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -8253,21 +8301,21 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40014</v>
+        <v>40016</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>기본 검</t>
+          <t>성장에너지</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Basic Sword</t>
+          <t>GROWTH_ENERGY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -8276,16 +8324,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>40015</v>
+        <v>40017</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>존재력</t>
+          <t>숙련의 정수</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>EXIST</t>
+          <t>MASTERY_ESSENCE</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8299,16 +8347,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>40016</v>
+        <v>40018</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>성장에너지</t>
+          <t>시간에너지</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GROWTH_ENERGY</t>
+          <t>TIME_ENERGY</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8322,16 +8370,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>40017</v>
+        <v>40019</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>숙련의 정수</t>
+          <t>골드</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MASTERY_ESSENCE</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8345,21 +8393,21 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>40018</v>
+        <v>40020</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>시간에너지</t>
+          <t>존재력 트리</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TIME_ENERGY</t>
+          <t>EXIST_TREE</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -8368,21 +8416,21 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>40019</v>
+        <v>40021</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>존재</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>EXIST_ABBR</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>CurrencyAbbr</t>
         </is>
       </c>
     </row>
@@ -8391,21 +8439,21 @@
         <v>16</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>40020</v>
+        <v>40022</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리</t>
+          <t>성장</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>EXIST_TREE</t>
+          <t>GROWTH_ABBR</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>CurrencyAbbr</t>
         </is>
       </c>
     </row>
@@ -8414,16 +8462,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>40021</v>
+        <v>40023</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>존재</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EXIST_ABBR</t>
+          <t>TIME_ABBR</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8437,16 +8485,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>40022</v>
+        <v>40024</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>성장</t>
+          <t>골드</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GROWTH_ABBR</t>
+          <t>GOLD_ABBR</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8460,16 +8508,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>40023</v>
+        <v>40025</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>TIME_ABBR</t>
+          <t>ESSENCE_ABBR</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8483,21 +8531,21 @@
         <v>20</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>40024</v>
+        <v>40026</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>성장</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>GOLD_ABBR</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CurrencyAbbr</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -8506,21 +8554,21 @@
         <v>21</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>40025</v>
+        <v>40027</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>무기고</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ESSENCE_ABBR</t>
+          <t>Armory</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CurrencyAbbr</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -8529,16 +8577,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>40026</v>
+        <v>40028</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>성장</t>
+          <t>가챠</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Gacha</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8552,16 +8600,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>40027</v>
+        <v>40029</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>무기고</t>
+          <t>존재력</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Armory</t>
+          <t>ExistTree</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8575,16 +8623,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>40028</v>
+        <v>40030</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gacha</t>
+          <t>Dogam</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8598,21 +8646,21 @@
         <v>25</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>40029</v>
+        <v>40031</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>존재력</t>
+          <t>닫기</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ExistTree</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -8621,21 +8669,21 @@
         <v>26</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>40030</v>
+        <v>40032</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Dogam</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -8644,16 +8692,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>40031</v>
+        <v>40033</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>닫기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8667,16 +8715,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>40032</v>
+        <v>40034</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>실행</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Execute</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8690,16 +8738,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>40033</v>
+        <v>40035</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>강탈</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Steal</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -8713,16 +8761,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>40034</v>
+        <v>40036</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>실행</t>
+          <t>받기</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8736,16 +8784,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>40035</v>
+        <v>40037</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>강탈</t>
+          <t>해금</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Steal</t>
+          <t>Unlock</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -8759,16 +8807,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>40036</v>
+        <v>40038</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>받기</t>
+          <t>강화</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8782,16 +8830,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>40037</v>
+        <v>40039</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>해금</t>
+          <t>수련</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Unlock</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -8805,16 +8853,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>40038</v>
+        <v>40040</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>업그레이드</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Upgrade</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8828,16 +8876,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>40039</v>
+        <v>40041</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>수련</t>
+          <t>최대로</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>MaxAll</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8851,16 +8899,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>40040</v>
+        <v>40042</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>업그레이드</t>
+          <t>뒤로</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8874,21 +8922,21 @@
         <v>37</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>40041</v>
+        <v>40043</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>최대로</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MaxAll</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -8897,21 +8945,21 @@
         <v>38</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>40042</v>
+        <v>40044</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>뒤로</t>
+          <t>해금됨</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Unlocked</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -8920,16 +8968,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>40043</v>
+        <v>40045</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>사용 가능</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -8943,16 +8991,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>40044</v>
+        <v>40046</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>해금됨</t>
+          <t>티어</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Unlocked</t>
+          <t>Tier</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8966,16 +9014,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>40045</v>
+        <v>40047</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>사용 가능</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -8989,16 +9037,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>40046</v>
+        <v>40048</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>티어</t>
+          <t>비용</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9012,21 +9060,21 @@
         <v>43</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>40047</v>
+        <v>40049</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>회차 보너스</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>RebirthBonus</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>RebirthBonus</t>
         </is>
       </c>
     </row>
@@ -9035,21 +9083,21 @@
         <v>44</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>40048</v>
+        <v>40050</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>현재 회차</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>CurrentCycle</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>RebirthBonus</t>
         </is>
       </c>
     </row>
@@ -9058,16 +9106,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>40049</v>
+        <v>40051</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스</t>
+          <t>누적 포인트</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>RebirthBonus</t>
+          <t>TotalPoints</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -9081,16 +9129,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>40050</v>
+        <v>40052</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>현재 회차</t>
+          <t>획득 예정 포인트</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CurrentCycle</t>
+          <t>PendingPoints</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -9104,16 +9152,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>40051</v>
+        <v>40053</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>누적 포인트</t>
+          <t>환급 배율</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>TotalPoints</t>
+          <t>RefundMultiplier</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -9127,16 +9175,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>40052</v>
+        <v>40054</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>획득 예정 포인트</t>
+          <t>최고 도달 스테이지</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PendingPoints</t>
+          <t>MaxStageReached</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -9150,21 +9198,21 @@
         <v>49</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>40053</v>
+        <v>40055</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>환급 배율</t>
+          <t>검</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>RefundMultiplier</t>
+          <t>Sword</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RebirthBonus</t>
+          <t>WeaponType</t>
         </is>
       </c>
     </row>
@@ -9173,21 +9221,21 @@
         <v>50</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>40054</v>
+        <v>40056</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>최고 도달 스테이지</t>
+          <t>창</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>MaxStageReached</t>
+          <t>Spear</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RebirthBonus</t>
+          <t>WeaponType</t>
         </is>
       </c>
     </row>
@@ -9196,16 +9244,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>40055</v>
+        <v>40057</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>검</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Sword</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -9219,21 +9267,21 @@
         <v>52</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>40056</v>
+        <v>40058</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>창</t>
+          <t>노말</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Spear</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>WeaponGrade</t>
         </is>
       </c>
     </row>
@@ -9242,21 +9290,21 @@
         <v>53</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>40057</v>
+        <v>40059</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>레어</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>WeaponGrade</t>
         </is>
       </c>
     </row>
@@ -9265,16 +9313,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>40058</v>
+        <v>40060</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>노말</t>
+          <t>에픽</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -9288,16 +9336,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>40059</v>
+        <v>40061</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>레어</t>
+          <t>유니크</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -9311,16 +9359,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>40060</v>
+        <v>40062</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>에픽</t>
+          <t>레전드리</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -9334,21 +9382,21 @@
         <v>57</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>40061</v>
+        <v>40063</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>유니크</t>
+          <t>힘의 유물</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Relic of Strength</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>WeaponGrade</t>
+          <t>RelicName</t>
         </is>
       </c>
     </row>
@@ -9357,21 +9405,21 @@
         <v>58</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>40062</v>
+        <v>40064</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>레전드리</t>
+          <t>방패의 유물</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Relic of Shield</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>WeaponGrade</t>
+          <t>RelicName</t>
         </is>
       </c>
     </row>
@@ -9380,16 +9428,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>40063</v>
+        <v>40065</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>힘의 유물</t>
+          <t>행운의 유물</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Relic of Strength</t>
+          <t>Relic of Luck</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -9403,16 +9451,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>40064</v>
+        <v>40066</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>방패의 유물</t>
+          <t>가속의 유물</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Relic of Shield</t>
+          <t>Relic of Haste</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -9426,16 +9474,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>40065</v>
+        <v>40067</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>행운의 유물</t>
+          <t>파괴의 유물</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Relic of Luck</t>
+          <t>Relic of Destruction</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -9449,16 +9497,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>40066</v>
+        <v>40068</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>가속의 유물</t>
+          <t>상인의 유물</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Relic of Haste</t>
+          <t>Relic of Merchant</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9472,16 +9520,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>40067</v>
+        <v>40069</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>파괴의 유물</t>
+          <t>균열의 유물</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Relic of Destruction</t>
+          <t>Relic of Rift</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -9495,16 +9543,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>40068</v>
+        <v>40070</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>상인의 유물</t>
+          <t>시간의 유물</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Relic of Merchant</t>
+          <t>Relic of Time</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -9518,16 +9566,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>40069</v>
+        <v>40071</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>균열의 유물</t>
+          <t>전능의 유물</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Relic of Rift</t>
+          <t>Relic of Omnipotence</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -9541,21 +9589,21 @@
         <v>66</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>40070</v>
+        <v>40072</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>시간의 유물</t>
+          <t>검 숙련</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Relic of Time</t>
+          <t>Sword Mastery</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RelicName</t>
+          <t>Mastery</t>
         </is>
       </c>
     </row>
@@ -9564,21 +9612,21 @@
         <v>67</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>40071</v>
+        <v>40073</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>전능의 유물</t>
+          <t>창 숙련</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Relic of Omnipotence</t>
+          <t>Spear Mastery</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RelicName</t>
+          <t>Mastery</t>
         </is>
       </c>
     </row>
@@ -9587,16 +9635,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="6" t="n">
-        <v>40072</v>
+        <v>40074</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>검 숙련</t>
+          <t>활 숙련</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Sword Mastery</t>
+          <t>Bow Mastery</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -9610,21 +9658,21 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>40073</v>
+        <v>40075</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>창 숙련</t>
+          <t>다이아</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Spear Mastery</t>
+          <t>DIAMOND</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Mastery</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -9633,21 +9681,21 @@
         <v>70</v>
       </c>
       <c r="B74" s="6" t="n">
-        <v>40074</v>
+        <v>40076</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>활 숙련</t>
+          <t>다이아</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Bow Mastery</t>
+          <t>DIAMOND_ABBR</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Mastery</t>
+          <t>CurrencyAbbr</t>
         </is>
       </c>
     </row>
@@ -9656,21 +9704,21 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="n">
-        <v>40075</v>
+        <v>40077</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>DIAMOND</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -9679,21 +9727,21 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="n">
-        <v>40076</v>
+        <v>40078</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>돌파</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>DIAMOND_ABBR</t>
+          <t>Breakthrough</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>CurrencyAbbr</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -9702,16 +9750,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="n">
-        <v>40077</v>
+        <v>40079</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>합성</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Fuse</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9725,21 +9773,21 @@
         <v>74</v>
       </c>
       <c r="B78" s="6" t="n">
-        <v>40078</v>
+        <v>40080</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>돌파</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Breakthrough</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>WeaponUi</t>
         </is>
       </c>
     </row>
@@ -9748,21 +9796,21 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="n">
-        <v>40079</v>
+        <v>40081</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>합성</t>
+          <t>유물</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Fuse</t>
+          <t>Relic</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>WeaponUi</t>
         </is>
       </c>
     </row>
@@ -9771,16 +9819,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="6" t="n">
-        <v>40080</v>
+        <v>40082</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>보유 효과</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Own Bonus</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9794,16 +9842,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>40081</v>
+        <v>40083</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>유물</t>
+          <t>장착 효과</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Relic</t>
+          <t>Equip Bonus</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -9817,16 +9865,16 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="n">
-        <v>40082</v>
+        <v>40084</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>보유 효과</t>
+          <t>장착 중</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Own Bonus</t>
+          <t>Equipped</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9840,16 +9888,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="6" t="n">
-        <v>40083</v>
+        <v>40085</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>장착 효과</t>
+          <t>장착된 무기 없음</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Equip Bonus</t>
+          <t>No Weapon Equipped</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9863,16 +9911,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="6" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>장착 중</t>
+          <t>보유 개수</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Equipped</t>
+          <t>Owned Count</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -9886,16 +9934,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="6" t="n">
-        <v>40085</v>
+        <v>40087</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>장착된 무기 없음</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>No Weapon Equipped</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -9909,21 +9957,21 @@
         <v>82</v>
       </c>
       <c r="B86" s="6" t="n">
-        <v>40086</v>
+        <v>40088</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>보유 개수</t>
+          <t>가챠 레벨</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Owned Count</t>
+          <t>Gacha Level</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>WeaponUi</t>
+          <t>GachaUi</t>
         </is>
       </c>
     </row>
@@ -9932,21 +9980,21 @@
         <v>83</v>
       </c>
       <c r="B87" s="6" t="n">
-        <v>40087</v>
+        <v>40089</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>다음 레벨까지</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>To Next Level</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WeaponUi</t>
+          <t>GachaUi</t>
         </is>
       </c>
     </row>
@@ -9955,16 +10003,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="6" t="n">
-        <v>40088</v>
+        <v>40090</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>가챠 레벨</t>
+          <t>1회 뽑기</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Gacha Level</t>
+          <t>Pull x1</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -9978,16 +10026,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="6" t="n">
-        <v>40089</v>
+        <v>40091</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>다음 레벨까지</t>
+          <t>10회 뽑기</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>To Next Level</t>
+          <t>Pull x10</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -10001,16 +10049,16 @@
         <v>86</v>
       </c>
       <c r="B90" s="6" t="n">
-        <v>40090</v>
+        <v>40092</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>1회 뽑기</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Pull x1</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -10024,16 +10072,16 @@
         <v>87</v>
       </c>
       <c r="B91" s="6" t="n">
-        <v>40091</v>
+        <v>40093</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>10회 뽑기</t>
+          <t>중복</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Pull x10</t>
+          <t>Duplicate</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -10047,21 +10095,21 @@
         <v>88</v>
       </c>
       <c r="B92" s="6" t="n">
-        <v>40092</v>
+        <v>40094</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유물 뽑기</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Pull Relic</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>GachaUi</t>
+          <t>RelicUi</t>
         </is>
       </c>
     </row>
@@ -10070,21 +10118,21 @@
         <v>89</v>
       </c>
       <c r="B93" s="6" t="n">
-        <v>40093</v>
+        <v>40095</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>중복</t>
+          <t>중복 환급</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Duplicate Refund</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>GachaUi</t>
+          <t>RelicUi</t>
         </is>
       </c>
     </row>
@@ -10093,16 +10141,16 @@
         <v>90</v>
       </c>
       <c r="B94" s="6" t="n">
-        <v>40094</v>
+        <v>40096</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>유물 뽑기</t>
+          <t>다음 슬롯</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Pull Relic</t>
+          <t>Next Slot</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -10116,16 +10164,16 @@
         <v>91</v>
       </c>
       <c r="B95" s="6" t="n">
-        <v>40095</v>
+        <v>40097</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>중복 환급</t>
+          <t>활성 슬롯</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Refund</t>
+          <t>Active Slots</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -10139,16 +10187,16 @@
         <v>92</v>
       </c>
       <c r="B96" s="6" t="n">
-        <v>40096</v>
+        <v>40098</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>다음 슬롯</t>
+          <t>보유 유물</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Next Slot</t>
+          <t>Owned Relics</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -10162,16 +10210,16 @@
         <v>93</v>
       </c>
       <c r="B97" s="6" t="n">
-        <v>40097</v>
+        <v>40099</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>활성 슬롯</t>
+          <t>슬롯이 가득 참</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Active Slots</t>
+          <t>Slots Full</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -10185,16 +10233,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="6" t="n">
-        <v>40098</v>
+        <v>40100</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>보유 유물</t>
+          <t>골드 획득량</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Owned Relics</t>
+          <t>Gold Gain</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -10208,16 +10256,16 @@
         <v>95</v>
       </c>
       <c r="B99" s="6" t="n">
-        <v>40099</v>
+        <v>40101</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>슬롯이 가득 참</t>
+          <t>타임 하이스트 쿨타임</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Slots Full</t>
+          <t>Time Heist Cooldown</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -10231,21 +10279,21 @@
         <v>96</v>
       </c>
       <c r="B100" s="6" t="n">
-        <v>40100</v>
+        <v>40102</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>골드 획득량</t>
+          <t>활성화</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Gold Gain</t>
+          <t>Activate</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RelicUi</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -10254,21 +10302,21 @@
         <v>97</v>
       </c>
       <c r="B101" s="6" t="n">
-        <v>40101</v>
+        <v>40103</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>타임 하이스트 쿨타임</t>
+          <t>비활성화</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Time Heist Cooldown</t>
+          <t>Deactivate</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RelicUi</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -10277,21 +10325,21 @@
         <v>98</v>
       </c>
       <c r="B102" s="6" t="n">
-        <v>40102</v>
+        <v>40104</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>활성화</t>
+          <t>스탯</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Stat</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>GrowthUi</t>
         </is>
       </c>
     </row>
@@ -10300,21 +10348,21 @@
         <v>99</v>
       </c>
       <c r="B103" s="6" t="n">
-        <v>40103</v>
+        <v>40105</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>비활성화</t>
+          <t>숙련</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Deactivate</t>
+          <t>Mastery</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>GrowthUi</t>
         </is>
       </c>
     </row>
@@ -10323,21 +10371,21 @@
         <v>100</v>
       </c>
       <c r="B104" s="6" t="n">
-        <v>40104</v>
+        <v>40106</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>스탯</t>
+          <t>적 HP</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Stat</t>
+          <t>Enemy HP</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>GrowthUi</t>
+          <t>CommonUi</t>
         </is>
       </c>
     </row>
@@ -10346,26 +10394,486 @@
         <v>101</v>
       </c>
       <c r="B105" s="6" t="n">
-        <v>40105</v>
+        <v>40107</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>숙련</t>
+          <t>적 공격력</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Mastery</t>
+          <t>Enemy ATK</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>GrowthUi</t>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>40108</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>처치 진행도</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Kill Progress</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>40109</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>스테이지 보상 (처치당)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Stage Reward (per kill)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>40110</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>40111</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>오프라인 보상</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Offline Reward</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>40112</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>비운 시간</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Time Away</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>40113</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>최대</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>40114</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>인정</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Recognized</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>40115</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>획득 재화</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Rewards Earned</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>40116</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>1회 비용</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Cost per Pull</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>40117</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>종</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Kinds</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>40118</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>노드</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Nodes</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>40119</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>대상 스테이지</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Target Stage</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>40120</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>클리어 환산</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Clears Converted</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>40121</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>획득 예정</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Expected Gain</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>40122</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>소모</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Consume</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>40123</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>사용 횟수</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Use Count</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>40124</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>쿨타임</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>40125</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Times</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>40126</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>등급 확률</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Grade Probability</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>40127</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Owned</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>CommonUi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E105"/>
+  <autoFilter ref="A4:E125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11553,7 +12061,7 @@
         <v>2</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>1.15</v>
@@ -11649,7 +12157,7 @@
         <v>4</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1.15</v>
@@ -11745,7 +12253,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1.15</v>
@@ -11841,7 +12349,7 @@
         <v>8</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1.15</v>
@@ -11937,7 +12445,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1.15</v>
@@ -12033,7 +12541,7 @@
         <v>12</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1.15</v>
@@ -12129,7 +12637,7 @@
         <v>14</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1.15</v>
@@ -12225,7 +12733,7 @@
         <v>16</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1.15</v>
@@ -12321,7 +12829,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1.15</v>
@@ -12417,7 +12925,7 @@
         <v>20</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>1.15</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -24,11 +24,12 @@
     <sheet name="RelicSlotTable" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="TimeHeistTable" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="RebirthTable" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="CommonTable" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="StringTable" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="RebirthRewardTable" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="CommonTable" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="StringTable" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StageTable'!$A$4:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$10</definedName>
@@ -44,9 +45,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RelicTable'!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'RelicSlotTable'!$A$4:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TimeHeistTable'!$A$4:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$R$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StringTable'!$A$4:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'RebirthRewardTable'!$A$4:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4584,12 +4586,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>다이아 지급 계수</t>
+          <t>포인트당 환급 증폭률</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>DiamondBase</t>
+          <t>RefundBonusPerPoint</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -4599,7 +4601,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>리버스 시 신규 지급되는 다이아 공식의 기준 계수. 지급량 = floor(DiamondBase × 도달스테이지^DiamondExponent). 환급이 아니라 신규 지급이라 rebirthSpent/환급 배율과 무관</t>
+          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -4612,12 +4614,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>다이아 지급 지수</t>
+          <t>환급 배율 상한</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>DiamondExponent</t>
+          <t>MaxRefundMultiplier</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -4627,7 +4629,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>다이아 지급 공식에서 도달 스테이지에 적용하는 지수</t>
+          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -4640,22 +4642,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>포인트당 환급 증폭률</t>
+          <t>보너스 설명</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>RefundBonusPerPoint</t>
+          <t>//BonusDescription</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>누적 보너스 포인트 1당 리버스 환급량에 곱연산으로 붙는 증폭률(%). 환급 배율 = 1 + (누적 포인트 × 이 값 / 100). 전투 중 재화 획득량/스탯에는 영향 없음</t>
+          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -4663,27 +4665,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RebirthTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>환급 배율 상한</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>MaxRefundMultiplier</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>환급 배율이 이 값을 넘지 않도록 제한</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -4691,27 +4693,27 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>RebirthTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>보너스 설명</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>//BonusDescription</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스 공식에 대한 참고 설명 (파싱 제외)</t>
+          <t>리버스 다이아 보상 구간 고유 ID (35100번대)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -4719,27 +4721,27 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>구간 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -4747,17 +4749,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>구간 시작 스테이지</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>StageFrom</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -4767,7 +4769,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>공용 상수 고유 ID (36000번대)</t>
+          <t>이 구간의 시작 스테이지(포함)</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -4775,27 +4777,27 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>구간 끝 스테이지</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>StageTo</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
+          <t>이 구간의 끝 스테이지(포함). 마지막 구간은 999999로 열어둔다</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -4803,27 +4805,27 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>다이아 지급량</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>//Name</t>
+          <t>DiamondReward</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>행 구분용 참고 이름 (파싱 제외)</t>
+          <t>리버스 시점의 도달 스테이지가 이 구간에 속하면 지급되는 다이아 수량(고정값)</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
@@ -4831,27 +4833,27 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>CommonTable</t>
+          <t>RebirthRewardTable</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>실제 값. 수정 대상</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
@@ -4864,22 +4866,22 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>값 타입</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>ValueType</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Value를 int/float 중 무엇으로 해석할지</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -4892,22 +4894,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>//Description</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>행에 대한 참고 설명 (파싱 제외)</t>
+          <t>공용 상수 고유 ID (36000번대)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -4915,27 +4917,27 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>순번</t>
+          <t>키</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>행 순번(표시용)</t>
+          <t>코드가 참조하는 식별자. 절대 수정 금지</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -4943,27 +4945,27 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>//Name</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
+          <t>행 구분용 참고 이름 (파싱 제외)</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -4971,27 +4973,27 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>값</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>한국어 표시 문자열</t>
+          <t>실제 값. 수정 대상</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -4999,17 +5001,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>영문</t>
+          <t>값 타입</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>ValueType</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5019,7 +5021,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>영문/내부 키 표시 문자열</t>
+          <t>Value를 int/float 중 무엇으로 해석할지</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -5027,17 +5029,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>StringTable</t>
+          <t>CommonTable</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>//Category</t>
+          <t>//Description</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5047,7 +5049,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>문자열 용도 분류 (파싱 제외)</t>
+          <t>행에 대한 참고 설명 (파싱 제외)</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -5055,23 +5057,27 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>enum 그룹</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr"/>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>enum 값이 속한 그룹 이름</t>
+          <t>행 순번(표시용)</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -5079,23 +5085,27 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>한글 라벨</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>기획 문서/화면에 쓰는 한글 표기</t>
+          <t>문자열 고유 ID (40000번대). 다른 테이블의 이름ID가 참조</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -5103,15 +5113,19 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>#EnumDefine</t>
+          <t>StringTable</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>영문 라벨</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr"/>
+          <t>한국어</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -5119,7 +5133,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>코드가 참조하는 영문 값</t>
+          <t>한국어 표시 문자열</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -5127,29 +5141,157 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>StringTable</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>영문</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>영문/내부 키 표시 문자열</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>StringTable</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>//Category</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>문자열 용도 분류 (파싱 제외)</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
           <t>#EnumDefine</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>enum 그룹</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>enum 값이 속한 그룹 이름</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>한글 라벨</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>기획 문서/화면에 쓰는 한글 표기</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>영문 라벨</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>코드가 참조하는 영문 값</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>#EnumDefine</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>사용처</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr"/>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>이 enum 그룹을 참조하는 테이블.칼럼 목록</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F164"/>
+  <autoFilter ref="A1:F169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7113,7 +7255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7129,11 +7271,9 @@
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="18.3" customWidth="1" min="12" max="12"/>
     <col width="18.3" customWidth="1" min="13" max="13"/>
-    <col width="18.3" customWidth="1" min="14" max="14"/>
-    <col width="18.3" customWidth="1" min="15" max="15"/>
-    <col width="22.1" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="22.1" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7153,8 +7293,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
-      <c r="R1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -7224,25 +7362,15 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>다이아 지급 계수</t>
+          <t>포인트당 환급 증폭률</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>다이아 지급 지수</t>
+          <t>환급 배율 상한</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>포인트당 환급 증폭률</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>환급 배율 상한</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>보너스 설명</t>
         </is>
@@ -7326,16 +7454,6 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
@@ -7408,25 +7526,15 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>DiamondBase</t>
+          <t>RefundBonusPerPoint</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>DiamondExponent</t>
+          <t>MaxRefundMultiplier</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>RefundBonusPerPoint</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>MaxRefundMultiplier</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>//BonusDescription</t>
         </is>
@@ -7467,7 +7575,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>스테이지/스탯/숙련 초기화 + 소비 재화 전액 환급 + 다이아 신규 지급. 존재력 트리는 유지</t>
+          <t>스테이지/스탯/숙련 초기화 + 소비 재화 전액 환급 + 다이아 신규 지급(RebirthRewardTable). 존재력 트리는 유지</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
@@ -7477,30 +7585,283 @@
         <v>0.5</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>포인트 = 1.0 × 도달스테이지^0.5 (소수점 유지, 최소 스테이지 제한 없음). 다이아 지급량 = floor(20.0 × 도달스테이지^0.6, 환급과 무관한 신규 지급). 환급 배율 = 1 + (누적 포인트 × 1.0 / 100), 최대 5.0배. 전투 중 재화 획득량/스탯에는 영향 없음</t>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>포인트 = 1.0 × 도달스테이지^0.5 (소수점 유지, 최소 스테이지 제한 없음). 환급 배율 = 1 + (누적 포인트 × 1.0 / 100), 최대 5.0배. 전투 중 재화 획득량/스탯에는 영향 없음. 다이아 신규 지급량은 RebirthRewardTable(구간별 고정값)에서 조회한다</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R5"/>
+  <autoFilter ref="A4:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13.6" customWidth="1" min="3" max="3"/>
+    <col width="20.2" customWidth="1" min="4" max="4"/>
+    <col width="18.3" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>구간 시작 스테이지</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>구간 끝 스테이지</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>다이아 지급량</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>//Name</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>StageFrom</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>StageTo</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>DiamondReward</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>//Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>35101</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1구간</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>35102</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2구간</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>35103</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3구간</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>35104</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4구간</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>35105</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5구간(최종)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>999999</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7985,7 +8346,842 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20.1" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>enum 그룹</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>한글 라벨</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>영문 라벨</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>사용처</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>존재력</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EXIST</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.GrantCurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>성장에너지</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GROWTH_ENERGY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.GrantCurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>숙련의정수</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MASTERY_ESSENCE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.GrantCurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>시간에너지</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>TIME_ENERGY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.GrantCurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.GrantCurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>공격력</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>방어력</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>공격속도</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>치명타확률</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CRIT</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>치명타피해</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CRIT_DMG</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>존재력획득량</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EXIST_GAIN</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>NodeEffectType</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>스탯상승</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NodeEffectType</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>재화지급</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GRANT</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ExistTreeTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>StageType</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>StageTable.StageType</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>StageType</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>보스</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>StageTable.StageType</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FeatureType</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>리버스</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>REBIRTH</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>FeatureUnlockTable.FeatureType</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FeatureType</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>타임하이스트</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>TIME_HEIST</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>FeatureUnlockTable.FeatureType</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>검</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>WeaponTypeTable.WeaponType</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>창</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>WeaponTypeTable.WeaponType</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>활</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Bow</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>WeaponTypeTable.WeaponType</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGrade</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>노말</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGradeTable.WeaponGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGrade</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGradeTable.WeaponGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGrade</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>에픽</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGradeTable.WeaponGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGrade</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>유니크</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGradeTable.WeaponGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGrade</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>레전드리</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>WeaponGradeTable.WeaponGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RelicGrade</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>노말</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.RelicGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RelicGrade</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.RelicGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RelicGrade</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>에픽</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.RelicGrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>공격력</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>STAT_ATK</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>방어력</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>STAT_DEF</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>공격속도</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>STAT_ASPD</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>치명타확률</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>STAT_CRIT</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>치명타피해</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>STAT_CRIT_DMG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>존재력획득량</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>STAT_EXIST_GAIN</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>골드획득량</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GOLD_GAIN</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RelicEffectType</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>타임하이스트쿨타임</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>TIMEHEIST_COOLDOWN</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>RelicTable.EffectType</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D37"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10874,841 +12070,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:E125"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20.1" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>enum 그룹</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>한글 라벨</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>영문 라벨</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>사용처</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>존재력</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>EXIST</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.GrantCurrency</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>성장에너지</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>GROWTH_ENERGY</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.GrantCurrency</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>숙련의정수</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>MASTERY_ESSENCE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.GrantCurrency</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>시간에너지</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>TIME_ENERGY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.GrantCurrency</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>골드</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>GOLD</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.GrantCurrency</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>공격력</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>방어력</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>공격속도</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>치명타확률</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>CRIT</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>치명타피해</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>CRIT_DMG</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>존재력획득량</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EXIST_GAIN</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>NodeEffectType</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>스탯상승</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>STAT</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>NodeEffectType</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>재화지급</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>GRANT</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>ExistTreeTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>StageType</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>StageTable.StageType</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>StageType</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>보스</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>StageTable.StageType</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>FeatureType</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>리버스</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>REBIRTH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>FeatureUnlockTable.FeatureType</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FeatureType</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>타임하이스트</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>TIME_HEIST</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>FeatureUnlockTable.FeatureType</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>WeaponType</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>검</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Sword</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>WeaponTypeTable.WeaponType</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>WeaponType</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>창</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Spear</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>WeaponTypeTable.WeaponType</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WeaponType</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>활</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Bow</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>WeaponTypeTable.WeaponType</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGrade</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>노말</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGrade</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>레어</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGrade</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>에픽</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGrade</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>유니크</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGrade</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>레전드리</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>RelicGrade</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>노말</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.RelicGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>RelicGrade</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>레어</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.RelicGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>RelicGrade</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>에픽</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.RelicGrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>공격력</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>STAT_ATK</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>방어력</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>STAT_DEF</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>공격속도</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>STAT_ASPD</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>치명타확률</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>STAT_CRIT</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>치명타피해</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>STAT_CRIT_DMG</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>존재력획득량</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>STAT_EXIST_GAIN</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>골드획득량</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>GOLD_GAIN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>타임하이스트쿨타임</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>TIMEHEIST_COOLDOWN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -48,7 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$P$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'RebirthRewardTable'!$A$4:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9187,7 +9187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>소환</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gacha</t>
+          <t>Summon</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>가챠 레벨</t>
+          <t>소환 레벨</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Gacha Level</t>
+          <t>Summon Level</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12068,8 +12068,31 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>40128</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>GachaUi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E125"/>
+  <autoFilter ref="A4:E126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -48,7 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$P$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'RebirthRewardTable'!$A$4:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9187,13 +9187,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="24.1" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -12091,8 +12091,123 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>40129</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>건너뛰기</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B128" s="6" t="n">
+        <v>40130</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>40131</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>시작하기</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>40132</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>다음 특별 해금까지</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Until Next Special Unlock</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>ExistUi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>40133</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>새 소식</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E126"/>
+  <autoFilter ref="A4:E131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -30,10 +30,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TableDefine'!$A$1:$F$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#EnumDefine'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StageTable'!$A$4:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ExistTreeTable'!$A$4:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'StatTable'!$A$4:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ExistTreeTable'!$A$4:$N$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'FeatureUnlockTable'!$A$4:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MasteryTable'!$A$4:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'WeaponTypeTable'!$A$4:$H$7</definedName>
@@ -48,7 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$P$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'RebirthRewardTable'!$A$4:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6620,11 +6620,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>STAT_DEF</t>
+          <t>STAT_ASPD</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>40</v>
@@ -8352,7 +8352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>방어력</t>
+          <t>공격속도</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>공격속도</t>
+          <t>치명타확률</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>CRIT</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>치명타확률</t>
+          <t>치명타피해</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CRIT</t>
+          <t>CRIT_DMG</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>치명타피해</t>
+          <t>존재력획득량</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CRIT_DMG</t>
+          <t>EXIST_GAIN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8606,22 +8606,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>StatType</t>
+          <t>NodeEffectType</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>존재력획득량</t>
+          <t>스탯상승</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EXIST_GAIN</t>
+          <t>STAT</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>StatTable.StatType, ExistTreeTable.StatType, WeaponTypeTable.PrimaryStat</t>
+          <t>ExistTreeTable.EffectType</t>
         </is>
       </c>
     </row>
@@ -8633,12 +8633,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>스탯상승</t>
+          <t>재화지급</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>STAT</t>
+          <t>GRANT</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -8650,22 +8650,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NodeEffectType</t>
+          <t>StageType</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>재화지급</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GRANT</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ExistTreeTable.EffectType</t>
+          <t>StageTable.StageType</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -8694,22 +8694,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>StageType</t>
+          <t>FeatureType</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>리버스</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>REBIRTH</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>StageTable.StageType</t>
+          <t>FeatureUnlockTable.FeatureType</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>리버스</t>
+          <t>타임하이스트</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>REBIRTH</t>
+          <t>TIME_HEIST</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -8738,22 +8738,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FeatureType</t>
+          <t>WeaponType</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>타임하이스트</t>
+          <t>검</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TIME_HEIST</t>
+          <t>Sword</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FeatureUnlockTable.FeatureType</t>
+          <t>WeaponTypeTable.WeaponType</t>
         </is>
       </c>
     </row>
@@ -8765,12 +8765,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>검</t>
+          <t>창</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sword</t>
+          <t>Spear</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>창</t>
+          <t>활</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Spear</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -8804,22 +8804,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>WeaponGrade</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>노말</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>WeaponTypeTable.WeaponType</t>
+          <t>WeaponGradeTable.WeaponGrade</t>
         </is>
       </c>
     </row>
@@ -8831,12 +8831,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>노말</t>
+          <t>레어</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>레어</t>
+          <t>에픽</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>에픽</t>
+          <t>유니크</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>유니크</t>
+          <t>레전드리</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -8914,22 +8914,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>WeaponGrade</t>
+          <t>RelicGrade</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>레전드리</t>
+          <t>노말</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>WeaponGradeTable.WeaponGrade</t>
+          <t>RelicTable.RelicGrade</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>노말</t>
+          <t>레어</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>레어</t>
+          <t>에픽</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -8980,22 +8980,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RelicGrade</t>
+          <t>RelicEffectType</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>에픽</t>
+          <t>공격력</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>STAT_ATK</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RelicTable.RelicGrade</t>
+          <t>RelicTable.EffectType</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9007,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>공격력</t>
+          <t>공격속도</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>STAT_ATK</t>
+          <t>STAT_ASPD</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>방어력</t>
+          <t>치명타확률</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>STAT_DEF</t>
+          <t>STAT_CRIT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>공격속도</t>
+          <t>치명타피해</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>STAT_ASPD</t>
+          <t>STAT_CRIT_DMG</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>치명타확률</t>
+          <t>존재력획득량</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>STAT_CRIT</t>
+          <t>STAT_EXIST_GAIN</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>치명타피해</t>
+          <t>골드획득량</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>STAT_CRIT_DMG</t>
+          <t>GOLD_GAIN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>존재력획득량</t>
+          <t>타임하이스트쿨타임</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>STAT_EXIST_GAIN</t>
+          <t>TIMEHEIST_COOLDOWN</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9131,52 +9131,8 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>골드획득량</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>GOLD_GAIN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RelicEffectType</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>타임하이스트쿨타임</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>TIMEHEIST_COOLDOWN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>RelicTable.EffectType</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D37"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9187,7 +9143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9313,16 +9269,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>40002</v>
+        <v>40003</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>방어력</t>
+          <t>공격속도</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9336,16 +9292,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>공격속도</t>
+          <t>치명타 확률</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>CRIT</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -9359,16 +9315,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>40004</v>
+        <v>40005</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>치명타 확률</t>
+          <t>치명타피해</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CRIT</t>
+          <t>CRIT_DMG</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9382,16 +9338,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>40005</v>
+        <v>40006</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>치명타피해</t>
+          <t>존재력 획득량</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CRIT_DMG</t>
+          <t>EXIST_GAIN</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -9405,21 +9361,21 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>40006</v>
+        <v>40007</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>존재력 획득량</t>
+          <t>리버스</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EXIST_GAIN</t>
+          <t>REBIRTH</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Stat</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -9428,16 +9384,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>40007</v>
+        <v>40008</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>리버스</t>
+          <t>타임 하이스트</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>REBIRTH</t>
+          <t>TIME_HEIST</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9451,21 +9407,21 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>40008</v>
+        <v>40015</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>타임 하이스트</t>
+          <t>존재력</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>TIME_HEIST</t>
+          <t>EXIST</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -9474,16 +9430,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>40015</v>
+        <v>40016</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>존재력</t>
+          <t>성장에너지</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>EXIST</t>
+          <t>GROWTH_ENERGY</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9497,16 +9453,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40016</v>
+        <v>40017</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>성장에너지</t>
+          <t>숙련의 정수</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>GROWTH_ENERGY</t>
+          <t>MASTERY_ESSENCE</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9520,16 +9476,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>40017</v>
+        <v>40018</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>숙련의 정수</t>
+          <t>시간에너지</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MASTERY_ESSENCE</t>
+          <t>TIME_ENERGY</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -9543,16 +9499,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>40018</v>
+        <v>40019</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>시간에너지</t>
+          <t>골드</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TIME_ENERGY</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9566,21 +9522,21 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>40019</v>
+        <v>40020</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>존재력 트리</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>EXIST_TREE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -9589,21 +9545,21 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>40020</v>
+        <v>40021</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>존재력 트리</t>
+          <t>존재</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>EXIST_TREE</t>
+          <t>EXIST_ABBR</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>CurrencyAbbr</t>
         </is>
       </c>
     </row>
@@ -9612,16 +9568,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>40021</v>
+        <v>40022</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>존재</t>
+          <t>성장</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>EXIST_ABBR</t>
+          <t>GROWTH_ABBR</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -9635,16 +9591,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>40022</v>
+        <v>40023</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>성장</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GROWTH_ABBR</t>
+          <t>TIME_ABBR</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9658,16 +9614,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>40023</v>
+        <v>40024</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>골드</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TIME_ABBR</t>
+          <t>GOLD_ABBR</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -9681,16 +9637,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>40024</v>
+        <v>40025</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GOLD_ABBR</t>
+          <t>ESSENCE_ABBR</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -9704,21 +9660,21 @@
         <v>19</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>40025</v>
+        <v>40026</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>성장</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ESSENCE_ABBR</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CurrencyAbbr</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -9727,16 +9683,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>40026</v>
+        <v>40027</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>성장</t>
+          <t>무기고</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Armory</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9750,16 +9706,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>40027</v>
+        <v>40028</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>무기고</t>
+          <t>소환</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Armory</t>
+          <t>Summon</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -9773,16 +9729,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>40028</v>
+        <v>40029</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>소환</t>
+          <t>존재력</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Summon</t>
+          <t>ExistTree</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -9796,16 +9752,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>40029</v>
+        <v>40030</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>존재력</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ExistTree</t>
+          <t>Dogam</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -9819,21 +9775,21 @@
         <v>24</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>40030</v>
+        <v>40031</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>닫기</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dogam</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -9842,16 +9798,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>40031</v>
+        <v>40032</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>닫기</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9865,16 +9821,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>40032</v>
+        <v>40033</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9888,16 +9844,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>40033</v>
+        <v>40034</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>실행</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Execute</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9911,16 +9867,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>40034</v>
+        <v>40035</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>실행</t>
+          <t>강탈</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Steal</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9934,16 +9890,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>40035</v>
+        <v>40036</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>강탈</t>
+          <t>받기</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Steal</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9957,16 +9913,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>40036</v>
+        <v>40037</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>받기</t>
+          <t>해금</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Unlock</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9980,16 +9936,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>40037</v>
+        <v>40038</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>해금</t>
+          <t>강화</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Unlock</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -10003,16 +9959,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>40038</v>
+        <v>40039</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>수련</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10026,16 +9982,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>40039</v>
+        <v>40040</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>수련</t>
+          <t>업그레이드</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Upgrade</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -10049,16 +10005,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>40040</v>
+        <v>40041</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>업그레이드</t>
+          <t>최대로</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>MaxAll</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10072,16 +10028,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>40041</v>
+        <v>40042</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>최대로</t>
+          <t>뒤로</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MaxAll</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -10095,21 +10051,21 @@
         <v>36</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>40042</v>
+        <v>40043</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>뒤로</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -10118,16 +10074,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>40043</v>
+        <v>40044</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>해금됨</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Unlocked</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -10141,16 +10097,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>40044</v>
+        <v>40045</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>해금됨</t>
+          <t>사용 가능</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Unlocked</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10164,16 +10120,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>40045</v>
+        <v>40046</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>사용 가능</t>
+          <t>티어</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Tier</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10187,16 +10143,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>40046</v>
+        <v>40047</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>티어</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10210,16 +10166,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>40047</v>
+        <v>40048</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>비용</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10233,21 +10189,21 @@
         <v>42</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>40048</v>
+        <v>40049</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>회차 보너스</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>RebirthBonus</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>RebirthBonus</t>
         </is>
       </c>
     </row>
@@ -10256,16 +10212,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>40049</v>
+        <v>40050</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>회차 보너스</t>
+          <t>현재 회차</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>RebirthBonus</t>
+          <t>CurrentCycle</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10279,16 +10235,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>40050</v>
+        <v>40051</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>현재 회차</t>
+          <t>누적 포인트</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CurrentCycle</t>
+          <t>TotalPoints</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10302,16 +10258,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>40051</v>
+        <v>40052</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>누적 포인트</t>
+          <t>획득 예정 포인트</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>TotalPoints</t>
+          <t>PendingPoints</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10325,16 +10281,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>40052</v>
+        <v>40053</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>획득 예정 포인트</t>
+          <t>환급 배율</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>PendingPoints</t>
+          <t>RefundMultiplier</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10348,16 +10304,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>40053</v>
+        <v>40054</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>환급 배율</t>
+          <t>최고 도달 스테이지</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>RefundMultiplier</t>
+          <t>MaxStageReached</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10371,21 +10327,21 @@
         <v>48</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>40054</v>
+        <v>40055</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>최고 도달 스테이지</t>
+          <t>검</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>MaxStageReached</t>
+          <t>Sword</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RebirthBonus</t>
+          <t>WeaponType</t>
         </is>
       </c>
     </row>
@@ -10394,16 +10350,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>40055</v>
+        <v>40056</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>검</t>
+          <t>창</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Sword</t>
+          <t>Spear</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10417,16 +10373,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>40056</v>
+        <v>40057</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>창</t>
+          <t>활</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Spear</t>
+          <t>Bow</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10440,21 +10396,21 @@
         <v>51</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>40057</v>
+        <v>40058</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>활</t>
+          <t>노말</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>WeaponGrade</t>
         </is>
       </c>
     </row>
@@ -10463,16 +10419,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>40058</v>
+        <v>40059</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>노말</t>
+          <t>레어</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10486,16 +10442,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>40059</v>
+        <v>40060</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>레어</t>
+          <t>에픽</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10509,16 +10465,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>40060</v>
+        <v>40061</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>에픽</t>
+          <t>유니크</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10532,16 +10488,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>40061</v>
+        <v>40062</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>유니크</t>
+          <t>레전드리</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -10555,21 +10511,21 @@
         <v>56</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>40062</v>
+        <v>40063</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>레전드리</t>
+          <t>힘의 유물</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Relic of Strength</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>WeaponGrade</t>
+          <t>RelicName</t>
         </is>
       </c>
     </row>
@@ -10578,16 +10534,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>40063</v>
+        <v>40064</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>힘의 유물</t>
+          <t>신속의 유물</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Relic of Strength</t>
+          <t>Relic of Swiftness</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -10601,16 +10557,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>40064</v>
+        <v>40065</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>방패의 유물</t>
+          <t>행운의 유물</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Relic of Shield</t>
+          <t>Relic of Luck</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -10624,16 +10580,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>40065</v>
+        <v>40066</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>행운의 유물</t>
+          <t>가속의 유물</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Relic of Luck</t>
+          <t>Relic of Haste</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -10647,16 +10603,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>40066</v>
+        <v>40067</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>가속의 유물</t>
+          <t>파괴의 유물</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Relic of Haste</t>
+          <t>Relic of Destruction</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -10670,16 +10626,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>40067</v>
+        <v>40068</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>파괴의 유물</t>
+          <t>상인의 유물</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Relic of Destruction</t>
+          <t>Relic of Merchant</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -10693,16 +10649,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>40068</v>
+        <v>40069</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>상인의 유물</t>
+          <t>균열의 유물</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Relic of Merchant</t>
+          <t>Relic of Rift</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -10716,16 +10672,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>40069</v>
+        <v>40070</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>균열의 유물</t>
+          <t>시간의 유물</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Relic of Rift</t>
+          <t>Relic of Time</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -10739,16 +10695,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>40070</v>
+        <v>40071</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>시간의 유물</t>
+          <t>전능의 유물</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Relic of Time</t>
+          <t>Relic of Omnipotence</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -10762,21 +10718,21 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>40071</v>
+        <v>40072</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>전능의 유물</t>
+          <t>검 숙련</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Relic of Omnipotence</t>
+          <t>Sword Mastery</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RelicName</t>
+          <t>Mastery</t>
         </is>
       </c>
     </row>
@@ -10785,16 +10741,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>40072</v>
+        <v>40073</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>검 숙련</t>
+          <t>창 숙련</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sword Mastery</t>
+          <t>Spear Mastery</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -10808,16 +10764,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>40073</v>
+        <v>40074</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>창 숙련</t>
+          <t>활 숙련</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Spear Mastery</t>
+          <t>Bow Mastery</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -10831,21 +10787,21 @@
         <v>68</v>
       </c>
       <c r="B72" s="6" t="n">
-        <v>40074</v>
+        <v>40075</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>활 숙련</t>
+          <t>다이아</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Bow Mastery</t>
+          <t>DIAMOND</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Mastery</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10810,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>40075</v>
+        <v>40076</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -10863,12 +10819,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DIAMOND</t>
+          <t>DIAMOND_ABBR</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>CurrencyAbbr</t>
         </is>
       </c>
     </row>
@@ -10877,21 +10833,21 @@
         <v>70</v>
       </c>
       <c r="B74" s="6" t="n">
-        <v>40076</v>
+        <v>40077</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DIAMOND_ABBR</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CurrencyAbbr</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -10900,16 +10856,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="n">
-        <v>40077</v>
+        <v>40078</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>돌파</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Breakthrough</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -10923,16 +10879,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="n">
-        <v>40078</v>
+        <v>40079</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>돌파</t>
+          <t>합성</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Breakthrough</t>
+          <t>Fuse</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -10946,21 +10902,21 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="n">
-        <v>40079</v>
+        <v>40080</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>합성</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Fuse</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>WeaponUi</t>
         </is>
       </c>
     </row>
@@ -10969,16 +10925,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="6" t="n">
-        <v>40080</v>
+        <v>40081</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>유물</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Relic</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -10992,16 +10948,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="n">
-        <v>40081</v>
+        <v>40082</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>유물</t>
+          <t>보유 효과</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Relic</t>
+          <t>Own Bonus</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -11015,16 +10971,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="6" t="n">
-        <v>40082</v>
+        <v>40083</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>보유 효과</t>
+          <t>장착 효과</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Own Bonus</t>
+          <t>Equip Bonus</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11038,16 +10994,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>40083</v>
+        <v>40084</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>장착 효과</t>
+          <t>장착 중</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Equip Bonus</t>
+          <t>Equipped</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -11061,16 +11017,16 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="n">
-        <v>40084</v>
+        <v>40085</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>장착 중</t>
+          <t>장착된 무기 없음</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Equipped</t>
+          <t>No Weapon Equipped</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -11084,16 +11040,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="6" t="n">
-        <v>40085</v>
+        <v>40086</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>장착된 무기 없음</t>
+          <t>보유 개수</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>No Weapon Equipped</t>
+          <t>Owned Count</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -11107,16 +11063,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="6" t="n">
-        <v>40086</v>
+        <v>40087</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>보유 개수</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Owned Count</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11130,21 +11086,21 @@
         <v>81</v>
       </c>
       <c r="B85" s="6" t="n">
-        <v>40087</v>
+        <v>40088</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>소환 레벨</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Summon Level</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>WeaponUi</t>
+          <t>GachaUi</t>
         </is>
       </c>
     </row>
@@ -11153,16 +11109,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="6" t="n">
-        <v>40088</v>
+        <v>40089</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>소환 레벨</t>
+          <t>다음 레벨까지</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Summon Level</t>
+          <t>To Next Level</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11176,16 +11132,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="6" t="n">
-        <v>40089</v>
+        <v>40090</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>다음 레벨까지</t>
+          <t>1회 뽑기</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>To Next Level</t>
+          <t>Pull x1</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -11199,16 +11155,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="6" t="n">
-        <v>40090</v>
+        <v>40091</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>1회 뽑기</t>
+          <t>10회 뽑기</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Pull x1</t>
+          <t>Pull x10</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -11222,16 +11178,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="6" t="n">
-        <v>40091</v>
+        <v>40092</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>10회 뽑기</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Pull x10</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -11245,16 +11201,16 @@
         <v>86</v>
       </c>
       <c r="B90" s="6" t="n">
-        <v>40092</v>
+        <v>40093</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>중복</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Duplicate</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11268,21 +11224,21 @@
         <v>87</v>
       </c>
       <c r="B91" s="6" t="n">
-        <v>40093</v>
+        <v>40094</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>중복</t>
+          <t>유물 뽑기</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Pull Relic</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>GachaUi</t>
+          <t>RelicUi</t>
         </is>
       </c>
     </row>
@@ -11291,16 +11247,16 @@
         <v>88</v>
       </c>
       <c r="B92" s="6" t="n">
-        <v>40094</v>
+        <v>40095</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>유물 뽑기</t>
+          <t>중복 환급</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Pull Relic</t>
+          <t>Duplicate Refund</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11314,16 +11270,16 @@
         <v>89</v>
       </c>
       <c r="B93" s="6" t="n">
-        <v>40095</v>
+        <v>40096</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>중복 환급</t>
+          <t>다음 슬롯</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Refund</t>
+          <t>Next Slot</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -11337,16 +11293,16 @@
         <v>90</v>
       </c>
       <c r="B94" s="6" t="n">
-        <v>40096</v>
+        <v>40097</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>다음 슬롯</t>
+          <t>활성 슬롯</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Next Slot</t>
+          <t>Active Slots</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11360,16 +11316,16 @@
         <v>91</v>
       </c>
       <c r="B95" s="6" t="n">
-        <v>40097</v>
+        <v>40098</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>활성 슬롯</t>
+          <t>보유 유물</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Active Slots</t>
+          <t>Owned Relics</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -11383,16 +11339,16 @@
         <v>92</v>
       </c>
       <c r="B96" s="6" t="n">
-        <v>40098</v>
+        <v>40099</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>보유 유물</t>
+          <t>슬롯이 가득 참</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Owned Relics</t>
+          <t>Slots Full</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11406,16 +11362,16 @@
         <v>93</v>
       </c>
       <c r="B97" s="6" t="n">
-        <v>40099</v>
+        <v>40100</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>슬롯이 가득 참</t>
+          <t>골드 획득량</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Slots Full</t>
+          <t>Gold Gain</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11429,16 +11385,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="6" t="n">
-        <v>40100</v>
+        <v>40101</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>골드 획득량</t>
+          <t>타임 하이스트 쿨타임</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Gold Gain</t>
+          <t>Time Heist Cooldown</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11452,21 +11408,21 @@
         <v>95</v>
       </c>
       <c r="B99" s="6" t="n">
-        <v>40101</v>
+        <v>40102</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>타임 하이스트 쿨타임</t>
+          <t>활성화</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Time Heist Cooldown</t>
+          <t>Activate</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RelicUi</t>
+          <t>Button</t>
         </is>
       </c>
     </row>
@@ -11475,16 +11431,16 @@
         <v>96</v>
       </c>
       <c r="B100" s="6" t="n">
-        <v>40102</v>
+        <v>40103</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>활성화</t>
+          <t>비활성화</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Deactivate</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -11498,21 +11454,21 @@
         <v>97</v>
       </c>
       <c r="B101" s="6" t="n">
-        <v>40103</v>
+        <v>40104</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>비활성화</t>
+          <t>스탯</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Deactivate</t>
+          <t>Stat</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>GrowthUi</t>
         </is>
       </c>
     </row>
@@ -11521,16 +11477,16 @@
         <v>98</v>
       </c>
       <c r="B102" s="6" t="n">
-        <v>40104</v>
+        <v>40105</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>스탯</t>
+          <t>숙련</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Stat</t>
+          <t>Mastery</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -11544,21 +11500,21 @@
         <v>99</v>
       </c>
       <c r="B103" s="6" t="n">
-        <v>40105</v>
+        <v>40106</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>숙련</t>
+          <t>적 HP</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Mastery</t>
+          <t>Enemy HP</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>GrowthUi</t>
+          <t>CommonUi</t>
         </is>
       </c>
     </row>
@@ -11567,16 +11523,16 @@
         <v>100</v>
       </c>
       <c r="B104" s="6" t="n">
-        <v>40106</v>
+        <v>40107</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>적 HP</t>
+          <t>적 공격력</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Enemy HP</t>
+          <t>Enemy ATK</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -11590,16 +11546,16 @@
         <v>101</v>
       </c>
       <c r="B105" s="6" t="n">
-        <v>40107</v>
+        <v>40108</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>적 공격력</t>
+          <t>처치 진행도</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Enemy ATK</t>
+          <t>Kill Progress</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -11613,16 +11569,16 @@
         <v>102</v>
       </c>
       <c r="B106" s="6" t="n">
-        <v>40108</v>
+        <v>40109</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>처치 진행도</t>
+          <t>스테이지 보상 (처치당)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Kill Progress</t>
+          <t>Stage Reward (per kill)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -11636,16 +11592,16 @@
         <v>103</v>
       </c>
       <c r="B107" s="6" t="n">
-        <v>40109</v>
+        <v>40110</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>스테이지 보상 (처치당)</t>
+          <t>회차</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Stage Reward (per kill)</t>
+          <t>Cycle</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -11659,16 +11615,16 @@
         <v>104</v>
       </c>
       <c r="B108" s="6" t="n">
-        <v>40110</v>
+        <v>40111</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>회차</t>
+          <t>오프라인 보상</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Offline Reward</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -11682,16 +11638,16 @@
         <v>105</v>
       </c>
       <c r="B109" s="6" t="n">
-        <v>40111</v>
+        <v>40112</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>오프라인 보상</t>
+          <t>비운 시간</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Offline Reward</t>
+          <t>Time Away</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -11705,16 +11661,16 @@
         <v>106</v>
       </c>
       <c r="B110" s="6" t="n">
-        <v>40112</v>
+        <v>40113</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>비운 시간</t>
+          <t>최대</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Time Away</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -11728,16 +11684,16 @@
         <v>107</v>
       </c>
       <c r="B111" s="6" t="n">
-        <v>40113</v>
+        <v>40114</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>최대</t>
+          <t>인정</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Recognized</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -11751,16 +11707,16 @@
         <v>108</v>
       </c>
       <c r="B112" s="6" t="n">
-        <v>40114</v>
+        <v>40115</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>인정</t>
+          <t>획득 재화</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Recognized</t>
+          <t>Rewards Earned</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -11774,16 +11730,16 @@
         <v>109</v>
       </c>
       <c r="B113" s="6" t="n">
-        <v>40115</v>
+        <v>40116</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>획득 재화</t>
+          <t>1회 비용</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Rewards Earned</t>
+          <t>Cost per Pull</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -11797,16 +11753,16 @@
         <v>110</v>
       </c>
       <c r="B114" s="6" t="n">
-        <v>40116</v>
+        <v>40117</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>1회 비용</t>
+          <t>종</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Cost per Pull</t>
+          <t>Kinds</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -11820,16 +11776,16 @@
         <v>111</v>
       </c>
       <c r="B115" s="6" t="n">
-        <v>40117</v>
+        <v>40118</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>종</t>
+          <t>노드</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Kinds</t>
+          <t>Nodes</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -11843,16 +11799,16 @@
         <v>112</v>
       </c>
       <c r="B116" s="6" t="n">
-        <v>40118</v>
+        <v>40119</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>노드</t>
+          <t>대상 스테이지</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>Target Stage</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -11866,16 +11822,16 @@
         <v>113</v>
       </c>
       <c r="B117" s="6" t="n">
-        <v>40119</v>
+        <v>40120</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>대상 스테이지</t>
+          <t>클리어 환산</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Target Stage</t>
+          <t>Clears Converted</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -11889,16 +11845,16 @@
         <v>114</v>
       </c>
       <c r="B118" s="6" t="n">
-        <v>40120</v>
+        <v>40121</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>클리어 환산</t>
+          <t>획득 예정</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Clears Converted</t>
+          <t>Expected Gain</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -11912,16 +11868,16 @@
         <v>115</v>
       </c>
       <c r="B119" s="6" t="n">
-        <v>40121</v>
+        <v>40122</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>획득 예정</t>
+          <t>소모</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Expected Gain</t>
+          <t>Consume</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -11935,16 +11891,16 @@
         <v>116</v>
       </c>
       <c r="B120" s="6" t="n">
-        <v>40122</v>
+        <v>40123</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>소모</t>
+          <t>사용 횟수</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Consume</t>
+          <t>Use Count</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -11958,16 +11914,16 @@
         <v>117</v>
       </c>
       <c r="B121" s="6" t="n">
-        <v>40123</v>
+        <v>40124</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>사용 횟수</t>
+          <t>쿨타임</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Use Count</t>
+          <t>Cooldown</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -11981,16 +11937,16 @@
         <v>118</v>
       </c>
       <c r="B122" s="6" t="n">
-        <v>40124</v>
+        <v>40125</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>쿨타임</t>
+          <t>회</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Cooldown</t>
+          <t>Times</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -12004,16 +11960,16 @@
         <v>119</v>
       </c>
       <c r="B123" s="6" t="n">
-        <v>40125</v>
+        <v>40126</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>회</t>
+          <t>등급 확률</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Times</t>
+          <t>Grade Probability</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -12027,16 +11983,16 @@
         <v>120</v>
       </c>
       <c r="B124" s="6" t="n">
-        <v>40126</v>
+        <v>40127</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>등급 확률</t>
+          <t>보유</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Grade Probability</t>
+          <t>Owned</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -12050,21 +12006,21 @@
         <v>121</v>
       </c>
       <c r="B125" s="6" t="n">
-        <v>40127</v>
+        <v>40128</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>무기</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>CommonUi</t>
+          <t>GachaUi</t>
         </is>
       </c>
     </row>
@@ -12073,21 +12029,21 @@
         <v>122</v>
       </c>
       <c r="B126" s="6" t="n">
-        <v>40128</v>
+        <v>40129</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>무기</t>
+          <t>건너뛰기</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>GachaUi</t>
+          <t>Onboarding</t>
         </is>
       </c>
     </row>
@@ -12096,16 +12052,16 @@
         <v>123</v>
       </c>
       <c r="B127" s="6" t="n">
-        <v>40129</v>
+        <v>40130</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>건너뛰기</t>
+          <t>다음</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -12119,16 +12075,16 @@
         <v>124</v>
       </c>
       <c r="B128" s="6" t="n">
-        <v>40130</v>
+        <v>40131</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>시작하기</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -12142,21 +12098,21 @@
         <v>125</v>
       </c>
       <c r="B129" s="6" t="n">
-        <v>40131</v>
+        <v>40132</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>시작하기</t>
+          <t>다음 특별 해금까지</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Until Next Special Unlock</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>ExistUi</t>
         </is>
       </c>
     </row>
@@ -12165,49 +12121,26 @@
         <v>126</v>
       </c>
       <c r="B130" s="6" t="n">
-        <v>40132</v>
+        <v>40133</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>다음 특별 해금까지</t>
+          <t>새 소식</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Until Next Special Unlock</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>ExistUi</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="B131" s="6" t="n">
-        <v>40133</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>새 소식</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
           <t>Badge</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E131"/>
+  <autoFilter ref="A4:E130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13445,7 +13378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13703,22 +13636,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>방어력</t>
+          <t>공격속도</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>40002</v>
+        <v>40003</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>8</v>
@@ -13731,7 +13664,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>방어력(DEF) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
+          <t>공격속도(ASPD) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
         </is>
       </c>
     </row>
@@ -13744,22 +13677,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>공격속도</t>
+          <t>치명타확률</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>CRIT</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>8</v>
@@ -13772,7 +13705,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>공격속도(ASPD) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
+          <t>치명타확률(CRIT) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
         </is>
       </c>
     </row>
@@ -13785,22 +13718,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>치명타확률</t>
+          <t>치명타피해</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CRIT</t>
+          <t>CRIT_DMG</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>40004</v>
+        <v>40005</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>8</v>
@@ -13813,7 +13746,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>치명타확률(CRIT) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
+          <t>치명타피해(CRIT_DMG) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
         </is>
       </c>
     </row>
@@ -13826,22 +13759,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>치명타피해</t>
+          <t>존재력획득량</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CRIT_DMG</t>
+          <t>EXIST_GAIN</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>40005</v>
+        <v>40006</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>8</v>
@@ -13854,53 +13787,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>치명타피해(CRIT_DMG) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>20006</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>존재력획득량</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>EXIST_GAIN</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>40006</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>9999</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
           <t>존재력획득량(EXIST_GAIN) 성장 스탯. 원본 공식과 동일한 기준값/증가치</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K10"/>
+  <autoFilter ref="A4:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13911,12 +13803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25.1" customWidth="1" min="3" max="3"/>
+    <col width="41.69999999999999" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -13927,7 +13819,7 @@
     <col width="15.4" customWidth="1" min="11" max="11"/>
     <col width="11.6" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="18.8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14183,7 +14075,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1티어: 공격력</t>
+          <t>1티어-A: 공격력</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -14193,7 +14085,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -14220,7 +14112,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>order 1~10 구간. 원본 노드별 5종 순환 효과를 티어 단위 단일 효과로 단순화함 — 다음 단계 리팩터링 시 재검토 필요</t>
+          <t>order 1~7 구간</t>
         </is>
       </c>
     </row>
@@ -14233,17 +14125,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2티어: 방어력</t>
+          <t>1티어-B: 치명타 확률</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -14252,25 +14144,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>CRIT</t>
         </is>
       </c>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>order 11~20 구간. 원본 노드별 5종 순환 효과를 티어 단위 단일 효과로 단순화함 — 다음 단계 리팩터링 시 재검토 필요</t>
+          <t>order 8~10 구간</t>
         </is>
       </c>
     </row>
@@ -14283,17 +14175,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3티어: 공격속도</t>
+          <t>2티어-A: 공격속도</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -14307,20 +14199,20 @@
       </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="6" t="n">
-        <v>17</v>
+        <v>0.8</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>4042</v>
+        <v>201</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>order 21~30 구간. 원본 노드별 5종 순환 효과를 티어 단위 단일 효과로 단순화함 — 다음 단계 리팩터링 시 재검토 필요</t>
+          <t>order 11~16 구간</t>
         </is>
       </c>
     </row>
@@ -14333,17 +14225,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4티어: 숙련의 정수 지급</t>
+          <t>2티어-B: 시간에너지 지급</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -14353,24 +14245,24 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>MASTERY_ESSENCE</t>
+          <t>TIME_ENERGY</t>
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>81285</v>
+        <v>1217</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>order 31~40 구간. 원본 노드별 5종 순환 효과를 티어 단위 단일 효과로 단순화함 — 다음 단계 리팩터링 시 재검토 필요</t>
+          <t>order 17~20 구간</t>
         </is>
       </c>
     </row>
@@ -14383,17 +14275,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5티어: 존재력획득량</t>
+          <t>3티어-A: 치명타피해</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -14402,30 +14294,280 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>EXIST_GAIN</t>
+          <t>CRIT_DMG</t>
         </is>
       </c>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="6" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>1634371</v>
+        <v>4042</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>order 41~50 구간. 원본 노드별 5종 순환 효과를 티어 단위 단일 효과로 단순화함 — 다음 단계 리팩터링 시 재검토 필요</t>
+          <t>order 21~26 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3티어-B: 숙련의 정수 지급</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>GRANT</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MASTERY_ESSENCE</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>24472</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>order 27~30 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4티어-A: 공격력 (1티어-A 연장)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>81285</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>order 31~37 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4티어-B: 숙련의 정수 지급 (3티어-B 연장)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>GRANT</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MASTERY_ESSENCE</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>664277</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>order 38~40 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>30009</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5티어-A: 존재력획득량</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>EXIST_GAIN</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>1634371</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>order 41~46 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5티어-B: 공격속도 (2티어-A 연장)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>9893577</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>order 47~50 구간</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N9"/>
+  <autoFilter ref="A4:N14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -6206,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
     </row>
@@ -6254,7 +6254,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
     </row>
@@ -6302,7 +6302,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
     </row>
@@ -6350,7 +6350,7 @@
         <v>8</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
     </row>
@@ -6398,7 +6398,7 @@
         <v>12</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
     </row>
@@ -7226,7 +7226,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1.5</v>
@@ -7759,7 +7759,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
@@ -7782,7 +7782,7 @@
         <v>49</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
@@ -7828,7 +7828,7 @@
         <v>199</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -7851,7 +7851,7 @@
         <v>999999</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
     <col width="13.6" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11.6" customWidth="1" min="7" max="7"/>
     <col width="14.5" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -12448,7 +12448,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>1.1</v>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>16</v>
@@ -12490,13 +12490,13 @@
         <v>9</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>15</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1.1</v>
@@ -12523,7 +12523,7 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>9</v>
@@ -12538,13 +12538,13 @@
         <v>4</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>1.1</v>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1420</v>
+        <v>360</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>50</v>
@@ -12586,13 +12586,13 @@
         <v>24</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>20</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>1.1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>28</v>
@@ -12634,13 +12634,13 @@
         <v>9</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1.1</v>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>5755</v>
+        <v>710</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>160</v>
@@ -12682,13 +12682,13 @@
         <v>54</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>25</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>1.1</v>
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1324</v>
+        <v>152</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>89</v>
@@ -12730,13 +12730,13 @@
         <v>20</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>1.1</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>23290</v>
+        <v>1395</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>498</v>
@@ -12778,13 +12778,13 @@
         <v>120</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>30</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1.1</v>
@@ -12811,7 +12811,7 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5357</v>
+        <v>299</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>279</v>
@@ -12826,13 +12826,13 @@
         <v>43</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>1.1</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>94230</v>
+        <v>2750</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>1548</v>
@@ -12874,13 +12874,13 @@
         <v>258</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>35</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>1.1</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>21673</v>
+        <v>589</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>867</v>
@@ -12922,13 +12922,13 @@
         <v>93</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1.1</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>381215</v>
+        <v>5415</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4808</v>
@@ -12970,13 +12970,13 @@
         <v>561</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>40</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>1.1</v>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>87679</v>
+        <v>1158</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>2692</v>
@@ -13018,13 +13018,13 @@
         <v>202</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>1.1</v>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1542235</v>
+        <v>10650</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>14934</v>
@@ -13066,13 +13066,13 @@
         <v>1212</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1.1</v>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>354714</v>
+        <v>2279</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>8363</v>
@@ -13114,13 +13114,13 @@
         <v>437</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1.1</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>6239205</v>
+        <v>20955</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46384</v>
@@ -13162,13 +13162,13 @@
         <v>2619</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>1.1</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1435017</v>
+        <v>4484</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>25975</v>
@@ -13210,13 +13210,13 @@
         <v>943</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1.1</v>
@@ -13243,7 +13243,7 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>25241070</v>
+        <v>41220</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>144062</v>
@@ -13258,13 +13258,13 @@
         <v>5658</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>55</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>1.1</v>
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5805446</v>
+        <v>8822</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>80675</v>
@@ -13306,13 +13306,13 @@
         <v>2037</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>1.1</v>
@@ -13339,7 +13339,7 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>102114210</v>
+        <v>81090</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>447440</v>
@@ -13354,13 +13354,13 @@
         <v>12219</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>60</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1.1</v>
@@ -14105,10 +14105,10 @@
         <v>0.6</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -14155,10 +14155,10 @@
         <v>0.6</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -14205,10 +14205,10 @@
         <v>0.15</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -14255,10 +14255,10 @@
         <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>1217</v>
+        <v>85</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -14305,10 +14305,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>4042</v>
+        <v>155</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>1</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>24472</v>
+        <v>379</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -14405,10 +14405,10 @@
         <v>0.6</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>81285</v>
+        <v>686</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -14455,10 +14455,10 @@
         <v>1</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>664277</v>
+        <v>1941</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -14505,10 +14505,10 @@
         <v>0.6</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>1634371</v>
+        <v>3029</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -14555,10 +14555,10 @@
         <v>0.15</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>9893577</v>
+        <v>7381</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>667</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>33</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>148142</v>
+        <v>924</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -48,7 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'RebirthTable'!$A$4:$P$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'RebirthRewardTable'!$A$4:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'CommonTable'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StringTable'!$A$4:$E$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9143,7 +9143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12139,8 +12139,31 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>40134</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>자동 업그레이드</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Auto Upgrade</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>GrowthUi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E130"/>
+  <autoFilter ref="A4:E131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12490,7 +12513,7 @@
         <v>9</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>15</v>
@@ -12538,7 +12561,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>0</v>
@@ -12586,7 +12609,7 @@
         <v>24</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>20</v>
@@ -12634,7 +12657,7 @@
         <v>9</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>0</v>
@@ -12682,7 +12705,7 @@
         <v>54</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>25</v>
@@ -12730,7 +12753,7 @@
         <v>20</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>0</v>
@@ -12778,7 +12801,7 @@
         <v>120</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>30</v>
@@ -12826,7 +12849,7 @@
         <v>43</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>0</v>
@@ -12874,7 +12897,7 @@
         <v>258</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>35</v>
@@ -12922,7 +12945,7 @@
         <v>93</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>0</v>
@@ -12970,7 +12993,7 @@
         <v>561</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>40</v>
@@ -13018,7 +13041,7 @@
         <v>202</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>0</v>
@@ -13066,7 +13089,7 @@
         <v>1212</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>45</v>
@@ -13114,7 +13137,7 @@
         <v>437</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>0</v>
@@ -13162,7 +13185,7 @@
         <v>2619</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>50</v>
@@ -13210,7 +13233,7 @@
         <v>943</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>0</v>
@@ -13258,7 +13281,7 @@
         <v>5658</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>55</v>
@@ -13306,7 +13329,7 @@
         <v>2037</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>0</v>
@@ -13354,7 +13377,7 @@
         <v>12219</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>60</v>
@@ -14105,10 +14128,10 @@
         <v>0.6</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -14155,10 +14178,10 @@
         <v>0.6</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -14205,10 +14228,10 @@
         <v>0.15</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -14255,10 +14278,10 @@
         <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -14305,10 +14328,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -14355,10 +14378,10 @@
         <v>1</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>379</v>
+        <v>287</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -14405,10 +14428,10 @@
         <v>0.6</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>686</v>
+        <v>469</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -14455,10 +14478,10 @@
         <v>1</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>1941</v>
+        <v>1104</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -14505,10 +14528,10 @@
         <v>0.6</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>3029</v>
+        <v>1593</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -14555,10 +14578,10 @@
         <v>0.15</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>7381</v>
+        <v>3317</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -14759,7 +14782,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -14791,7 +14814,7 @@
         <v>33</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>924</v>
+        <v>599</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3164" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="747">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -1394,6 +1394,99 @@
   </si>
   <si>
     <t>Auto Upgrade</t>
+  </si>
+  <si>
+    <t>스테이지·스탯·숙련을 초기화하고 무기·유물을 소멸/초기화하는 대신, 그동안 소비한 재화를 전액 돌려받고 도달 스테이지에 비례한 다이아를 새로 받습니다. 존재력 트리는 그대로 유지됩니다.</t>
+  </si>
+  <si>
+    <t>RebirthModal</t>
+  </si>
+  <si>
+    <t>(도달 스테이지 기준, 이번 환급에 바로 반영)</t>
+  </si>
+  <si>
+    <t>초기화 / 소멸</t>
+  </si>
+  <si>
+    <t>스테이지 → 1-1</t>
+  </si>
+  <si>
+    <t>5스탯 레벨 전부 0</t>
+  </si>
+  <si>
+    <t>무기 전부 소멸</t>
+  </si>
+  <si>
+    <t>유물 전부 초기화</t>
+  </si>
+  <si>
+    <t>무기 숙련 레벨 0</t>
+  </si>
+  <si>
+    <t>지급</t>
+  </si>
+  <si>
+    <t>→ 스테이지</t>
+  </si>
+  <si>
+    <t>도달 시</t>
+  </si>
+  <si>
+    <t>유지</t>
+  </si>
+  <si>
+    <t>리버스 · 타임 하이스트 해금 상태</t>
+  </si>
+  <si>
+    <t>존재력(EXIST), 시간에너지 보유량</t>
+  </si>
+  <si>
+    <t>설계 완료 · 프로토타입 미구현</t>
+  </si>
+  <si>
+    <t>StubPanel</t>
+  </si>
+  <si>
+    <t>플레이어</t>
+  </si>
+  <si>
+    <t>BattleArea</t>
+  </si>
+  <si>
+    <t>레벨</t>
+  </si>
+  <si>
+    <t>WeaponDetailModal</t>
+  </si>
+  <si>
+    <t>개</t>
+  </si>
+  <si>
+    <t>합성 불가</t>
+  </si>
+  <si>
+    <t>돌파·합성 모두 항상 1개 보존 · 합성 재료</t>
+  </si>
+  <si>
+    <t>개 필요</t>
+  </si>
+  <si>
+    <t>자리를 비운 동안 전투가 계속된 것으로 계산해 보상을 지급합니다.</t>
+  </si>
+  <si>
+    <t>OfflineRewardModal</t>
+  </si>
+  <si>
+    <t>미래 스테이지의 보상을 시간에너지로 미리 훔쳐옵니다. 스테이지 진행에는 영향을 주지 않습니다.</t>
+  </si>
+  <si>
+    <t>TimeHeistModal</t>
+  </si>
+  <si>
+    <t>보유하지 않은 유물입니다</t>
+  </si>
+  <si>
+    <t>RelicDetailModal</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -2688,27 +2781,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="B1" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="C1" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="D1" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="E1" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="F1" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B2" t="s">
         <v>91</v>
@@ -2728,7 +2821,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B3" t="s">
         <v>92</v>
@@ -2748,7 +2841,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B4" t="s">
         <v>93</v>
@@ -2768,13 +2861,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B5" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="C5" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -2788,10 +2881,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B6" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -2803,18 +2896,18 @@
         <v>201</v>
       </c>
       <c r="F6" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B7" t="s">
         <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -2828,13 +2921,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B8" t="s">
         <v>397</v>
       </c>
       <c r="C8" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="D8" t="s">
         <v>115</v>
@@ -2848,13 +2941,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B9" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="C9" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="D9" t="s">
         <v>99</v>
@@ -2868,13 +2961,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B10" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="C10" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
@@ -2888,13 +2981,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B11" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
@@ -2908,13 +3001,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="C12" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -2928,13 +3021,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B13" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="C13" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
@@ -2948,13 +3041,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B14" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="C14" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D14" t="s">
         <v>115</v>
@@ -2968,13 +3061,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B15" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="C15" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="D15" t="s">
         <v>115</v>
@@ -2988,7 +3081,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -3008,7 +3101,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B17" t="s">
         <v>92</v>
@@ -3028,7 +3121,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
@@ -3048,7 +3141,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B19" t="s">
         <v>292</v>
@@ -3068,13 +3161,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B20" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="C20" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -3088,13 +3181,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B21" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C21" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="D21" t="s">
         <v>99</v>
@@ -3108,7 +3201,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B22" t="s">
         <v>151</v>
@@ -3123,15 +3216,15 @@
         <v>201</v>
       </c>
       <c r="F22" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B23" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -3143,18 +3236,18 @@
         <v>201</v>
       </c>
       <c r="F23" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B24" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="C24" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="D24" t="s">
         <v>101</v>
@@ -3163,18 +3256,18 @@
         <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B25" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="C25" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="D25" t="s">
         <v>115</v>
@@ -3188,13 +3281,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B26" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="C26" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="D26" t="s">
         <v>115</v>
@@ -3208,13 +3301,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B27" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="C27" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -3228,13 +3321,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B28" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="C28" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -3248,7 +3341,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -3268,7 +3361,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B30" t="s">
         <v>91</v>
@@ -3288,7 +3381,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B31" t="s">
         <v>92</v>
@@ -3308,7 +3401,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B32" t="s">
         <v>93</v>
@@ -3328,7 +3421,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B33" t="s">
         <v>94</v>
@@ -3348,7 +3441,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B34" t="s">
         <v>95</v>
@@ -3368,7 +3461,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B35" t="s">
         <v>96</v>
@@ -3388,7 +3481,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -3408,7 +3501,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="B37" t="s">
         <v>98</v>
@@ -3428,7 +3521,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B38" t="s">
         <v>91</v>
@@ -3448,7 +3541,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B39" t="s">
         <v>92</v>
@@ -3468,7 +3561,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B40" t="s">
         <v>113</v>
@@ -3488,7 +3581,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B41" t="s">
         <v>95</v>
@@ -3508,7 +3601,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B42" t="s">
         <v>114</v>
@@ -3528,7 +3621,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
@@ -3548,7 +3641,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B44" t="s">
         <v>91</v>
@@ -3568,7 +3661,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B45" t="s">
         <v>92</v>
@@ -3588,13 +3681,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B46" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="C46" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="D46" t="s">
         <v>99</v>
@@ -3608,13 +3701,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B47" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="C47" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
       <c r="D47" t="s">
         <v>99</v>
@@ -3628,13 +3721,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B48" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="C48" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="D48" t="s">
         <v>115</v>
@@ -3648,13 +3741,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B49" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="C49" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="D49" t="s">
         <v>115</v>
@@ -3668,13 +3761,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B50" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="C50" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="D50" t="s">
         <v>115</v>
@@ -3688,13 +3781,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B51" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="C51" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="D51" t="s">
         <v>115</v>
@@ -3708,7 +3801,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B52" t="s">
         <v>98</v>
@@ -3728,7 +3821,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B53" t="s">
         <v>91</v>
@@ -3748,7 +3841,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B54" t="s">
         <v>92</v>
@@ -3768,7 +3861,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -3788,7 +3881,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B56" t="s">
         <v>118</v>
@@ -3808,7 +3901,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B57" t="s">
         <v>119</v>
@@ -3828,7 +3921,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B58" t="s">
         <v>98</v>
@@ -3848,7 +3941,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B59" t="s">
         <v>91</v>
@@ -3868,7 +3961,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B60" t="s">
         <v>92</v>
@@ -3888,13 +3981,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B61" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="C61" t="s">
-        <v>561</v>
+        <v>592</v>
       </c>
       <c r="D61" t="s">
         <v>99</v>
@@ -3908,13 +4001,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B62" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="C62" t="s">
-        <v>563</v>
+        <v>594</v>
       </c>
       <c r="D62" t="s">
         <v>99</v>
@@ -3928,13 +4021,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B63" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="C63" t="s">
-        <v>565</v>
+        <v>596</v>
       </c>
       <c r="D63" t="s">
         <v>99</v>
@@ -3948,7 +4041,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="B64" t="s">
         <v>98</v>
@@ -3968,7 +4061,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B65" t="s">
         <v>91</v>
@@ -3988,7 +4081,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B66" t="s">
         <v>92</v>
@@ -4008,7 +4101,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B67" t="s">
         <v>123</v>
@@ -4028,7 +4121,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B68" t="s">
         <v>124</v>
@@ -4048,7 +4141,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B69" t="s">
         <v>125</v>
@@ -4068,7 +4161,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B70" t="s">
         <v>126</v>
@@ -4088,7 +4181,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s">
         <v>127</v>
@@ -4108,7 +4201,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B72" t="s">
         <v>128</v>
@@ -4128,7 +4221,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B73" t="s">
         <v>129</v>
@@ -4148,7 +4241,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B74" t="s">
         <v>130</v>
@@ -4168,7 +4261,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B75" t="s">
         <v>131</v>
@@ -4188,7 +4281,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B76" t="s">
         <v>132</v>
@@ -4208,7 +4301,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B77" t="s">
         <v>133</v>
@@ -4228,7 +4321,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B78" t="s">
         <v>134</v>
@@ -4248,7 +4341,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s">
         <v>135</v>
@@ -4268,7 +4361,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="B80" t="s">
         <v>98</v>
@@ -4288,7 +4381,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B81" t="s">
         <v>91</v>
@@ -4308,7 +4401,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B82" t="s">
         <v>92</v>
@@ -4328,7 +4421,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
@@ -4348,7 +4441,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B84" t="s">
         <v>95</v>
@@ -4368,7 +4461,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B85" t="s">
         <v>151</v>
@@ -4388,7 +4481,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B86" t="s">
         <v>152</v>
@@ -4408,7 +4501,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B87" t="s">
         <v>153</v>
@@ -4428,7 +4521,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B88" t="s">
         <v>98</v>
@@ -4448,7 +4541,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -4468,7 +4561,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -4488,7 +4581,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s">
         <v>157</v>
@@ -4508,7 +4601,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="B92" t="s">
         <v>158</v>
@@ -4528,7 +4621,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s">
         <v>98</v>
@@ -4548,7 +4641,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s">
         <v>91</v>
@@ -4568,7 +4661,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B95" t="s">
         <v>92</v>
@@ -4588,19 +4681,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B96" t="s">
         <v>429</v>
       </c>
       <c r="C96" t="s">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="D96" t="s">
         <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="F96" t="s">
         <v>201</v>
@@ -4608,10 +4701,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B97" t="s">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="C97" t="s">
         <v>297</v>
@@ -4628,13 +4721,13 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="C98" t="s">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="D98" t="s">
         <v>115</v>
@@ -4648,13 +4741,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="C99" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="D99" t="s">
         <v>115</v>
@@ -4668,7 +4761,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="B100" t="s">
         <v>98</v>
@@ -4688,7 +4781,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B101" t="s">
         <v>91</v>
@@ -4708,7 +4801,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B102" t="s">
         <v>92</v>
@@ -4728,7 +4821,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B103" t="s">
         <v>93</v>
@@ -4748,13 +4841,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B104" t="s">
-        <v>578</v>
+        <v>609</v>
       </c>
       <c r="C104" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="D104" t="s">
         <v>99</v>
@@ -4768,13 +4861,13 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B105" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="C105" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="D105" t="s">
         <v>99</v>
@@ -4788,13 +4881,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B106" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="C106" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="D106" t="s">
         <v>99</v>
@@ -4808,19 +4901,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="C107" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="D107" t="s">
         <v>115</v>
       </c>
       <c r="E107" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="F107" t="s">
         <v>201</v>
@@ -4828,19 +4921,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B108" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="C108" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="D108" t="s">
         <v>115</v>
       </c>
       <c r="E108" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="F108" t="s">
         <v>201</v>
@@ -4848,7 +4941,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B109" t="s">
         <v>98</v>
@@ -4868,7 +4961,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B110" t="s">
         <v>91</v>
@@ -4888,7 +4981,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B111" t="s">
         <v>92</v>
@@ -4908,7 +5001,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B112" t="s">
         <v>161</v>
@@ -4928,7 +5021,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B113" t="s">
         <v>93</v>
@@ -4948,7 +5041,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s">
         <v>162</v>
@@ -4968,7 +5061,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -4988,7 +5081,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="B116" t="s">
         <v>98</v>
@@ -5008,7 +5101,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s">
         <v>91</v>
@@ -5028,7 +5121,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B118" t="s">
         <v>92</v>
@@ -5048,7 +5141,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B119" t="s">
         <v>227</v>
@@ -5068,7 +5161,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B120" t="s">
         <v>228</v>
@@ -5088,7 +5181,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B121" t="s">
         <v>229</v>
@@ -5108,10 +5201,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B122" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="C122" t="s">
         <v>102</v>
@@ -5128,7 +5221,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B123" t="s">
         <v>103</v>
@@ -5148,13 +5241,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B124" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="C124" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D124" t="s">
         <v>100</v>
@@ -5168,13 +5261,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B125" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="C125" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="D125" t="s">
         <v>115</v>
@@ -5188,13 +5281,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B126" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="C126" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="D126" t="s">
         <v>115</v>
@@ -5208,13 +5301,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B127" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="C127" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="D127" t="s">
         <v>115</v>
@@ -5228,13 +5321,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B128" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="C128" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="D128" t="s">
         <v>115</v>
@@ -5248,13 +5341,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="C129" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="D129" t="s">
         <v>99</v>
@@ -5268,7 +5361,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="B130" t="s">
         <v>98</v>
@@ -5288,10 +5381,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B131" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="C131" t="s">
         <v>102</v>
@@ -5308,7 +5401,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B132" t="s">
         <v>103</v>
@@ -5328,13 +5421,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B133" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="C133" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="D133" t="s">
         <v>101</v>
@@ -5343,18 +5436,18 @@
         <v>201</v>
       </c>
       <c r="F133" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B134" t="s">
         <v>93</v>
       </c>
       <c r="C134" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="D134" t="s">
         <v>99</v>
@@ -5368,16 +5461,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B135" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="C135" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="D135" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="E135" t="s">
         <v>201</v>
@@ -5388,16 +5481,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B136" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="C136" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="D136" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="E136" t="s">
         <v>201</v>
@@ -5408,16 +5501,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B137" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="C137" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="D137" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="E137" t="s">
         <v>201</v>
@@ -5428,13 +5521,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B138" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="C138" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="D138" t="s">
         <v>99</v>
@@ -5448,7 +5541,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B139" t="s">
         <v>98</v>
@@ -5468,10 +5561,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B140" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="C140" t="s">
         <v>102</v>
@@ -5488,7 +5581,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B141" t="s">
         <v>103</v>
@@ -5508,13 +5601,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B142" t="s">
         <v>113</v>
       </c>
       <c r="C142" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="D142" t="s">
         <v>101</v>
@@ -5528,13 +5621,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B143" t="s">
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="D143" t="s">
         <v>99</v>
@@ -5548,13 +5641,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B144" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="C144" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="D144" t="s">
         <v>100</v>
@@ -5568,13 +5661,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B145" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="C145" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="D145" t="s">
         <v>115</v>
@@ -5588,13 +5681,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B146" t="s">
         <v>3</v>
       </c>
       <c r="C146" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="D146" t="s">
         <v>101</v>
@@ -5603,18 +5696,18 @@
         <v>201</v>
       </c>
       <c r="F146" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B147" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="C147" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="D147" t="s">
         <v>99</v>
@@ -5628,7 +5721,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B148" t="s">
         <v>91</v>
@@ -5648,7 +5741,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B149" t="s">
         <v>92</v>
@@ -5668,7 +5761,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B150" t="s">
         <v>93</v>
@@ -5688,10 +5781,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B151" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="C151" t="s">
         <v>16</v>
@@ -5703,12 +5796,12 @@
         <v>201</v>
       </c>
       <c r="F151" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B152" t="s">
         <v>95</v>
@@ -5728,13 +5821,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B153" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="C153" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="D153" t="s">
         <v>115</v>
@@ -5748,13 +5841,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B154" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="C154" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="D154" t="s">
         <v>115</v>
@@ -5768,13 +5861,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B155" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="C155" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D155" t="s">
         <v>100</v>
@@ -5783,18 +5876,18 @@
         <v>201</v>
       </c>
       <c r="F155" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B156" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="C156" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="D156" t="s">
         <v>99</v>
@@ -5808,7 +5901,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="B157" t="s">
         <v>98</v>
@@ -5828,7 +5921,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B158" t="s">
         <v>0</v>
@@ -5840,7 +5933,7 @@
         <v>100</v>
       </c>
       <c r="E158" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="F158" t="s">
         <v>201</v>
@@ -5848,7 +5941,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B159" t="s">
         <v>1</v>
@@ -5860,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="E159" t="s">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="F159" t="s">
         <v>201</v>
@@ -5868,7 +5961,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B160" t="s">
         <v>2</v>
@@ -5880,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="E160" t="s">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="F160" t="s">
         <v>201</v>
@@ -5888,7 +5981,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B161" t="s">
         <v>3</v>
@@ -5900,7 +5993,7 @@
         <v>100</v>
       </c>
       <c r="E161" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F161" t="s">
         <v>201</v>
@@ -5908,7 +6001,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B162" t="s">
         <v>91</v>
@@ -5928,7 +6021,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B163" t="s">
         <v>92</v>
@@ -5948,19 +6041,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B164" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="C164" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="D164" t="s">
         <v>100</v>
       </c>
       <c r="E164" t="s">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="F164" t="s">
         <v>201</v>
@@ -5968,13 +6061,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B165" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="C165" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="D165" t="s">
         <v>101</v>
@@ -5983,32 +6076,32 @@
         <v>201</v>
       </c>
       <c r="F165" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B166" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="C166" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="D166" t="s">
         <v>101</v>
       </c>
       <c r="E166" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="F166" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B167" t="s">
         <v>113</v>
@@ -6028,10 +6121,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B168" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="C168" t="s">
         <v>293</v>
@@ -6040,7 +6133,7 @@
         <v>99</v>
       </c>
       <c r="E168" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
       <c r="F168" t="s">
         <v>201</v>
@@ -6048,19 +6141,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B169" t="s">
         <v>95</v>
       </c>
       <c r="C169" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="D169" t="s">
         <v>99</v>
       </c>
       <c r="E169" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="F169" t="s">
         <v>90</v>
@@ -6068,19 +6161,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B170" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C170" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="D170" t="s">
         <v>99</v>
       </c>
       <c r="E170" t="s">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="F170" t="s">
         <v>90</v>
@@ -6088,19 +6181,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B171" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="C171" t="s">
-        <v>620</v>
+        <v>651</v>
       </c>
       <c r="D171" t="s">
         <v>115</v>
       </c>
       <c r="E171" t="s">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="F171" t="s">
         <v>201</v>
@@ -6108,13 +6201,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B172" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="C172" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="D172" t="s">
         <v>115</v>
@@ -6128,13 +6221,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B173" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="C173" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="D173" t="s">
         <v>115</v>
@@ -6148,13 +6241,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B174" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C174" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D174" t="s">
         <v>100</v>
@@ -6163,12 +6256,12 @@
         <v>201</v>
       </c>
       <c r="F174" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B175" t="s">
         <v>98</v>
@@ -6188,7 +6281,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B176" t="s">
         <v>3</v>
@@ -6200,7 +6293,7 @@
         <v>100</v>
       </c>
       <c r="E176" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F176" t="s">
         <v>201</v>
@@ -6208,13 +6301,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B177" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C177" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D177" t="s">
         <v>100</v>
@@ -6223,12 +6316,12 @@
         <v>201</v>
       </c>
       <c r="F177" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B178" t="s">
         <v>98</v>
@@ -6248,7 +6341,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B179" t="s">
         <v>3</v>
@@ -6260,7 +6353,7 @@
         <v>100</v>
       </c>
       <c r="E179" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F179" t="s">
         <v>201</v>
@@ -6268,27 +6361,27 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B180" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="C180" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="D180" t="s">
         <v>101</v>
       </c>
       <c r="E180" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="F180" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B181" t="s">
         <v>113</v>
@@ -6308,10 +6401,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B182" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="C182" t="s">
         <v>293</v>
@@ -6320,7 +6413,7 @@
         <v>99</v>
       </c>
       <c r="E182" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
       <c r="F182" t="s">
         <v>201</v>
@@ -6328,19 +6421,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B183" t="s">
         <v>95</v>
       </c>
       <c r="C183" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="D183" t="s">
         <v>99</v>
       </c>
       <c r="E183" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="F183" t="s">
         <v>90</v>
@@ -6348,19 +6441,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B184" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C184" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="D184" t="s">
         <v>99</v>
       </c>
       <c r="E184" t="s">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="F184" t="s">
         <v>90</v>
@@ -6368,19 +6461,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B185" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="C185" t="s">
-        <v>620</v>
+        <v>651</v>
       </c>
       <c r="D185" t="s">
         <v>115</v>
       </c>
       <c r="E185" t="s">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="F185" t="s">
         <v>201</v>
@@ -6388,13 +6481,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B186" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="C186" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="D186" t="s">
         <v>115</v>
@@ -6408,13 +6501,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B187" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="C187" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="D187" t="s">
         <v>115</v>
@@ -6428,13 +6521,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B188" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C188" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D188" t="s">
         <v>100</v>
@@ -6443,12 +6536,12 @@
         <v>201</v>
       </c>
       <c r="F188" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B189" t="s">
         <v>98</v>
@@ -6468,7 +6561,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B190" t="s">
         <v>3</v>
@@ -6480,7 +6573,7 @@
         <v>100</v>
       </c>
       <c r="E190" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F190" t="s">
         <v>201</v>
@@ -6488,13 +6581,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B191" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="C191" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D191" t="s">
         <v>100</v>
@@ -6503,12 +6596,12 @@
         <v>201</v>
       </c>
       <c r="F191" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="B192" t="s">
         <v>98</v>
@@ -6528,7 +6621,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>3</v>
@@ -6540,7 +6633,7 @@
         <v>100</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>201</v>
@@ -8874,7 +8967,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -11098,6 +11191,448 @@
       </c>
       <c r="E131" s="2" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>128</v>
+      </c>
+      <c r="B132">
+        <v>41000</v>
+      </c>
+      <c r="C132" t="s">
+        <v>453</v>
+      </c>
+      <c r="D132" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>129</v>
+      </c>
+      <c r="B133">
+        <v>41001</v>
+      </c>
+      <c r="C133" t="s">
+        <v>455</v>
+      </c>
+      <c r="D133" t="s">
+        <v>455</v>
+      </c>
+      <c r="E133" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>130</v>
+      </c>
+      <c r="B134">
+        <v>41002</v>
+      </c>
+      <c r="C134" t="s">
+        <v>456</v>
+      </c>
+      <c r="D134" t="s">
+        <v>456</v>
+      </c>
+      <c r="E134" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>131</v>
+      </c>
+      <c r="B135">
+        <v>41003</v>
+      </c>
+      <c r="C135" t="s">
+        <v>457</v>
+      </c>
+      <c r="D135" t="s">
+        <v>457</v>
+      </c>
+      <c r="E135" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>132</v>
+      </c>
+      <c r="B136">
+        <v>41004</v>
+      </c>
+      <c r="C136" t="s">
+        <v>458</v>
+      </c>
+      <c r="D136" t="s">
+        <v>458</v>
+      </c>
+      <c r="E136" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>133</v>
+      </c>
+      <c r="B137">
+        <v>41005</v>
+      </c>
+      <c r="C137" t="s">
+        <v>459</v>
+      </c>
+      <c r="D137" t="s">
+        <v>459</v>
+      </c>
+      <c r="E137" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>134</v>
+      </c>
+      <c r="B138">
+        <v>41006</v>
+      </c>
+      <c r="C138" t="s">
+        <v>460</v>
+      </c>
+      <c r="D138" t="s">
+        <v>460</v>
+      </c>
+      <c r="E138" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>135</v>
+      </c>
+      <c r="B139">
+        <v>41007</v>
+      </c>
+      <c r="C139" t="s">
+        <v>461</v>
+      </c>
+      <c r="D139" t="s">
+        <v>461</v>
+      </c>
+      <c r="E139" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>136</v>
+      </c>
+      <c r="B140">
+        <v>41008</v>
+      </c>
+      <c r="C140" t="s">
+        <v>462</v>
+      </c>
+      <c r="D140" t="s">
+        <v>462</v>
+      </c>
+      <c r="E140" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>137</v>
+      </c>
+      <c r="B141">
+        <v>41009</v>
+      </c>
+      <c r="C141" t="s">
+        <v>463</v>
+      </c>
+      <c r="D141" t="s">
+        <v>463</v>
+      </c>
+      <c r="E141" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>138</v>
+      </c>
+      <c r="B142">
+        <v>41010</v>
+      </c>
+      <c r="C142" t="s">
+        <v>464</v>
+      </c>
+      <c r="D142" t="s">
+        <v>464</v>
+      </c>
+      <c r="E142" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>139</v>
+      </c>
+      <c r="B143">
+        <v>41011</v>
+      </c>
+      <c r="C143" t="s">
+        <v>465</v>
+      </c>
+      <c r="D143" t="s">
+        <v>465</v>
+      </c>
+      <c r="E143" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>140</v>
+      </c>
+      <c r="B144">
+        <v>41012</v>
+      </c>
+      <c r="C144" t="s">
+        <v>273</v>
+      </c>
+      <c r="D144" t="s">
+        <v>273</v>
+      </c>
+      <c r="E144" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>141</v>
+      </c>
+      <c r="B145">
+        <v>41013</v>
+      </c>
+      <c r="C145" t="s">
+        <v>466</v>
+      </c>
+      <c r="D145" t="s">
+        <v>466</v>
+      </c>
+      <c r="E145" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>142</v>
+      </c>
+      <c r="B146">
+        <v>41014</v>
+      </c>
+      <c r="C146" t="s">
+        <v>467</v>
+      </c>
+      <c r="D146" t="s">
+        <v>467</v>
+      </c>
+      <c r="E146" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>143</v>
+      </c>
+      <c r="B147">
+        <v>41015</v>
+      </c>
+      <c r="C147" t="s">
+        <v>468</v>
+      </c>
+      <c r="D147" t="s">
+        <v>468</v>
+      </c>
+      <c r="E147" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>144</v>
+      </c>
+      <c r="B148">
+        <v>41016</v>
+      </c>
+      <c r="C148" t="s">
+        <v>470</v>
+      </c>
+      <c r="D148" t="s">
+        <v>470</v>
+      </c>
+      <c r="E148" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>145</v>
+      </c>
+      <c r="B149">
+        <v>41017</v>
+      </c>
+      <c r="C149" t="s">
+        <v>472</v>
+      </c>
+      <c r="D149" t="s">
+        <v>472</v>
+      </c>
+      <c r="E149" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>146</v>
+      </c>
+      <c r="B150">
+        <v>41018</v>
+      </c>
+      <c r="C150" t="s">
+        <v>409</v>
+      </c>
+      <c r="D150" t="s">
+        <v>409</v>
+      </c>
+      <c r="E150" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>147</v>
+      </c>
+      <c r="B151">
+        <v>41019</v>
+      </c>
+      <c r="C151" t="s">
+        <v>474</v>
+      </c>
+      <c r="D151" t="s">
+        <v>474</v>
+      </c>
+      <c r="E151" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>148</v>
+      </c>
+      <c r="B152">
+        <v>41020</v>
+      </c>
+      <c r="C152" t="s">
+        <v>475</v>
+      </c>
+      <c r="D152" t="s">
+        <v>475</v>
+      </c>
+      <c r="E152" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>149</v>
+      </c>
+      <c r="B153">
+        <v>41021</v>
+      </c>
+      <c r="C153" t="s">
+        <v>476</v>
+      </c>
+      <c r="D153" t="s">
+        <v>476</v>
+      </c>
+      <c r="E153" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>150</v>
+      </c>
+      <c r="B154">
+        <v>41022</v>
+      </c>
+      <c r="C154" t="s">
+        <v>477</v>
+      </c>
+      <c r="D154" t="s">
+        <v>477</v>
+      </c>
+      <c r="E154" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>151</v>
+      </c>
+      <c r="B155">
+        <v>41023</v>
+      </c>
+      <c r="C155" t="s">
+        <v>478</v>
+      </c>
+      <c r="D155" t="s">
+        <v>478</v>
+      </c>
+      <c r="E155" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>152</v>
+      </c>
+      <c r="B156">
+        <v>41024</v>
+      </c>
+      <c r="C156" t="s">
+        <v>480</v>
+      </c>
+      <c r="D156" t="s">
+        <v>480</v>
+      </c>
+      <c r="E156" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>153</v>
+      </c>
+      <c r="B157">
+        <v>41025</v>
+      </c>
+      <c r="C157" t="s">
+        <v>482</v>
+      </c>
+      <c r="D157" t="s">
+        <v>482</v>
+      </c>
+      <c r="E157" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -11137,22 +11672,22 @@
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -11189,22 +11724,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -11215,7 +11750,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -11241,7 +11776,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -11267,7 +11802,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -11293,7 +11828,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -11319,7 +11854,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -11345,7 +11880,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -11371,7 +11906,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -11415,7 +11950,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>90</v>
@@ -11428,28 +11963,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>93</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>98</v>
@@ -11469,13 +12004,13 @@
         <v>99</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>99</v>
@@ -11492,22 +12027,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>108</v>
@@ -11539,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -11568,7 +12103,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -11655,7 +12190,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>469</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -11684,7 +12219,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -11719,13 +12254,13 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>103</v>
@@ -11737,16 +12272,16 @@
         <v>93</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -11783,22 +12318,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -11815,7 +12350,7 @@
         <v>40058</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="F5" s="12">
         <v>1</v>
@@ -11841,7 +12376,7 @@
         <v>40059</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="F6" s="12">
         <v>2</v>
@@ -11867,7 +12402,7 @@
         <v>40060</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="F7" s="12">
         <v>4</v>
@@ -11893,7 +12428,7 @@
         <v>40061</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="F8" s="12">
         <v>8</v>
@@ -11919,7 +12454,7 @@
         <v>40062</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="F9" s="12">
         <v>16</v>
@@ -11961,10 +12496,10 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>112</v>
@@ -11980,7 +12515,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="N1" s="8"/>
     </row>
@@ -11992,37 +12527,37 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>113</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>98</v>
@@ -12080,13 +12615,13 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>356</v>
@@ -12095,22 +12630,22 @@
         <v>293</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>620</v>
+        <v>651</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>108</v>
@@ -12124,7 +12659,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -12154,7 +12689,7 @@
         <v>5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>201</v>
@@ -12168,7 +12703,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>48</v>
@@ -12198,7 +12733,7 @@
         <v>5.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>201</v>
@@ -12212,7 +12747,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
@@ -12242,7 +12777,7 @@
         <v>6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>201</v>
@@ -12256,7 +12791,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -12286,7 +12821,7 @@
         <v>6.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>201</v>
@@ -12300,7 +12835,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>645</v>
+        <v>676</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>48</v>
@@ -12330,7 +12865,7 @@
         <v>7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>201</v>
@@ -12344,7 +12879,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>48</v>
@@ -12374,7 +12909,7 @@
         <v>10</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>201</v>
@@ -12388,7 +12923,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>48</v>
@@ -12418,7 +12953,7 @@
         <v>11</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>201</v>
@@ -12432,7 +12967,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>48</v>
@@ -12462,7 +12997,7 @@
         <v>12</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>201</v>
@@ -12476,7 +13011,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>48</v>
@@ -12506,7 +13041,7 @@
         <v>13</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>201</v>
@@ -12520,7 +13055,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>650</v>
+        <v>681</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>48</v>
@@ -12550,7 +13085,7 @@
         <v>14</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>201</v>
@@ -12564,7 +13099,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>48</v>
@@ -12594,7 +13129,7 @@
         <v>20</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>201</v>
@@ -12608,7 +13143,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>48</v>
@@ -12638,7 +13173,7 @@
         <v>22</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>201</v>
@@ -12652,7 +13187,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>48</v>
@@ -12682,7 +13217,7 @@
         <v>24</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>201</v>
@@ -12696,7 +13231,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>48</v>
@@ -12726,7 +13261,7 @@
         <v>26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>201</v>
@@ -12740,7 +13275,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>655</v>
+        <v>686</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>48</v>
@@ -12770,7 +13305,7 @@
         <v>28</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>201</v>
@@ -12784,7 +13319,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
@@ -12814,7 +13349,7 @@
         <v>40</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>201</v>
@@ -12828,7 +13363,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>48</v>
@@ -12858,7 +13393,7 @@
         <v>44</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>201</v>
@@ -12872,7 +13407,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>48</v>
@@ -12902,7 +13437,7 @@
         <v>48</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>201</v>
@@ -12916,7 +13451,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>48</v>
@@ -12946,7 +13481,7 @@
         <v>52</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>201</v>
@@ -12960,7 +13495,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>48</v>
@@ -12990,7 +13525,7 @@
         <v>56</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>201</v>
@@ -13004,7 +13539,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>48</v>
@@ -13034,7 +13569,7 @@
         <v>80</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>201</v>
@@ -13048,7 +13583,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>48</v>
@@ -13078,7 +13613,7 @@
         <v>88</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>201</v>
@@ -13092,7 +13627,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>48</v>
@@ -13122,7 +13657,7 @@
         <v>96</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>201</v>
@@ -13136,7 +13671,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>48</v>
@@ -13166,7 +13701,7 @@
         <v>104</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>201</v>
@@ -13180,7 +13715,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>48</v>
@@ -13210,7 +13745,7 @@
         <v>112</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>201</v>
@@ -13224,7 +13759,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>51</v>
@@ -13254,7 +13789,7 @@
         <v>0.2</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>201</v>
@@ -13268,7 +13803,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>51</v>
@@ -13298,7 +13833,7 @@
         <v>0.22</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>201</v>
@@ -13312,7 +13847,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>51</v>
@@ -13342,7 +13877,7 @@
         <v>0.24</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>201</v>
@@ -13356,7 +13891,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>51</v>
@@ -13386,7 +13921,7 @@
         <v>0.26</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>201</v>
@@ -13400,7 +13935,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>670</v>
+        <v>701</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>51</v>
@@ -13430,7 +13965,7 @@
         <v>0.28</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>201</v>
@@ -13444,7 +13979,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>51</v>
@@ -13474,7 +14009,7 @@
         <v>0.4</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>201</v>
@@ -13488,7 +14023,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>51</v>
@@ -13518,7 +14053,7 @@
         <v>0.44</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>201</v>
@@ -13532,7 +14067,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>51</v>
@@ -13562,7 +14097,7 @@
         <v>0.48</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>201</v>
@@ -13576,7 +14111,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>51</v>
@@ -13606,7 +14141,7 @@
         <v>0.52</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>201</v>
@@ -13620,7 +14155,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>51</v>
@@ -13650,7 +14185,7 @@
         <v>0.56</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>201</v>
@@ -13664,7 +14199,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>51</v>
@@ -13694,7 +14229,7 @@
         <v>0.8</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>201</v>
@@ -13708,7 +14243,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>51</v>
@@ -13738,7 +14273,7 @@
         <v>0.88</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>201</v>
@@ -13752,7 +14287,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>51</v>
@@ -13782,7 +14317,7 @@
         <v>0.96</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>201</v>
@@ -13796,7 +14331,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>679</v>
+        <v>710</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>51</v>
@@ -13826,7 +14361,7 @@
         <v>1.04</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>201</v>
@@ -13840,7 +14375,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>51</v>
@@ -13870,7 +14405,7 @@
         <v>1.12</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>201</v>
@@ -13884,7 +14419,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>681</v>
+        <v>712</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>51</v>
@@ -13914,7 +14449,7 @@
         <v>1.6</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>201</v>
@@ -13928,7 +14463,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>682</v>
+        <v>713</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>51</v>
@@ -13958,7 +14493,7 @@
         <v>1.76</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>201</v>
@@ -13972,7 +14507,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>51</v>
@@ -14002,7 +14537,7 @@
         <v>1.92</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>201</v>
@@ -14016,7 +14551,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>684</v>
+        <v>715</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>51</v>
@@ -14046,7 +14581,7 @@
         <v>2.08</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>201</v>
@@ -14060,7 +14595,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>51</v>
@@ -14090,7 +14625,7 @@
         <v>2.24</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>201</v>
@@ -14104,7 +14639,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>686</v>
+        <v>717</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>51</v>
@@ -14134,7 +14669,7 @@
         <v>3.2</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>201</v>
@@ -14148,7 +14683,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>51</v>
@@ -14178,7 +14713,7 @@
         <v>3.52</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>201</v>
@@ -14192,7 +14727,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>51</v>
@@ -14222,7 +14757,7 @@
         <v>3.84</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>201</v>
@@ -14236,7 +14771,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>51</v>
@@ -14266,7 +14801,7 @@
         <v>4.16</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>201</v>
@@ -14280,7 +14815,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>690</v>
+        <v>721</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>51</v>
@@ -14310,7 +14845,7 @@
         <v>4.48</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>201</v>
@@ -14324,7 +14859,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>53</v>
@@ -14354,7 +14889,7 @@
         <v>3</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>201</v>
@@ -14368,7 +14903,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>53</v>
@@ -14398,7 +14933,7 @@
         <v>3.3</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>201</v>
@@ -14412,7 +14947,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>693</v>
+        <v>724</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>53</v>
@@ -14442,7 +14977,7 @@
         <v>3.6</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>201</v>
@@ -14456,7 +14991,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>694</v>
+        <v>725</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>53</v>
@@ -14486,7 +15021,7 @@
         <v>3.9</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>201</v>
@@ -14500,7 +15035,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>53</v>
@@ -14530,7 +15065,7 @@
         <v>4.2</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>201</v>
@@ -14544,7 +15079,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>696</v>
+        <v>727</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>53</v>
@@ -14574,7 +15109,7 @@
         <v>6</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>201</v>
@@ -14588,7 +15123,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>53</v>
@@ -14618,7 +15153,7 @@
         <v>6.6</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>201</v>
@@ -14632,7 +15167,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>53</v>
@@ -14662,7 +15197,7 @@
         <v>7.2</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>201</v>
@@ -14676,7 +15211,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>53</v>
@@ -14706,7 +15241,7 @@
         <v>7.8</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>201</v>
@@ -14720,7 +15255,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>53</v>
@@ -14750,7 +15285,7 @@
         <v>8.4</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>201</v>
@@ -14764,7 +15299,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>701</v>
+        <v>732</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>53</v>
@@ -14794,7 +15329,7 @@
         <v>12</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>201</v>
@@ -14808,7 +15343,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>53</v>
@@ -14838,7 +15373,7 @@
         <v>13.2</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>201</v>
@@ -14852,7 +15387,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>703</v>
+        <v>734</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>53</v>
@@ -14882,7 +15417,7 @@
         <v>14.4</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>201</v>
@@ -14896,7 +15431,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>704</v>
+        <v>735</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>53</v>
@@ -14926,7 +15461,7 @@
         <v>15.6</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>201</v>
@@ -14940,7 +15475,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>53</v>
@@ -14970,7 +15505,7 @@
         <v>16.8</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>201</v>
@@ -14984,7 +15519,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>53</v>
@@ -15014,7 +15549,7 @@
         <v>24</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>201</v>
@@ -15028,7 +15563,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>707</v>
+        <v>738</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>53</v>
@@ -15058,7 +15593,7 @@
         <v>26.4</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>201</v>
@@ -15072,7 +15607,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>53</v>
@@ -15102,7 +15637,7 @@
         <v>28.8</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>201</v>
@@ -15116,7 +15651,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>709</v>
+        <v>740</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>53</v>
@@ -15146,7 +15681,7 @@
         <v>31.2</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>201</v>
@@ -15160,7 +15695,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>53</v>
@@ -15190,7 +15725,7 @@
         <v>33.6</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>201</v>
@@ -15204,7 +15739,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>711</v>
+        <v>742</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>53</v>
@@ -15234,7 +15769,7 @@
         <v>48</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>201</v>
@@ -15248,7 +15783,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>712</v>
+        <v>743</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>53</v>
@@ -15278,7 +15813,7 @@
         <v>52.8</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>201</v>
@@ -15292,7 +15827,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>713</v>
+        <v>744</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>53</v>
@@ -15322,7 +15857,7 @@
         <v>57.6</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>201</v>
@@ -15336,7 +15871,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>53</v>
@@ -15366,7 +15901,7 @@
         <v>62.4</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>201</v>
@@ -15380,7 +15915,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>715</v>
+        <v>746</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>53</v>
@@ -15410,7 +15945,7 @@
         <v>67.2</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>201</v>
@@ -15448,7 +15983,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -15469,13 +16004,13 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>394</v>
@@ -15484,19 +16019,19 @@
         <v>397</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>95</v>
@@ -15551,37 +16086,37 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -23810,7 +24345,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>90</v>
@@ -23818,7 +24353,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -23834,22 +24369,22 @@
         <v>93</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>98</v>
@@ -23904,16 +24439,16 @@
         <v>105</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>108</v>
@@ -23942,13 +24477,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -23974,13 +24509,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -24006,13 +24541,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -24038,13 +24573,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -24070,13 +24605,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -24114,13 +24649,13 @@
         <v>90</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -24133,7 +24668,7 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>292</v>
@@ -24142,22 +24677,22 @@
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>151</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>629</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -24203,16 +24738,16 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>630</v>
+        <v>661</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>293</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>154</v>
@@ -24221,7 +24756,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>165</v>
@@ -26187,13 +26722,13 @@
         <v>429</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>98</v>
@@ -26230,16 +26765,16 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>297</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>108</v>
@@ -26514,19 +27049,19 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>578</v>
+        <v>609</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>98</v>
@@ -26566,19 +27101,19 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>108</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3763" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3796" uniqueCount="987">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2241,6 +2241,66 @@
   </si>
   <si>
     <t>First Clear</t>
+  </si>
+  <si>
+    <t>랭킹</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>RankingModal</t>
+  </si>
+  <si>
+    <t>순위</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>최고 스테이지</t>
+  </si>
+  <si>
+    <t>Best Stage</t>
+  </si>
+  <si>
+    <t>플레이 시간</t>
+  </si>
+  <si>
+    <t>Play Time</t>
+  </si>
+  <si>
+    <t>Rebirths</t>
+  </si>
+  <si>
+    <t>불러오는 중...</t>
+  </si>
+  <si>
+    <t>Loading...</t>
+  </si>
+  <si>
+    <t>랭킹을 불러오지 못했습니다</t>
+  </si>
+  <si>
+    <t>Failed to load ranking</t>
+  </si>
+  <si>
+    <t>다시 시도</t>
+  </si>
+  <si>
+    <t>Retry</t>
+  </si>
+  <si>
+    <t>아직 등록된 기록이 없습니다</t>
+  </si>
+  <si>
+    <t>No records yet</t>
+  </si>
+  <si>
+    <t>내 기록</t>
+  </si>
+  <si>
+    <t>My Record</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3439,27 +3499,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="B1" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="C1" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="D1" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
       <c r="E1" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="F1" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B2" t="s">
         <v>91</v>
@@ -3479,7 +3539,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B3" t="s">
         <v>92</v>
@@ -3499,13 +3559,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B4" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="C4" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="D4" t="s">
         <v>99</v>
@@ -3519,13 +3579,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B5" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="C5" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -3539,10 +3599,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B6" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3554,18 +3614,18 @@
         <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B7" t="s">
         <v>383</v>
       </c>
       <c r="C7" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
       <c r="D7" t="s">
         <v>99</v>
@@ -3579,13 +3639,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B8" t="s">
         <v>386</v>
       </c>
       <c r="C8" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
@@ -3599,13 +3659,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B9" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="C9" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="D9" t="s">
         <v>99</v>
@@ -3619,13 +3679,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B10" t="s">
-        <v>788</v>
+        <v>808</v>
       </c>
       <c r="C10" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
@@ -3639,13 +3699,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B11" t="s">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="C11" t="s">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
@@ -3659,13 +3719,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B12" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="C12" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -3679,13 +3739,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B13" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="C13" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
@@ -3699,13 +3759,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B14" t="s">
         <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3719,19 +3779,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B15" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
       <c r="C15" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="F15" t="s">
         <v>189</v>
@@ -3739,7 +3799,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -3759,7 +3819,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B17" t="s">
         <v>92</v>
@@ -3779,13 +3839,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B18" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="C18" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="D18" t="s">
         <v>99</v>
@@ -3799,7 +3859,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B19" t="s">
         <v>280</v>
@@ -3819,13 +3879,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B20" t="s">
         <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -3839,13 +3899,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B21" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="C21" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="D21" t="s">
         <v>99</v>
@@ -3859,13 +3919,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B22" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="C22" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -3874,15 +3934,15 @@
         <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B23" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -3894,18 +3954,18 @@
         <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B24" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="C24" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="D24" t="s">
         <v>101</v>
@@ -3914,15 +3974,15 @@
         <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B25" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="C25" t="s">
         <v>153</v>
@@ -3939,7 +3999,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B26" t="s">
         <v>284</v>
@@ -3959,7 +4019,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B27" t="s">
         <v>91</v>
@@ -3979,7 +4039,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B28" t="s">
         <v>92</v>
@@ -3999,7 +4059,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B29" t="s">
         <v>93</v>
@@ -4019,7 +4079,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B30" t="s">
         <v>94</v>
@@ -4039,7 +4099,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B31" t="s">
         <v>95</v>
@@ -4059,7 +4119,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B32" t="s">
         <v>96</v>
@@ -4079,7 +4139,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -4099,7 +4159,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B34" t="s">
         <v>98</v>
@@ -4119,7 +4179,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B35" t="s">
         <v>91</v>
@@ -4139,7 +4199,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B36" t="s">
         <v>92</v>
@@ -4159,7 +4219,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B37" t="s">
         <v>112</v>
@@ -4179,7 +4239,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B38" t="s">
         <v>113</v>
@@ -4199,7 +4259,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B39" t="s">
         <v>114</v>
@@ -4219,7 +4279,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B40" t="s">
         <v>98</v>
@@ -4239,7 +4299,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B41" t="s">
         <v>91</v>
@@ -4259,7 +4319,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B42" t="s">
         <v>92</v>
@@ -4279,19 +4339,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B43" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="C43" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="D43" t="s">
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="F43" t="s">
         <v>189</v>
@@ -4299,13 +4359,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B44" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="C44" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="D44" t="s">
         <v>101</v>
@@ -4314,32 +4374,32 @@
         <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B45" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="C45" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="D45" t="s">
         <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="F45" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B46" t="s">
         <v>344</v>
@@ -4354,24 +4414,24 @@
         <v>189</v>
       </c>
       <c r="F46" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B47" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="C47" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D47" t="s">
         <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="F47" t="s">
         <v>90</v>
@@ -4379,19 +4439,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B48" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C48" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="D48" t="s">
         <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="F48" t="s">
         <v>189</v>
@@ -4399,10 +4459,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B49" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C49" t="s">
         <v>281</v>
@@ -4411,7 +4471,7 @@
         <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="F49" t="s">
         <v>189</v>
@@ -4419,19 +4479,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B50" t="s">
         <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="D50" t="s">
         <v>99</v>
       </c>
       <c r="E50" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="F50" t="s">
         <v>90</v>
@@ -4439,19 +4499,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B51" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="C51" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="D51" t="s">
         <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="F51" t="s">
         <v>90</v>
@@ -4459,13 +4519,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B52" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="C52" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="D52" t="s">
         <v>131</v>
@@ -4479,13 +4539,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B53" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="C53" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="D53" t="s">
         <v>131</v>
@@ -4499,13 +4559,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B54" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="C54" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="D54" t="s">
         <v>131</v>
@@ -4519,13 +4579,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B55" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="C55" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="D55" t="s">
         <v>100</v>
@@ -4534,12 +4594,12 @@
         <v>189</v>
       </c>
       <c r="F55" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B56" t="s">
         <v>98</v>
@@ -4559,7 +4619,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B57" t="s">
         <v>91</v>
@@ -4579,7 +4639,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B58" t="s">
         <v>92</v>
@@ -4599,7 +4659,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B59" t="s">
         <v>118</v>
@@ -4619,7 +4679,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B60" t="s">
         <v>119</v>
@@ -4639,7 +4699,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B61" t="s">
         <v>120</v>
@@ -4659,7 +4719,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B62" t="s">
         <v>121</v>
@@ -4679,7 +4739,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B63" t="s">
         <v>122</v>
@@ -4699,7 +4759,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B64" t="s">
         <v>123</v>
@@ -4719,7 +4779,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B65" t="s">
         <v>124</v>
@@ -4739,7 +4799,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B66" t="s">
         <v>125</v>
@@ -4759,7 +4819,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B67" t="s">
         <v>126</v>
@@ -4779,7 +4839,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B68" t="s">
         <v>127</v>
@@ -4799,7 +4859,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B69" t="s">
         <v>128</v>
@@ -4819,7 +4879,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B70" t="s">
         <v>129</v>
@@ -4839,7 +4899,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B71" t="s">
         <v>130</v>
@@ -4859,7 +4919,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B72" t="s">
         <v>98</v>
@@ -4879,7 +4939,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B73" t="s">
         <v>91</v>
@@ -4899,7 +4959,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B74" t="s">
         <v>92</v>
@@ -4919,7 +4979,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B75" t="s">
         <v>344</v>
@@ -4934,12 +4994,12 @@
         <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B76" t="s">
         <v>95</v>
@@ -4959,19 +5019,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B77" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="C77" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="D77" t="s">
         <v>99</v>
       </c>
       <c r="E77" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="F77" t="s">
         <v>90</v>
@@ -4979,19 +5039,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B78" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="C78" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D78" t="s">
         <v>99</v>
       </c>
       <c r="E78" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="F78" t="s">
         <v>90</v>
@@ -4999,19 +5059,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B79" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C79" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="D79" t="s">
         <v>100</v>
       </c>
       <c r="E79" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="F79" t="s">
         <v>189</v>
@@ -5019,13 +5079,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B80" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="C80" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="D80" t="s">
         <v>101</v>
@@ -5034,18 +5094,18 @@
         <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B81" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="C81" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="D81" t="s">
         <v>131</v>
@@ -5059,13 +5119,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B82" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="C82" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="D82" t="s">
         <v>131</v>
@@ -5079,7 +5139,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B83" t="s">
         <v>98</v>
@@ -5099,7 +5159,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B84" t="s">
         <v>91</v>
@@ -5119,7 +5179,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B85" t="s">
         <v>92</v>
@@ -5139,7 +5199,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B86" t="s">
         <v>145</v>
@@ -5159,7 +5219,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B87" t="s">
         <v>146</v>
@@ -5179,7 +5239,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B88" t="s">
         <v>98</v>
@@ -5199,7 +5259,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -5219,7 +5279,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -5239,19 +5299,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B91" t="s">
         <v>418</v>
       </c>
       <c r="C91" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="D91" t="s">
         <v>99</v>
       </c>
       <c r="E91" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="F91" t="s">
         <v>189</v>
@@ -5259,10 +5319,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B92" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="C92" t="s">
         <v>285</v>
@@ -5279,13 +5339,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B93" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="C93" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="D93" t="s">
         <v>131</v>
@@ -5299,13 +5359,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B94" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="C94" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="D94" t="s">
         <v>131</v>
@@ -5319,7 +5379,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -5339,7 +5399,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B96" t="s">
         <v>91</v>
@@ -5359,7 +5419,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B97" t="s">
         <v>92</v>
@@ -5379,13 +5439,13 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B98" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="C98" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="D98" t="s">
         <v>99</v>
@@ -5399,13 +5459,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B99" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="C99" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="D99" t="s">
         <v>99</v>
@@ -5419,13 +5479,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B100" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="C100" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="D100" t="s">
         <v>99</v>
@@ -5439,13 +5499,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B101" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="C101" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="D101" t="s">
         <v>131</v>
@@ -5459,13 +5519,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B102" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="C102" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
       <c r="D102" t="s">
         <v>131</v>
@@ -5479,7 +5539,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B103" t="s">
         <v>98</v>
@@ -5499,7 +5559,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B104" t="s">
         <v>91</v>
@@ -5519,7 +5579,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B105" t="s">
         <v>92</v>
@@ -5539,7 +5599,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B106" t="s">
         <v>149</v>
@@ -5559,7 +5619,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B107" t="s">
         <v>93</v>
@@ -5579,7 +5639,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B108" t="s">
         <v>150</v>
@@ -5599,7 +5659,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B109" t="s">
         <v>151</v>
@@ -5619,7 +5679,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B110" t="s">
         <v>98</v>
@@ -5639,7 +5699,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B111" t="s">
         <v>91</v>
@@ -5659,7 +5719,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B112" t="s">
         <v>92</v>
@@ -5679,7 +5739,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B113" t="s">
         <v>215</v>
@@ -5699,7 +5759,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B114" t="s">
         <v>216</v>
@@ -5719,7 +5779,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B115" t="s">
         <v>217</v>
@@ -5739,7 +5799,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B116" t="s">
         <v>91</v>
@@ -5759,7 +5819,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B117" t="s">
         <v>103</v>
@@ -5779,13 +5839,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B118" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="C118" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="D118" t="s">
         <v>100</v>
@@ -5799,13 +5859,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B119" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="C119" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="D119" t="s">
         <v>131</v>
@@ -5819,13 +5879,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B120" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C120" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="D120" t="s">
         <v>131</v>
@@ -5839,13 +5899,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B121" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="C121" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="D121" t="s">
         <v>131</v>
@@ -5859,13 +5919,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B122" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="C122" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="D122" t="s">
         <v>131</v>
@@ -5879,13 +5939,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="B123" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="C123" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="D123" t="s">
         <v>99</v>
@@ -5899,10 +5959,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B124" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="C124" t="s">
         <v>102</v>
@@ -5919,7 +5979,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B125" t="s">
         <v>103</v>
@@ -5939,13 +5999,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B126" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="C126" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="D126" t="s">
         <v>101</v>
@@ -5954,18 +6014,18 @@
         <v>189</v>
       </c>
       <c r="F126" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B127" t="s">
         <v>93</v>
       </c>
       <c r="C127" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="D127" t="s">
         <v>99</v>
@@ -5979,16 +6039,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B128" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="C128" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="D128" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="E128" t="s">
         <v>189</v>
@@ -5999,16 +6059,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B129" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="C129" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="D129" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="E129" t="s">
         <v>189</v>
@@ -6019,16 +6079,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B130" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="C130" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="D130" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="E130" t="s">
         <v>189</v>
@@ -6039,13 +6099,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B131" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="C131" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="D131" t="s">
         <v>99</v>
@@ -6059,7 +6119,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B132" t="s">
         <v>98</v>
@@ -6079,7 +6139,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B133" t="s">
         <v>91</v>
@@ -6099,7 +6159,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B134" t="s">
         <v>92</v>
@@ -6119,7 +6179,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B135" t="s">
         <v>93</v>
@@ -6139,10 +6199,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B136" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="C136" t="s">
         <v>16</v>
@@ -6154,12 +6214,12 @@
         <v>189</v>
       </c>
       <c r="F136" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B137" t="s">
         <v>95</v>
@@ -6179,13 +6239,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B138" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="C138" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="D138" t="s">
         <v>131</v>
@@ -6199,13 +6259,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B139" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="C139" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="D139" t="s">
         <v>131</v>
@@ -6219,13 +6279,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B140" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="C140" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="D140" t="s">
         <v>100</v>
@@ -6234,18 +6294,18 @@
         <v>189</v>
       </c>
       <c r="F140" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B141" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="C141" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="D141" t="s">
         <v>99</v>
@@ -6259,7 +6319,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="B142" t="s">
         <v>98</v>
@@ -6310,13 +6370,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>90</v>
@@ -6333,7 +6393,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6345,43 +6405,43 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>344</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>98</v>
@@ -6445,43 +6505,43 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>345</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>281</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>108</v>
@@ -6495,7 +6555,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -6510,7 +6570,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -6531,7 +6591,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>189</v>
@@ -6545,7 +6605,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -6560,7 +6620,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -6581,7 +6641,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>189</v>
@@ -6595,7 +6655,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -6610,7 +6670,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -6631,7 +6691,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>189</v>
@@ -6645,7 +6705,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -6660,7 +6720,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -6681,7 +6741,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>189</v>
@@ -6695,7 +6755,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -6710,7 +6770,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -6731,7 +6791,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>189</v>
@@ -6745,7 +6805,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -6760,7 +6820,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -6781,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>189</v>
@@ -6795,7 +6855,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -6810,7 +6870,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -6831,7 +6891,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>189</v>
@@ -6845,7 +6905,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -6860,7 +6920,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -6881,7 +6941,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>189</v>
@@ -6895,7 +6955,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -6910,7 +6970,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -6931,7 +6991,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>189</v>
@@ -6945,7 +7005,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -6960,7 +7020,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -6981,7 +7041,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>189</v>
@@ -6995,7 +7055,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7010,7 +7070,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7031,7 +7091,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>189</v>
@@ -7045,7 +7105,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7060,7 +7120,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7081,7 +7141,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>189</v>
@@ -7095,7 +7155,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>902</v>
+        <v>922</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7110,7 +7170,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7131,7 +7191,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>189</v>
@@ -7145,7 +7205,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7160,7 +7220,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7181,7 +7241,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>189</v>
@@ -7195,7 +7255,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7210,7 +7270,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7231,7 +7291,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>189</v>
@@ -7245,7 +7305,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7260,7 +7320,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7281,7 +7341,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>189</v>
@@ -7295,7 +7355,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7310,7 +7370,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7331,7 +7391,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>189</v>
@@ -7345,7 +7405,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7360,7 +7420,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7381,7 +7441,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>189</v>
@@ -7395,7 +7455,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7410,7 +7470,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7431,7 +7491,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>189</v>
@@ -7445,7 +7505,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7460,7 +7520,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -7481,7 +7541,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>189</v>
@@ -7495,7 +7555,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -7510,7 +7570,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -7531,7 +7591,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>189</v>
@@ -7545,7 +7605,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -7560,7 +7620,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -7581,7 +7641,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>189</v>
@@ -7595,7 +7655,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -7610,7 +7670,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -7631,7 +7691,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>189</v>
@@ -7645,7 +7705,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -7660,7 +7720,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -7681,7 +7741,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>189</v>
@@ -7695,7 +7755,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -7710,7 +7770,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -7731,7 +7791,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>189</v>
@@ -7745,7 +7805,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -7760,7 +7820,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -7781,7 +7841,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>189</v>
@@ -7795,7 +7855,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -7810,7 +7870,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -7831,7 +7891,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>189</v>
@@ -7845,7 +7905,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -7860,7 +7920,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -7881,7 +7941,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>189</v>
@@ -7895,7 +7955,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -7910,7 +7970,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -7931,7 +7991,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>189</v>
@@ -7945,7 +8005,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -7960,7 +8020,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -7981,7 +8041,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>189</v>
@@ -7995,7 +8055,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8010,7 +8070,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8031,7 +8091,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>189</v>
@@ -8045,7 +8105,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8060,7 +8120,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8081,7 +8141,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>189</v>
@@ -8095,7 +8155,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8110,7 +8170,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8131,7 +8191,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>189</v>
@@ -8145,7 +8205,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8160,7 +8220,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8181,7 +8241,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>189</v>
@@ -8195,7 +8255,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8210,7 +8270,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8231,7 +8291,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>189</v>
@@ -8245,7 +8305,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8260,7 +8320,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8281,7 +8341,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>189</v>
@@ -8295,7 +8355,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8310,7 +8370,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8331,7 +8391,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>189</v>
@@ -8345,7 +8405,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8360,7 +8420,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8381,7 +8441,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>189</v>
@@ -8395,7 +8455,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8410,7 +8470,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8431,7 +8491,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>189</v>
@@ -8445,7 +8505,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8460,7 +8520,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -8481,7 +8541,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>189</v>
@@ -8495,7 +8555,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -8510,7 +8570,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -8531,7 +8591,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>189</v>
@@ -8545,7 +8605,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -8560,7 +8620,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -8581,7 +8641,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>189</v>
@@ -8595,7 +8655,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -8610,7 +8670,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -8631,7 +8691,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>189</v>
@@ -8645,7 +8705,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -8660,7 +8720,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -8681,7 +8741,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>189</v>
@@ -8695,7 +8755,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -8710,7 +8770,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -8731,7 +8791,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>189</v>
@@ -8745,7 +8805,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -8760,7 +8820,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -8781,7 +8841,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>189</v>
@@ -8795,7 +8855,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -8810,7 +8870,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -8831,7 +8891,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>189</v>
@@ -8845,7 +8905,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -8860,7 +8920,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -8881,7 +8941,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>189</v>
@@ -8895,7 +8955,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -8910,7 +8970,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -8931,7 +8991,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>189</v>
@@ -8945,7 +9005,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -8960,7 +9020,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -8981,7 +9041,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>189</v>
@@ -8995,7 +9055,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9010,7 +9070,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9031,7 +9091,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>189</v>
@@ -9045,7 +9105,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9060,7 +9120,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9081,7 +9141,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>189</v>
@@ -9095,7 +9155,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9110,7 +9170,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9131,7 +9191,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>189</v>
@@ -9145,7 +9205,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9160,7 +9220,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9181,7 +9241,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>189</v>
@@ -9195,7 +9255,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9210,7 +9270,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9231,7 +9291,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>189</v>
@@ -9245,7 +9305,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9260,7 +9320,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9281,7 +9341,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>189</v>
@@ -9295,7 +9355,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9310,7 +9370,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9331,7 +9391,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>189</v>
@@ -9345,7 +9405,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9360,7 +9420,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9381,7 +9441,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>189</v>
@@ -9395,7 +9455,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9410,7 +9470,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9431,7 +9491,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>189</v>
@@ -9445,7 +9505,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9460,7 +9520,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -9481,7 +9541,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>189</v>
@@ -9495,7 +9555,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -9510,7 +9570,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -9531,7 +9591,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>189</v>
@@ -9545,7 +9605,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -9560,7 +9620,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -9581,7 +9641,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>189</v>
@@ -9595,7 +9655,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -9610,7 +9670,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -9631,7 +9691,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>189</v>
@@ -9645,7 +9705,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -9660,7 +9720,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -9681,7 +9741,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>189</v>
@@ -9695,7 +9755,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>956</v>
+        <v>976</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -9710,7 +9770,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -9731,7 +9791,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>189</v>
@@ -9745,7 +9805,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -9760,7 +9820,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -9781,7 +9841,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>189</v>
@@ -9795,7 +9855,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -9810,7 +9870,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -9831,7 +9891,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>189</v>
@@ -9845,7 +9905,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>959</v>
+        <v>979</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -9860,7 +9920,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -9881,7 +9941,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>189</v>
@@ -9895,7 +9955,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -9910,7 +9970,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -9931,7 +9991,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>189</v>
@@ -9945,7 +10005,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>961</v>
+        <v>981</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -9960,7 +10020,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -9981,7 +10041,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>189</v>
@@ -9995,7 +10055,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>962</v>
+        <v>982</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10010,7 +10070,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10031,7 +10091,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>189</v>
@@ -10045,7 +10105,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>963</v>
+        <v>983</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10060,7 +10120,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10081,7 +10141,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>189</v>
@@ -10095,7 +10155,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>964</v>
+        <v>984</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10110,7 +10170,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10131,7 +10191,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>189</v>
@@ -10145,7 +10205,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>965</v>
+        <v>985</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10160,7 +10220,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10181,7 +10241,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>189</v>
@@ -10195,7 +10255,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10210,7 +10270,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10231,7 +10291,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>189</v>
@@ -10443,7 +10503,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>90</v>
@@ -10456,7 +10516,7 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -10476,22 +10536,22 @@
         <v>95</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>98</v>
@@ -10546,22 +10606,22 @@
         <v>105</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>108</v>
@@ -10587,7 +10647,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -10622,7 +10682,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -10657,7 +10717,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -10692,7 +10752,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -10727,7 +10787,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -10762,7 +10822,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -10797,7 +10857,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -10832,7 +10892,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -10867,7 +10927,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -12699,7 +12759,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E417"/>
+  <dimension ref="A1:E428"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -19785,6 +19845,193 @@
       </c>
       <c r="E417" t="s">
         <v>460</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>414</v>
+      </c>
+      <c r="B418">
+        <v>41027</v>
+      </c>
+      <c r="C418" t="s">
+        <v>736</v>
+      </c>
+      <c r="D418" t="s">
+        <v>737</v>
+      </c>
+      <c r="E418" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>415</v>
+      </c>
+      <c r="B419">
+        <v>41028</v>
+      </c>
+      <c r="C419" t="s">
+        <v>739</v>
+      </c>
+      <c r="D419" t="s">
+        <v>740</v>
+      </c>
+      <c r="E419" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>416</v>
+      </c>
+      <c r="B420">
+        <v>41029</v>
+      </c>
+      <c r="C420" t="s">
+        <v>93</v>
+      </c>
+      <c r="D420" t="s">
+        <v>105</v>
+      </c>
+      <c r="E420" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>417</v>
+      </c>
+      <c r="B421">
+        <v>41030</v>
+      </c>
+      <c r="C421" t="s">
+        <v>741</v>
+      </c>
+      <c r="D421" t="s">
+        <v>742</v>
+      </c>
+      <c r="E421" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>418</v>
+      </c>
+      <c r="B422">
+        <v>41031</v>
+      </c>
+      <c r="C422" t="s">
+        <v>743</v>
+      </c>
+      <c r="D422" t="s">
+        <v>744</v>
+      </c>
+      <c r="E422" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>419</v>
+      </c>
+      <c r="B423">
+        <v>41032</v>
+      </c>
+      <c r="C423" t="s">
+        <v>41</v>
+      </c>
+      <c r="D423" t="s">
+        <v>745</v>
+      </c>
+      <c r="E423" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>420</v>
+      </c>
+      <c r="B424">
+        <v>41033</v>
+      </c>
+      <c r="C424" t="s">
+        <v>746</v>
+      </c>
+      <c r="D424" t="s">
+        <v>747</v>
+      </c>
+      <c r="E424" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>421</v>
+      </c>
+      <c r="B425">
+        <v>41034</v>
+      </c>
+      <c r="C425" t="s">
+        <v>748</v>
+      </c>
+      <c r="D425" t="s">
+        <v>749</v>
+      </c>
+      <c r="E425" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>422</v>
+      </c>
+      <c r="B426">
+        <v>41035</v>
+      </c>
+      <c r="C426" t="s">
+        <v>750</v>
+      </c>
+      <c r="D426" t="s">
+        <v>751</v>
+      </c>
+      <c r="E426" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>423</v>
+      </c>
+      <c r="B427">
+        <v>41036</v>
+      </c>
+      <c r="C427" t="s">
+        <v>752</v>
+      </c>
+      <c r="D427" t="s">
+        <v>753</v>
+      </c>
+      <c r="E427" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>424</v>
+      </c>
+      <c r="B428">
+        <v>41037</v>
+      </c>
+      <c r="C428" t="s">
+        <v>754</v>
+      </c>
+      <c r="D428" t="s">
+        <v>755</v>
+      </c>
+      <c r="E428" t="s">
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -19824,22 +20071,22 @@
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -19876,22 +20123,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -19902,7 +20149,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -19928,7 +20175,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -19954,7 +20201,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -19980,7 +20227,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -20006,7 +20253,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -20032,7 +20279,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -20058,7 +20305,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -20102,7 +20349,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>90</v>
@@ -20115,28 +20362,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>93</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>98</v>
@@ -20156,13 +20403,13 @@
         <v>99</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>99</v>
@@ -20179,22 +20426,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>108</v>
@@ -20226,7 +20473,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -20255,7 +20502,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -20342,7 +20589,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -20371,7 +20618,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -20407,7 +20654,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -20429,13 +20676,13 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>383</v>
@@ -20444,25 +20691,25 @@
         <v>386</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>788</v>
+        <v>808</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -20517,40 +20764,40 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -29379,7 +29626,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>90</v>
@@ -29387,7 +29634,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -29403,22 +29650,22 @@
         <v>93</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>98</v>
@@ -29473,16 +29720,16 @@
         <v>105</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>108</v>
@@ -29511,13 +29758,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -29543,13 +29790,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -29575,13 +29822,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -29607,13 +29854,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -29639,13 +29886,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -29680,13 +29927,13 @@
         <v>90</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -29699,7 +29946,7 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>280</v>
@@ -29708,19 +29955,19 @@
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>284</v>
@@ -29769,25 +30016,25 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>281</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>153</v>
@@ -31753,13 +32000,13 @@
         <v>418</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>98</v>
@@ -31796,16 +32043,16 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>285</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>108</v>
@@ -32080,19 +32327,19 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>98</v>
@@ -32132,19 +32379,19 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>108</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3796" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3823" uniqueCount="1006">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2301,6 +2301,63 @@
   </si>
   <si>
     <t>My Record</t>
+  </si>
+  <si>
+    <t>저장 데이터가 초기화되었습니다</t>
+  </si>
+  <si>
+    <t>Save data has been reset</t>
+  </si>
+  <si>
+    <t>ProfileUi</t>
+  </si>
+  <si>
+    <t>데이터 구조가 변경되어 기존 진행 상황을 이어갈 수 없습니다.</t>
+  </si>
+  <si>
+    <t>The save structure changed, so previous progress can't be carried over.</t>
+  </si>
+  <si>
+    <t>이름을 입력해주세요</t>
+  </si>
+  <si>
+    <t>Enter your name</t>
+  </si>
+  <si>
+    <t>랭킹에 표시될 이름입니다. 2~12자로 입력해주세요.</t>
+  </si>
+  <si>
+    <t>This will be your name on the leaderboard. Use 2-12 characters.</t>
+  </si>
+  <si>
+    <t>이름 입력</t>
+  </si>
+  <si>
+    <t>Enter name</t>
+  </si>
+  <si>
+    <t>2~12자로 입력해주세요(공백 제외)</t>
+  </si>
+  <si>
+    <t>Use 2-12 characters (spaces don't count)</t>
+  </si>
+  <si>
+    <t>프로필</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>총 플레이 시간</t>
+  </si>
+  <si>
+    <t>Total Play Time</t>
+  </si>
+  <si>
+    <t>이름 수정</t>
+  </si>
+  <si>
+    <t>Edit name</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3499,27 +3556,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
       <c r="B1" t="s">
-        <v>792</v>
+        <v>811</v>
       </c>
       <c r="C1" t="s">
-        <v>793</v>
+        <v>812</v>
       </c>
       <c r="D1" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="E1" t="s">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="F1" t="s">
-        <v>796</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B2" t="s">
         <v>91</v>
@@ -3539,7 +3596,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B3" t="s">
         <v>92</v>
@@ -3559,13 +3616,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B4" t="s">
-        <v>798</v>
+        <v>817</v>
       </c>
       <c r="C4" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="D4" t="s">
         <v>99</v>
@@ -3579,13 +3636,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B5" t="s">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="C5" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -3599,10 +3656,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B6" t="s">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3614,18 +3671,18 @@
         <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>803</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B7" t="s">
         <v>383</v>
       </c>
       <c r="C7" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="D7" t="s">
         <v>99</v>
@@ -3639,13 +3696,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B8" t="s">
         <v>386</v>
       </c>
       <c r="C8" t="s">
-        <v>805</v>
+        <v>824</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
@@ -3659,13 +3716,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B9" t="s">
-        <v>806</v>
+        <v>825</v>
       </c>
       <c r="C9" t="s">
-        <v>807</v>
+        <v>826</v>
       </c>
       <c r="D9" t="s">
         <v>99</v>
@@ -3679,13 +3736,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B10" t="s">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="C10" t="s">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
@@ -3699,13 +3756,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B11" t="s">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="C11" t="s">
-        <v>811</v>
+        <v>830</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
@@ -3719,13 +3776,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B12" t="s">
-        <v>812</v>
+        <v>831</v>
       </c>
       <c r="C12" t="s">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -3739,13 +3796,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B13" t="s">
-        <v>814</v>
+        <v>833</v>
       </c>
       <c r="C13" t="s">
-        <v>815</v>
+        <v>834</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
@@ -3759,13 +3816,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B14" t="s">
         <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3779,19 +3836,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="B15" t="s">
-        <v>816</v>
+        <v>835</v>
       </c>
       <c r="C15" t="s">
-        <v>817</v>
+        <v>836</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="F15" t="s">
         <v>189</v>
@@ -3799,7 +3856,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -3819,7 +3876,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B17" t="s">
         <v>92</v>
@@ -3839,13 +3896,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B18" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="C18" t="s">
-        <v>821</v>
+        <v>840</v>
       </c>
       <c r="D18" t="s">
         <v>99</v>
@@ -3859,7 +3916,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B19" t="s">
         <v>280</v>
@@ -3879,13 +3936,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B20" t="s">
         <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
@@ -3899,13 +3956,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B21" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C21" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D21" t="s">
         <v>99</v>
@@ -3919,13 +3976,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B22" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="C22" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -3934,15 +3991,15 @@
         <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B23" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -3954,18 +4011,18 @@
         <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B24" t="s">
-        <v>827</v>
+        <v>846</v>
       </c>
       <c r="C24" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
       <c r="D24" t="s">
         <v>101</v>
@@ -3974,15 +4031,15 @@
         <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B25" t="s">
-        <v>829</v>
+        <v>848</v>
       </c>
       <c r="C25" t="s">
         <v>153</v>
@@ -3999,7 +4056,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="B26" t="s">
         <v>284</v>
@@ -4019,7 +4076,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B27" t="s">
         <v>91</v>
@@ -4039,7 +4096,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B28" t="s">
         <v>92</v>
@@ -4059,7 +4116,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B29" t="s">
         <v>93</v>
@@ -4079,7 +4136,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B30" t="s">
         <v>94</v>
@@ -4099,7 +4156,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B31" t="s">
         <v>95</v>
@@ -4119,7 +4176,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B32" t="s">
         <v>96</v>
@@ -4139,7 +4196,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -4159,7 +4216,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="B34" t="s">
         <v>98</v>
@@ -4179,7 +4236,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B35" t="s">
         <v>91</v>
@@ -4199,7 +4256,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B36" t="s">
         <v>92</v>
@@ -4219,7 +4276,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B37" t="s">
         <v>112</v>
@@ -4239,7 +4296,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B38" t="s">
         <v>113</v>
@@ -4259,7 +4316,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B39" t="s">
         <v>114</v>
@@ -4279,7 +4336,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="B40" t="s">
         <v>98</v>
@@ -4299,7 +4356,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B41" t="s">
         <v>91</v>
@@ -4319,7 +4376,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B42" t="s">
         <v>92</v>
@@ -4339,19 +4396,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B43" t="s">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="C43" t="s">
-        <v>834</v>
+        <v>853</v>
       </c>
       <c r="D43" t="s">
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>835</v>
+        <v>854</v>
       </c>
       <c r="F43" t="s">
         <v>189</v>
@@ -4359,13 +4416,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B44" t="s">
-        <v>836</v>
+        <v>855</v>
       </c>
       <c r="C44" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="D44" t="s">
         <v>101</v>
@@ -4374,32 +4431,32 @@
         <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>837</v>
+        <v>856</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B45" t="s">
-        <v>838</v>
+        <v>857</v>
       </c>
       <c r="C45" t="s">
-        <v>839</v>
+        <v>858</v>
       </c>
       <c r="D45" t="s">
         <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>840</v>
+        <v>859</v>
       </c>
       <c r="F45" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B46" t="s">
         <v>344</v>
@@ -4414,24 +4471,24 @@
         <v>189</v>
       </c>
       <c r="F46" t="s">
-        <v>841</v>
+        <v>860</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B47" t="s">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="C47" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="D47" t="s">
         <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>844</v>
+        <v>863</v>
       </c>
       <c r="F47" t="s">
         <v>90</v>
@@ -4439,19 +4496,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B48" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="C48" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="D48" t="s">
         <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>844</v>
+        <v>863</v>
       </c>
       <c r="F48" t="s">
         <v>189</v>
@@ -4459,10 +4516,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B49" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="C49" t="s">
         <v>281</v>
@@ -4471,7 +4528,7 @@
         <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>848</v>
+        <v>867</v>
       </c>
       <c r="F49" t="s">
         <v>189</v>
@@ -4479,19 +4536,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B50" t="s">
         <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="D50" t="s">
         <v>99</v>
       </c>
       <c r="E50" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="F50" t="s">
         <v>90</v>
@@ -4499,19 +4556,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B51" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C51" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D51" t="s">
         <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>850</v>
+        <v>869</v>
       </c>
       <c r="F51" t="s">
         <v>90</v>
@@ -4519,13 +4576,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B52" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="C52" t="s">
-        <v>852</v>
+        <v>871</v>
       </c>
       <c r="D52" t="s">
         <v>131</v>
@@ -4539,13 +4596,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B53" t="s">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="C53" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="D53" t="s">
         <v>131</v>
@@ -4559,13 +4616,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B54" t="s">
-        <v>855</v>
+        <v>874</v>
       </c>
       <c r="C54" t="s">
-        <v>856</v>
+        <v>875</v>
       </c>
       <c r="D54" t="s">
         <v>131</v>
@@ -4579,13 +4636,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B55" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="C55" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="D55" t="s">
         <v>100</v>
@@ -4594,12 +4651,12 @@
         <v>189</v>
       </c>
       <c r="F55" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B56" t="s">
         <v>98</v>
@@ -4619,7 +4676,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B57" t="s">
         <v>91</v>
@@ -4639,7 +4696,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B58" t="s">
         <v>92</v>
@@ -4659,7 +4716,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B59" t="s">
         <v>118</v>
@@ -4679,7 +4736,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B60" t="s">
         <v>119</v>
@@ -4699,7 +4756,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B61" t="s">
         <v>120</v>
@@ -4719,7 +4776,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B62" t="s">
         <v>121</v>
@@ -4739,7 +4796,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B63" t="s">
         <v>122</v>
@@ -4759,7 +4816,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B64" t="s">
         <v>123</v>
@@ -4779,7 +4836,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B65" t="s">
         <v>124</v>
@@ -4799,7 +4856,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B66" t="s">
         <v>125</v>
@@ -4819,7 +4876,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B67" t="s">
         <v>126</v>
@@ -4839,7 +4896,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B68" t="s">
         <v>127</v>
@@ -4859,7 +4916,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B69" t="s">
         <v>128</v>
@@ -4879,7 +4936,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B70" t="s">
         <v>129</v>
@@ -4899,7 +4956,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B71" t="s">
         <v>130</v>
@@ -4919,7 +4976,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B72" t="s">
         <v>98</v>
@@ -4939,7 +4996,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B73" t="s">
         <v>91</v>
@@ -4959,7 +5016,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B74" t="s">
         <v>92</v>
@@ -4979,7 +5036,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B75" t="s">
         <v>344</v>
@@ -4994,12 +5051,12 @@
         <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>860</v>
+        <v>879</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B76" t="s">
         <v>95</v>
@@ -5019,19 +5076,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B77" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="C77" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="D77" t="s">
         <v>99</v>
       </c>
       <c r="E77" t="s">
-        <v>861</v>
+        <v>880</v>
       </c>
       <c r="F77" t="s">
         <v>90</v>
@@ -5039,19 +5096,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B78" t="s">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="C78" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="D78" t="s">
         <v>99</v>
       </c>
       <c r="E78" t="s">
-        <v>862</v>
+        <v>881</v>
       </c>
       <c r="F78" t="s">
         <v>90</v>
@@ -5059,19 +5116,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B79" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="C79" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="D79" t="s">
         <v>100</v>
       </c>
       <c r="E79" t="s">
-        <v>862</v>
+        <v>881</v>
       </c>
       <c r="F79" t="s">
         <v>189</v>
@@ -5079,13 +5136,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B80" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="C80" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="D80" t="s">
         <v>101</v>
@@ -5094,18 +5151,18 @@
         <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B81" t="s">
-        <v>864</v>
+        <v>883</v>
       </c>
       <c r="C81" t="s">
-        <v>865</v>
+        <v>884</v>
       </c>
       <c r="D81" t="s">
         <v>131</v>
@@ -5119,13 +5176,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B82" t="s">
-        <v>866</v>
+        <v>885</v>
       </c>
       <c r="C82" t="s">
-        <v>867</v>
+        <v>886</v>
       </c>
       <c r="D82" t="s">
         <v>131</v>
@@ -5139,7 +5196,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B83" t="s">
         <v>98</v>
@@ -5159,7 +5216,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B84" t="s">
         <v>91</v>
@@ -5179,7 +5236,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B85" t="s">
         <v>92</v>
@@ -5199,7 +5256,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B86" t="s">
         <v>145</v>
@@ -5219,7 +5276,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B87" t="s">
         <v>146</v>
@@ -5239,7 +5296,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B88" t="s">
         <v>98</v>
@@ -5259,7 +5316,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -5279,7 +5336,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -5299,19 +5356,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B91" t="s">
         <v>418</v>
       </c>
       <c r="C91" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="D91" t="s">
         <v>99</v>
       </c>
       <c r="E91" t="s">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="F91" t="s">
         <v>189</v>
@@ -5319,10 +5376,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B92" t="s">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="C92" t="s">
         <v>285</v>
@@ -5339,13 +5396,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B93" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
       <c r="C93" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="D93" t="s">
         <v>131</v>
@@ -5359,13 +5416,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B94" t="s">
-        <v>875</v>
+        <v>894</v>
       </c>
       <c r="C94" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="D94" t="s">
         <v>131</v>
@@ -5379,7 +5436,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -5399,7 +5456,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B96" t="s">
         <v>91</v>
@@ -5419,7 +5476,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B97" t="s">
         <v>92</v>
@@ -5439,13 +5496,13 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B98" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="C98" t="s">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="D98" t="s">
         <v>99</v>
@@ -5459,13 +5516,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B99" t="s">
-        <v>880</v>
+        <v>899</v>
       </c>
       <c r="C99" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="D99" t="s">
         <v>99</v>
@@ -5479,13 +5536,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B100" t="s">
-        <v>882</v>
+        <v>901</v>
       </c>
       <c r="C100" t="s">
-        <v>883</v>
+        <v>902</v>
       </c>
       <c r="D100" t="s">
         <v>99</v>
@@ -5499,13 +5556,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B101" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="C101" t="s">
-        <v>885</v>
+        <v>904</v>
       </c>
       <c r="D101" t="s">
         <v>131</v>
@@ -5519,13 +5576,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B102" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="C102" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="D102" t="s">
         <v>131</v>
@@ -5539,7 +5596,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B103" t="s">
         <v>98</v>
@@ -5559,7 +5616,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B104" t="s">
         <v>91</v>
@@ -5579,7 +5636,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B105" t="s">
         <v>92</v>
@@ -5599,7 +5656,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B106" t="s">
         <v>149</v>
@@ -5619,7 +5676,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B107" t="s">
         <v>93</v>
@@ -5639,7 +5696,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B108" t="s">
         <v>150</v>
@@ -5659,7 +5716,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B109" t="s">
         <v>151</v>
@@ -5679,7 +5736,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="B110" t="s">
         <v>98</v>
@@ -5699,7 +5756,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B111" t="s">
         <v>91</v>
@@ -5719,7 +5776,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B112" t="s">
         <v>92</v>
@@ -5739,7 +5796,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B113" t="s">
         <v>215</v>
@@ -5759,7 +5816,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B114" t="s">
         <v>216</v>
@@ -5779,7 +5836,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B115" t="s">
         <v>217</v>
@@ -5799,7 +5856,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B116" t="s">
         <v>91</v>
@@ -5819,7 +5876,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B117" t="s">
         <v>103</v>
@@ -5839,13 +5896,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B118" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="C118" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="D118" t="s">
         <v>100</v>
@@ -5859,13 +5916,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B119" t="s">
-        <v>892</v>
+        <v>911</v>
       </c>
       <c r="C119" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="D119" t="s">
         <v>131</v>
@@ -5879,13 +5936,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B120" t="s">
-        <v>894</v>
+        <v>913</v>
       </c>
       <c r="C120" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="D120" t="s">
         <v>131</v>
@@ -5899,13 +5956,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B121" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="C121" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="D121" t="s">
         <v>131</v>
@@ -5919,13 +5976,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B122" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="C122" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="D122" t="s">
         <v>131</v>
@@ -5939,13 +5996,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="B123" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
       <c r="C123" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="D123" t="s">
         <v>99</v>
@@ -5959,10 +6016,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B124" t="s">
-        <v>757</v>
+        <v>776</v>
       </c>
       <c r="C124" t="s">
         <v>102</v>
@@ -5979,7 +6036,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B125" t="s">
         <v>103</v>
@@ -5999,13 +6056,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B126" t="s">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="C126" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="D126" t="s">
         <v>101</v>
@@ -6014,18 +6071,18 @@
         <v>189</v>
       </c>
       <c r="F126" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B127" t="s">
         <v>93</v>
       </c>
       <c r="C127" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="D127" t="s">
         <v>99</v>
@@ -6039,16 +6096,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B128" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="C128" t="s">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="D128" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="E128" t="s">
         <v>189</v>
@@ -6059,16 +6116,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B129" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="C129" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="D129" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="E129" t="s">
         <v>189</v>
@@ -6079,16 +6136,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B130" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="C130" t="s">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="D130" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="E130" t="s">
         <v>189</v>
@@ -6099,13 +6156,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B131" t="s">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="C131" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="D131" t="s">
         <v>99</v>
@@ -6119,7 +6176,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B132" t="s">
         <v>98</v>
@@ -6139,7 +6196,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B133" t="s">
         <v>91</v>
@@ -6159,7 +6216,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B134" t="s">
         <v>92</v>
@@ -6179,7 +6236,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B135" t="s">
         <v>93</v>
@@ -6199,10 +6256,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B136" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="C136" t="s">
         <v>16</v>
@@ -6214,12 +6271,12 @@
         <v>189</v>
       </c>
       <c r="F136" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B137" t="s">
         <v>95</v>
@@ -6239,13 +6296,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B138" t="s">
-        <v>777</v>
+        <v>796</v>
       </c>
       <c r="C138" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
       <c r="D138" t="s">
         <v>131</v>
@@ -6259,13 +6316,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B139" t="s">
-        <v>778</v>
+        <v>797</v>
       </c>
       <c r="C139" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="D139" t="s">
         <v>131</v>
@@ -6279,13 +6336,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B140" t="s">
-        <v>779</v>
+        <v>798</v>
       </c>
       <c r="C140" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="D140" t="s">
         <v>100</v>
@@ -6294,18 +6351,18 @@
         <v>189</v>
       </c>
       <c r="F140" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B141" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
       <c r="C141" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="D141" t="s">
         <v>99</v>
@@ -6319,7 +6376,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="B142" t="s">
         <v>98</v>
@@ -6370,13 +6427,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>837</v>
+        <v>856</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>841</v>
+        <v>860</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>90</v>
@@ -6393,7 +6450,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6405,43 +6462,43 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>836</v>
+        <v>855</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>838</v>
+        <v>857</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>344</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>855</v>
+        <v>874</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>98</v>
@@ -6505,43 +6562,43 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>834</v>
+        <v>853</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>839</v>
+        <v>858</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>345</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>281</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>852</v>
+        <v>871</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>856</v>
+        <v>875</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>108</v>
@@ -6555,7 +6612,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -6570,7 +6627,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -6591,7 +6648,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>189</v>
@@ -6605,7 +6662,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>909</v>
+        <v>928</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -6620,7 +6677,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -6641,7 +6698,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>189</v>
@@ -6655,7 +6712,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -6670,7 +6727,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -6691,7 +6748,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>189</v>
@@ -6705,7 +6762,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -6720,7 +6777,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -6741,7 +6798,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>189</v>
@@ -6755,7 +6812,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>912</v>
+        <v>931</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -6770,7 +6827,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -6791,7 +6848,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>189</v>
@@ -6805,7 +6862,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>913</v>
+        <v>932</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -6820,7 +6877,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -6841,7 +6898,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>189</v>
@@ -6855,7 +6912,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>915</v>
+        <v>934</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -6870,7 +6927,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -6891,7 +6948,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>189</v>
@@ -6905,7 +6962,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>916</v>
+        <v>935</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -6920,7 +6977,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -6941,7 +6998,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>189</v>
@@ -6955,7 +7012,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>917</v>
+        <v>936</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -6970,7 +7027,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -6991,7 +7048,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>189</v>
@@ -7005,7 +7062,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>918</v>
+        <v>937</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7020,7 +7077,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -7041,7 +7098,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>189</v>
@@ -7055,7 +7112,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>919</v>
+        <v>938</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7070,7 +7127,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7091,7 +7148,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>189</v>
@@ -7105,7 +7162,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7120,7 +7177,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7141,7 +7198,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>189</v>
@@ -7155,7 +7212,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>922</v>
+        <v>941</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7170,7 +7227,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7191,7 +7248,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>189</v>
@@ -7205,7 +7262,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>923</v>
+        <v>942</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7220,7 +7277,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7241,7 +7298,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>189</v>
@@ -7255,7 +7312,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7270,7 +7327,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7291,7 +7348,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>189</v>
@@ -7305,7 +7362,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>925</v>
+        <v>944</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7320,7 +7377,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7341,7 +7398,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>189</v>
@@ -7355,7 +7412,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>927</v>
+        <v>946</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7370,7 +7427,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7391,7 +7448,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>189</v>
@@ -7405,7 +7462,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>928</v>
+        <v>947</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7420,7 +7477,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7441,7 +7498,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>189</v>
@@ -7455,7 +7512,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>929</v>
+        <v>948</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7470,7 +7527,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7491,7 +7548,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>189</v>
@@ -7505,7 +7562,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7520,7 +7577,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -7541,7 +7598,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>189</v>
@@ -7555,7 +7612,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -7570,7 +7627,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -7591,7 +7648,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>189</v>
@@ -7605,7 +7662,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>933</v>
+        <v>952</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -7620,7 +7677,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -7641,7 +7698,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>189</v>
@@ -7655,7 +7712,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>934</v>
+        <v>953</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -7670,7 +7727,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -7691,7 +7748,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>189</v>
@@ -7705,7 +7762,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -7720,7 +7777,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -7741,7 +7798,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>189</v>
@@ -7755,7 +7812,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>936</v>
+        <v>955</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -7770,7 +7827,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -7791,7 +7848,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>189</v>
@@ -7805,7 +7862,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>937</v>
+        <v>956</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -7820,7 +7877,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -7841,7 +7898,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>189</v>
@@ -7855,7 +7912,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -7870,7 +7927,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -7891,7 +7948,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>189</v>
@@ -7905,7 +7962,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -7920,7 +7977,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -7941,7 +7998,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>189</v>
@@ -7955,7 +8012,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -7970,7 +8027,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -7991,7 +8048,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>189</v>
@@ -8005,7 +8062,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8020,7 +8077,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -8041,7 +8098,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>189</v>
@@ -8055,7 +8112,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>942</v>
+        <v>961</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8070,7 +8127,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8091,7 +8148,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>189</v>
@@ -8105,7 +8162,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>943</v>
+        <v>962</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8120,7 +8177,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8141,7 +8198,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>189</v>
@@ -8155,7 +8212,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>944</v>
+        <v>963</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8170,7 +8227,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8191,7 +8248,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>189</v>
@@ -8205,7 +8262,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>945</v>
+        <v>964</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8220,7 +8277,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8241,7 +8298,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>189</v>
@@ -8255,7 +8312,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8270,7 +8327,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8291,7 +8348,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>189</v>
@@ -8305,7 +8362,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8320,7 +8377,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8341,7 +8398,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>189</v>
@@ -8355,7 +8412,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>948</v>
+        <v>967</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8370,7 +8427,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8391,7 +8448,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>189</v>
@@ -8405,7 +8462,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>949</v>
+        <v>968</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8420,7 +8477,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8441,7 +8498,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>189</v>
@@ -8455,7 +8512,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>950</v>
+        <v>969</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8470,7 +8527,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8491,7 +8548,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>189</v>
@@ -8505,7 +8562,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>951</v>
+        <v>970</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8520,7 +8577,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -8541,7 +8598,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>189</v>
@@ -8555,7 +8612,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>952</v>
+        <v>971</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -8570,7 +8627,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -8591,7 +8648,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>189</v>
@@ -8605,7 +8662,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>953</v>
+        <v>972</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -8620,7 +8677,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -8641,7 +8698,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>189</v>
@@ -8655,7 +8712,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -8670,7 +8727,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -8691,7 +8748,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>189</v>
@@ -8705,7 +8762,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>955</v>
+        <v>974</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -8720,7 +8777,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -8741,7 +8798,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>189</v>
@@ -8755,7 +8812,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>956</v>
+        <v>975</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -8770,7 +8827,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -8791,7 +8848,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>189</v>
@@ -8805,7 +8862,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>957</v>
+        <v>976</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -8820,7 +8877,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -8841,7 +8898,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>189</v>
@@ -8855,7 +8912,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>958</v>
+        <v>977</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -8870,7 +8927,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -8891,7 +8948,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>189</v>
@@ -8905,7 +8962,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>959</v>
+        <v>978</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -8920,7 +8977,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -8941,7 +8998,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>189</v>
@@ -8955,7 +9012,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>960</v>
+        <v>979</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -8970,7 +9027,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -8991,7 +9048,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>189</v>
@@ -9005,7 +9062,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>961</v>
+        <v>980</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9020,7 +9077,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -9041,7 +9098,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>189</v>
@@ -9055,7 +9112,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>962</v>
+        <v>981</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9070,7 +9127,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9091,7 +9148,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>189</v>
@@ -9105,7 +9162,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>963</v>
+        <v>982</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9120,7 +9177,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9141,7 +9198,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>189</v>
@@ -9155,7 +9212,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>964</v>
+        <v>983</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9170,7 +9227,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9191,7 +9248,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>189</v>
@@ -9205,7 +9262,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>965</v>
+        <v>984</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9220,7 +9277,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9241,7 +9298,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>189</v>
@@ -9255,7 +9312,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>966</v>
+        <v>985</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9270,7 +9327,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9291,7 +9348,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>189</v>
@@ -9305,7 +9362,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>967</v>
+        <v>986</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9320,7 +9377,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9341,7 +9398,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>189</v>
@@ -9355,7 +9412,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>968</v>
+        <v>987</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9370,7 +9427,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9391,7 +9448,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>189</v>
@@ -9405,7 +9462,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>969</v>
+        <v>988</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9420,7 +9477,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9441,7 +9498,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>189</v>
@@ -9455,7 +9512,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>970</v>
+        <v>989</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9470,7 +9527,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9491,7 +9548,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>189</v>
@@ -9505,7 +9562,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>971</v>
+        <v>990</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9520,7 +9577,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -9541,7 +9598,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>189</v>
@@ -9555,7 +9612,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>972</v>
+        <v>991</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -9570,7 +9627,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -9591,7 +9648,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>189</v>
@@ -9605,7 +9662,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>973</v>
+        <v>992</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -9620,7 +9677,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -9641,7 +9698,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>189</v>
@@ -9655,7 +9712,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>974</v>
+        <v>993</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -9670,7 +9727,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -9691,7 +9748,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>189</v>
@@ -9705,7 +9762,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>975</v>
+        <v>994</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -9720,7 +9777,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -9741,7 +9798,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>189</v>
@@ -9755,7 +9812,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>976</v>
+        <v>995</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -9770,7 +9827,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -9791,7 +9848,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>189</v>
@@ -9805,7 +9862,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>977</v>
+        <v>996</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -9820,7 +9877,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -9841,7 +9898,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>189</v>
@@ -9855,7 +9912,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>978</v>
+        <v>997</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -9870,7 +9927,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -9891,7 +9948,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>189</v>
@@ -9905,7 +9962,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -9920,7 +9977,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -9941,7 +9998,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>189</v>
@@ -9955,7 +10012,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>980</v>
+        <v>999</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -9970,7 +10027,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -9991,7 +10048,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>189</v>
@@ -10005,7 +10062,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>981</v>
+        <v>1000</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10020,7 +10077,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -10041,7 +10098,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>189</v>
@@ -10055,7 +10112,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>982</v>
+        <v>1001</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10070,7 +10127,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10091,7 +10148,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>189</v>
@@ -10105,7 +10162,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>983</v>
+        <v>1002</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10120,7 +10177,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10141,7 +10198,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>189</v>
@@ -10155,7 +10212,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>984</v>
+        <v>1003</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10170,7 +10227,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10191,7 +10248,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>189</v>
@@ -10205,7 +10262,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>985</v>
+        <v>1004</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10220,7 +10277,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10241,7 +10298,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>189</v>
@@ -10255,7 +10312,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>986</v>
+        <v>1005</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10270,7 +10327,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10291,7 +10348,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>189</v>
@@ -10503,7 +10560,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>860</v>
+        <v>879</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>90</v>
@@ -10516,7 +10573,7 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -10536,22 +10593,22 @@
         <v>95</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>864</v>
+        <v>883</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>866</v>
+        <v>885</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>98</v>
@@ -10606,22 +10663,22 @@
         <v>105</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>865</v>
+        <v>884</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>867</v>
+        <v>886</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>108</v>
@@ -10647,7 +10704,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -10682,7 +10739,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -10717,7 +10774,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -10752,7 +10809,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -10787,7 +10844,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -10822,7 +10879,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -10857,7 +10914,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -10892,7 +10949,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -10927,7 +10984,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -12759,7 +12816,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E428"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -20032,6 +20089,159 @@
       </c>
       <c r="E428" t="s">
         <v>738</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>425</v>
+      </c>
+      <c r="B429">
+        <v>41038</v>
+      </c>
+      <c r="C429" t="s">
+        <v>756</v>
+      </c>
+      <c r="D429" t="s">
+        <v>757</v>
+      </c>
+      <c r="E429" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>426</v>
+      </c>
+      <c r="B430">
+        <v>41039</v>
+      </c>
+      <c r="C430" t="s">
+        <v>759</v>
+      </c>
+      <c r="D430" t="s">
+        <v>760</v>
+      </c>
+      <c r="E430" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>427</v>
+      </c>
+      <c r="B431">
+        <v>41040</v>
+      </c>
+      <c r="C431" t="s">
+        <v>761</v>
+      </c>
+      <c r="D431" t="s">
+        <v>762</v>
+      </c>
+      <c r="E431" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>428</v>
+      </c>
+      <c r="B432">
+        <v>41041</v>
+      </c>
+      <c r="C432" t="s">
+        <v>763</v>
+      </c>
+      <c r="D432" t="s">
+        <v>764</v>
+      </c>
+      <c r="E432" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>429</v>
+      </c>
+      <c r="B433">
+        <v>41042</v>
+      </c>
+      <c r="C433" t="s">
+        <v>765</v>
+      </c>
+      <c r="D433" t="s">
+        <v>766</v>
+      </c>
+      <c r="E433" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>430</v>
+      </c>
+      <c r="B434">
+        <v>41043</v>
+      </c>
+      <c r="C434" t="s">
+        <v>767</v>
+      </c>
+      <c r="D434" t="s">
+        <v>768</v>
+      </c>
+      <c r="E434" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>431</v>
+      </c>
+      <c r="B435">
+        <v>41044</v>
+      </c>
+      <c r="C435" t="s">
+        <v>769</v>
+      </c>
+      <c r="D435" t="s">
+        <v>770</v>
+      </c>
+      <c r="E435" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>432</v>
+      </c>
+      <c r="B436">
+        <v>41045</v>
+      </c>
+      <c r="C436" t="s">
+        <v>771</v>
+      </c>
+      <c r="D436" t="s">
+        <v>772</v>
+      </c>
+      <c r="E436" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>433</v>
+      </c>
+      <c r="B437">
+        <v>41046</v>
+      </c>
+      <c r="C437" t="s">
+        <v>773</v>
+      </c>
+      <c r="D437" t="s">
+        <v>774</v>
+      </c>
+      <c r="E437" t="s">
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -20071,22 +20281,22 @@
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>892</v>
+        <v>911</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>894</v>
+        <v>913</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -20123,22 +20333,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -20149,7 +20359,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -20175,7 +20385,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>901</v>
+        <v>920</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -20201,7 +20411,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -20227,7 +20437,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -20253,7 +20463,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -20279,7 +20489,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -20305,7 +20515,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -20349,7 +20559,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>90</v>
@@ -20362,28 +20572,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>757</v>
+        <v>776</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>93</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>98</v>
@@ -20403,13 +20613,13 @@
         <v>99</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>99</v>
@@ -20426,22 +20636,22 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>108</v>
@@ -20473,7 +20683,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>770</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -20502,7 +20712,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>771</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -20589,7 +20799,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -20618,7 +20828,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>773</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>
@@ -20654,7 +20864,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>803</v>
+        <v>822</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -20676,13 +20886,13 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>798</v>
+        <v>817</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>383</v>
@@ -20691,25 +20901,25 @@
         <v>386</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>806</v>
+        <v>825</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>812</v>
+        <v>831</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>814</v>
+        <v>833</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>816</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -20764,40 +20974,40 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>805</v>
+        <v>824</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>807</v>
+        <v>826</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>811</v>
+        <v>830</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>815</v>
+        <v>834</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>817</v>
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -29626,7 +29836,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>90</v>
@@ -29634,7 +29844,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -29650,22 +29860,22 @@
         <v>93</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>777</v>
+        <v>796</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>778</v>
+        <v>797</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>779</v>
+        <v>798</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>98</v>
@@ -29720,16 +29930,16 @@
         <v>105</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>108</v>
@@ -29758,13 +29968,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>786</v>
+        <v>805</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -29790,13 +30000,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>787</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -29822,13 +30032,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>788</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -29854,13 +30064,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -29886,13 +30096,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>790</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -29927,13 +30137,13 @@
         <v>90</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -29946,7 +30156,7 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>280</v>
@@ -29955,19 +30165,19 @@
         <v>95</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>827</v>
+        <v>846</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>829</v>
+        <v>848</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>284</v>
@@ -30016,25 +30226,25 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>821</v>
+        <v>840</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>281</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>153</v>
@@ -32000,13 +32210,13 @@
         <v>418</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>875</v>
+        <v>894</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>98</v>
@@ -32043,16 +32253,16 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>285</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>108</v>
@@ -32327,19 +32537,19 @@
         <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>880</v>
+        <v>899</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>882</v>
+        <v>901</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>98</v>
@@ -32379,19 +32589,19 @@
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>883</v>
+        <v>902</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>885</v>
+        <v>904</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>108</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4047" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="1071">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2482,6 +2482,24 @@
   </si>
   <si>
     <t>재화 획득량 조정</t>
+  </si>
+  <si>
+    <t>Re: NOVA</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>NONLINEAR OSCILLATION VOID APPARATUS</t>
+  </si>
+  <si>
+    <t>Created by ______</t>
+  </si>
+  <si>
+    <t>게임 제목 "Re: NOVA" 공개</t>
+  </si>
+  <si>
+    <t>로딩 화면 추가</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3734,27 +3752,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B1" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C1" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="D1" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="E1" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="F1" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B2" t="s">
         <v>105</v>
@@ -3774,7 +3792,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -3794,13 +3812,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B4" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C4" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -3814,13 +3832,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C5" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -3834,10 +3852,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B6" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3849,18 +3867,18 @@
         <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B7" t="s">
         <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3874,13 +3892,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -3894,13 +3912,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B9" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C9" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -3914,13 +3932,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B10" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C10" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -3934,13 +3952,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B11" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C11" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -3954,13 +3972,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B12" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C12" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -3974,13 +3992,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B13" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C13" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -3994,13 +4012,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4014,19 +4032,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B15" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C15" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="F15" t="s">
         <v>203</v>
@@ -4034,7 +4052,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
@@ -4054,7 +4072,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
@@ -4074,13 +4092,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B18" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="C18" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -4094,7 +4112,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B19" t="s">
         <v>297</v>
@@ -4114,13 +4132,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -4134,13 +4152,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B21" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C21" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -4154,13 +4172,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B22" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C22" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -4169,15 +4187,15 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B23" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4189,18 +4207,18 @@
         <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B24" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="C24" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -4209,15 +4227,15 @@
         <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B25" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
@@ -4234,7 +4252,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B26" t="s">
         <v>301</v>
@@ -4254,7 +4272,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B27" t="s">
         <v>105</v>
@@ -4274,7 +4292,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B28" t="s">
         <v>106</v>
@@ -4294,7 +4312,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
@@ -4314,7 +4332,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -4334,7 +4352,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -4354,7 +4372,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
@@ -4374,7 +4392,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -4394,7 +4412,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B34" t="s">
         <v>112</v>
@@ -4414,7 +4432,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B35" t="s">
         <v>105</v>
@@ -4434,7 +4452,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
@@ -4454,7 +4472,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -4474,7 +4492,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -4494,7 +4512,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -4514,7 +4532,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B40" t="s">
         <v>112</v>
@@ -4534,7 +4552,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
@@ -4554,7 +4572,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B42" t="s">
         <v>106</v>
@@ -4574,19 +4592,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B43" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C43" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D43" t="s">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="F43" t="s">
         <v>203</v>
@@ -4594,13 +4612,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B44" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C44" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4609,32 +4627,32 @@
         <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B45" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="C45" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="F45" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B46" t="s">
         <v>361</v>
@@ -4649,24 +4667,24 @@
         <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B47" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="C47" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F47" t="s">
         <v>104</v>
@@ -4674,19 +4692,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B48" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C48" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="D48" t="s">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F48" t="s">
         <v>203</v>
@@ -4694,10 +4712,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B49" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C49" t="s">
         <v>298</v>
@@ -4706,7 +4724,7 @@
         <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="F49" t="s">
         <v>203</v>
@@ -4714,19 +4732,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D50" t="s">
         <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="F50" t="s">
         <v>104</v>
@@ -4734,19 +4752,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B51" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C51" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D51" t="s">
         <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
@@ -4754,13 +4772,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B52" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="C52" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -4774,13 +4792,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B53" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="C53" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -4794,13 +4812,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B54" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="C54" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D54" t="s">
         <v>145</v>
@@ -4814,13 +4832,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B55" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="C55" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D55" t="s">
         <v>114</v>
@@ -4829,12 +4847,12 @@
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -4854,7 +4872,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
@@ -4874,7 +4892,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B58" t="s">
         <v>106</v>
@@ -4894,7 +4912,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B59" t="s">
         <v>132</v>
@@ -4914,7 +4932,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -4934,7 +4952,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B61" t="s">
         <v>134</v>
@@ -4954,7 +4972,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B62" t="s">
         <v>135</v>
@@ -4974,7 +4992,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B63" t="s">
         <v>136</v>
@@ -4994,7 +5012,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B64" t="s">
         <v>137</v>
@@ -5014,7 +5032,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -5034,7 +5052,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -5054,7 +5072,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B67" t="s">
         <v>140</v>
@@ -5074,7 +5092,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
@@ -5094,7 +5112,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B69" t="s">
         <v>142</v>
@@ -5114,7 +5132,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B70" t="s">
         <v>143</v>
@@ -5134,7 +5152,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B71" t="s">
         <v>144</v>
@@ -5154,7 +5172,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B72" t="s">
         <v>112</v>
@@ -5174,7 +5192,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
@@ -5194,7 +5212,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
@@ -5214,7 +5232,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B75" t="s">
         <v>361</v>
@@ -5229,12 +5247,12 @@
         <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B76" t="s">
         <v>109</v>
@@ -5254,19 +5272,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B77" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C77" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="F77" t="s">
         <v>104</v>
@@ -5274,19 +5292,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B78" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="C78" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="F78" t="s">
         <v>104</v>
@@ -5294,19 +5312,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B79" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C79" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="D79" t="s">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="F79" t="s">
         <v>203</v>
@@ -5314,13 +5332,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B80" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C80" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="D80" t="s">
         <v>115</v>
@@ -5329,18 +5347,18 @@
         <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B81" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="C81" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -5354,13 +5372,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B82" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C82" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -5374,7 +5392,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -5394,10 +5412,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B84" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -5409,12 +5427,12 @@
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -5434,7 +5452,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B86" t="s">
         <v>106</v>
@@ -5454,7 +5472,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -5474,7 +5492,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B88" t="s">
         <v>160</v>
@@ -5494,7 +5512,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B89" t="s">
         <v>112</v>
@@ -5514,7 +5532,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B90" t="s">
         <v>105</v>
@@ -5534,7 +5552,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B91" t="s">
         <v>106</v>
@@ -5554,19 +5572,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B92" t="s">
         <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="F92" t="s">
         <v>203</v>
@@ -5574,10 +5592,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B93" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="C93" t="s">
         <v>302</v>
@@ -5594,13 +5612,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B94" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="C94" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D94" t="s">
         <v>145</v>
@@ -5614,13 +5632,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B95" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C95" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
@@ -5634,7 +5652,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B96" t="s">
         <v>112</v>
@@ -5654,7 +5672,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B97" t="s">
         <v>105</v>
@@ -5674,7 +5692,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B98" t="s">
         <v>106</v>
@@ -5694,13 +5712,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B99" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="C99" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
@@ -5714,13 +5732,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B100" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C100" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
@@ -5734,13 +5752,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B101" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C101" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
@@ -5754,13 +5772,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B102" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="C102" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="D102" t="s">
         <v>113</v>
@@ -5774,13 +5792,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B103" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="C103" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D103" t="s">
         <v>113</v>
@@ -5794,13 +5812,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B104" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="C104" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="D104" t="s">
         <v>113</v>
@@ -5814,7 +5832,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B105" t="s">
         <v>112</v>
@@ -5877,10 +5895,10 @@
         <v>800</v>
       </c>
       <c r="B108" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="C108" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -5897,10 +5915,10 @@
         <v>800</v>
       </c>
       <c r="B109" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="C109" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -5920,7 +5938,7 @@
         <v>234</v>
       </c>
       <c r="C110" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="D110" t="s">
         <v>115</v>
@@ -5929,7 +5947,7 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5937,10 +5955,10 @@
         <v>800</v>
       </c>
       <c r="B111" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C111" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D111" t="s">
         <v>113</v>
@@ -5957,10 +5975,10 @@
         <v>800</v>
       </c>
       <c r="B112" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C112" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D112" t="s">
         <v>113</v>
@@ -5974,7 +5992,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B113" t="s">
         <v>105</v>
@@ -5994,7 +6012,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B114" t="s">
         <v>106</v>
@@ -6014,7 +6032,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -6034,7 +6052,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B116" t="s">
         <v>107</v>
@@ -6054,7 +6072,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B117" t="s">
         <v>164</v>
@@ -6074,7 +6092,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B118" t="s">
         <v>165</v>
@@ -6094,7 +6112,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B119" t="s">
         <v>112</v>
@@ -6114,7 +6132,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
@@ -6134,7 +6152,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B121" t="s">
         <v>106</v>
@@ -6154,7 +6172,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B122" t="s">
         <v>232</v>
@@ -6174,7 +6192,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B123" t="s">
         <v>233</v>
@@ -6194,7 +6212,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B124" t="s">
         <v>234</v>
@@ -6214,7 +6232,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B125" t="s">
         <v>105</v>
@@ -6234,7 +6252,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -6254,13 +6272,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B127" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="C127" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D127" t="s">
         <v>114</v>
@@ -6274,13 +6292,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B128" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C128" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -6294,13 +6312,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B129" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="C129" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -6314,13 +6332,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B130" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C130" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -6334,13 +6352,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B131" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="C131" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -6354,13 +6372,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B132" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C132" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D132" t="s">
         <v>113</v>
@@ -6374,10 +6392,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B133" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C133" t="s">
         <v>116</v>
@@ -6394,7 +6412,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B134" t="s">
         <v>117</v>
@@ -6414,13 +6432,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B135" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C135" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -6429,18 +6447,18 @@
         <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B136" t="s">
         <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D136" t="s">
         <v>113</v>
@@ -6454,16 +6472,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B137" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C137" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="D137" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E137" t="s">
         <v>203</v>
@@ -6474,16 +6492,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B138" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C138" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D138" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E138" t="s">
         <v>203</v>
@@ -6494,16 +6512,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B139" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C139" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D139" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E139" t="s">
         <v>203</v>
@@ -6514,13 +6532,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B140" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C140" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D140" t="s">
         <v>113</v>
@@ -6534,7 +6552,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B141" t="s">
         <v>112</v>
@@ -6554,7 +6572,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B142" t="s">
         <v>105</v>
@@ -6574,7 +6592,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B143" t="s">
         <v>106</v>
@@ -6594,7 +6612,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B144" t="s">
         <v>107</v>
@@ -6614,10 +6632,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B145" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -6629,12 +6647,12 @@
         <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B146" t="s">
         <v>109</v>
@@ -6654,13 +6672,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B147" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C147" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D147" t="s">
         <v>145</v>
@@ -6674,13 +6692,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B148" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C148" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="D148" t="s">
         <v>145</v>
@@ -6694,13 +6712,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B149" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C149" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D149" t="s">
         <v>114</v>
@@ -6709,18 +6727,18 @@
         <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B150" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C150" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D150" t="s">
         <v>113</v>
@@ -6734,7 +6752,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B151" t="s">
         <v>112</v>
@@ -6785,13 +6803,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>104</v>
@@ -6808,7 +6826,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6820,43 +6838,43 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>361</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>112</v>
@@ -6920,43 +6938,43 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>362</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>122</v>
@@ -6970,7 +6988,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -6985,7 +7003,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -7006,7 +7024,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>203</v>
@@ -7020,7 +7038,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7035,7 +7053,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -7056,7 +7074,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>203</v>
@@ -7070,7 +7088,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -7085,7 +7103,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -7106,7 +7124,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>203</v>
@@ -7120,7 +7138,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -7135,7 +7153,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -7156,7 +7174,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>203</v>
@@ -7170,7 +7188,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -7185,7 +7203,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -7206,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>203</v>
@@ -7220,7 +7238,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -7235,7 +7253,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -7256,7 +7274,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>203</v>
@@ -7270,7 +7288,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -7285,7 +7303,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -7306,7 +7324,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>203</v>
@@ -7320,7 +7338,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -7335,7 +7353,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -7356,7 +7374,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>203</v>
@@ -7370,7 +7388,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -7385,7 +7403,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -7406,7 +7424,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>203</v>
@@ -7420,7 +7438,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7435,7 +7453,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -7456,7 +7474,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>203</v>
@@ -7470,7 +7488,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7485,7 +7503,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7506,7 +7524,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>203</v>
@@ -7520,7 +7538,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7535,7 +7553,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7556,7 +7574,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>203</v>
@@ -7570,7 +7588,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7585,7 +7603,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7606,7 +7624,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>203</v>
@@ -7620,7 +7638,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7635,7 +7653,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7656,7 +7674,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>203</v>
@@ -7670,7 +7688,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7685,7 +7703,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7706,7 +7724,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>203</v>
@@ -7720,7 +7738,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7735,7 +7753,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7756,7 +7774,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>203</v>
@@ -7770,7 +7788,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7785,7 +7803,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7806,7 +7824,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>203</v>
@@ -7820,7 +7838,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7835,7 +7853,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7856,7 +7874,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>203</v>
@@ -7870,7 +7888,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7885,7 +7903,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7906,7 +7924,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>203</v>
@@ -7920,7 +7938,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7935,7 +7953,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -7956,7 +7974,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>203</v>
@@ -7970,7 +7988,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -7985,7 +8003,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -8006,7 +8024,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>203</v>
@@ -8020,7 +8038,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8035,7 +8053,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -8056,7 +8074,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>203</v>
@@ -8070,7 +8088,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -8085,7 +8103,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -8106,7 +8124,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>203</v>
@@ -8120,7 +8138,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -8135,7 +8153,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -8156,7 +8174,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>203</v>
@@ -8170,7 +8188,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -8185,7 +8203,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -8206,7 +8224,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>203</v>
@@ -8220,7 +8238,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -8235,7 +8253,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -8256,7 +8274,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>203</v>
@@ -8270,7 +8288,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -8285,7 +8303,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -8306,7 +8324,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>203</v>
@@ -8320,7 +8338,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -8335,7 +8353,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -8356,7 +8374,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>203</v>
@@ -8370,7 +8388,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -8385,7 +8403,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -8406,7 +8424,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>203</v>
@@ -8420,7 +8438,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8435,7 +8453,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -8456,7 +8474,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>203</v>
@@ -8470,7 +8488,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8485,7 +8503,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8506,7 +8524,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>203</v>
@@ -8520,7 +8538,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8535,7 +8553,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8556,7 +8574,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>203</v>
@@ -8570,7 +8588,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8585,7 +8603,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8606,7 +8624,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>203</v>
@@ -8620,7 +8638,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8635,7 +8653,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8656,7 +8674,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>203</v>
@@ -8670,7 +8688,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8685,7 +8703,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8706,7 +8724,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>203</v>
@@ -8720,7 +8738,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8735,7 +8753,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8756,7 +8774,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>203</v>
@@ -8770,7 +8788,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8785,7 +8803,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8806,7 +8824,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>203</v>
@@ -8820,7 +8838,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8835,7 +8853,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8856,7 +8874,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>203</v>
@@ -8870,7 +8888,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8885,7 +8903,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8906,7 +8924,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>203</v>
@@ -8920,7 +8938,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8935,7 +8953,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -8956,7 +8974,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>203</v>
@@ -8970,7 +8988,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -8985,7 +9003,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -9006,7 +9024,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>203</v>
@@ -9020,7 +9038,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9035,7 +9053,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -9056,7 +9074,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>203</v>
@@ -9070,7 +9088,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -9085,7 +9103,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -9106,7 +9124,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>203</v>
@@ -9120,7 +9138,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -9135,7 +9153,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -9156,7 +9174,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>203</v>
@@ -9170,7 +9188,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -9185,7 +9203,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -9206,7 +9224,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>203</v>
@@ -9220,7 +9238,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -9235,7 +9253,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -9256,7 +9274,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>203</v>
@@ -9270,7 +9288,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -9285,7 +9303,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -9306,7 +9324,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>203</v>
@@ -9320,7 +9338,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -9335,7 +9353,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -9356,7 +9374,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>203</v>
@@ -9370,7 +9388,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -9385,7 +9403,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -9406,7 +9424,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>203</v>
@@ -9420,7 +9438,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9435,7 +9453,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -9456,7 +9474,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>203</v>
@@ -9470,7 +9488,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9485,7 +9503,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9506,7 +9524,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>203</v>
@@ -9520,7 +9538,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9535,7 +9553,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9556,7 +9574,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>203</v>
@@ -9570,7 +9588,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9585,7 +9603,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9606,7 +9624,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>203</v>
@@ -9620,7 +9638,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9635,7 +9653,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9656,7 +9674,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>203</v>
@@ -9670,7 +9688,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9685,7 +9703,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9706,7 +9724,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>203</v>
@@ -9720,7 +9738,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9735,7 +9753,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9756,7 +9774,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>203</v>
@@ -9770,7 +9788,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9785,7 +9803,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9806,7 +9824,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>203</v>
@@ -9820,7 +9838,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9835,7 +9853,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9856,7 +9874,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>203</v>
@@ -9870,7 +9888,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9885,7 +9903,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9906,7 +9924,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>203</v>
@@ -9920,7 +9938,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9935,7 +9953,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -9956,7 +9974,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>203</v>
@@ -9970,7 +9988,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -9985,7 +10003,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -10006,7 +10024,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>203</v>
@@ -10020,7 +10038,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10035,7 +10053,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -10056,7 +10074,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>203</v>
@@ -10070,7 +10088,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -10085,7 +10103,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -10106,7 +10124,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>203</v>
@@ -10120,7 +10138,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -10135,7 +10153,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -10156,7 +10174,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>203</v>
@@ -10170,7 +10188,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -10185,7 +10203,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -10206,7 +10224,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>203</v>
@@ -10220,7 +10238,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -10235,7 +10253,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -10256,7 +10274,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>203</v>
@@ -10270,7 +10288,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -10285,7 +10303,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -10306,7 +10324,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>203</v>
@@ -10320,7 +10338,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -10335,7 +10353,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -10356,7 +10374,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>203</v>
@@ -10370,7 +10388,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -10385,7 +10403,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -10406,7 +10424,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>203</v>
@@ -10420,7 +10438,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10435,7 +10453,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -10456,7 +10474,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>203</v>
@@ -10470,7 +10488,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10485,7 +10503,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10506,7 +10524,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>203</v>
@@ -10520,7 +10538,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10535,7 +10553,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10556,7 +10574,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>203</v>
@@ -10570,7 +10588,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10585,7 +10603,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10606,7 +10624,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>203</v>
@@ -10620,7 +10638,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10635,7 +10653,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10656,7 +10674,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>203</v>
@@ -10670,7 +10688,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10685,7 +10703,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10706,7 +10724,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>203</v>
@@ -10918,7 +10936,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -10931,13 +10949,13 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10954,28 +10972,28 @@
         <v>109</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11030,22 +11048,22 @@
         <v>119</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>122</v>
@@ -11074,7 +11092,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -11112,7 +11130,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -11150,7 +11168,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -11188,7 +11206,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -11226,7 +11244,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -11264,7 +11282,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -11302,7 +11320,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -11340,7 +11358,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -11378,7 +11396,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -13323,7 +13341,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E458"/>
+  <dimension ref="A1:E463"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -21105,6 +21123,91 @@
         <v>815</v>
       </c>
       <c r="E458" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>455</v>
+      </c>
+      <c r="B459">
+        <v>55014</v>
+      </c>
+      <c r="C459" t="s">
+        <v>816</v>
+      </c>
+      <c r="D459" t="s">
+        <v>816</v>
+      </c>
+      <c r="E459" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>456</v>
+      </c>
+      <c r="B460">
+        <v>55015</v>
+      </c>
+      <c r="C460" t="s">
+        <v>818</v>
+      </c>
+      <c r="D460" t="s">
+        <v>818</v>
+      </c>
+      <c r="E460" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>457</v>
+      </c>
+      <c r="B461">
+        <v>55016</v>
+      </c>
+      <c r="C461" t="s">
+        <v>819</v>
+      </c>
+      <c r="D461" t="s">
+        <v>819</v>
+      </c>
+      <c r="E461" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>458</v>
+      </c>
+      <c r="B462">
+        <v>55017</v>
+      </c>
+      <c r="C462" t="s">
+        <v>820</v>
+      </c>
+      <c r="D462" t="s">
+        <v>820</v>
+      </c>
+      <c r="E462" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>459</v>
+      </c>
+      <c r="B463">
+        <v>55018</v>
+      </c>
+      <c r="C463" t="s">
+        <v>821</v>
+      </c>
+      <c r="D463" t="s">
+        <v>821</v>
+      </c>
+      <c r="E463" t="s">
         <v>800</v>
       </c>
     </row>
@@ -21145,22 +21248,22 @@
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -21197,22 +21300,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -21223,7 +21326,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -21249,7 +21352,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -21275,7 +21378,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -21301,7 +21404,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -21327,7 +21430,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -21353,7 +21456,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -21379,7 +21482,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -21423,7 +21526,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -21436,28 +21539,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>112</v>
@@ -21477,13 +21580,13 @@
         <v>113</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>113</v>
@@ -21500,22 +21603,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>122</v>
@@ -21547,7 +21650,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -21576,7 +21679,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -21663,7 +21766,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -21692,7 +21795,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -21728,7 +21831,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -21750,13 +21853,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>400</v>
@@ -21765,25 +21868,25 @@
         <v>403</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -21838,40 +21941,40 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -30700,7 +30803,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>104</v>
@@ -30708,7 +30811,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -30724,22 +30827,22 @@
         <v>107</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>112</v>
@@ -30794,16 +30897,16 @@
         <v>119</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>122</v>
@@ -30832,13 +30935,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -30864,13 +30967,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -30896,13 +30999,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -30928,13 +31031,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -30960,13 +31063,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -31001,13 +31104,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31020,7 +31123,7 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>297</v>
@@ -31029,19 +31132,19 @@
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>301</v>
@@ -31090,25 +31193,25 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>167</v>
@@ -33074,13 +33177,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>112</v>
@@ -33117,16 +33220,16 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>302</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>122</v>
@@ -33382,22 +33485,22 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D2" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="E2" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F2" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="G2" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="H2" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="I2" t="s">
         <v>112</v>
@@ -33440,22 +33543,22 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D4" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E4" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="F4" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="G4" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="H4" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="I4" t="s">
         <v>122</v>
@@ -33615,12 +33718,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="F1" t="s">
         <v>104</v>
@@ -33634,19 +33737,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D2" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="E2" t="s">
         <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="G2" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -33680,19 +33783,19 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="D4" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="E4" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="F4" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="G4" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -33703,10 +33806,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D5" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -33726,10 +33829,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D6" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -33749,10 +33852,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D7" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -33772,10 +33875,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D8" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -33795,10 +33898,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D9" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -33818,10 +33921,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D10" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -33841,10 +33944,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D11" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -33864,10 +33967,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D12" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -33887,10 +33990,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D13" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -33910,10 +34013,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D14" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -33933,10 +34036,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D15" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -33956,10 +34059,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D16" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -33979,10 +34082,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D17" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -34002,10 +34105,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D18" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -34015,6 +34118,52 @@
       </c>
       <c r="G18">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>33015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19">
+        <v>55017</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>33016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20">
+        <v>55018</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4077" uniqueCount="1074">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -1413,7 +1413,7 @@
     <t>Auto Upgrade</t>
   </si>
   <si>
-    <t>스테이지·스탯·숙련을 초기화하고 무기·유물을 소멸/초기화하는 대신, 그동안 소비한 재화를 전액 돌려받고 도달 스테이지에 비례한 다이아를 새로 받습니다. 존재력 트리는 그대로 유지됩니다.</t>
+    <t>스테이지·스탯·숙련을 초기화하고 무기·유물을 소멸/초기화합니다. 골드·성장에너지·숙련의 정수·다이아는 초기화된 뒤 도달 스테이지 구간에 맞춰 새로 지급되고, 존재력은 초기화만 됩니다(시간에너지는 그대로 유지). 존재력 트리는 그대로 유지됩니다.</t>
   </si>
   <si>
     <t>RebirthModal</t>
@@ -1455,7 +1455,7 @@
     <t>리버스 · 타임 하이스트 해금 상태</t>
   </si>
   <si>
-    <t>존재력(EXIST), 시간에너지 보유량</t>
+    <t>시간에너지 보유량</t>
   </si>
   <si>
     <t>설계 완료 · 프로토타입 미구현</t>
@@ -2500,6 +2500,15 @@
   </si>
   <si>
     <t>로딩 화면 추가</t>
+  </si>
+  <si>
+    <t>다이아 · 존재력 재화 초기화</t>
+  </si>
+  <si>
+    <t>RebirthUi</t>
+  </si>
+  <si>
+    <t>리버스 재화 초기화 범위 확대</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3752,27 +3761,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B1" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="F1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B2" t="s">
         <v>105</v>
@@ -3792,7 +3801,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -3812,13 +3821,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B4" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -3832,13 +3841,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -3852,10 +3861,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B6" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3867,18 +3876,18 @@
         <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B7" t="s">
         <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3892,13 +3901,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -3912,13 +3921,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B9" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C9" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -3932,13 +3941,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B10" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C10" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -3952,13 +3961,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B11" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C11" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -3972,13 +3981,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B12" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C12" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -3992,13 +4001,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B13" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C13" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -4012,13 +4021,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4032,19 +4041,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B15" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C15" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="F15" t="s">
         <v>203</v>
@@ -4052,7 +4061,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
@@ -4072,7 +4081,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
@@ -4092,13 +4101,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B18" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C18" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -4112,7 +4121,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B19" t="s">
         <v>297</v>
@@ -4132,13 +4141,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -4152,13 +4161,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B21" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C21" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -4172,13 +4181,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B22" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C22" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -4187,15 +4196,15 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B23" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4207,18 +4216,18 @@
         <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B24" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="C24" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -4227,15 +4236,15 @@
         <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B25" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
@@ -4252,7 +4261,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B26" t="s">
         <v>301</v>
@@ -4272,7 +4281,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B27" t="s">
         <v>105</v>
@@ -4292,7 +4301,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B28" t="s">
         <v>106</v>
@@ -4312,7 +4321,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
@@ -4332,7 +4341,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -4352,7 +4361,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -4372,7 +4381,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
@@ -4392,7 +4401,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -4412,7 +4421,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B34" t="s">
         <v>112</v>
@@ -4432,7 +4441,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B35" t="s">
         <v>105</v>
@@ -4452,7 +4461,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
@@ -4472,7 +4481,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -4492,7 +4501,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -4512,7 +4521,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -4532,7 +4541,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B40" t="s">
         <v>112</v>
@@ -4552,7 +4561,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
@@ -4572,7 +4581,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B42" t="s">
         <v>106</v>
@@ -4592,19 +4601,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B43" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C43" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D43" t="s">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="F43" t="s">
         <v>203</v>
@@ -4612,13 +4621,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B44" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C44" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4627,32 +4636,32 @@
         <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B45" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C45" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="F45" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B46" t="s">
         <v>361</v>
@@ -4667,24 +4676,24 @@
         <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B47" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C47" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="F47" t="s">
         <v>104</v>
@@ -4692,19 +4701,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B48" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C48" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D48" t="s">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="F48" t="s">
         <v>203</v>
@@ -4712,10 +4721,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B49" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C49" t="s">
         <v>298</v>
@@ -4724,7 +4733,7 @@
         <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="F49" t="s">
         <v>203</v>
@@ -4732,19 +4741,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D50" t="s">
         <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="F50" t="s">
         <v>104</v>
@@ -4752,19 +4761,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B51" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C51" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D51" t="s">
         <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
@@ -4772,13 +4781,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B52" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C52" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -4792,13 +4801,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B53" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C53" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -4812,13 +4821,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B54" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C54" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="D54" t="s">
         <v>145</v>
@@ -4832,13 +4841,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B55" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C55" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D55" t="s">
         <v>114</v>
@@ -4847,12 +4856,12 @@
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -4872,7 +4881,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
@@ -4892,7 +4901,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B58" t="s">
         <v>106</v>
@@ -4912,7 +4921,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B59" t="s">
         <v>132</v>
@@ -4932,7 +4941,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -4952,7 +4961,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B61" t="s">
         <v>134</v>
@@ -4972,7 +4981,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B62" t="s">
         <v>135</v>
@@ -4992,7 +5001,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B63" t="s">
         <v>136</v>
@@ -5012,7 +5021,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B64" t="s">
         <v>137</v>
@@ -5032,7 +5041,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -5052,7 +5061,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -5072,7 +5081,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B67" t="s">
         <v>140</v>
@@ -5092,7 +5101,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
@@ -5112,7 +5121,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B69" t="s">
         <v>142</v>
@@ -5132,7 +5141,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B70" t="s">
         <v>143</v>
@@ -5152,7 +5161,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B71" t="s">
         <v>144</v>
@@ -5172,7 +5181,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B72" t="s">
         <v>112</v>
@@ -5192,7 +5201,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
@@ -5212,7 +5221,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
@@ -5232,7 +5241,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B75" t="s">
         <v>361</v>
@@ -5247,12 +5256,12 @@
         <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B76" t="s">
         <v>109</v>
@@ -5272,19 +5281,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B77" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C77" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="F77" t="s">
         <v>104</v>
@@ -5292,19 +5301,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B78" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C78" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F78" t="s">
         <v>104</v>
@@ -5312,19 +5321,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B79" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C79" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D79" t="s">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F79" t="s">
         <v>203</v>
@@ -5332,13 +5341,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B80" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C80" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D80" t="s">
         <v>115</v>
@@ -5347,18 +5356,18 @@
         <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B81" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C81" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -5372,13 +5381,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B82" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C82" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -5392,7 +5401,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -5412,10 +5421,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B84" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -5427,12 +5436,12 @@
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -5452,7 +5461,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B86" t="s">
         <v>106</v>
@@ -5472,7 +5481,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -5492,7 +5501,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B88" t="s">
         <v>160</v>
@@ -5512,7 +5521,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B89" t="s">
         <v>112</v>
@@ -5532,7 +5541,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B90" t="s">
         <v>105</v>
@@ -5552,7 +5561,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B91" t="s">
         <v>106</v>
@@ -5572,19 +5581,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B92" t="s">
         <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="F92" t="s">
         <v>203</v>
@@ -5592,10 +5601,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B93" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C93" t="s">
         <v>302</v>
@@ -5612,13 +5621,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B94" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C94" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D94" t="s">
         <v>145</v>
@@ -5632,13 +5641,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B95" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C95" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
@@ -5652,7 +5661,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B96" t="s">
         <v>112</v>
@@ -5672,7 +5681,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B97" t="s">
         <v>105</v>
@@ -5692,7 +5701,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B98" t="s">
         <v>106</v>
@@ -5712,13 +5721,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B99" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C99" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
@@ -5732,13 +5741,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B100" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C100" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
@@ -5752,13 +5761,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B101" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C101" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
@@ -5772,13 +5781,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B102" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C102" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D102" t="s">
         <v>113</v>
@@ -5792,13 +5801,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B103" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C103" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D103" t="s">
         <v>113</v>
@@ -5812,13 +5821,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B104" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C104" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D104" t="s">
         <v>113</v>
@@ -5832,7 +5841,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B105" t="s">
         <v>112</v>
@@ -5895,10 +5904,10 @@
         <v>800</v>
       </c>
       <c r="B108" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C108" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -5915,10 +5924,10 @@
         <v>800</v>
       </c>
       <c r="B109" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C109" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -5938,7 +5947,7 @@
         <v>234</v>
       </c>
       <c r="C110" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D110" t="s">
         <v>115</v>
@@ -5947,7 +5956,7 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5955,10 +5964,10 @@
         <v>800</v>
       </c>
       <c r="B111" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C111" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D111" t="s">
         <v>113</v>
@@ -5975,10 +5984,10 @@
         <v>800</v>
       </c>
       <c r="B112" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C112" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D112" t="s">
         <v>113</v>
@@ -5992,7 +6001,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B113" t="s">
         <v>105</v>
@@ -6012,7 +6021,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B114" t="s">
         <v>106</v>
@@ -6032,7 +6041,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -6052,7 +6061,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B116" t="s">
         <v>107</v>
@@ -6072,7 +6081,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B117" t="s">
         <v>164</v>
@@ -6092,7 +6101,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B118" t="s">
         <v>165</v>
@@ -6112,7 +6121,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B119" t="s">
         <v>112</v>
@@ -6132,7 +6141,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
@@ -6152,7 +6161,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B121" t="s">
         <v>106</v>
@@ -6172,7 +6181,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B122" t="s">
         <v>232</v>
@@ -6192,7 +6201,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B123" t="s">
         <v>233</v>
@@ -6212,7 +6221,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B124" t="s">
         <v>234</v>
@@ -6232,7 +6241,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B125" t="s">
         <v>105</v>
@@ -6252,7 +6261,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -6272,13 +6281,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B127" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C127" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D127" t="s">
         <v>114</v>
@@ -6292,13 +6301,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B128" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C128" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -6312,13 +6321,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B129" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C129" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -6332,13 +6341,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B130" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C130" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -6352,13 +6361,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B131" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C131" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -6372,13 +6381,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B132" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C132" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D132" t="s">
         <v>113</v>
@@ -6392,10 +6401,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B133" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C133" t="s">
         <v>116</v>
@@ -6412,7 +6421,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B134" t="s">
         <v>117</v>
@@ -6432,13 +6441,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B135" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C135" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -6447,18 +6456,18 @@
         <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B136" t="s">
         <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D136" t="s">
         <v>113</v>
@@ -6472,16 +6481,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B137" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C137" t="s">
+        <v>835</v>
+      </c>
+      <c r="D137" t="s">
         <v>832</v>
-      </c>
-      <c r="D137" t="s">
-        <v>829</v>
       </c>
       <c r="E137" t="s">
         <v>203</v>
@@ -6492,16 +6501,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B138" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C138" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D138" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E138" t="s">
         <v>203</v>
@@ -6512,16 +6521,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B139" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C139" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D139" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E139" t="s">
         <v>203</v>
@@ -6532,13 +6541,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B140" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C140" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D140" t="s">
         <v>113</v>
@@ -6552,7 +6561,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B141" t="s">
         <v>112</v>
@@ -6572,7 +6581,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B142" t="s">
         <v>105</v>
@@ -6592,7 +6601,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B143" t="s">
         <v>106</v>
@@ -6612,7 +6621,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B144" t="s">
         <v>107</v>
@@ -6632,10 +6641,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B145" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -6647,12 +6656,12 @@
         <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B146" t="s">
         <v>109</v>
@@ -6672,13 +6681,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B147" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C147" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D147" t="s">
         <v>145</v>
@@ -6692,13 +6701,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B148" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C148" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D148" t="s">
         <v>145</v>
@@ -6712,13 +6721,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B149" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C149" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D149" t="s">
         <v>114</v>
@@ -6727,18 +6736,18 @@
         <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B150" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C150" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D150" t="s">
         <v>113</v>
@@ -6752,7 +6761,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B151" t="s">
         <v>112</v>
@@ -6803,13 +6812,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>104</v>
@@ -6826,7 +6835,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6838,43 +6847,43 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>361</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>112</v>
@@ -6938,43 +6947,43 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>362</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>122</v>
@@ -6988,7 +6997,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -7003,7 +7012,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -7024,7 +7033,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>203</v>
@@ -7038,7 +7047,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7053,7 +7062,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -7074,7 +7083,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>203</v>
@@ -7088,7 +7097,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -7103,7 +7112,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -7124,7 +7133,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>203</v>
@@ -7138,7 +7147,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -7153,7 +7162,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -7174,7 +7183,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>203</v>
@@ -7188,7 +7197,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -7203,7 +7212,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -7224,7 +7233,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>203</v>
@@ -7238,7 +7247,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -7253,7 +7262,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -7274,7 +7283,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>203</v>
@@ -7288,7 +7297,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -7303,7 +7312,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -7324,7 +7333,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>203</v>
@@ -7338,7 +7347,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -7353,7 +7362,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -7374,7 +7383,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>203</v>
@@ -7388,7 +7397,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -7403,7 +7412,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -7424,7 +7433,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>203</v>
@@ -7438,7 +7447,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7453,7 +7462,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -7474,7 +7483,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>203</v>
@@ -7488,7 +7497,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7503,7 +7512,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7524,7 +7533,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>203</v>
@@ -7538,7 +7547,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7553,7 +7562,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7574,7 +7583,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>203</v>
@@ -7588,7 +7597,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7603,7 +7612,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7624,7 +7633,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>203</v>
@@ -7638,7 +7647,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7653,7 +7662,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7674,7 +7683,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>203</v>
@@ -7688,7 +7697,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7703,7 +7712,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7724,7 +7733,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>203</v>
@@ -7738,7 +7747,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7753,7 +7762,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7774,7 +7783,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>203</v>
@@ -7788,7 +7797,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7803,7 +7812,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7824,7 +7833,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>203</v>
@@ -7838,7 +7847,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7853,7 +7862,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7874,7 +7883,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>203</v>
@@ -7888,7 +7897,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7903,7 +7912,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7924,7 +7933,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>203</v>
@@ -7938,7 +7947,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7953,7 +7962,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -7974,7 +7983,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>203</v>
@@ -7988,7 +7997,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -8003,7 +8012,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -8024,7 +8033,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>203</v>
@@ -8038,7 +8047,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8053,7 +8062,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -8074,7 +8083,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>203</v>
@@ -8088,7 +8097,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -8103,7 +8112,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -8124,7 +8133,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>203</v>
@@ -8138,7 +8147,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -8153,7 +8162,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -8174,7 +8183,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>203</v>
@@ -8188,7 +8197,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -8203,7 +8212,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -8224,7 +8233,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>203</v>
@@ -8238,7 +8247,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -8253,7 +8262,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -8274,7 +8283,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>203</v>
@@ -8288,7 +8297,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -8303,7 +8312,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -8324,7 +8333,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>203</v>
@@ -8338,7 +8347,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -8353,7 +8362,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -8374,7 +8383,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>203</v>
@@ -8388,7 +8397,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -8403,7 +8412,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -8424,7 +8433,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>203</v>
@@ -8438,7 +8447,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8453,7 +8462,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -8474,7 +8483,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>203</v>
@@ -8488,7 +8497,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8503,7 +8512,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8524,7 +8533,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>203</v>
@@ -8538,7 +8547,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8553,7 +8562,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8574,7 +8583,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>203</v>
@@ -8588,7 +8597,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8603,7 +8612,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8624,7 +8633,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>203</v>
@@ -8638,7 +8647,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8653,7 +8662,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8674,7 +8683,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>203</v>
@@ -8688,7 +8697,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8703,7 +8712,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8724,7 +8733,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>203</v>
@@ -8738,7 +8747,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8753,7 +8762,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8774,7 +8783,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>203</v>
@@ -8788,7 +8797,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8803,7 +8812,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8824,7 +8833,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>203</v>
@@ -8838,7 +8847,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8853,7 +8862,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8874,7 +8883,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>203</v>
@@ -8888,7 +8897,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8903,7 +8912,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8924,7 +8933,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>203</v>
@@ -8938,7 +8947,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8953,7 +8962,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -8974,7 +8983,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>203</v>
@@ -8988,7 +8997,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -9003,7 +9012,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -9024,7 +9033,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>203</v>
@@ -9038,7 +9047,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9053,7 +9062,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -9074,7 +9083,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>203</v>
@@ -9088,7 +9097,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -9103,7 +9112,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -9124,7 +9133,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>203</v>
@@ -9138,7 +9147,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -9153,7 +9162,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -9174,7 +9183,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>203</v>
@@ -9188,7 +9197,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -9203,7 +9212,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -9224,7 +9233,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>203</v>
@@ -9238,7 +9247,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -9253,7 +9262,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -9274,7 +9283,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>203</v>
@@ -9288,7 +9297,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -9303,7 +9312,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -9324,7 +9333,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>203</v>
@@ -9338,7 +9347,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -9353,7 +9362,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -9374,7 +9383,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>203</v>
@@ -9388,7 +9397,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -9403,7 +9412,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -9424,7 +9433,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>203</v>
@@ -9438,7 +9447,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9453,7 +9462,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -9474,7 +9483,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>203</v>
@@ -9488,7 +9497,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9503,7 +9512,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9524,7 +9533,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>203</v>
@@ -9538,7 +9547,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9553,7 +9562,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9574,7 +9583,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>203</v>
@@ -9588,7 +9597,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9603,7 +9612,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9624,7 +9633,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>203</v>
@@ -9638,7 +9647,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9653,7 +9662,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9674,7 +9683,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>203</v>
@@ -9688,7 +9697,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9703,7 +9712,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9724,7 +9733,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>203</v>
@@ -9738,7 +9747,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9753,7 +9762,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9774,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>203</v>
@@ -9788,7 +9797,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9803,7 +9812,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9824,7 +9833,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>203</v>
@@ -9838,7 +9847,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9853,7 +9862,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9874,7 +9883,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>203</v>
@@ -9888,7 +9897,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9903,7 +9912,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9924,7 +9933,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>203</v>
@@ -9938,7 +9947,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9953,7 +9962,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -9974,7 +9983,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>203</v>
@@ -9988,7 +9997,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -10003,7 +10012,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -10024,7 +10033,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>203</v>
@@ -10038,7 +10047,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10053,7 +10062,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -10074,7 +10083,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>203</v>
@@ -10088,7 +10097,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -10103,7 +10112,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -10124,7 +10133,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>203</v>
@@ -10138,7 +10147,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -10153,7 +10162,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -10174,7 +10183,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>203</v>
@@ -10188,7 +10197,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -10203,7 +10212,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -10224,7 +10233,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>203</v>
@@ -10238,7 +10247,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -10253,7 +10262,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -10274,7 +10283,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>203</v>
@@ -10288,7 +10297,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -10303,7 +10312,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -10324,7 +10333,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>203</v>
@@ -10338,7 +10347,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -10353,7 +10362,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -10374,7 +10383,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>203</v>
@@ -10388,7 +10397,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -10403,7 +10412,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -10424,7 +10433,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>203</v>
@@ -10438,7 +10447,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10453,7 +10462,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -10474,7 +10483,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>203</v>
@@ -10488,7 +10497,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10503,7 +10512,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10524,7 +10533,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>203</v>
@@ -10538,7 +10547,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10553,7 +10562,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10574,7 +10583,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>203</v>
@@ -10588,7 +10597,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10603,7 +10612,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10624,7 +10633,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>203</v>
@@ -10638,7 +10647,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10653,7 +10662,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10674,7 +10683,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>203</v>
@@ -10688,7 +10697,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10703,7 +10712,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10724,7 +10733,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>203</v>
@@ -10936,7 +10945,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -10949,13 +10958,13 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10972,28 +10981,28 @@
         <v>109</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11048,22 +11057,22 @@
         <v>119</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>122</v>
@@ -11092,7 +11101,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -11130,7 +11139,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -11168,7 +11177,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -11206,7 +11215,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -11244,7 +11253,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -11282,7 +11291,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -11320,7 +11329,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -11358,7 +11367,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -11396,7 +11405,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -13341,7 +13350,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E463"/>
+  <dimension ref="A1:E465"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -21208,6 +21217,40 @@
         <v>821</v>
       </c>
       <c r="E463" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>460</v>
+      </c>
+      <c r="B464">
+        <v>41054</v>
+      </c>
+      <c r="C464" t="s">
+        <v>822</v>
+      </c>
+      <c r="D464" t="s">
+        <v>822</v>
+      </c>
+      <c r="E464" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>461</v>
+      </c>
+      <c r="B465">
+        <v>55019</v>
+      </c>
+      <c r="C465" t="s">
+        <v>824</v>
+      </c>
+      <c r="D465" t="s">
+        <v>824</v>
+      </c>
+      <c r="E465" t="s">
         <v>800</v>
       </c>
     </row>
@@ -21248,22 +21291,22 @@
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -21300,22 +21343,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -21326,7 +21369,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -21352,7 +21395,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -21378,7 +21421,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -21404,7 +21447,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -21430,7 +21473,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -21456,7 +21499,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -21482,7 +21525,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -21526,7 +21569,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -21539,28 +21582,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>112</v>
@@ -21580,13 +21623,13 @@
         <v>113</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>113</v>
@@ -21603,22 +21646,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>122</v>
@@ -21638,10 +21681,10 @@
         <v>40075</v>
       </c>
       <c r="E5" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="12" t="b">
         <v>1</v>
@@ -21650,7 +21693,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -21667,7 +21710,7 @@
         <v>40015</v>
       </c>
       <c r="E6" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="12" t="b">
         <v>0</v>
@@ -21679,7 +21722,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -21696,7 +21739,7 @@
         <v>40016</v>
       </c>
       <c r="E7" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="12" t="b">
         <v>1</v>
@@ -21725,7 +21768,7 @@
         <v>40019</v>
       </c>
       <c r="E8" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="12" t="b">
         <v>1</v>
@@ -21754,7 +21797,7 @@
         <v>40017</v>
       </c>
       <c r="E9" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="12" t="b">
         <v>1</v>
@@ -21766,7 +21809,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -21795,7 +21838,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -21831,7 +21874,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -21853,13 +21896,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>400</v>
@@ -21868,25 +21911,25 @@
         <v>403</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -21941,40 +21984,40 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -30803,7 +30846,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>104</v>
@@ -30811,7 +30854,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -30827,22 +30870,22 @@
         <v>107</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>112</v>
@@ -30897,16 +30940,16 @@
         <v>119</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>122</v>
@@ -30935,13 +30978,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -30967,13 +31010,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -30999,13 +31042,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -31031,13 +31074,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -31063,13 +31106,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -31104,13 +31147,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31123,7 +31166,7 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>297</v>
@@ -31132,19 +31175,19 @@
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>301</v>
@@ -31193,25 +31236,25 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>167</v>
@@ -33177,13 +33220,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>112</v>
@@ -33220,16 +33263,16 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>302</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>122</v>
@@ -33485,22 +33528,22 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D2" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G2" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="H2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="I2" t="s">
         <v>112</v>
@@ -33543,22 +33586,22 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D4" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E4" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="F4" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="G4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="H4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="I4" t="s">
         <v>122</v>
@@ -33718,12 +33761,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="F1" t="s">
         <v>104</v>
@@ -33737,19 +33780,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E2" t="s">
         <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="G2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -33783,19 +33826,19 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D4" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E4" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="F4" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -33806,10 +33849,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D5" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -33829,10 +33872,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D6" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -33852,10 +33895,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D7" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -33875,10 +33918,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -33898,10 +33941,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D9" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -33921,10 +33964,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D10" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -33944,10 +33987,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D11" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -33967,10 +34010,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D12" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -33990,10 +34033,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D13" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -34013,10 +34056,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D14" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -34036,10 +34079,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D15" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -34059,10 +34102,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D16" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -34082,10 +34125,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D17" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -34105,10 +34148,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -34128,10 +34171,10 @@
         <v>33015</v>
       </c>
       <c r="C19" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D19" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -34151,10 +34194,10 @@
         <v>33016</v>
       </c>
       <c r="C20" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D20" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -34164,6 +34207,29 @@
       </c>
       <c r="G20">
         <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21">
+        <v>33017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21">
+        <v>55019</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4077" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="1081">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2511,6 +2511,21 @@
     <t>리버스 재화 초기화 범위 확대</t>
   </si>
   <si>
+    <t>몬스터 스프라이트 추가</t>
+  </si>
+  <si>
+    <t>INITIALIZING</t>
+  </si>
+  <si>
+    <t>LOADING ARCHIVE</t>
+  </si>
+  <si>
+    <t>READY</t>
+  </si>
+  <si>
+    <t>로고·로딩 화면 리디자인</t>
+  </si>
+  <si>
     <t>EnumDefine/CurrencyType</t>
   </si>
   <si>
@@ -3256,6 +3271,12 @@
   </si>
   <si>
     <t>v0.3.0</t>
+  </si>
+  <si>
+    <t>v0.4.0</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
 </sst>
 </file>
@@ -3761,27 +3782,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B1" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C1" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="D1" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="E1" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="F1" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B2" t="s">
         <v>105</v>
@@ -3801,7 +3822,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -3821,13 +3842,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B4" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C4" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -3841,13 +3862,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B5" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -3861,10 +3882,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B6" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3876,18 +3897,18 @@
         <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B7" t="s">
         <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3901,13 +3922,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -3921,13 +3942,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B9" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C9" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -3941,13 +3962,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B10" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -3961,13 +3982,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B11" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C11" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -3981,13 +4002,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B12" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="C12" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -4001,13 +4022,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B13" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="C13" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -4021,13 +4042,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4041,19 +4062,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B15" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="C15" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="F15" t="s">
         <v>203</v>
@@ -4061,7 +4082,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
@@ -4081,7 +4102,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
@@ -4101,13 +4122,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B18" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C18" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -4121,7 +4142,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B19" t="s">
         <v>297</v>
@@ -4141,13 +4162,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -4161,13 +4182,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B21" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C21" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -4181,13 +4202,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B22" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C22" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -4196,15 +4217,15 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B23" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4216,18 +4237,18 @@
         <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B24" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="C24" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -4236,15 +4257,15 @@
         <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B25" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
@@ -4261,7 +4282,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B26" t="s">
         <v>301</v>
@@ -4281,7 +4302,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B27" t="s">
         <v>105</v>
@@ -4301,7 +4322,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B28" t="s">
         <v>106</v>
@@ -4321,7 +4342,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
@@ -4341,7 +4362,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -4361,7 +4382,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -4381,7 +4402,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
@@ -4401,7 +4422,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -4421,7 +4442,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B34" t="s">
         <v>112</v>
@@ -4441,7 +4462,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B35" t="s">
         <v>105</v>
@@ -4461,7 +4482,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
@@ -4481,7 +4502,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -4501,7 +4522,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -4521,7 +4542,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -4541,7 +4562,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B40" t="s">
         <v>112</v>
@@ -4561,7 +4582,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
@@ -4581,7 +4602,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B42" t="s">
         <v>106</v>
@@ -4601,19 +4622,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B43" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="C43" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D43" t="s">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="F43" t="s">
         <v>203</v>
@@ -4621,13 +4642,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B44" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="C44" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4636,32 +4657,32 @@
         <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B45" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="C45" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="F45" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B46" t="s">
         <v>361</v>
@@ -4676,24 +4697,24 @@
         <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B47" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C47" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="F47" t="s">
         <v>104</v>
@@ -4701,19 +4722,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B48" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C48" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="D48" t="s">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="F48" t="s">
         <v>203</v>
@@ -4721,10 +4742,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B49" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="C49" t="s">
         <v>298</v>
@@ -4733,7 +4754,7 @@
         <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="F49" t="s">
         <v>203</v>
@@ -4741,19 +4762,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D50" t="s">
         <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="F50" t="s">
         <v>104</v>
@@ -4761,19 +4782,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B51" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C51" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D51" t="s">
         <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
@@ -4781,13 +4802,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B52" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C52" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -4801,13 +4822,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B53" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="C53" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -4821,13 +4842,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B54" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C54" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="D54" t="s">
         <v>145</v>
@@ -4841,13 +4862,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B55" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C55" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D55" t="s">
         <v>114</v>
@@ -4856,12 +4877,12 @@
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -4881,7 +4902,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
@@ -4901,7 +4922,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B58" t="s">
         <v>106</v>
@@ -4921,7 +4942,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B59" t="s">
         <v>132</v>
@@ -4941,7 +4962,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -4961,7 +4982,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B61" t="s">
         <v>134</v>
@@ -4981,7 +5002,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B62" t="s">
         <v>135</v>
@@ -5001,7 +5022,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B63" t="s">
         <v>136</v>
@@ -5021,7 +5042,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B64" t="s">
         <v>137</v>
@@ -5041,7 +5062,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -5061,7 +5082,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -5081,7 +5102,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B67" t="s">
         <v>140</v>
@@ -5101,7 +5122,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
@@ -5121,7 +5142,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B69" t="s">
         <v>142</v>
@@ -5141,7 +5162,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B70" t="s">
         <v>143</v>
@@ -5161,7 +5182,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B71" t="s">
         <v>144</v>
@@ -5181,7 +5202,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B72" t="s">
         <v>112</v>
@@ -5201,7 +5222,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
@@ -5221,7 +5242,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
@@ -5241,7 +5262,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B75" t="s">
         <v>361</v>
@@ -5256,12 +5277,12 @@
         <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B76" t="s">
         <v>109</v>
@@ -5281,19 +5302,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B77" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C77" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="F77" t="s">
         <v>104</v>
@@ -5301,19 +5322,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B78" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C78" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="F78" t="s">
         <v>104</v>
@@ -5321,19 +5342,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B79" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C79" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="D79" t="s">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="F79" t="s">
         <v>203</v>
@@ -5341,13 +5362,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B80" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C80" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D80" t="s">
         <v>115</v>
@@ -5356,18 +5377,18 @@
         <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B81" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="C81" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -5381,13 +5402,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B82" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="C82" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -5401,7 +5422,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -5421,10 +5442,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B84" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -5436,12 +5457,12 @@
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -5461,7 +5482,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B86" t="s">
         <v>106</v>
@@ -5481,7 +5502,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -5501,7 +5522,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B88" t="s">
         <v>160</v>
@@ -5521,7 +5542,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B89" t="s">
         <v>112</v>
@@ -5541,7 +5562,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B90" t="s">
         <v>105</v>
@@ -5561,7 +5582,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B91" t="s">
         <v>106</v>
@@ -5581,19 +5602,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B92" t="s">
         <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="F92" t="s">
         <v>203</v>
@@ -5601,10 +5622,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B93" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="C93" t="s">
         <v>302</v>
@@ -5621,13 +5642,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B94" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C94" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="D94" t="s">
         <v>145</v>
@@ -5641,13 +5662,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B95" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="C95" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
@@ -5661,7 +5682,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B96" t="s">
         <v>112</v>
@@ -5681,7 +5702,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B97" t="s">
         <v>105</v>
@@ -5701,7 +5722,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B98" t="s">
         <v>106</v>
@@ -5721,13 +5742,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B99" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="C99" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
@@ -5741,13 +5762,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B100" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="C100" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
@@ -5761,13 +5782,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B101" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="C101" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
@@ -5781,13 +5802,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B102" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="C102" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="D102" t="s">
         <v>113</v>
@@ -5801,13 +5822,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B103" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="C103" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="D103" t="s">
         <v>113</v>
@@ -5821,13 +5842,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B104" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="C104" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="D104" t="s">
         <v>113</v>
@@ -5841,7 +5862,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B105" t="s">
         <v>112</v>
@@ -5904,10 +5925,10 @@
         <v>800</v>
       </c>
       <c r="B108" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="C108" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -5924,10 +5945,10 @@
         <v>800</v>
       </c>
       <c r="B109" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="C109" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -5947,7 +5968,7 @@
         <v>234</v>
       </c>
       <c r="C110" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="D110" t="s">
         <v>115</v>
@@ -5956,7 +5977,7 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5964,10 +5985,10 @@
         <v>800</v>
       </c>
       <c r="B111" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="C111" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="D111" t="s">
         <v>113</v>
@@ -5984,10 +6005,10 @@
         <v>800</v>
       </c>
       <c r="B112" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="C112" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D112" t="s">
         <v>113</v>
@@ -6001,7 +6022,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B113" t="s">
         <v>105</v>
@@ -6021,7 +6042,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B114" t="s">
         <v>106</v>
@@ -6041,7 +6062,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -6061,7 +6082,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B116" t="s">
         <v>107</v>
@@ -6081,7 +6102,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B117" t="s">
         <v>164</v>
@@ -6101,7 +6122,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B118" t="s">
         <v>165</v>
@@ -6121,7 +6142,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B119" t="s">
         <v>112</v>
@@ -6141,7 +6162,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
@@ -6161,7 +6182,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B121" t="s">
         <v>106</v>
@@ -6181,7 +6202,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B122" t="s">
         <v>232</v>
@@ -6201,7 +6222,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B123" t="s">
         <v>233</v>
@@ -6221,7 +6242,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B124" t="s">
         <v>234</v>
@@ -6241,7 +6262,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B125" t="s">
         <v>105</v>
@@ -6261,7 +6282,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -6281,13 +6302,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B127" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="C127" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D127" t="s">
         <v>114</v>
@@ -6301,13 +6322,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B128" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="C128" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -6321,13 +6342,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B129" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C129" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -6341,13 +6362,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B130" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="C130" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -6361,13 +6382,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B131" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="C131" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -6381,13 +6402,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B132" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C132" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D132" t="s">
         <v>113</v>
@@ -6401,10 +6422,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B133" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C133" t="s">
         <v>116</v>
@@ -6421,7 +6442,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B134" t="s">
         <v>117</v>
@@ -6441,13 +6462,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B135" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C135" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -6456,18 +6477,18 @@
         <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B136" t="s">
         <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D136" t="s">
         <v>113</v>
@@ -6481,16 +6502,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B137" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="C137" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="D137" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="E137" t="s">
         <v>203</v>
@@ -6501,16 +6522,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B138" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C138" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D138" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="E138" t="s">
         <v>203</v>
@@ -6521,16 +6542,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B139" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C139" t="s">
+        <v>842</v>
+      </c>
+      <c r="D139" t="s">
         <v>837</v>
-      </c>
-      <c r="D139" t="s">
-        <v>832</v>
       </c>
       <c r="E139" t="s">
         <v>203</v>
@@ -6541,13 +6562,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B140" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C140" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D140" t="s">
         <v>113</v>
@@ -6561,7 +6582,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B141" t="s">
         <v>112</v>
@@ -6581,7 +6602,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B142" t="s">
         <v>105</v>
@@ -6601,7 +6622,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B143" t="s">
         <v>106</v>
@@ -6621,7 +6642,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B144" t="s">
         <v>107</v>
@@ -6641,10 +6662,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B145" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -6656,12 +6677,12 @@
         <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B146" t="s">
         <v>109</v>
@@ -6681,13 +6702,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B147" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C147" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="D147" t="s">
         <v>145</v>
@@ -6701,13 +6722,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B148" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C148" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="D148" t="s">
         <v>145</v>
@@ -6721,13 +6742,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B149" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C149" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D149" t="s">
         <v>114</v>
@@ -6736,18 +6757,18 @@
         <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B150" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C150" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D150" t="s">
         <v>113</v>
@@ -6761,7 +6782,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B151" t="s">
         <v>112</v>
@@ -6812,13 +6833,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>104</v>
@@ -6835,7 +6856,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6847,43 +6868,43 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>361</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>112</v>
@@ -6947,43 +6968,43 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>362</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>122</v>
@@ -6997,7 +7018,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -7012,7 +7033,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -7033,7 +7054,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>203</v>
@@ -7047,7 +7068,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7062,7 +7083,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -7083,7 +7104,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>203</v>
@@ -7097,7 +7118,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -7112,7 +7133,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -7133,7 +7154,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>203</v>
@@ -7147,7 +7168,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -7162,7 +7183,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -7183,7 +7204,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>203</v>
@@ -7197,7 +7218,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -7212,7 +7233,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -7233,7 +7254,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>203</v>
@@ -7247,7 +7268,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -7262,7 +7283,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -7283,7 +7304,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>203</v>
@@ -7297,7 +7318,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -7312,7 +7333,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -7333,7 +7354,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>203</v>
@@ -7347,7 +7368,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -7362,7 +7383,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -7383,7 +7404,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>203</v>
@@ -7397,7 +7418,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -7412,7 +7433,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -7433,7 +7454,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>203</v>
@@ -7447,7 +7468,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7462,7 +7483,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -7483,7 +7504,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>203</v>
@@ -7497,7 +7518,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7512,7 +7533,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7533,7 +7554,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>203</v>
@@ -7547,7 +7568,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7562,7 +7583,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7583,7 +7604,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>203</v>
@@ -7597,7 +7618,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7612,7 +7633,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7633,7 +7654,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>203</v>
@@ -7647,7 +7668,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7662,7 +7683,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7683,7 +7704,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>203</v>
@@ -7697,7 +7718,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7712,7 +7733,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7733,7 +7754,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>203</v>
@@ -7747,7 +7768,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7762,7 +7783,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7783,7 +7804,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>203</v>
@@ -7797,7 +7818,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7812,7 +7833,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7833,7 +7854,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>203</v>
@@ -7847,7 +7868,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7862,7 +7883,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7883,7 +7904,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>203</v>
@@ -7897,7 +7918,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7912,7 +7933,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7933,7 +7954,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>203</v>
@@ -7947,7 +7968,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7962,7 +7983,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -7983,7 +8004,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>203</v>
@@ -7997,7 +8018,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -8012,7 +8033,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -8033,7 +8054,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>203</v>
@@ -8047,7 +8068,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8062,7 +8083,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -8083,7 +8104,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>203</v>
@@ -8097,7 +8118,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -8112,7 +8133,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -8133,7 +8154,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>203</v>
@@ -8147,7 +8168,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -8162,7 +8183,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -8183,7 +8204,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>203</v>
@@ -8197,7 +8218,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -8212,7 +8233,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -8233,7 +8254,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>203</v>
@@ -8247,7 +8268,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -8262,7 +8283,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -8283,7 +8304,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>203</v>
@@ -8297,7 +8318,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -8312,7 +8333,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -8333,7 +8354,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>203</v>
@@ -8347,7 +8368,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -8362,7 +8383,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -8383,7 +8404,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>203</v>
@@ -8397,7 +8418,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -8412,7 +8433,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -8433,7 +8454,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>203</v>
@@ -8447,7 +8468,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8462,7 +8483,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -8483,7 +8504,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>203</v>
@@ -8497,7 +8518,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8512,7 +8533,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8533,7 +8554,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>203</v>
@@ -8547,7 +8568,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8562,7 +8583,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8583,7 +8604,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>203</v>
@@ -8597,7 +8618,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8612,7 +8633,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8633,7 +8654,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>203</v>
@@ -8647,7 +8668,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8662,7 +8683,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8683,7 +8704,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>203</v>
@@ -8697,7 +8718,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8712,7 +8733,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8733,7 +8754,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>203</v>
@@ -8747,7 +8768,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8762,7 +8783,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8783,7 +8804,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>203</v>
@@ -8797,7 +8818,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8812,7 +8833,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8833,7 +8854,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>203</v>
@@ -8847,7 +8868,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8862,7 +8883,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8883,7 +8904,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>203</v>
@@ -8897,7 +8918,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8912,7 +8933,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8933,7 +8954,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>203</v>
@@ -8947,7 +8968,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8962,7 +8983,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -8983,7 +9004,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>203</v>
@@ -8997,7 +9018,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -9012,7 +9033,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -9033,7 +9054,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>203</v>
@@ -9047,7 +9068,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9062,7 +9083,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -9083,7 +9104,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>203</v>
@@ -9097,7 +9118,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -9112,7 +9133,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -9133,7 +9154,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>203</v>
@@ -9147,7 +9168,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -9162,7 +9183,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -9183,7 +9204,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>203</v>
@@ -9197,7 +9218,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -9212,7 +9233,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -9233,7 +9254,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>203</v>
@@ -9247,7 +9268,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -9262,7 +9283,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -9283,7 +9304,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>203</v>
@@ -9297,7 +9318,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -9312,7 +9333,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -9333,7 +9354,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>203</v>
@@ -9347,7 +9368,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -9362,7 +9383,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -9383,7 +9404,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>203</v>
@@ -9397,7 +9418,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -9412,7 +9433,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -9433,7 +9454,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>203</v>
@@ -9447,7 +9468,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9462,7 +9483,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -9483,7 +9504,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>203</v>
@@ -9497,7 +9518,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9512,7 +9533,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9533,7 +9554,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>203</v>
@@ -9547,7 +9568,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9562,7 +9583,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9583,7 +9604,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>203</v>
@@ -9597,7 +9618,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9612,7 +9633,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9633,7 +9654,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>203</v>
@@ -9647,7 +9668,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9662,7 +9683,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9683,7 +9704,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>203</v>
@@ -9697,7 +9718,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9712,7 +9733,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9733,7 +9754,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>203</v>
@@ -9747,7 +9768,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9762,7 +9783,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9783,7 +9804,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>203</v>
@@ -9797,7 +9818,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9812,7 +9833,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9833,7 +9854,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>203</v>
@@ -9847,7 +9868,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9862,7 +9883,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9883,7 +9904,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>203</v>
@@ -9897,7 +9918,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9912,7 +9933,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9933,7 +9954,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>203</v>
@@ -9947,7 +9968,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9962,7 +9983,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -9983,7 +10004,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>203</v>
@@ -9997,7 +10018,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -10012,7 +10033,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -10033,7 +10054,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>203</v>
@@ -10047,7 +10068,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10062,7 +10083,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -10083,7 +10104,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>203</v>
@@ -10097,7 +10118,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -10112,7 +10133,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -10133,7 +10154,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>203</v>
@@ -10147,7 +10168,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -10162,7 +10183,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -10183,7 +10204,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>203</v>
@@ -10197,7 +10218,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -10212,7 +10233,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -10233,7 +10254,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>203</v>
@@ -10247,7 +10268,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -10262,7 +10283,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -10283,7 +10304,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>203</v>
@@ -10297,7 +10318,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -10312,7 +10333,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -10333,7 +10354,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>203</v>
@@ -10347,7 +10368,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -10362,7 +10383,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -10383,7 +10404,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>203</v>
@@ -10397,7 +10418,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -10412,7 +10433,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -10433,7 +10454,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>203</v>
@@ -10447,7 +10468,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10462,7 +10483,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -10483,7 +10504,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>203</v>
@@ -10497,7 +10518,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10512,7 +10533,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10533,7 +10554,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>203</v>
@@ -10547,7 +10568,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10562,7 +10583,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10583,7 +10604,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>203</v>
@@ -10597,7 +10618,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10612,7 +10633,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10633,7 +10654,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>203</v>
@@ -10647,7 +10668,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10662,7 +10683,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10683,7 +10704,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>203</v>
@@ -10697,7 +10718,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10712,7 +10733,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10733,7 +10754,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>203</v>
@@ -10945,7 +10966,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -10958,13 +10979,13 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10981,28 +11002,28 @@
         <v>109</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11057,22 +11078,22 @@
         <v>119</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>122</v>
@@ -11101,7 +11122,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -11139,7 +11160,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -11177,7 +11198,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -11215,7 +11236,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -11253,7 +11274,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -11291,7 +11312,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -11329,7 +11350,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -11367,7 +11388,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -11405,7 +11426,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -13350,7 +13371,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E465"/>
+  <dimension ref="A1:E470"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -21251,6 +21272,91 @@
         <v>824</v>
       </c>
       <c r="E465" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>462</v>
+      </c>
+      <c r="B466">
+        <v>55020</v>
+      </c>
+      <c r="C466" t="s">
+        <v>825</v>
+      </c>
+      <c r="D466" t="s">
+        <v>825</v>
+      </c>
+      <c r="E466" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>463</v>
+      </c>
+      <c r="B467">
+        <v>55021</v>
+      </c>
+      <c r="C467" t="s">
+        <v>826</v>
+      </c>
+      <c r="D467" t="s">
+        <v>826</v>
+      </c>
+      <c r="E467" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>464</v>
+      </c>
+      <c r="B468">
+        <v>55022</v>
+      </c>
+      <c r="C468" t="s">
+        <v>827</v>
+      </c>
+      <c r="D468" t="s">
+        <v>827</v>
+      </c>
+      <c r="E468" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>465</v>
+      </c>
+      <c r="B469">
+        <v>55023</v>
+      </c>
+      <c r="C469" t="s">
+        <v>828</v>
+      </c>
+      <c r="D469" t="s">
+        <v>828</v>
+      </c>
+      <c r="E469" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>466</v>
+      </c>
+      <c r="B470">
+        <v>55024</v>
+      </c>
+      <c r="C470" t="s">
+        <v>829</v>
+      </c>
+      <c r="D470" t="s">
+        <v>829</v>
+      </c>
+      <c r="E470" t="s">
         <v>800</v>
       </c>
     </row>
@@ -21291,22 +21397,22 @@
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -21343,22 +21449,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -21369,7 +21475,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -21395,7 +21501,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -21421,7 +21527,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -21447,7 +21553,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -21473,7 +21579,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -21499,7 +21605,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -21525,7 +21631,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -21569,7 +21675,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -21582,28 +21688,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>112</v>
@@ -21623,13 +21729,13 @@
         <v>113</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>113</v>
@@ -21646,22 +21752,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>122</v>
@@ -21693,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -21722,7 +21828,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -21809,7 +21915,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -21838,7 +21944,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -21874,7 +21980,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -21896,13 +22002,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>400</v>
@@ -21911,25 +22017,25 @@
         <v>403</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -21984,40 +22090,40 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -30846,7 +30952,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>104</v>
@@ -30854,7 +30960,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -30870,22 +30976,22 @@
         <v>107</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>112</v>
@@ -30940,16 +31046,16 @@
         <v>119</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>122</v>
@@ -30978,13 +31084,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -31010,13 +31116,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -31042,13 +31148,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -31074,13 +31180,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -31106,13 +31212,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -31147,13 +31253,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31166,7 +31272,7 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>297</v>
@@ -31175,19 +31281,19 @@
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>301</v>
@@ -31236,25 +31342,25 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>167</v>
@@ -33220,13 +33326,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>112</v>
@@ -33263,16 +33369,16 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>302</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>122</v>
@@ -33528,22 +33634,22 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="D2" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E2" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="F2" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G2" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="H2" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="I2" t="s">
         <v>112</v>
@@ -33586,22 +33692,22 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D4" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="E4" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="F4" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G4" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="H4" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="I4" t="s">
         <v>122</v>
@@ -33761,12 +33867,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="F1" t="s">
         <v>104</v>
@@ -33780,19 +33886,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="D2" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="E2" t="s">
         <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="G2" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -33826,19 +33932,19 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D4" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="E4" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F4" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="G4" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -33849,10 +33955,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D5" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -33872,10 +33978,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D6" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -33895,10 +34001,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D7" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -33918,10 +34024,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D8" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -33941,10 +34047,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D9" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -33964,10 +34070,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D10" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -33987,10 +34093,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D11" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -34010,10 +34116,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D12" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -34033,10 +34139,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D13" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -34056,10 +34162,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D14" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -34079,10 +34185,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D15" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -34102,10 +34208,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D16" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -34125,10 +34231,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D17" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -34148,10 +34254,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D18" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -34171,10 +34277,10 @@
         <v>33015</v>
       </c>
       <c r="C19" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D19" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -34194,10 +34300,10 @@
         <v>33016</v>
       </c>
       <c r="C20" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D20" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -34217,10 +34323,10 @@
         <v>33017</v>
       </c>
       <c r="C21" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D21" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
@@ -34230,6 +34336,52 @@
       </c>
       <c r="G21">
         <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <v>33018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22">
+        <v>55020</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23">
+        <v>33019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23">
+        <v>55024</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4107" uniqueCount="1084">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2364,10 +2364,10 @@
     <t>ProfileUi</t>
   </si>
   <si>
-    <t>데이터 구조가 변경되어 기존 진행 상황을 이어갈 수 없습니다.</t>
-  </si>
-  <si>
-    <t>The save structure changed, so previous progress can't be carried over.</t>
+    <t>버전이 올라가며 기존 진행 상황이 초기화되었습니다.</t>
+  </si>
+  <si>
+    <t>Progress was reset because the app was updated to a new version.</t>
   </si>
   <si>
     <t>이름을 입력해주세요</t>
@@ -2524,6 +2524,15 @@
   </si>
   <si>
     <t>로고·로딩 화면 리디자인</t>
+  </si>
+  <si>
+    <t>버전이 올라갈 때마다 진행 상황이 초기화됩니다.</t>
+  </si>
+  <si>
+    <t>Progress resets with every version bump.</t>
+  </si>
+  <si>
+    <t>스탯 화면 표시 정리</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3782,27 +3791,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E1" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="F1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B2" t="s">
         <v>105</v>
@@ -3822,7 +3831,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -3842,13 +3851,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B4" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C4" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -3862,13 +3871,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -3882,10 +3891,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B6" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3897,18 +3906,18 @@
         <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B7" t="s">
         <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3922,13 +3931,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -3942,13 +3951,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B9" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C9" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -3962,13 +3971,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B10" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C10" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -3982,13 +3991,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B11" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C11" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -4002,13 +4011,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B12" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C12" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -4022,13 +4031,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B13" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C13" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -4042,13 +4051,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4062,19 +4071,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B15" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C15" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="F15" t="s">
         <v>203</v>
@@ -4082,7 +4091,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
@@ -4102,7 +4111,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
@@ -4122,13 +4131,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B18" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C18" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -4142,7 +4151,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B19" t="s">
         <v>297</v>
@@ -4162,13 +4171,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -4182,13 +4191,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B21" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C21" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -4202,13 +4211,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B22" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C22" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -4217,15 +4226,15 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B23" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4237,18 +4246,18 @@
         <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B24" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C24" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -4257,15 +4266,15 @@
         <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B25" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
@@ -4282,7 +4291,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B26" t="s">
         <v>301</v>
@@ -4302,7 +4311,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B27" t="s">
         <v>105</v>
@@ -4322,7 +4331,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B28" t="s">
         <v>106</v>
@@ -4342,7 +4351,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
@@ -4362,7 +4371,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -4382,7 +4391,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -4402,7 +4411,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
@@ -4422,7 +4431,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -4442,7 +4451,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B34" t="s">
         <v>112</v>
@@ -4462,7 +4471,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B35" t="s">
         <v>105</v>
@@ -4482,7 +4491,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
@@ -4502,7 +4511,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -4522,7 +4531,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -4542,7 +4551,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -4562,7 +4571,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B40" t="s">
         <v>112</v>
@@ -4582,7 +4591,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
@@ -4602,7 +4611,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B42" t="s">
         <v>106</v>
@@ -4622,19 +4631,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B43" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C43" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D43" t="s">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F43" t="s">
         <v>203</v>
@@ -4642,13 +4651,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B44" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C44" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4657,32 +4666,32 @@
         <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B45" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C45" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="F45" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B46" t="s">
         <v>361</v>
@@ -4697,24 +4706,24 @@
         <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B47" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C47" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F47" t="s">
         <v>104</v>
@@ -4722,19 +4731,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B48" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C48" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D48" t="s">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F48" t="s">
         <v>203</v>
@@ -4742,10 +4751,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B49" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C49" t="s">
         <v>298</v>
@@ -4754,7 +4763,7 @@
         <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="F49" t="s">
         <v>203</v>
@@ -4762,19 +4771,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D50" t="s">
         <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="F50" t="s">
         <v>104</v>
@@ -4782,19 +4791,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B51" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C51" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D51" t="s">
         <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
@@ -4802,13 +4811,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B52" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C52" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -4822,13 +4831,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B53" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C53" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -4842,13 +4851,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B54" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C54" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D54" t="s">
         <v>145</v>
@@ -4862,13 +4871,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B55" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C55" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D55" t="s">
         <v>114</v>
@@ -4877,12 +4886,12 @@
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -4902,7 +4911,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
@@ -4922,7 +4931,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B58" t="s">
         <v>106</v>
@@ -4942,7 +4951,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B59" t="s">
         <v>132</v>
@@ -4962,7 +4971,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -4982,7 +4991,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B61" t="s">
         <v>134</v>
@@ -5002,7 +5011,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B62" t="s">
         <v>135</v>
@@ -5022,7 +5031,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B63" t="s">
         <v>136</v>
@@ -5042,7 +5051,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B64" t="s">
         <v>137</v>
@@ -5062,7 +5071,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -5082,7 +5091,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -5102,7 +5111,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B67" t="s">
         <v>140</v>
@@ -5122,7 +5131,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
@@ -5142,7 +5151,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B69" t="s">
         <v>142</v>
@@ -5162,7 +5171,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B70" t="s">
         <v>143</v>
@@ -5182,7 +5191,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B71" t="s">
         <v>144</v>
@@ -5202,7 +5211,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B72" t="s">
         <v>112</v>
@@ -5222,7 +5231,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
@@ -5242,7 +5251,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
@@ -5262,7 +5271,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B75" t="s">
         <v>361</v>
@@ -5277,12 +5286,12 @@
         <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B76" t="s">
         <v>109</v>
@@ -5302,19 +5311,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B77" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C77" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="F77" t="s">
         <v>104</v>
@@ -5322,19 +5331,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B78" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C78" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F78" t="s">
         <v>104</v>
@@ -5342,19 +5351,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B79" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C79" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D79" t="s">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F79" t="s">
         <v>203</v>
@@ -5362,13 +5371,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B80" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C80" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D80" t="s">
         <v>115</v>
@@ -5377,18 +5386,18 @@
         <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B81" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C81" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -5402,13 +5411,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B82" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C82" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -5422,7 +5431,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -5442,10 +5451,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B84" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -5457,12 +5466,12 @@
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -5482,7 +5491,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B86" t="s">
         <v>106</v>
@@ -5502,7 +5511,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -5522,7 +5531,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B88" t="s">
         <v>160</v>
@@ -5542,7 +5551,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B89" t="s">
         <v>112</v>
@@ -5562,7 +5571,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B90" t="s">
         <v>105</v>
@@ -5582,7 +5591,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B91" t="s">
         <v>106</v>
@@ -5602,19 +5611,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B92" t="s">
         <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="F92" t="s">
         <v>203</v>
@@ -5622,10 +5631,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B93" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C93" t="s">
         <v>302</v>
@@ -5642,13 +5651,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B94" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C94" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D94" t="s">
         <v>145</v>
@@ -5662,13 +5671,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B95" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C95" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
@@ -5682,7 +5691,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B96" t="s">
         <v>112</v>
@@ -5702,7 +5711,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B97" t="s">
         <v>105</v>
@@ -5722,7 +5731,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B98" t="s">
         <v>106</v>
@@ -5742,13 +5751,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B99" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C99" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
@@ -5762,13 +5771,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B100" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C100" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
@@ -5782,13 +5791,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B101" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C101" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
@@ -5802,13 +5811,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B102" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C102" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D102" t="s">
         <v>113</v>
@@ -5822,13 +5831,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B103" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C103" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D103" t="s">
         <v>113</v>
@@ -5842,13 +5851,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B104" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C104" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D104" t="s">
         <v>113</v>
@@ -5862,7 +5871,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B105" t="s">
         <v>112</v>
@@ -5925,10 +5934,10 @@
         <v>800</v>
       </c>
       <c r="B108" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C108" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -5945,10 +5954,10 @@
         <v>800</v>
       </c>
       <c r="B109" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C109" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -5968,7 +5977,7 @@
         <v>234</v>
       </c>
       <c r="C110" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D110" t="s">
         <v>115</v>
@@ -5977,7 +5986,7 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5985,10 +5994,10 @@
         <v>800</v>
       </c>
       <c r="B111" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C111" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D111" t="s">
         <v>113</v>
@@ -6005,10 +6014,10 @@
         <v>800</v>
       </c>
       <c r="B112" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C112" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D112" t="s">
         <v>113</v>
@@ -6022,7 +6031,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B113" t="s">
         <v>105</v>
@@ -6042,7 +6051,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B114" t="s">
         <v>106</v>
@@ -6062,7 +6071,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -6082,7 +6091,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B116" t="s">
         <v>107</v>
@@ -6102,7 +6111,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B117" t="s">
         <v>164</v>
@@ -6122,7 +6131,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B118" t="s">
         <v>165</v>
@@ -6142,7 +6151,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B119" t="s">
         <v>112</v>
@@ -6162,7 +6171,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
@@ -6182,7 +6191,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B121" t="s">
         <v>106</v>
@@ -6202,7 +6211,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B122" t="s">
         <v>232</v>
@@ -6222,7 +6231,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B123" t="s">
         <v>233</v>
@@ -6242,7 +6251,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B124" t="s">
         <v>234</v>
@@ -6262,7 +6271,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B125" t="s">
         <v>105</v>
@@ -6282,7 +6291,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -6302,13 +6311,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B127" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C127" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D127" t="s">
         <v>114</v>
@@ -6322,13 +6331,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B128" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C128" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -6342,13 +6351,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B129" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C129" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -6362,13 +6371,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B130" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C130" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -6382,13 +6391,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B131" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C131" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -6402,13 +6411,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B132" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C132" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D132" t="s">
         <v>113</v>
@@ -6422,10 +6431,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B133" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C133" t="s">
         <v>116</v>
@@ -6442,7 +6451,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B134" t="s">
         <v>117</v>
@@ -6462,13 +6471,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B135" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C135" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -6477,18 +6486,18 @@
         <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B136" t="s">
         <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D136" t="s">
         <v>113</v>
@@ -6502,16 +6511,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B137" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C137" t="s">
+        <v>843</v>
+      </c>
+      <c r="D137" t="s">
         <v>840</v>
-      </c>
-      <c r="D137" t="s">
-        <v>837</v>
       </c>
       <c r="E137" t="s">
         <v>203</v>
@@ -6522,16 +6531,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B138" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C138" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D138" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E138" t="s">
         <v>203</v>
@@ -6542,16 +6551,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B139" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C139" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D139" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E139" t="s">
         <v>203</v>
@@ -6562,13 +6571,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B140" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C140" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D140" t="s">
         <v>113</v>
@@ -6582,7 +6591,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B141" t="s">
         <v>112</v>
@@ -6602,7 +6611,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B142" t="s">
         <v>105</v>
@@ -6622,7 +6631,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B143" t="s">
         <v>106</v>
@@ -6642,7 +6651,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B144" t="s">
         <v>107</v>
@@ -6662,10 +6671,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B145" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -6677,12 +6686,12 @@
         <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B146" t="s">
         <v>109</v>
@@ -6702,13 +6711,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B147" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C147" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D147" t="s">
         <v>145</v>
@@ -6722,13 +6731,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B148" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C148" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D148" t="s">
         <v>145</v>
@@ -6742,13 +6751,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B149" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C149" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D149" t="s">
         <v>114</v>
@@ -6757,18 +6766,18 @@
         <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B150" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C150" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D150" t="s">
         <v>113</v>
@@ -6782,7 +6791,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B151" t="s">
         <v>112</v>
@@ -6833,13 +6842,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>104</v>
@@ -6856,7 +6865,7 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="P1" s="8"/>
     </row>
@@ -6868,43 +6877,43 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>361</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="P2" s="9" t="s">
         <v>112</v>
@@ -6968,43 +6977,43 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>362</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>122</v>
@@ -7018,7 +7027,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -7033,7 +7042,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
@@ -7054,7 +7063,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>203</v>
@@ -7068,7 +7077,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7083,7 +7092,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I6" s="12">
         <v>2</v>
@@ -7104,7 +7113,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>203</v>
@@ -7118,7 +7127,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -7133,7 +7142,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I7" s="12">
         <v>3</v>
@@ -7154,7 +7163,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>203</v>
@@ -7168,7 +7177,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -7183,7 +7192,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I8" s="12">
         <v>4</v>
@@ -7204,7 +7213,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>203</v>
@@ -7218,7 +7227,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -7233,7 +7242,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I9" s="12">
         <v>5</v>
@@ -7254,7 +7263,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>203</v>
@@ -7268,7 +7277,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -7283,7 +7292,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -7304,7 +7313,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>203</v>
@@ -7318,7 +7327,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -7333,7 +7342,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I11" s="12">
         <v>2</v>
@@ -7354,7 +7363,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>203</v>
@@ -7368,7 +7377,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -7383,7 +7392,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I12" s="12">
         <v>3</v>
@@ -7404,7 +7413,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>203</v>
@@ -7418,7 +7427,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -7433,7 +7442,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I13" s="12">
         <v>4</v>
@@ -7454,7 +7463,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>203</v>
@@ -7468,7 +7477,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7483,7 +7492,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I14" s="12">
         <v>5</v>
@@ -7504,7 +7513,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>203</v>
@@ -7518,7 +7527,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7533,7 +7542,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I15" s="12">
         <v>1</v>
@@ -7554,7 +7563,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>203</v>
@@ -7568,7 +7577,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7583,7 +7592,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I16" s="12">
         <v>2</v>
@@ -7604,7 +7613,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>203</v>
@@ -7618,7 +7627,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7633,7 +7642,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I17" s="12">
         <v>3</v>
@@ -7654,7 +7663,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>203</v>
@@ -7668,7 +7677,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7683,7 +7692,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I18" s="12">
         <v>4</v>
@@ -7704,7 +7713,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>203</v>
@@ -7718,7 +7727,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7733,7 +7742,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I19" s="12">
         <v>5</v>
@@ -7754,7 +7763,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>203</v>
@@ -7768,7 +7777,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7783,7 +7792,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
@@ -7804,7 +7813,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>203</v>
@@ -7818,7 +7827,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7833,7 +7842,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
@@ -7854,7 +7863,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>203</v>
@@ -7868,7 +7877,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7883,7 +7892,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I22" s="12">
         <v>3</v>
@@ -7904,7 +7913,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>203</v>
@@ -7918,7 +7927,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7933,7 +7942,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I23" s="12">
         <v>4</v>
@@ -7954,7 +7963,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>203</v>
@@ -7968,7 +7977,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -7983,7 +7992,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I24" s="12">
         <v>5</v>
@@ -8004,7 +8013,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>203</v>
@@ -8018,7 +8027,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -8033,7 +8042,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I25" s="12">
         <v>1</v>
@@ -8054,7 +8063,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>203</v>
@@ -8068,7 +8077,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8083,7 +8092,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I26" s="12">
         <v>2</v>
@@ -8104,7 +8113,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>203</v>
@@ -8118,7 +8127,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -8133,7 +8142,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I27" s="12">
         <v>3</v>
@@ -8154,7 +8163,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>203</v>
@@ -8168,7 +8177,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -8183,7 +8192,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I28" s="12">
         <v>4</v>
@@ -8204,7 +8213,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>203</v>
@@ -8218,7 +8227,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -8233,7 +8242,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I29" s="12">
         <v>5</v>
@@ -8254,7 +8263,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>203</v>
@@ -8268,7 +8277,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -8283,7 +8292,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I30" s="12">
         <v>1</v>
@@ -8304,7 +8313,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>203</v>
@@ -8318,7 +8327,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -8333,7 +8342,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I31" s="12">
         <v>2</v>
@@ -8354,7 +8363,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>203</v>
@@ -8368,7 +8377,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -8383,7 +8392,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I32" s="12">
         <v>3</v>
@@ -8404,7 +8413,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>203</v>
@@ -8418,7 +8427,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -8433,7 +8442,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I33" s="12">
         <v>4</v>
@@ -8454,7 +8463,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>203</v>
@@ -8468,7 +8477,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8483,7 +8492,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I34" s="12">
         <v>5</v>
@@ -8504,7 +8513,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>203</v>
@@ -8518,7 +8527,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8533,7 +8542,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I35" s="12">
         <v>1</v>
@@ -8554,7 +8563,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>203</v>
@@ -8568,7 +8577,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8583,7 +8592,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I36" s="12">
         <v>2</v>
@@ -8604,7 +8613,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>203</v>
@@ -8618,7 +8627,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8633,7 +8642,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I37" s="12">
         <v>3</v>
@@ -8654,7 +8663,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>203</v>
@@ -8668,7 +8677,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8683,7 +8692,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I38" s="12">
         <v>4</v>
@@ -8704,7 +8713,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>203</v>
@@ -8718,7 +8727,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8733,7 +8742,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I39" s="12">
         <v>5</v>
@@ -8754,7 +8763,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>203</v>
@@ -8768,7 +8777,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8783,7 +8792,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
@@ -8804,7 +8813,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>203</v>
@@ -8818,7 +8827,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8833,7 +8842,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I41" s="12">
         <v>2</v>
@@ -8854,7 +8863,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>203</v>
@@ -8868,7 +8877,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8883,7 +8892,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I42" s="12">
         <v>3</v>
@@ -8904,7 +8913,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>203</v>
@@ -8918,7 +8927,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8933,7 +8942,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I43" s="12">
         <v>4</v>
@@ -8954,7 +8963,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>203</v>
@@ -8968,7 +8977,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -8983,7 +8992,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I44" s="12">
         <v>5</v>
@@ -9004,7 +9013,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>203</v>
@@ -9018,7 +9027,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -9033,7 +9042,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I45" s="12">
         <v>1</v>
@@ -9054,7 +9063,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>203</v>
@@ -9068,7 +9077,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9083,7 +9092,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I46" s="12">
         <v>2</v>
@@ -9104,7 +9113,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>203</v>
@@ -9118,7 +9127,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -9133,7 +9142,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I47" s="12">
         <v>3</v>
@@ -9154,7 +9163,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>203</v>
@@ -9168,7 +9177,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -9183,7 +9192,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I48" s="12">
         <v>4</v>
@@ -9204,7 +9213,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>203</v>
@@ -9218,7 +9227,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -9233,7 +9242,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I49" s="12">
         <v>5</v>
@@ -9254,7 +9263,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>203</v>
@@ -9268,7 +9277,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -9283,7 +9292,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
@@ -9304,7 +9313,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>203</v>
@@ -9318,7 +9327,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -9333,7 +9342,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I51" s="12">
         <v>2</v>
@@ -9354,7 +9363,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>203</v>
@@ -9368,7 +9377,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -9383,7 +9392,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I52" s="12">
         <v>3</v>
@@ -9404,7 +9413,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>203</v>
@@ -9418,7 +9427,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -9433,7 +9442,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I53" s="12">
         <v>4</v>
@@ -9454,7 +9463,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>203</v>
@@ -9468,7 +9477,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9483,7 +9492,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I54" s="12">
         <v>5</v>
@@ -9504,7 +9513,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>203</v>
@@ -9518,7 +9527,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9533,7 +9542,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I55" s="12">
         <v>1</v>
@@ -9554,7 +9563,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>203</v>
@@ -9568,7 +9577,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9583,7 +9592,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I56" s="12">
         <v>2</v>
@@ -9604,7 +9613,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>203</v>
@@ -9618,7 +9627,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9633,7 +9642,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I57" s="12">
         <v>3</v>
@@ -9654,7 +9663,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>203</v>
@@ -9668,7 +9677,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9683,7 +9692,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I58" s="12">
         <v>4</v>
@@ -9704,7 +9713,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>203</v>
@@ -9718,7 +9727,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9733,7 +9742,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I59" s="12">
         <v>5</v>
@@ -9754,7 +9763,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>203</v>
@@ -9768,7 +9777,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9783,7 +9792,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I60" s="12">
         <v>1</v>
@@ -9804,7 +9813,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>203</v>
@@ -9818,7 +9827,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9833,7 +9842,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I61" s="12">
         <v>2</v>
@@ -9854,7 +9863,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>203</v>
@@ -9868,7 +9877,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9883,7 +9892,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I62" s="12">
         <v>3</v>
@@ -9904,7 +9913,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>203</v>
@@ -9918,7 +9927,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9933,7 +9942,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I63" s="12">
         <v>4</v>
@@ -9954,7 +9963,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>203</v>
@@ -9968,7 +9977,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -9983,7 +9992,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="I64" s="12">
         <v>5</v>
@@ -10004,7 +10013,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>203</v>
@@ -10018,7 +10027,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -10033,7 +10042,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I65" s="12">
         <v>1</v>
@@ -10054,7 +10063,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>203</v>
@@ -10068,7 +10077,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10083,7 +10092,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -10104,7 +10113,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>203</v>
@@ -10118,7 +10127,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -10133,7 +10142,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I67" s="12">
         <v>3</v>
@@ -10154,7 +10163,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>203</v>
@@ -10168,7 +10177,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -10183,7 +10192,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I68" s="12">
         <v>4</v>
@@ -10204,7 +10213,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>203</v>
@@ -10218,7 +10227,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -10233,7 +10242,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I69" s="12">
         <v>5</v>
@@ -10254,7 +10263,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>203</v>
@@ -10268,7 +10277,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -10283,7 +10292,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I70" s="12">
         <v>1</v>
@@ -10304,7 +10313,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>203</v>
@@ -10318,7 +10327,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -10333,7 +10342,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I71" s="12">
         <v>2</v>
@@ -10354,7 +10363,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>203</v>
@@ -10368,7 +10377,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -10383,7 +10392,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I72" s="12">
         <v>3</v>
@@ -10404,7 +10413,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>203</v>
@@ -10418,7 +10427,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -10433,7 +10442,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I73" s="12">
         <v>4</v>
@@ -10454,7 +10463,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>203</v>
@@ -10468,7 +10477,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10483,7 +10492,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="I74" s="12">
         <v>5</v>
@@ -10504,7 +10513,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>203</v>
@@ -10518,7 +10527,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10533,7 +10542,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I75" s="12">
         <v>1</v>
@@ -10554,7 +10563,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>203</v>
@@ -10568,7 +10577,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10583,7 +10592,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I76" s="12">
         <v>2</v>
@@ -10604,7 +10613,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>203</v>
@@ -10618,7 +10627,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10633,7 +10642,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I77" s="12">
         <v>3</v>
@@ -10654,7 +10663,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>203</v>
@@ -10668,7 +10677,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10683,7 +10692,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I78" s="12">
         <v>4</v>
@@ -10704,7 +10713,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>203</v>
@@ -10718,7 +10727,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10733,7 +10742,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="I79" s="12">
         <v>5</v>
@@ -10754,7 +10763,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>203</v>
@@ -10966,7 +10975,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -10979,13 +10988,13 @@
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -11002,28 +11011,28 @@
         <v>109</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11078,22 +11087,22 @@
         <v>119</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>122</v>
@@ -11122,7 +11131,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -11160,7 +11169,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -11198,7 +11207,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -11236,7 +11245,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -11274,7 +11283,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -11312,7 +11321,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -11350,7 +11359,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -11388,7 +11397,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -11426,7 +11435,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -13371,7 +13380,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E470"/>
+  <dimension ref="A1:E472"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -21357,6 +21366,40 @@
         <v>829</v>
       </c>
       <c r="E470" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>467</v>
+      </c>
+      <c r="B471">
+        <v>55025</v>
+      </c>
+      <c r="C471" t="s">
+        <v>830</v>
+      </c>
+      <c r="D471" t="s">
+        <v>831</v>
+      </c>
+      <c r="E471" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>468</v>
+      </c>
+      <c r="B472">
+        <v>55026</v>
+      </c>
+      <c r="C472" t="s">
+        <v>832</v>
+      </c>
+      <c r="D472" t="s">
+        <v>832</v>
+      </c>
+      <c r="E472" t="s">
         <v>800</v>
       </c>
     </row>
@@ -21397,22 +21440,22 @@
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -21449,22 +21492,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -21475,7 +21518,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D5" s="12">
         <v>8</v>
@@ -21501,7 +21544,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D6" s="12">
         <v>10</v>
@@ -21527,7 +21570,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -21553,7 +21596,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D8" s="12">
         <v>30</v>
@@ -21579,7 +21622,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D9" s="12">
         <v>60</v>
@@ -21605,7 +21648,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D10" s="12">
         <v>120</v>
@@ -21631,7 +21674,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D11" s="12">
         <v>240</v>
@@ -21675,7 +21718,7 @@
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>104</v>
@@ -21688,28 +21731,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>112</v>
@@ -21729,13 +21772,13 @@
         <v>113</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>113</v>
@@ -21752,22 +21795,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>122</v>
@@ -21799,7 +21842,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -21828,7 +21871,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -21915,7 +21958,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -21944,7 +21987,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -21980,7 +22023,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -22002,13 +22045,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>400</v>
@@ -22017,25 +22060,25 @@
         <v>403</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -22090,40 +22133,40 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -30952,7 +30995,7 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>104</v>
@@ -30960,7 +31003,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -30976,22 +31019,22 @@
         <v>107</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>112</v>
@@ -31046,16 +31089,16 @@
         <v>119</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>122</v>
@@ -31084,13 +31127,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I5" s="12">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -31116,13 +31159,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I6" s="12">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -31148,13 +31191,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I7" s="12">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -31180,13 +31223,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I8" s="12">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -31212,13 +31255,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I9" s="12">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -31253,13 +31296,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31272,7 +31315,7 @@
         <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>297</v>
@@ -31281,19 +31324,19 @@
         <v>109</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>301</v>
@@ -31342,25 +31385,25 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>298</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>167</v>
@@ -33326,13 +33369,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>112</v>
@@ -33369,16 +33412,16 @@
         <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>302</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>122</v>
@@ -33634,22 +33677,22 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="F2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G2" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="H2" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="I2" t="s">
         <v>112</v>
@@ -33692,22 +33735,22 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="E4" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="F4" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="G4" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="H4" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="I4" t="s">
         <v>122</v>
@@ -33867,12 +33910,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="F1" t="s">
         <v>104</v>
@@ -33886,19 +33929,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D2" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E2" t="s">
         <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="G2" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -33932,19 +33975,19 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D4" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="F4" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="G4" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -33955,10 +33998,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -33978,10 +34021,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D6" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -34001,10 +34044,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D7" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -34024,10 +34067,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D8" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -34047,10 +34090,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D9" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -34070,10 +34113,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D10" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -34093,10 +34136,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D11" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -34116,10 +34159,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D12" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -34139,10 +34182,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D13" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -34162,10 +34205,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D14" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -34185,10 +34228,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D15" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -34208,10 +34251,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D16" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -34231,10 +34274,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D17" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -34254,10 +34297,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D18" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -34277,10 +34320,10 @@
         <v>33015</v>
       </c>
       <c r="C19" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D19" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -34300,10 +34343,10 @@
         <v>33016</v>
       </c>
       <c r="C20" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D20" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -34323,10 +34366,10 @@
         <v>33017</v>
       </c>
       <c r="C21" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D21" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
@@ -34346,10 +34389,10 @@
         <v>33018</v>
       </c>
       <c r="C22" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D22" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="E22" t="s">
         <v>91</v>
@@ -34369,10 +34412,10 @@
         <v>33019</v>
       </c>
       <c r="C23" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D23" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="E23" t="s">
         <v>94</v>
@@ -34382,6 +34425,29 @@
       </c>
       <c r="G23">
         <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24">
+        <v>33020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24">
+        <v>55026</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4516" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4622" uniqueCount="1088">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -2542,6 +2542,9 @@
   </si>
   <si>
     <t>Jump to current</t>
+  </si>
+  <si>
+    <t>스테이지 300개로 확장</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -3800,27 +3803,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B2" t="s">
         <v>105</v>
@@ -3840,7 +3843,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -3860,13 +3863,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -3880,13 +3883,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B5" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C5" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -3900,10 +3903,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -3915,18 +3918,18 @@
         <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B7" t="s">
         <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3940,13 +3943,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -3960,13 +3963,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B9" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -3980,13 +3983,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B10" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C10" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -4000,13 +4003,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C11" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -4020,13 +4023,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B12" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C12" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
@@ -4040,13 +4043,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B13" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C13" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -4060,13 +4063,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4080,19 +4083,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B15" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C15" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F15" t="s">
         <v>203</v>
@@ -4100,7 +4103,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B16" t="s">
         <v>105</v>
@@ -4120,7 +4123,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B17" t="s">
         <v>106</v>
@@ -4140,13 +4143,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B18" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C18" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -4160,7 +4163,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B19" t="s">
         <v>297</v>
@@ -4180,13 +4183,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -4200,13 +4203,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B21" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C21" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -4220,13 +4223,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B22" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C22" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -4235,15 +4238,15 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B23" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -4255,18 +4258,18 @@
         <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B24" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C24" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -4275,15 +4278,15 @@
         <v>203</v>
       </c>
       <c r="F24" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B25" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C25" t="s">
         <v>167</v>
@@ -4300,7 +4303,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B26" t="s">
         <v>301</v>
@@ -4320,7 +4323,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B27" t="s">
         <v>105</v>
@@ -4340,7 +4343,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B28" t="s">
         <v>106</v>
@@ -4360,7 +4363,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B29" t="s">
         <v>107</v>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -4400,7 +4403,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -4420,7 +4423,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
@@ -4440,7 +4443,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -4460,7 +4463,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B34" t="s">
         <v>112</v>
@@ -4480,7 +4483,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B35" t="s">
         <v>105</v>
@@ -4500,7 +4503,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B37" t="s">
         <v>126</v>
@@ -4540,7 +4543,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B38" t="s">
         <v>127</v>
@@ -4560,7 +4563,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B39" t="s">
         <v>128</v>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B40" t="s">
         <v>112</v>
@@ -4600,7 +4603,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B41" t="s">
         <v>105</v>
@@ -4620,7 +4623,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B42" t="s">
         <v>106</v>
@@ -4640,19 +4643,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B43" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C43" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D43" t="s">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F43" t="s">
         <v>203</v>
@@ -4660,13 +4663,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B44" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C44" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -4675,32 +4678,32 @@
         <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B45" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C45" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F45" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B46" t="s">
         <v>361</v>
@@ -4715,24 +4718,24 @@
         <v>203</v>
       </c>
       <c r="F46" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B47" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C47" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F47" t="s">
         <v>104</v>
@@ -4740,19 +4743,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B48" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C48" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D48" t="s">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F48" t="s">
         <v>203</v>
@@ -4760,10 +4763,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B49" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C49" t="s">
         <v>298</v>
@@ -4772,7 +4775,7 @@
         <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F49" t="s">
         <v>203</v>
@@ -4780,19 +4783,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D50" t="s">
         <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F50" t="s">
         <v>104</v>
@@ -4800,19 +4803,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B51" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C51" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D51" t="s">
         <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
@@ -4820,13 +4823,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B52" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C52" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -4840,13 +4843,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B53" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C53" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -4860,13 +4863,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B54" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C54" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D54" t="s">
         <v>145</v>
@@ -4880,13 +4883,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B55" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C55" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D55" t="s">
         <v>114</v>
@@ -4895,12 +4898,12 @@
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -4920,7 +4923,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
@@ -4940,7 +4943,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B58" t="s">
         <v>106</v>
@@ -4960,7 +4963,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B59" t="s">
         <v>132</v>
@@ -4980,7 +4983,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -5000,7 +5003,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B61" t="s">
         <v>134</v>
@@ -5020,7 +5023,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B62" t="s">
         <v>135</v>
@@ -5040,7 +5043,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B63" t="s">
         <v>136</v>
@@ -5060,7 +5063,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B64" t="s">
         <v>137</v>
@@ -5080,7 +5083,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -5100,7 +5103,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -5120,7 +5123,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B67" t="s">
         <v>140</v>
@@ -5140,7 +5143,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
@@ -5160,7 +5163,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B69" t="s">
         <v>142</v>
@@ -5180,7 +5183,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B70" t="s">
         <v>143</v>
@@ -5200,7 +5203,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B71" t="s">
         <v>144</v>
@@ -5220,7 +5223,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B72" t="s">
         <v>112</v>
@@ -5240,7 +5243,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
@@ -5260,7 +5263,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B75" t="s">
         <v>361</v>
@@ -5295,12 +5298,12 @@
         <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B76" t="s">
         <v>109</v>
@@ -5320,19 +5323,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B77" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C77" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F77" t="s">
         <v>104</v>
@@ -5340,19 +5343,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B78" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C78" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F78" t="s">
         <v>104</v>
@@ -5360,19 +5363,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B79" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C79" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D79" t="s">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F79" t="s">
         <v>203</v>
@@ -5380,13 +5383,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B80" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C80" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D80" t="s">
         <v>115</v>
@@ -5395,18 +5398,18 @@
         <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B81" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C81" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -5420,13 +5423,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B82" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C82" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -5440,7 +5443,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -5460,10 +5463,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B84" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -5475,12 +5478,12 @@
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -5500,7 +5503,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B86" t="s">
         <v>106</v>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B87" t="s">
         <v>159</v>
@@ -5540,7 +5543,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B88" t="s">
         <v>160</v>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B89" t="s">
         <v>112</v>
@@ -5580,7 +5583,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B90" t="s">
         <v>105</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B91" t="s">
         <v>106</v>
@@ -5620,19 +5623,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B92" t="s">
         <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F92" t="s">
         <v>203</v>
@@ -5640,10 +5643,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B93" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C93" t="s">
         <v>302</v>
@@ -5660,13 +5663,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B94" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C94" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D94" t="s">
         <v>145</v>
@@ -5680,13 +5683,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B95" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C95" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
@@ -5700,7 +5703,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B96" t="s">
         <v>112</v>
@@ -5720,7 +5723,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B97" t="s">
         <v>105</v>
@@ -5740,7 +5743,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B98" t="s">
         <v>106</v>
@@ -5760,13 +5763,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B99" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C99" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
@@ -5780,13 +5783,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B100" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C100" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
@@ -5800,13 +5803,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B101" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C101" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
@@ -5820,13 +5823,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B102" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C102" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D102" t="s">
         <v>113</v>
@@ -5840,13 +5843,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B103" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C103" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D103" t="s">
         <v>113</v>
@@ -5860,13 +5863,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B104" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C104" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D104" t="s">
         <v>113</v>
@@ -5880,7 +5883,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B105" t="s">
         <v>112</v>
@@ -5943,10 +5946,10 @@
         <v>800</v>
       </c>
       <c r="B108" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C108" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -5963,10 +5966,10 @@
         <v>800</v>
       </c>
       <c r="B109" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C109" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -5986,7 +5989,7 @@
         <v>234</v>
       </c>
       <c r="C110" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D110" t="s">
         <v>115</v>
@@ -5995,7 +5998,7 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -6003,10 +6006,10 @@
         <v>800</v>
       </c>
       <c r="B111" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C111" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D111" t="s">
         <v>113</v>
@@ -6023,10 +6026,10 @@
         <v>800</v>
       </c>
       <c r="B112" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C112" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D112" t="s">
         <v>113</v>
@@ -6040,7 +6043,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B113" t="s">
         <v>105</v>
@@ -6060,7 +6063,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B114" t="s">
         <v>106</v>
@@ -6080,7 +6083,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B115" t="s">
         <v>163</v>
@@ -6100,7 +6103,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B116" t="s">
         <v>107</v>
@@ -6120,7 +6123,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B117" t="s">
         <v>164</v>
@@ -6140,7 +6143,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B118" t="s">
         <v>165</v>
@@ -6160,7 +6163,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B119" t="s">
         <v>112</v>
@@ -6180,7 +6183,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
@@ -6200,7 +6203,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B121" t="s">
         <v>106</v>
@@ -6220,7 +6223,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B122" t="s">
         <v>232</v>
@@ -6240,7 +6243,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B123" t="s">
         <v>233</v>
@@ -6260,7 +6263,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B124" t="s">
         <v>234</v>
@@ -6280,7 +6283,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B125" t="s">
         <v>105</v>
@@ -6300,7 +6303,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -6320,13 +6323,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B127" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C127" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D127" t="s">
         <v>114</v>
@@ -6340,13 +6343,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B128" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C128" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -6360,13 +6363,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B129" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C129" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -6380,13 +6383,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B130" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C130" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -6400,13 +6403,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B131" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C131" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -6420,13 +6423,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B132" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C132" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D132" t="s">
         <v>113</v>
@@ -6440,10 +6443,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B133" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C133" t="s">
         <v>116</v>
@@ -6460,7 +6463,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B134" t="s">
         <v>117</v>
@@ -6480,13 +6483,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B135" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C135" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -6495,18 +6498,18 @@
         <v>203</v>
       </c>
       <c r="F135" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B136" t="s">
         <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D136" t="s">
         <v>113</v>
@@ -6520,16 +6523,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B137" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C137" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D137" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E137" t="s">
         <v>203</v>
@@ -6540,16 +6543,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B138" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C138" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D138" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E138" t="s">
         <v>203</v>
@@ -6560,16 +6563,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B139" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C139" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D139" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E139" t="s">
         <v>203</v>
@@ -6580,13 +6583,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B140" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C140" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D140" t="s">
         <v>113</v>
@@ -6600,7 +6603,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B141" t="s">
         <v>112</v>
@@ -6620,7 +6623,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B142" t="s">
         <v>105</v>
@@ -6640,7 +6643,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B143" t="s">
         <v>106</v>
@@ -6660,7 +6663,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B144" t="s">
         <v>107</v>
@@ -6680,10 +6683,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B145" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -6695,12 +6698,12 @@
         <v>203</v>
       </c>
       <c r="F145" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B146" t="s">
         <v>109</v>
@@ -6720,13 +6723,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B147" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C147" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D147" t="s">
         <v>145</v>
@@ -6740,13 +6743,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B148" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C148" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D148" t="s">
         <v>145</v>
@@ -6760,13 +6763,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B149" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C149" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D149" t="s">
         <v>114</v>
@@ -6775,18 +6778,18 @@
         <v>203</v>
       </c>
       <c r="F149" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B150" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C150" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D150" t="s">
         <v>113</v>
@@ -6800,7 +6803,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B151" t="s">
         <v>112</v>
@@ -6851,13 +6854,13 @@
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>104</v>
@@ -6874,7 +6877,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="P1" s="9"/>
     </row>
@@ -6886,43 +6889,43 @@
         <v>106</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>361</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>109</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="P2" s="10" t="s">
         <v>112</v>
@@ -6986,43 +6989,43 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>362</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>298</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>122</v>
@@ -7036,7 +7039,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -7051,7 +7054,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I5" s="8">
         <v>1</v>
@@ -7072,7 +7075,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>203</v>
@@ -7086,7 +7089,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7101,7 +7104,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I6" s="8">
         <v>2</v>
@@ -7122,7 +7125,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>203</v>
@@ -7136,7 +7139,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -7151,7 +7154,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I7" s="8">
         <v>3</v>
@@ -7172,7 +7175,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>203</v>
@@ -7186,7 +7189,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -7201,7 +7204,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I8" s="8">
         <v>4</v>
@@ -7222,7 +7225,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>203</v>
@@ -7236,7 +7239,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -7251,7 +7254,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I9" s="8">
         <v>5</v>
@@ -7272,7 +7275,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>203</v>
@@ -7286,7 +7289,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -7301,7 +7304,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I10" s="8">
         <v>1</v>
@@ -7322,7 +7325,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>203</v>
@@ -7336,7 +7339,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -7351,7 +7354,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I11" s="8">
         <v>2</v>
@@ -7372,7 +7375,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>203</v>
@@ -7386,7 +7389,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -7401,7 +7404,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I12" s="8">
         <v>3</v>
@@ -7422,7 +7425,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>203</v>
@@ -7436,7 +7439,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -7451,7 +7454,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I13" s="8">
         <v>4</v>
@@ -7472,7 +7475,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>203</v>
@@ -7486,7 +7489,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -7501,7 +7504,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I14" s="8">
         <v>5</v>
@@ -7522,7 +7525,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>203</v>
@@ -7536,7 +7539,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -7551,7 +7554,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I15" s="8">
         <v>1</v>
@@ -7572,7 +7575,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>203</v>
@@ -7586,7 +7589,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -7601,7 +7604,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I16" s="8">
         <v>2</v>
@@ -7622,7 +7625,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>203</v>
@@ -7636,7 +7639,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -7651,7 +7654,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I17" s="8">
         <v>3</v>
@@ -7672,7 +7675,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>203</v>
@@ -7686,7 +7689,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -7701,7 +7704,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I18" s="8">
         <v>4</v>
@@ -7722,7 +7725,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>203</v>
@@ -7736,7 +7739,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -7751,7 +7754,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I19" s="8">
         <v>5</v>
@@ -7772,7 +7775,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>203</v>
@@ -7786,7 +7789,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -7801,7 +7804,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I20" s="8">
         <v>1</v>
@@ -7822,7 +7825,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>203</v>
@@ -7836,7 +7839,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -7851,7 +7854,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I21" s="8">
         <v>2</v>
@@ -7872,7 +7875,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>203</v>
@@ -7886,7 +7889,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -7901,7 +7904,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I22" s="8">
         <v>3</v>
@@ -7922,7 +7925,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>203</v>
@@ -7936,7 +7939,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -7951,7 +7954,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I23" s="8">
         <v>4</v>
@@ -7972,7 +7975,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>203</v>
@@ -7986,7 +7989,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -8001,7 +8004,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I24" s="8">
         <v>5</v>
@@ -8022,7 +8025,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>203</v>
@@ -8036,7 +8039,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -8051,7 +8054,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I25" s="8">
         <v>1</v>
@@ -8072,7 +8075,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>203</v>
@@ -8086,7 +8089,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8101,7 +8104,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I26" s="8">
         <v>2</v>
@@ -8122,7 +8125,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>203</v>
@@ -8136,7 +8139,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -8151,7 +8154,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I27" s="8">
         <v>3</v>
@@ -8172,7 +8175,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>203</v>
@@ -8186,7 +8189,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -8201,7 +8204,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I28" s="8">
         <v>4</v>
@@ -8222,7 +8225,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>203</v>
@@ -8236,7 +8239,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -8251,7 +8254,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I29" s="8">
         <v>5</v>
@@ -8272,7 +8275,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>203</v>
@@ -8286,7 +8289,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -8301,7 +8304,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I30" s="8">
         <v>1</v>
@@ -8322,7 +8325,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>203</v>
@@ -8336,7 +8339,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -8351,7 +8354,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I31" s="8">
         <v>2</v>
@@ -8372,7 +8375,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>203</v>
@@ -8386,7 +8389,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -8401,7 +8404,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I32" s="8">
         <v>3</v>
@@ -8422,7 +8425,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>203</v>
@@ -8436,7 +8439,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -8451,7 +8454,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I33" s="8">
         <v>4</v>
@@ -8472,7 +8475,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>203</v>
@@ -8486,7 +8489,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -8501,7 +8504,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I34" s="8">
         <v>5</v>
@@ -8522,7 +8525,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>203</v>
@@ -8536,7 +8539,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -8551,7 +8554,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I35" s="8">
         <v>1</v>
@@ -8572,7 +8575,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>203</v>
@@ -8586,7 +8589,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -8601,7 +8604,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I36" s="8">
         <v>2</v>
@@ -8622,7 +8625,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>203</v>
@@ -8636,7 +8639,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -8651,7 +8654,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I37" s="8">
         <v>3</v>
@@ -8672,7 +8675,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>203</v>
@@ -8686,7 +8689,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -8701,7 +8704,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I38" s="8">
         <v>4</v>
@@ -8722,7 +8725,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>203</v>
@@ -8736,7 +8739,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -8751,7 +8754,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
@@ -8772,7 +8775,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>203</v>
@@ -8786,7 +8789,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -8801,7 +8804,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I40" s="8">
         <v>1</v>
@@ -8822,7 +8825,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>203</v>
@@ -8836,7 +8839,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -8851,7 +8854,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I41" s="8">
         <v>2</v>
@@ -8872,7 +8875,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>203</v>
@@ -8886,7 +8889,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -8901,7 +8904,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I42" s="8">
         <v>3</v>
@@ -8922,7 +8925,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>203</v>
@@ -8936,7 +8939,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -8951,7 +8954,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I43" s="8">
         <v>4</v>
@@ -8972,7 +8975,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>203</v>
@@ -8986,7 +8989,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -9001,7 +9004,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I44" s="8">
         <v>5</v>
@@ -9022,7 +9025,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>203</v>
@@ -9036,7 +9039,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -9051,7 +9054,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I45" s="8">
         <v>1</v>
@@ -9072,7 +9075,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>203</v>
@@ -9086,7 +9089,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9101,7 +9104,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I46" s="8">
         <v>2</v>
@@ -9122,7 +9125,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>203</v>
@@ -9136,7 +9139,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -9151,7 +9154,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I47" s="8">
         <v>3</v>
@@ -9172,7 +9175,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>203</v>
@@ -9186,7 +9189,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -9201,7 +9204,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I48" s="8">
         <v>4</v>
@@ -9222,7 +9225,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>203</v>
@@ -9236,7 +9239,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -9251,7 +9254,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I49" s="8">
         <v>5</v>
@@ -9272,7 +9275,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>203</v>
@@ -9286,7 +9289,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -9301,7 +9304,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I50" s="8">
         <v>1</v>
@@ -9322,7 +9325,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>203</v>
@@ -9336,7 +9339,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -9351,7 +9354,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I51" s="8">
         <v>2</v>
@@ -9372,7 +9375,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>203</v>
@@ -9386,7 +9389,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -9401,7 +9404,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I52" s="8">
         <v>3</v>
@@ -9422,7 +9425,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>203</v>
@@ -9436,7 +9439,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -9451,7 +9454,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I53" s="8">
         <v>4</v>
@@ -9472,7 +9475,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>203</v>
@@ -9486,7 +9489,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -9501,7 +9504,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I54" s="8">
         <v>5</v>
@@ -9522,7 +9525,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>203</v>
@@ -9536,7 +9539,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -9551,7 +9554,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I55" s="8">
         <v>1</v>
@@ -9572,7 +9575,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>203</v>
@@ -9586,7 +9589,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -9601,7 +9604,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I56" s="8">
         <v>2</v>
@@ -9622,7 +9625,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>203</v>
@@ -9636,7 +9639,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -9651,7 +9654,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I57" s="8">
         <v>3</v>
@@ -9672,7 +9675,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>203</v>
@@ -9686,7 +9689,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -9701,7 +9704,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I58" s="8">
         <v>4</v>
@@ -9722,7 +9725,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>203</v>
@@ -9736,7 +9739,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -9751,7 +9754,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I59" s="8">
         <v>5</v>
@@ -9772,7 +9775,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>203</v>
@@ -9786,7 +9789,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -9801,7 +9804,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I60" s="8">
         <v>1</v>
@@ -9822,7 +9825,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>203</v>
@@ -9836,7 +9839,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -9851,7 +9854,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I61" s="8">
         <v>2</v>
@@ -9872,7 +9875,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>203</v>
@@ -9886,7 +9889,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -9901,7 +9904,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I62" s="8">
         <v>3</v>
@@ -9922,7 +9925,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>203</v>
@@ -9936,7 +9939,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -9951,7 +9954,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I63" s="8">
         <v>4</v>
@@ -9972,7 +9975,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>203</v>
@@ -9986,7 +9989,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -10001,7 +10004,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I64" s="8">
         <v>5</v>
@@ -10022,7 +10025,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>203</v>
@@ -10036,7 +10039,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -10051,7 +10054,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I65" s="8">
         <v>1</v>
@@ -10072,7 +10075,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>203</v>
@@ -10086,7 +10089,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10101,7 +10104,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I66" s="8">
         <v>2</v>
@@ -10122,7 +10125,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>203</v>
@@ -10136,7 +10139,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -10151,7 +10154,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I67" s="8">
         <v>3</v>
@@ -10172,7 +10175,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>203</v>
@@ -10186,7 +10189,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -10201,7 +10204,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I68" s="8">
         <v>4</v>
@@ -10222,7 +10225,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>203</v>
@@ -10236,7 +10239,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -10251,7 +10254,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="I69" s="8">
         <v>5</v>
@@ -10272,7 +10275,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>203</v>
@@ -10286,7 +10289,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -10301,7 +10304,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I70" s="8">
         <v>1</v>
@@ -10322,7 +10325,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>203</v>
@@ -10336,7 +10339,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -10351,7 +10354,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I71" s="8">
         <v>2</v>
@@ -10372,7 +10375,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>203</v>
@@ -10386,7 +10389,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -10401,7 +10404,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I72" s="8">
         <v>3</v>
@@ -10422,7 +10425,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>203</v>
@@ -10436,7 +10439,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -10451,7 +10454,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I73" s="8">
         <v>4</v>
@@ -10472,7 +10475,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>203</v>
@@ -10486,7 +10489,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -10501,7 +10504,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I74" s="8">
         <v>5</v>
@@ -10522,7 +10525,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>203</v>
@@ -10536,7 +10539,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -10551,7 +10554,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I75" s="8">
         <v>1</v>
@@ -10572,7 +10575,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>203</v>
@@ -10586,7 +10589,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -10601,7 +10604,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I76" s="8">
         <v>2</v>
@@ -10622,7 +10625,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>203</v>
@@ -10636,7 +10639,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -10651,7 +10654,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I77" s="8">
         <v>3</v>
@@ -10672,7 +10675,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>203</v>
@@ -10686,7 +10689,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -10701,7 +10704,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I78" s="8">
         <v>4</v>
@@ -10722,7 +10725,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>203</v>
@@ -10736,7 +10739,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -10751,7 +10754,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I79" s="8">
         <v>5</v>
@@ -10772,7 +10775,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>203</v>
@@ -10984,7 +10987,7 @@
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>104</v>
@@ -10997,13 +11000,13 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
       <c r="L1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -11020,28 +11023,28 @@
         <v>109</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11096,22 +11099,22 @@
         <v>119</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>122</v>
@@ -11140,7 +11143,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -11178,7 +11181,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -11216,7 +11219,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -11254,7 +11257,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -11292,7 +11295,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -11330,7 +11333,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -11368,7 +11371,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -11406,7 +11409,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -11444,7 +11447,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -13434,7 +13437,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E474"/>
+  <dimension ref="A1:E475"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -21489,6 +21492,23 @@
       </c>
       <c r="E474" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>471</v>
+      </c>
+      <c r="B475">
+        <v>55028</v>
+      </c>
+      <c r="C475" t="s">
+        <v>836</v>
+      </c>
+      <c r="D475" t="s">
+        <v>836</v>
+      </c>
+      <c r="E475" t="s">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -21528,22 +21548,22 @@
         <v>117</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -21580,22 +21600,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>988</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>990</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>862</v>
-      </c>
       <c r="H4" s="12" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -21606,7 +21626,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D5" s="8">
         <v>8</v>
@@ -21632,7 +21652,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D6" s="8">
         <v>10</v>
@@ -21658,7 +21678,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
@@ -21684,7 +21704,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D8" s="8">
         <v>30</v>
@@ -21710,7 +21730,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D9" s="8">
         <v>60</v>
@@ -21736,7 +21756,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D10" s="8">
         <v>120</v>
@@ -21762,7 +21782,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="8">
         <v>240</v>
@@ -21806,7 +21826,7 @@
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>104</v>
@@ -21819,28 +21839,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>112</v>
@@ -21860,13 +21880,13 @@
         <v>113</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>113</v>
@@ -21883,22 +21903,22 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>122</v>
@@ -21930,7 +21950,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -21959,7 +21979,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -22046,7 +22066,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -22075,7 +22095,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -22087,7 +22107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:N304"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -22111,7 +22131,7 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
@@ -22133,13 +22153,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>400</v>
@@ -22148,25 +22168,25 @@
         <v>403</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>109</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -22221,40 +22241,40 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -31057,8 +31077,4408 @@
         <v>417</v>
       </c>
     </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" s="8">
+        <v>201</v>
+      </c>
+      <c r="B205" s="8">
+        <v>10201</v>
+      </c>
+      <c r="C205" s="8">
+        <v>201</v>
+      </c>
+      <c r="D205" s="8">
+        <v>21</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F205" s="8">
+        <v>38258051</v>
+      </c>
+      <c r="G205" s="8">
+        <v>20927906559</v>
+      </c>
+      <c r="H205" s="8">
+        <v>5</v>
+      </c>
+      <c r="I205" s="8">
+        <v>237381598</v>
+      </c>
+      <c r="J205" s="8">
+        <v>4355054</v>
+      </c>
+      <c r="K205" s="8">
+        <v>42</v>
+      </c>
+      <c r="L205" s="8">
+        <v>0</v>
+      </c>
+      <c r="M205" s="8">
+        <v>0</v>
+      </c>
+      <c r="N205" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="8">
+        <v>202</v>
+      </c>
+      <c r="B206" s="8">
+        <v>10202</v>
+      </c>
+      <c r="C206" s="8">
+        <v>202</v>
+      </c>
+      <c r="D206" s="8">
+        <v>21</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206" s="8">
+        <v>41127405</v>
+      </c>
+      <c r="G206" s="8">
+        <v>22392860015</v>
+      </c>
+      <c r="H206" s="8">
+        <v>5</v>
+      </c>
+      <c r="I206" s="8">
+        <v>261119758</v>
+      </c>
+      <c r="J206" s="8">
+        <v>4790556</v>
+      </c>
+      <c r="K206" s="8">
+        <v>46</v>
+      </c>
+      <c r="L206" s="8">
+        <v>0</v>
+      </c>
+      <c r="M206" s="8">
+        <v>0</v>
+      </c>
+      <c r="N206" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="8">
+        <v>203</v>
+      </c>
+      <c r="B207" s="8">
+        <v>10203</v>
+      </c>
+      <c r="C207" s="8">
+        <v>203</v>
+      </c>
+      <c r="D207" s="8">
+        <v>21</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="8">
+        <v>44211959</v>
+      </c>
+      <c r="G207" s="8">
+        <v>23960360218</v>
+      </c>
+      <c r="H207" s="8">
+        <v>5</v>
+      </c>
+      <c r="I207" s="8">
+        <v>287231734</v>
+      </c>
+      <c r="J207" s="8">
+        <v>5269613</v>
+      </c>
+      <c r="K207" s="8">
+        <v>50</v>
+      </c>
+      <c r="L207" s="8">
+        <v>0</v>
+      </c>
+      <c r="M207" s="8">
+        <v>0</v>
+      </c>
+      <c r="N207" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="8">
+        <v>204</v>
+      </c>
+      <c r="B208" s="8">
+        <v>10204</v>
+      </c>
+      <c r="C208" s="8">
+        <v>204</v>
+      </c>
+      <c r="D208" s="8">
+        <v>21</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F208" s="8">
+        <v>47527856</v>
+      </c>
+      <c r="G208" s="8">
+        <v>25637585434</v>
+      </c>
+      <c r="H208" s="8">
+        <v>5</v>
+      </c>
+      <c r="I208" s="8">
+        <v>315954908</v>
+      </c>
+      <c r="J208" s="8">
+        <v>5796574</v>
+      </c>
+      <c r="K208" s="8">
+        <v>55</v>
+      </c>
+      <c r="L208" s="8">
+        <v>0</v>
+      </c>
+      <c r="M208" s="8">
+        <v>0</v>
+      </c>
+      <c r="N208" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="8">
+        <v>205</v>
+      </c>
+      <c r="B209" s="8">
+        <v>10205</v>
+      </c>
+      <c r="C209" s="8">
+        <v>205</v>
+      </c>
+      <c r="D209" s="8">
+        <v>21</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F209" s="8">
+        <v>51092447</v>
+      </c>
+      <c r="G209" s="8">
+        <v>27432216412</v>
+      </c>
+      <c r="H209" s="8">
+        <v>5</v>
+      </c>
+      <c r="I209" s="8">
+        <v>347550398</v>
+      </c>
+      <c r="J209" s="8">
+        <v>6376233</v>
+      </c>
+      <c r="K209" s="8">
+        <v>61</v>
+      </c>
+      <c r="L209" s="8">
+        <v>0</v>
+      </c>
+      <c r="M209" s="8">
+        <v>0</v>
+      </c>
+      <c r="N209" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="8">
+        <v>206</v>
+      </c>
+      <c r="B210" s="8">
+        <v>10206</v>
+      </c>
+      <c r="C210" s="8">
+        <v>206</v>
+      </c>
+      <c r="D210" s="8">
+        <v>21</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210" s="8">
+        <v>54924379</v>
+      </c>
+      <c r="G210" s="8">
+        <v>29352471561</v>
+      </c>
+      <c r="H210" s="8">
+        <v>5</v>
+      </c>
+      <c r="I210" s="8">
+        <v>382305438</v>
+      </c>
+      <c r="J210" s="8">
+        <v>7013856</v>
+      </c>
+      <c r="K210" s="8">
+        <v>67</v>
+      </c>
+      <c r="L210" s="8">
+        <v>0</v>
+      </c>
+      <c r="M210" s="8">
+        <v>0</v>
+      </c>
+      <c r="N210" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="8">
+        <v>207</v>
+      </c>
+      <c r="B211" s="8">
+        <v>10207</v>
+      </c>
+      <c r="C211" s="8">
+        <v>207</v>
+      </c>
+      <c r="D211" s="8">
+        <v>21</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="8">
+        <v>59043709</v>
+      </c>
+      <c r="G211" s="8">
+        <v>31407144571</v>
+      </c>
+      <c r="H211" s="8">
+        <v>5</v>
+      </c>
+      <c r="I211" s="8">
+        <v>420535981</v>
+      </c>
+      <c r="J211" s="8">
+        <v>7715241</v>
+      </c>
+      <c r="K211" s="8">
+        <v>74</v>
+      </c>
+      <c r="L211" s="8">
+        <v>0</v>
+      </c>
+      <c r="M211" s="8">
+        <v>0</v>
+      </c>
+      <c r="N211" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" s="8">
+        <v>208</v>
+      </c>
+      <c r="B212" s="8">
+        <v>10208</v>
+      </c>
+      <c r="C212" s="8">
+        <v>208</v>
+      </c>
+      <c r="D212" s="8">
+        <v>21</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F212" s="8">
+        <v>63471986</v>
+      </c>
+      <c r="G212" s="8">
+        <v>33605644691</v>
+      </c>
+      <c r="H212" s="8">
+        <v>5</v>
+      </c>
+      <c r="I212" s="8">
+        <v>462589581</v>
+      </c>
+      <c r="J212" s="8">
+        <v>8486767</v>
+      </c>
+      <c r="K212" s="8">
+        <v>81</v>
+      </c>
+      <c r="L212" s="8">
+        <v>0</v>
+      </c>
+      <c r="M212" s="8">
+        <v>0</v>
+      </c>
+      <c r="N212" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" s="8">
+        <v>209</v>
+      </c>
+      <c r="B213" s="8">
+        <v>10209</v>
+      </c>
+      <c r="C213" s="8">
+        <v>209</v>
+      </c>
+      <c r="D213" s="8">
+        <v>21</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" s="8">
+        <v>68232386</v>
+      </c>
+      <c r="G213" s="8">
+        <v>35958039821</v>
+      </c>
+      <c r="H213" s="8">
+        <v>5</v>
+      </c>
+      <c r="I213" s="8">
+        <v>508848537</v>
+      </c>
+      <c r="J213" s="8">
+        <v>9335443</v>
+      </c>
+      <c r="K213" s="8">
+        <v>90</v>
+      </c>
+      <c r="L213" s="8">
+        <v>0</v>
+      </c>
+      <c r="M213" s="8">
+        <v>0</v>
+      </c>
+      <c r="N213" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" s="8">
+        <v>210</v>
+      </c>
+      <c r="B214" s="8">
+        <v>10210</v>
+      </c>
+      <c r="C214" s="8">
+        <v>210</v>
+      </c>
+      <c r="D214" s="8">
+        <v>21</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F214" s="8">
+        <v>366749080</v>
+      </c>
+      <c r="G214" s="8">
+        <v>116069466236</v>
+      </c>
+      <c r="H214" s="8">
+        <v>1</v>
+      </c>
+      <c r="I214" s="8">
+        <v>1679200182</v>
+      </c>
+      <c r="J214" s="8">
+        <v>26117318</v>
+      </c>
+      <c r="K214" s="8">
+        <v>88</v>
+      </c>
+      <c r="L214" s="8">
+        <v>115</v>
+      </c>
+      <c r="M214" s="8">
+        <v>0</v>
+      </c>
+      <c r="N214" s="8">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A215" s="8">
+        <v>211</v>
+      </c>
+      <c r="B215" s="8">
+        <v>10211</v>
+      </c>
+      <c r="C215" s="8">
+        <v>211</v>
+      </c>
+      <c r="D215" s="8">
+        <v>22</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F215" s="8">
+        <v>76466165</v>
+      </c>
+      <c r="G215" s="8">
+        <v>61264785240</v>
+      </c>
+      <c r="H215" s="8">
+        <v>5</v>
+      </c>
+      <c r="I215" s="8">
+        <v>592133625</v>
+      </c>
+      <c r="J215" s="8">
+        <v>9131773</v>
+      </c>
+      <c r="K215" s="8">
+        <v>42</v>
+      </c>
+      <c r="L215" s="8">
+        <v>0</v>
+      </c>
+      <c r="M215" s="8">
+        <v>0</v>
+      </c>
+      <c r="N215" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A216" s="8">
+        <v>212</v>
+      </c>
+      <c r="B216" s="8">
+        <v>10212</v>
+      </c>
+      <c r="C216" s="8">
+        <v>212</v>
+      </c>
+      <c r="D216" s="8">
+        <v>22</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" s="8">
+        <v>82201128</v>
+      </c>
+      <c r="G216" s="8">
+        <v>65553320198</v>
+      </c>
+      <c r="H216" s="8">
+        <v>5</v>
+      </c>
+      <c r="I216" s="8">
+        <v>651346988</v>
+      </c>
+      <c r="J216" s="8">
+        <v>10044943</v>
+      </c>
+      <c r="K216" s="8">
+        <v>46</v>
+      </c>
+      <c r="L216" s="8">
+        <v>0</v>
+      </c>
+      <c r="M216" s="8">
+        <v>0</v>
+      </c>
+      <c r="N216" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="8">
+        <v>213</v>
+      </c>
+      <c r="B217" s="8">
+        <v>10213</v>
+      </c>
+      <c r="C217" s="8">
+        <v>213</v>
+      </c>
+      <c r="D217" s="8">
+        <v>22</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" s="8">
+        <v>88366210</v>
+      </c>
+      <c r="G217" s="8">
+        <v>70142052618</v>
+      </c>
+      <c r="H217" s="8">
+        <v>5</v>
+      </c>
+      <c r="I217" s="8">
+        <v>716481688</v>
+      </c>
+      <c r="J217" s="8">
+        <v>11049440</v>
+      </c>
+      <c r="K217" s="8">
+        <v>50</v>
+      </c>
+      <c r="L217" s="8">
+        <v>0</v>
+      </c>
+      <c r="M217" s="8">
+        <v>0</v>
+      </c>
+      <c r="N217" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" s="8">
+        <v>214</v>
+      </c>
+      <c r="B218" s="8">
+        <v>10214</v>
+      </c>
+      <c r="C218" s="8">
+        <v>214</v>
+      </c>
+      <c r="D218" s="8">
+        <v>22</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="8">
+        <v>94993676</v>
+      </c>
+      <c r="G218" s="8">
+        <v>75051996303</v>
+      </c>
+      <c r="H218" s="8">
+        <v>5</v>
+      </c>
+      <c r="I218" s="8">
+        <v>788129858</v>
+      </c>
+      <c r="J218" s="8">
+        <v>12154384</v>
+      </c>
+      <c r="K218" s="8">
+        <v>55</v>
+      </c>
+      <c r="L218" s="8">
+        <v>0</v>
+      </c>
+      <c r="M218" s="8">
+        <v>0</v>
+      </c>
+      <c r="N218" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="8">
+        <v>215</v>
+      </c>
+      <c r="B219" s="8">
+        <v>10215</v>
+      </c>
+      <c r="C219" s="8">
+        <v>215</v>
+      </c>
+      <c r="D219" s="8">
+        <v>22</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F219" s="8">
+        <v>102118205</v>
+      </c>
+      <c r="G219" s="8">
+        <v>80305636037</v>
+      </c>
+      <c r="H219" s="8">
+        <v>5</v>
+      </c>
+      <c r="I219" s="8">
+        <v>866942842</v>
+      </c>
+      <c r="J219" s="8">
+        <v>13369825</v>
+      </c>
+      <c r="K219" s="8">
+        <v>61</v>
+      </c>
+      <c r="L219" s="8">
+        <v>0</v>
+      </c>
+      <c r="M219" s="8">
+        <v>0</v>
+      </c>
+      <c r="N219" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" s="8">
+        <v>216</v>
+      </c>
+      <c r="B220" s="8">
+        <v>10216</v>
+      </c>
+      <c r="C220" s="8">
+        <v>216</v>
+      </c>
+      <c r="D220" s="8">
+        <v>22</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F220" s="8">
+        <v>109777068</v>
+      </c>
+      <c r="G220" s="8">
+        <v>85927030560</v>
+      </c>
+      <c r="H220" s="8">
+        <v>5</v>
+      </c>
+      <c r="I220" s="8">
+        <v>953637127</v>
+      </c>
+      <c r="J220" s="8">
+        <v>14706807</v>
+      </c>
+      <c r="K220" s="8">
+        <v>67</v>
+      </c>
+      <c r="L220" s="8">
+        <v>0</v>
+      </c>
+      <c r="M220" s="8">
+        <v>0</v>
+      </c>
+      <c r="N220" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" s="8">
+        <v>217</v>
+      </c>
+      <c r="B221" s="8">
+        <v>10217</v>
+      </c>
+      <c r="C221" s="8">
+        <v>217</v>
+      </c>
+      <c r="D221" s="8">
+        <v>22</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221" s="8">
+        <v>118010351</v>
+      </c>
+      <c r="G221" s="8">
+        <v>91941922702</v>
+      </c>
+      <c r="H221" s="8">
+        <v>5</v>
+      </c>
+      <c r="I221" s="8">
+        <v>1049000837</v>
+      </c>
+      <c r="J221" s="8">
+        <v>16177487</v>
+      </c>
+      <c r="K221" s="8">
+        <v>74</v>
+      </c>
+      <c r="L221" s="8">
+        <v>0</v>
+      </c>
+      <c r="M221" s="8">
+        <v>0</v>
+      </c>
+      <c r="N221" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A222" s="8">
+        <v>218</v>
+      </c>
+      <c r="B222" s="8">
+        <v>10218</v>
+      </c>
+      <c r="C222" s="8">
+        <v>218</v>
+      </c>
+      <c r="D222" s="8">
+        <v>22</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F222" s="8">
+        <v>126861125</v>
+      </c>
+      <c r="G222" s="8">
+        <v>98377857291</v>
+      </c>
+      <c r="H222" s="8">
+        <v>5</v>
+      </c>
+      <c r="I222" s="8">
+        <v>1153900926</v>
+      </c>
+      <c r="J222" s="8">
+        <v>17795240</v>
+      </c>
+      <c r="K222" s="8">
+        <v>81</v>
+      </c>
+      <c r="L222" s="8">
+        <v>0</v>
+      </c>
+      <c r="M222" s="8">
+        <v>0</v>
+      </c>
+      <c r="N222" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="8">
+        <v>219</v>
+      </c>
+      <c r="B223" s="8">
+        <v>10219</v>
+      </c>
+      <c r="C223" s="8">
+        <v>219</v>
+      </c>
+      <c r="D223" s="8">
+        <v>22</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F223" s="8">
+        <v>136375712</v>
+      </c>
+      <c r="G223" s="8">
+        <v>105264307306</v>
+      </c>
+      <c r="H223" s="8">
+        <v>5</v>
+      </c>
+      <c r="I223" s="8">
+        <v>1269291013</v>
+      </c>
+      <c r="J223" s="8">
+        <v>19574762</v>
+      </c>
+      <c r="K223" s="8">
+        <v>90</v>
+      </c>
+      <c r="L223" s="8">
+        <v>0</v>
+      </c>
+      <c r="M223" s="8">
+        <v>0</v>
+      </c>
+      <c r="N223" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="8">
+        <v>220</v>
+      </c>
+      <c r="B224" s="8">
+        <v>10220</v>
+      </c>
+      <c r="C224" s="8">
+        <v>220</v>
+      </c>
+      <c r="D224" s="8">
+        <v>22</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F224" s="8">
+        <v>733019462</v>
+      </c>
+      <c r="G224" s="8">
+        <v>339784149069</v>
+      </c>
+      <c r="H224" s="8">
+        <v>1</v>
+      </c>
+      <c r="I224" s="8">
+        <v>4188660370</v>
+      </c>
+      <c r="J224" s="8">
+        <v>54763368</v>
+      </c>
+      <c r="K224" s="8">
+        <v>88</v>
+      </c>
+      <c r="L224" s="8">
+        <v>120</v>
+      </c>
+      <c r="M224" s="8">
+        <v>0</v>
+      </c>
+      <c r="N224" s="8">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" s="8">
+        <v>221</v>
+      </c>
+      <c r="B225" s="8">
+        <v>10221</v>
+      </c>
+      <c r="C225" s="8">
+        <v>221</v>
+      </c>
+      <c r="D225" s="8">
+        <v>23</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="8">
+        <v>148065863</v>
+      </c>
+      <c r="G225" s="8">
+        <v>168416468494</v>
+      </c>
+      <c r="H225" s="8">
+        <v>5</v>
+      </c>
+      <c r="I225" s="8">
+        <v>1418238818</v>
+      </c>
+      <c r="J225" s="8">
+        <v>18580594</v>
+      </c>
+      <c r="K225" s="8">
+        <v>42</v>
+      </c>
+      <c r="L225" s="8">
+        <v>0</v>
+      </c>
+      <c r="M225" s="8">
+        <v>0</v>
+      </c>
+      <c r="N225" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" s="8">
+        <v>222</v>
+      </c>
+      <c r="B226" s="8">
+        <v>10222</v>
+      </c>
+      <c r="C226" s="8">
+        <v>222</v>
+      </c>
+      <c r="D226" s="8">
+        <v>23</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F226" s="8">
+        <v>159170804</v>
+      </c>
+      <c r="G226" s="8">
+        <v>180205621264</v>
+      </c>
+      <c r="H226" s="8">
+        <v>5</v>
+      </c>
+      <c r="I226" s="8">
+        <v>1560062701</v>
+      </c>
+      <c r="J226" s="8">
+        <v>20438639</v>
+      </c>
+      <c r="K226" s="8">
+        <v>46</v>
+      </c>
+      <c r="L226" s="8">
+        <v>0</v>
+      </c>
+      <c r="M226" s="8">
+        <v>0</v>
+      </c>
+      <c r="N226" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A227" s="8">
+        <v>223</v>
+      </c>
+      <c r="B227" s="8">
+        <v>10223</v>
+      </c>
+      <c r="C227" s="8">
+        <v>223</v>
+      </c>
+      <c r="D227" s="8">
+        <v>23</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="8">
+        <v>171108609</v>
+      </c>
+      <c r="G227" s="8">
+        <v>192820014769</v>
+      </c>
+      <c r="H227" s="8">
+        <v>5</v>
+      </c>
+      <c r="I227" s="8">
+        <v>1716068974</v>
+      </c>
+      <c r="J227" s="8">
+        <v>22482508</v>
+      </c>
+      <c r="K227" s="8">
+        <v>50</v>
+      </c>
+      <c r="L227" s="8">
+        <v>0</v>
+      </c>
+      <c r="M227" s="8">
+        <v>0</v>
+      </c>
+      <c r="N227" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A228" s="8">
+        <v>224</v>
+      </c>
+      <c r="B228" s="8">
+        <v>10224</v>
+      </c>
+      <c r="C228" s="8">
+        <v>224</v>
+      </c>
+      <c r="D228" s="8">
+        <v>23</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228" s="8">
+        <v>183941756</v>
+      </c>
+      <c r="G228" s="8">
+        <v>206317415808</v>
+      </c>
+      <c r="H228" s="8">
+        <v>5</v>
+      </c>
+      <c r="I228" s="8">
+        <v>1887675874</v>
+      </c>
+      <c r="J228" s="8">
+        <v>24730759</v>
+      </c>
+      <c r="K228" s="8">
+        <v>55</v>
+      </c>
+      <c r="L228" s="8">
+        <v>0</v>
+      </c>
+      <c r="M228" s="8">
+        <v>0</v>
+      </c>
+      <c r="N228" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A229" s="8">
+        <v>225</v>
+      </c>
+      <c r="B229" s="8">
+        <v>10225</v>
+      </c>
+      <c r="C229" s="8">
+        <v>225</v>
+      </c>
+      <c r="D229" s="8">
+        <v>23</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F229" s="8">
+        <v>197737394</v>
+      </c>
+      <c r="G229" s="8">
+        <v>220759634895</v>
+      </c>
+      <c r="H229" s="8">
+        <v>5</v>
+      </c>
+      <c r="I229" s="8">
+        <v>2076443458</v>
+      </c>
+      <c r="J229" s="8">
+        <v>27203840</v>
+      </c>
+      <c r="K229" s="8">
+        <v>61</v>
+      </c>
+      <c r="L229" s="8">
+        <v>0</v>
+      </c>
+      <c r="M229" s="8">
+        <v>0</v>
+      </c>
+      <c r="N229" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
+        <v>226</v>
+      </c>
+      <c r="B230" s="8">
+        <v>10226</v>
+      </c>
+      <c r="C230" s="8">
+        <v>226</v>
+      </c>
+      <c r="D230" s="8">
+        <v>23</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F230" s="8">
+        <v>212567694</v>
+      </c>
+      <c r="G230" s="8">
+        <v>236212809339</v>
+      </c>
+      <c r="H230" s="8">
+        <v>5</v>
+      </c>
+      <c r="I230" s="8">
+        <v>2284087805</v>
+      </c>
+      <c r="J230" s="8">
+        <v>29924223</v>
+      </c>
+      <c r="K230" s="8">
+        <v>67</v>
+      </c>
+      <c r="L230" s="8">
+        <v>0</v>
+      </c>
+      <c r="M230" s="8">
+        <v>0</v>
+      </c>
+      <c r="N230" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A231" s="8">
+        <v>227</v>
+      </c>
+      <c r="B231" s="8">
+        <v>10227</v>
+      </c>
+      <c r="C231" s="8">
+        <v>227</v>
+      </c>
+      <c r="D231" s="8">
+        <v>23</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231" s="8">
+        <v>228510276</v>
+      </c>
+      <c r="G231" s="8">
+        <v>252747706000</v>
+      </c>
+      <c r="H231" s="8">
+        <v>5</v>
+      </c>
+      <c r="I231" s="8">
+        <v>2512496580</v>
+      </c>
+      <c r="J231" s="8">
+        <v>32916644</v>
+      </c>
+      <c r="K231" s="8">
+        <v>74</v>
+      </c>
+      <c r="L231" s="8">
+        <v>0</v>
+      </c>
+      <c r="M231" s="8">
+        <v>0</v>
+      </c>
+      <c r="N231" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A232" s="8">
+        <v>228</v>
+      </c>
+      <c r="B232" s="8">
+        <v>10228</v>
+      </c>
+      <c r="C232" s="8">
+        <v>228</v>
+      </c>
+      <c r="D232" s="8">
+        <v>23</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F232" s="8">
+        <v>245648543</v>
+      </c>
+      <c r="G232" s="8">
+        <v>270440045420</v>
+      </c>
+      <c r="H232" s="8">
+        <v>5</v>
+      </c>
+      <c r="I232" s="8">
+        <v>2763746250</v>
+      </c>
+      <c r="J232" s="8">
+        <v>36208318</v>
+      </c>
+      <c r="K232" s="8">
+        <v>81</v>
+      </c>
+      <c r="L232" s="8">
+        <v>0</v>
+      </c>
+      <c r="M232" s="8">
+        <v>0</v>
+      </c>
+      <c r="N232" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A233" s="8">
+        <v>229</v>
+      </c>
+      <c r="B233" s="8">
+        <v>10229</v>
+      </c>
+      <c r="C233" s="8">
+        <v>229</v>
+      </c>
+      <c r="D233" s="8">
+        <v>23</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F233" s="8">
+        <v>264072188</v>
+      </c>
+      <c r="G233" s="8">
+        <v>289370848612</v>
+      </c>
+      <c r="H233" s="8">
+        <v>5</v>
+      </c>
+      <c r="I233" s="8">
+        <v>3040120862</v>
+      </c>
+      <c r="J233" s="8">
+        <v>39829145</v>
+      </c>
+      <c r="K233" s="8">
+        <v>90</v>
+      </c>
+      <c r="L233" s="8">
+        <v>0</v>
+      </c>
+      <c r="M233" s="8">
+        <v>0</v>
+      </c>
+      <c r="N233" s="8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A234" s="8">
+        <v>230</v>
+      </c>
+      <c r="B234" s="8">
+        <v>10230</v>
+      </c>
+      <c r="C234" s="8">
+        <v>230</v>
+      </c>
+      <c r="D234" s="8">
+        <v>23</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F234" s="8">
+        <v>1419388034</v>
+      </c>
+      <c r="G234" s="8">
+        <v>934064262403</v>
+      </c>
+      <c r="H234" s="8">
+        <v>1</v>
+      </c>
+      <c r="I234" s="8">
+        <v>10032398910</v>
+      </c>
+      <c r="J234" s="8">
+        <v>111428081</v>
+      </c>
+      <c r="K234" s="8">
+        <v>88</v>
+      </c>
+      <c r="L234" s="8">
+        <v>125</v>
+      </c>
+      <c r="M234" s="8">
+        <v>0</v>
+      </c>
+      <c r="N234" s="8">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A235" s="8">
+        <v>231</v>
+      </c>
+      <c r="B235" s="8">
+        <v>10231</v>
+      </c>
+      <c r="C235" s="8">
+        <v>231</v>
+      </c>
+      <c r="D235" s="8">
+        <v>24</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F235" s="8">
+        <v>277478546</v>
+      </c>
+      <c r="G235" s="8">
+        <v>432925557928</v>
+      </c>
+      <c r="H235" s="8">
+        <v>5</v>
+      </c>
+      <c r="I235" s="8">
+        <v>3256032861</v>
+      </c>
+      <c r="J235" s="8">
+        <v>36652386</v>
+      </c>
+      <c r="K235" s="8">
+        <v>42</v>
+      </c>
+      <c r="L235" s="8">
+        <v>0</v>
+      </c>
+      <c r="M235" s="8">
+        <v>0</v>
+      </c>
+      <c r="N235" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A236" s="8">
+        <v>232</v>
+      </c>
+      <c r="B236" s="8">
+        <v>10232</v>
+      </c>
+      <c r="C236" s="8">
+        <v>232</v>
+      </c>
+      <c r="D236" s="8">
+        <v>24</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F236" s="8">
+        <v>298289439</v>
+      </c>
+      <c r="G236" s="8">
+        <v>463230346920</v>
+      </c>
+      <c r="H236" s="8">
+        <v>5</v>
+      </c>
+      <c r="I236" s="8">
+        <v>3581636150</v>
+      </c>
+      <c r="J236" s="8">
+        <v>40317597</v>
+      </c>
+      <c r="K236" s="8">
+        <v>46</v>
+      </c>
+      <c r="L236" s="8">
+        <v>0</v>
+      </c>
+      <c r="M236" s="8">
+        <v>0</v>
+      </c>
+      <c r="N236" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A237" s="8">
+        <v>233</v>
+      </c>
+      <c r="B237" s="8">
+        <v>10233</v>
+      </c>
+      <c r="C237" s="8">
+        <v>233</v>
+      </c>
+      <c r="D237" s="8">
+        <v>24</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F237" s="8">
+        <v>320661137</v>
+      </c>
+      <c r="G237" s="8">
+        <v>495656471247</v>
+      </c>
+      <c r="H237" s="8">
+        <v>5</v>
+      </c>
+      <c r="I237" s="8">
+        <v>3939799772</v>
+      </c>
+      <c r="J237" s="8">
+        <v>44349366</v>
+      </c>
+      <c r="K237" s="8">
+        <v>50</v>
+      </c>
+      <c r="L237" s="8">
+        <v>0</v>
+      </c>
+      <c r="M237" s="8">
+        <v>0</v>
+      </c>
+      <c r="N237" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A238" s="8">
+        <v>234</v>
+      </c>
+      <c r="B238" s="8">
+        <v>10234</v>
+      </c>
+      <c r="C238" s="8">
+        <v>234</v>
+      </c>
+      <c r="D238" s="8">
+        <v>24</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="8">
+        <v>344710725</v>
+      </c>
+      <c r="G238" s="8">
+        <v>530352424247</v>
+      </c>
+      <c r="H238" s="8">
+        <v>5</v>
+      </c>
+      <c r="I238" s="8">
+        <v>4333779755</v>
+      </c>
+      <c r="J238" s="8">
+        <v>48784304</v>
+      </c>
+      <c r="K238" s="8">
+        <v>55</v>
+      </c>
+      <c r="L238" s="8">
+        <v>0</v>
+      </c>
+      <c r="M238" s="8">
+        <v>0</v>
+      </c>
+      <c r="N238" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" s="8">
+        <v>235</v>
+      </c>
+      <c r="B239" s="8">
+        <v>10235</v>
+      </c>
+      <c r="C239" s="8">
+        <v>235</v>
+      </c>
+      <c r="D239" s="8">
+        <v>24</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F239" s="8">
+        <v>370564042</v>
+      </c>
+      <c r="G239" s="8">
+        <v>567477093895</v>
+      </c>
+      <c r="H239" s="8">
+        <v>5</v>
+      </c>
+      <c r="I239" s="8">
+        <v>4767157723</v>
+      </c>
+      <c r="J239" s="8">
+        <v>53662744</v>
+      </c>
+      <c r="K239" s="8">
+        <v>61</v>
+      </c>
+      <c r="L239" s="8">
+        <v>0</v>
+      </c>
+      <c r="M239" s="8">
+        <v>0</v>
+      </c>
+      <c r="N239" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A240" s="8">
+        <v>236</v>
+      </c>
+      <c r="B240" s="8">
+        <v>10236</v>
+      </c>
+      <c r="C240" s="8">
+        <v>236</v>
+      </c>
+      <c r="D240" s="8">
+        <v>24</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F240" s="8">
+        <v>398356336</v>
+      </c>
+      <c r="G240" s="8">
+        <v>607200490471</v>
+      </c>
+      <c r="H240" s="8">
+        <v>5</v>
+      </c>
+      <c r="I240" s="8">
+        <v>5243873498</v>
+      </c>
+      <c r="J240" s="8">
+        <v>59029017</v>
+      </c>
+      <c r="K240" s="8">
+        <v>67</v>
+      </c>
+      <c r="L240" s="8">
+        <v>0</v>
+      </c>
+      <c r="M240" s="8">
+        <v>0</v>
+      </c>
+      <c r="N240" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A241" s="8">
+        <v>237</v>
+      </c>
+      <c r="B241" s="8">
+        <v>10237</v>
+      </c>
+      <c r="C241" s="8">
+        <v>237</v>
+      </c>
+      <c r="D241" s="8">
+        <v>24</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F241" s="8">
+        <v>428233071</v>
+      </c>
+      <c r="G241" s="8">
+        <v>649704524822</v>
+      </c>
+      <c r="H241" s="8">
+        <v>5</v>
+      </c>
+      <c r="I241" s="8">
+        <v>5768260835</v>
+      </c>
+      <c r="J241" s="8">
+        <v>64931916</v>
+      </c>
+      <c r="K241" s="8">
+        <v>74</v>
+      </c>
+      <c r="L241" s="8">
+        <v>0</v>
+      </c>
+      <c r="M241" s="8">
+        <v>0</v>
+      </c>
+      <c r="N241" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A242" s="8">
+        <v>238</v>
+      </c>
+      <c r="B242" s="8">
+        <v>10238</v>
+      </c>
+      <c r="C242" s="8">
+        <v>238</v>
+      </c>
+      <c r="D242" s="8">
+        <v>24</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" s="8">
+        <v>460350544</v>
+      </c>
+      <c r="G242" s="8">
+        <v>695183841560</v>
+      </c>
+      <c r="H242" s="8">
+        <v>5</v>
+      </c>
+      <c r="I242" s="8">
+        <v>6345086946</v>
+      </c>
+      <c r="J242" s="8">
+        <v>71425126</v>
+      </c>
+      <c r="K242" s="8">
+        <v>81</v>
+      </c>
+      <c r="L242" s="8">
+        <v>0</v>
+      </c>
+      <c r="M242" s="8">
+        <v>0</v>
+      </c>
+      <c r="N242" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A243" s="8">
+        <v>239</v>
+      </c>
+      <c r="B243" s="8">
+        <v>10239</v>
+      </c>
+      <c r="C243" s="8">
+        <v>239</v>
+      </c>
+      <c r="D243" s="8">
+        <v>24</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F243" s="8">
+        <v>494876843</v>
+      </c>
+      <c r="G243" s="8">
+        <v>743846710502</v>
+      </c>
+      <c r="H243" s="8">
+        <v>5</v>
+      </c>
+      <c r="I243" s="8">
+        <v>6979595611</v>
+      </c>
+      <c r="J243" s="8">
+        <v>78567629</v>
+      </c>
+      <c r="K243" s="8">
+        <v>90</v>
+      </c>
+      <c r="L243" s="8">
+        <v>0</v>
+      </c>
+      <c r="M243" s="8">
+        <v>0</v>
+      </c>
+      <c r="N243" s="8">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A244" s="8">
+        <v>240</v>
+      </c>
+      <c r="B244" s="8">
+        <v>10240</v>
+      </c>
+      <c r="C244" s="8">
+        <v>240</v>
+      </c>
+      <c r="D244" s="8">
+        <v>24</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F244" s="8">
+        <v>2659963077</v>
+      </c>
+      <c r="G244" s="8">
+        <v>2401073336580</v>
+      </c>
+      <c r="H244" s="8">
+        <v>1</v>
+      </c>
+      <c r="I244" s="8">
+        <v>23032665668</v>
+      </c>
+      <c r="J244" s="8">
+        <v>219804874</v>
+      </c>
+      <c r="K244" s="8">
+        <v>88</v>
+      </c>
+      <c r="L244" s="8">
+        <v>130</v>
+      </c>
+      <c r="M244" s="8">
+        <v>0</v>
+      </c>
+      <c r="N244" s="8">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A245" s="8">
+        <v>241</v>
+      </c>
+      <c r="B245" s="8">
+        <v>10241</v>
+      </c>
+      <c r="C245" s="8">
+        <v>241</v>
+      </c>
+      <c r="D245" s="8">
+        <v>25</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F245" s="8">
+        <v>502703503</v>
+      </c>
+      <c r="G245" s="8">
+        <v>1035617630187</v>
+      </c>
+      <c r="H245" s="8">
+        <v>5</v>
+      </c>
+      <c r="I245" s="8">
+        <v>7151953057</v>
+      </c>
+      <c r="J245" s="8">
+        <v>70024888</v>
+      </c>
+      <c r="K245" s="8">
+        <v>42</v>
+      </c>
+      <c r="L245" s="8">
+        <v>0</v>
+      </c>
+      <c r="M245" s="8">
+        <v>0</v>
+      </c>
+      <c r="N245" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A246" s="8">
+        <v>242</v>
+      </c>
+      <c r="B246" s="8">
+        <v>10242</v>
+      </c>
+      <c r="C246" s="8">
+        <v>242</v>
+      </c>
+      <c r="D246" s="8">
+        <v>25</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F246" s="8">
+        <v>540406270</v>
+      </c>
+      <c r="G246" s="8">
+        <v>1108110864150</v>
+      </c>
+      <c r="H246" s="8">
+        <v>5</v>
+      </c>
+      <c r="I246" s="8">
+        <v>7867148369</v>
+      </c>
+      <c r="J246" s="8">
+        <v>77027324</v>
+      </c>
+      <c r="K246" s="8">
+        <v>46</v>
+      </c>
+      <c r="L246" s="8">
+        <v>0</v>
+      </c>
+      <c r="M246" s="8">
+        <v>0</v>
+      </c>
+      <c r="N246" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A247" s="8">
+        <v>243</v>
+      </c>
+      <c r="B247" s="8">
+        <v>10243</v>
+      </c>
+      <c r="C247" s="8">
+        <v>243</v>
+      </c>
+      <c r="D247" s="8">
+        <v>25</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" s="8">
+        <v>580936722</v>
+      </c>
+      <c r="G247" s="8">
+        <v>1185678624742</v>
+      </c>
+      <c r="H247" s="8">
+        <v>5</v>
+      </c>
+      <c r="I247" s="8">
+        <v>8653863222</v>
+      </c>
+      <c r="J247" s="8">
+        <v>84730074</v>
+      </c>
+      <c r="K247" s="8">
+        <v>50</v>
+      </c>
+      <c r="L247" s="8">
+        <v>0</v>
+      </c>
+      <c r="M247" s="8">
+        <v>0</v>
+      </c>
+      <c r="N247" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A248" s="8">
+        <v>244</v>
+      </c>
+      <c r="B248" s="8">
+        <v>10244</v>
+      </c>
+      <c r="C248" s="8">
+        <v>244</v>
+      </c>
+      <c r="D248" s="8">
+        <v>25</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" s="8">
+        <v>624506981</v>
+      </c>
+      <c r="G248" s="8">
+        <v>1268676128505</v>
+      </c>
+      <c r="H248" s="8">
+        <v>5</v>
+      </c>
+      <c r="I248" s="8">
+        <v>9519249557</v>
+      </c>
+      <c r="J248" s="8">
+        <v>93203084</v>
+      </c>
+      <c r="K248" s="8">
+        <v>55</v>
+      </c>
+      <c r="L248" s="8">
+        <v>0</v>
+      </c>
+      <c r="M248" s="8">
+        <v>0</v>
+      </c>
+      <c r="N248" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A249" s="8">
+        <v>245</v>
+      </c>
+      <c r="B249" s="8">
+        <v>10245</v>
+      </c>
+      <c r="C249" s="8">
+        <v>245</v>
+      </c>
+      <c r="D249" s="8">
+        <v>25</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F249" s="8">
+        <v>671345028</v>
+      </c>
+      <c r="G249" s="8">
+        <v>1357483457382</v>
+      </c>
+      <c r="H249" s="8">
+        <v>5</v>
+      </c>
+      <c r="I249" s="8">
+        <v>10471174496</v>
+      </c>
+      <c r="J249" s="8">
+        <v>102523411</v>
+      </c>
+      <c r="K249" s="8">
+        <v>61</v>
+      </c>
+      <c r="L249" s="8">
+        <v>0</v>
+      </c>
+      <c r="M249" s="8">
+        <v>0</v>
+      </c>
+      <c r="N249" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A250" s="8">
+        <v>246</v>
+      </c>
+      <c r="B250" s="8">
+        <v>10246</v>
+      </c>
+      <c r="C250" s="8">
+        <v>246</v>
+      </c>
+      <c r="D250" s="8">
+        <v>25</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F250" s="8">
+        <v>721695888</v>
+      </c>
+      <c r="G250" s="8">
+        <v>1452507299407</v>
+      </c>
+      <c r="H250" s="8">
+        <v>5</v>
+      </c>
+      <c r="I250" s="8">
+        <v>11518291952</v>
+      </c>
+      <c r="J250" s="8">
+        <v>112775750</v>
+      </c>
+      <c r="K250" s="8">
+        <v>67</v>
+      </c>
+      <c r="L250" s="8">
+        <v>0</v>
+      </c>
+      <c r="M250" s="8">
+        <v>0</v>
+      </c>
+      <c r="N250" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A251" s="8">
+        <v>247</v>
+      </c>
+      <c r="B251" s="8">
+        <v>10247</v>
+      </c>
+      <c r="C251" s="8">
+        <v>247</v>
+      </c>
+      <c r="D251" s="8">
+        <v>25</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F251" s="8">
+        <v>775823098</v>
+      </c>
+      <c r="G251" s="8">
+        <v>1554182810409</v>
+      </c>
+      <c r="H251" s="8">
+        <v>5</v>
+      </c>
+      <c r="I251" s="8">
+        <v>12670121119</v>
+      </c>
+      <c r="J251" s="8">
+        <v>124053320</v>
+      </c>
+      <c r="K251" s="8">
+        <v>74</v>
+      </c>
+      <c r="L251" s="8">
+        <v>0</v>
+      </c>
+      <c r="M251" s="8">
+        <v>0</v>
+      </c>
+      <c r="N251" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A252" s="8">
+        <v>248</v>
+      </c>
+      <c r="B252" s="8">
+        <v>10248</v>
+      </c>
+      <c r="C252" s="8">
+        <v>248</v>
+      </c>
+      <c r="D252" s="8">
+        <v>25</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F252" s="8">
+        <v>834009817</v>
+      </c>
+      <c r="G252" s="8">
+        <v>1662975607139</v>
+      </c>
+      <c r="H252" s="8">
+        <v>5</v>
+      </c>
+      <c r="I252" s="8">
+        <v>13937133291</v>
+      </c>
+      <c r="J252" s="8">
+        <v>136458687</v>
+      </c>
+      <c r="K252" s="8">
+        <v>81</v>
+      </c>
+      <c r="L252" s="8">
+        <v>0</v>
+      </c>
+      <c r="M252" s="8">
+        <v>0</v>
+      </c>
+      <c r="N252" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A253" s="8">
+        <v>249</v>
+      </c>
+      <c r="B253" s="8">
+        <v>10249</v>
+      </c>
+      <c r="C253" s="8">
+        <v>249</v>
+      </c>
+      <c r="D253" s="8">
+        <v>25</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F253" s="8">
+        <v>896560568</v>
+      </c>
+      <c r="G253" s="8">
+        <v>1779383899717</v>
+      </c>
+      <c r="H253" s="8">
+        <v>5</v>
+      </c>
+      <c r="I253" s="8">
+        <v>15330846555</v>
+      </c>
+      <c r="J253" s="8">
+        <v>150104537</v>
+      </c>
+      <c r="K253" s="8">
+        <v>90</v>
+      </c>
+      <c r="L253" s="8">
+        <v>0</v>
+      </c>
+      <c r="M253" s="8">
+        <v>0</v>
+      </c>
+      <c r="N253" s="8">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A254" s="8">
+        <v>250</v>
+      </c>
+      <c r="B254" s="8">
+        <v>10250</v>
+      </c>
+      <c r="C254" s="8">
+        <v>250</v>
+      </c>
+      <c r="D254" s="8">
+        <v>25</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F254" s="8">
+        <v>4819013138</v>
+      </c>
+      <c r="G254" s="8">
+        <v>5743698502433</v>
+      </c>
+      <c r="H254" s="8">
+        <v>1</v>
+      </c>
+      <c r="I254" s="8">
+        <v>50591793966</v>
+      </c>
+      <c r="J254" s="8">
+        <v>419940240</v>
+      </c>
+      <c r="K254" s="8">
+        <v>88</v>
+      </c>
+      <c r="L254" s="8">
+        <v>135</v>
+      </c>
+      <c r="M254" s="8">
+        <v>0</v>
+      </c>
+      <c r="N254" s="8">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A255" s="8">
+        <v>251</v>
+      </c>
+      <c r="B255" s="8">
+        <v>10251</v>
+      </c>
+      <c r="C255" s="8">
+        <v>251</v>
+      </c>
+      <c r="D255" s="8">
+        <v>26</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F255" s="8">
+        <v>879403054</v>
+      </c>
+      <c r="G255" s="8">
+        <v>2292557426313</v>
+      </c>
+      <c r="H255" s="8">
+        <v>5</v>
+      </c>
+      <c r="I255" s="8">
+        <v>14999211043</v>
+      </c>
+      <c r="J255" s="8">
+        <v>129434774</v>
+      </c>
+      <c r="K255" s="8">
+        <v>42</v>
+      </c>
+      <c r="L255" s="8">
+        <v>0</v>
+      </c>
+      <c r="M255" s="8">
+        <v>0</v>
+      </c>
+      <c r="N255" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A256" s="8">
+        <v>252</v>
+      </c>
+      <c r="B256" s="8">
+        <v>10252</v>
+      </c>
+      <c r="C256" s="8">
+        <v>252</v>
+      </c>
+      <c r="D256" s="8">
+        <v>26</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F256" s="8">
+        <v>945358291</v>
+      </c>
+      <c r="G256" s="8">
+        <v>2453036445823</v>
+      </c>
+      <c r="H256" s="8">
+        <v>5</v>
+      </c>
+      <c r="I256" s="8">
+        <v>16499132161</v>
+      </c>
+      <c r="J256" s="8">
+        <v>142378154</v>
+      </c>
+      <c r="K256" s="8">
+        <v>46</v>
+      </c>
+      <c r="L256" s="8">
+        <v>0</v>
+      </c>
+      <c r="M256" s="8">
+        <v>0</v>
+      </c>
+      <c r="N256" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A257" s="8">
+        <v>253</v>
+      </c>
+      <c r="B257" s="8">
+        <v>10253</v>
+      </c>
+      <c r="C257" s="8">
+        <v>253</v>
+      </c>
+      <c r="D257" s="8">
+        <v>26</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F257" s="8">
+        <v>1016260131</v>
+      </c>
+      <c r="G257" s="8">
+        <v>2624748997255</v>
+      </c>
+      <c r="H257" s="8">
+        <v>5</v>
+      </c>
+      <c r="I257" s="8">
+        <v>18149045411</v>
+      </c>
+      <c r="J257" s="8">
+        <v>156616002</v>
+      </c>
+      <c r="K257" s="8">
+        <v>50</v>
+      </c>
+      <c r="L257" s="8">
+        <v>0</v>
+      </c>
+      <c r="M257" s="8">
+        <v>0</v>
+      </c>
+      <c r="N257" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A258" s="8">
+        <v>254</v>
+      </c>
+      <c r="B258" s="8">
+        <v>10254</v>
+      </c>
+      <c r="C258" s="8">
+        <v>254</v>
+      </c>
+      <c r="D258" s="8">
+        <v>26</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F258" s="8">
+        <v>1092479649</v>
+      </c>
+      <c r="G258" s="8">
+        <v>2808481427132</v>
+      </c>
+      <c r="H258" s="8">
+        <v>5</v>
+      </c>
+      <c r="I258" s="8">
+        <v>19963949978</v>
+      </c>
+      <c r="J258" s="8">
+        <v>172277607</v>
+      </c>
+      <c r="K258" s="8">
+        <v>55</v>
+      </c>
+      <c r="L258" s="8">
+        <v>0</v>
+      </c>
+      <c r="M258" s="8">
+        <v>0</v>
+      </c>
+      <c r="N258" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A259" s="8">
+        <v>255</v>
+      </c>
+      <c r="B259" s="8">
+        <v>10255</v>
+      </c>
+      <c r="C259" s="8">
+        <v>255</v>
+      </c>
+      <c r="D259" s="8">
+        <v>26</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F259" s="8">
+        <v>1174415664</v>
+      </c>
+      <c r="G259" s="8">
+        <v>3005075126769</v>
+      </c>
+      <c r="H259" s="8">
+        <v>5</v>
+      </c>
+      <c r="I259" s="8">
+        <v>21960344941</v>
+      </c>
+      <c r="J259" s="8">
+        <v>189505402</v>
+      </c>
+      <c r="K259" s="8">
+        <v>61</v>
+      </c>
+      <c r="L259" s="8">
+        <v>0</v>
+      </c>
+      <c r="M259" s="8">
+        <v>0</v>
+      </c>
+      <c r="N259" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" s="8">
+        <v>256</v>
+      </c>
+      <c r="B260" s="8">
+        <v>10256</v>
+      </c>
+      <c r="C260" s="8">
+        <v>256</v>
+      </c>
+      <c r="D260" s="8">
+        <v>26</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F260" s="8">
+        <v>1262496809</v>
+      </c>
+      <c r="G260" s="8">
+        <v>3215430385661</v>
+      </c>
+      <c r="H260" s="8">
+        <v>5</v>
+      </c>
+      <c r="I260" s="8">
+        <v>24156379449</v>
+      </c>
+      <c r="J260" s="8">
+        <v>208455939</v>
+      </c>
+      <c r="K260" s="8">
+        <v>67</v>
+      </c>
+      <c r="L260" s="8">
+        <v>0</v>
+      </c>
+      <c r="M260" s="8">
+        <v>0</v>
+      </c>
+      <c r="N260" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A261" s="8">
+        <v>257</v>
+      </c>
+      <c r="B261" s="8">
+        <v>10257</v>
+      </c>
+      <c r="C261" s="8">
+        <v>257</v>
+      </c>
+      <c r="D261" s="8">
+        <v>26</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F261" s="8">
+        <v>1357184102</v>
+      </c>
+      <c r="G261" s="8">
+        <v>3440510512754</v>
+      </c>
+      <c r="H261" s="8">
+        <v>5</v>
+      </c>
+      <c r="I261" s="8">
+        <v>26572017335</v>
+      </c>
+      <c r="J261" s="8">
+        <v>229301524</v>
+      </c>
+      <c r="K261" s="8">
+        <v>74</v>
+      </c>
+      <c r="L261" s="8">
+        <v>0</v>
+      </c>
+      <c r="M261" s="8">
+        <v>0</v>
+      </c>
+      <c r="N261" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A262" s="8">
+        <v>258</v>
+      </c>
+      <c r="B262" s="8">
+        <v>10258</v>
+      </c>
+      <c r="C262" s="8">
+        <v>258</v>
+      </c>
+      <c r="D262" s="8">
+        <v>26</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F262" s="8">
+        <v>1458972886</v>
+      </c>
+      <c r="G262" s="8">
+        <v>3681346248649</v>
+      </c>
+      <c r="H262" s="8">
+        <v>5</v>
+      </c>
+      <c r="I262" s="8">
+        <v>29229219194</v>
+      </c>
+      <c r="J262" s="8">
+        <v>252231741</v>
+      </c>
+      <c r="K262" s="8">
+        <v>81</v>
+      </c>
+      <c r="L262" s="8">
+        <v>0</v>
+      </c>
+      <c r="M262" s="8">
+        <v>0</v>
+      </c>
+      <c r="N262" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A263" s="8">
+        <v>259</v>
+      </c>
+      <c r="B263" s="8">
+        <v>10259</v>
+      </c>
+      <c r="C263" s="8">
+        <v>259</v>
+      </c>
+      <c r="D263" s="8">
+        <v>26</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F263" s="8">
+        <v>1568395878</v>
+      </c>
+      <c r="G263" s="8">
+        <v>3939040486228</v>
+      </c>
+      <c r="H263" s="8">
+        <v>5</v>
+      </c>
+      <c r="I263" s="8">
+        <v>32152140977</v>
+      </c>
+      <c r="J263" s="8">
+        <v>277454880</v>
+      </c>
+      <c r="K263" s="8">
+        <v>90</v>
+      </c>
+      <c r="L263" s="8">
+        <v>0</v>
+      </c>
+      <c r="M263" s="8">
+        <v>0</v>
+      </c>
+      <c r="N263" s="8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A264" s="8">
+        <v>260</v>
+      </c>
+      <c r="B264" s="8">
+        <v>10260</v>
+      </c>
+      <c r="C264" s="8">
+        <v>260</v>
+      </c>
+      <c r="D264" s="8">
+        <v>26</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F264" s="8">
+        <v>8430127996</v>
+      </c>
+      <c r="G264" s="8">
+        <v>12714884598749</v>
+      </c>
+      <c r="H264" s="8">
+        <v>1</v>
+      </c>
+      <c r="I264" s="8">
+        <v>106102065928</v>
+      </c>
+      <c r="J264" s="8">
+        <v>776222168</v>
+      </c>
+      <c r="K264" s="8">
+        <v>88</v>
+      </c>
+      <c r="L264" s="8">
+        <v>140</v>
+      </c>
+      <c r="M264" s="8">
+        <v>0</v>
+      </c>
+      <c r="N264" s="8">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" s="8">
+        <v>261</v>
+      </c>
+      <c r="B265" s="8">
+        <v>10261</v>
+      </c>
+      <c r="C265" s="8">
+        <v>261</v>
+      </c>
+      <c r="D265" s="8">
+        <v>27</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F265" s="8">
+        <v>1483562215</v>
+      </c>
+      <c r="G265" s="8">
+        <v>4666002544949</v>
+      </c>
+      <c r="H265" s="8">
+        <v>5</v>
+      </c>
+      <c r="I265" s="8">
+        <v>29967136231</v>
+      </c>
+      <c r="J265" s="8">
+        <v>231210406</v>
+      </c>
+      <c r="K265" s="8">
+        <v>42</v>
+      </c>
+      <c r="L265" s="8">
+        <v>0</v>
+      </c>
+      <c r="M265" s="8">
+        <v>0</v>
+      </c>
+      <c r="N265" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A266" s="8">
+        <v>262</v>
+      </c>
+      <c r="B266" s="8">
+        <v>10262</v>
+      </c>
+      <c r="C266" s="8">
+        <v>262</v>
+      </c>
+      <c r="D266" s="8">
+        <v>27</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F266" s="8">
+        <v>1594829394</v>
+      </c>
+      <c r="G266" s="8">
+        <v>4992622722420</v>
+      </c>
+      <c r="H266" s="8">
+        <v>5</v>
+      </c>
+      <c r="I266" s="8">
+        <v>32963849882</v>
+      </c>
+      <c r="J266" s="8">
+        <v>254331273</v>
+      </c>
+      <c r="K266" s="8">
+        <v>46</v>
+      </c>
+      <c r="L266" s="8">
+        <v>0</v>
+      </c>
+      <c r="M266" s="8">
+        <v>0</v>
+      </c>
+      <c r="N266" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A267" s="8">
+        <v>263</v>
+      </c>
+      <c r="B267" s="8">
+        <v>10263</v>
+      </c>
+      <c r="C267" s="8">
+        <v>263</v>
+      </c>
+      <c r="D267" s="8">
+        <v>27</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" s="8">
+        <v>1714441545</v>
+      </c>
+      <c r="G267" s="8">
+        <v>5342106313447</v>
+      </c>
+      <c r="H267" s="8">
+        <v>5</v>
+      </c>
+      <c r="I267" s="8">
+        <v>36260234938</v>
+      </c>
+      <c r="J267" s="8">
+        <v>279764459</v>
+      </c>
+      <c r="K267" s="8">
+        <v>50</v>
+      </c>
+      <c r="L267" s="8">
+        <v>0</v>
+      </c>
+      <c r="M267" s="8">
+        <v>0</v>
+      </c>
+      <c r="N267" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A268" s="8">
+        <v>264</v>
+      </c>
+      <c r="B268" s="8">
+        <v>10264</v>
+      </c>
+      <c r="C268" s="8">
+        <v>264</v>
+      </c>
+      <c r="D268" s="8">
+        <v>27</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F268" s="8">
+        <v>1843024675</v>
+      </c>
+      <c r="G268" s="8">
+        <v>5716053755529</v>
+      </c>
+      <c r="H268" s="8">
+        <v>5</v>
+      </c>
+      <c r="I268" s="8">
+        <v>39886258483</v>
+      </c>
+      <c r="J268" s="8">
+        <v>307740913</v>
+      </c>
+      <c r="K268" s="8">
+        <v>55</v>
+      </c>
+      <c r="L268" s="8">
+        <v>0</v>
+      </c>
+      <c r="M268" s="8">
+        <v>0</v>
+      </c>
+      <c r="N268" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A269" s="8">
+        <v>265</v>
+      </c>
+      <c r="B269" s="8">
+        <v>10265</v>
+      </c>
+      <c r="C269" s="8">
+        <v>265</v>
+      </c>
+      <c r="D269" s="8">
+        <v>27</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F269" s="8">
+        <v>1981251595</v>
+      </c>
+      <c r="G269" s="8">
+        <v>6116177517882</v>
+      </c>
+      <c r="H269" s="8">
+        <v>5</v>
+      </c>
+      <c r="I269" s="8">
+        <v>43874884262</v>
+      </c>
+      <c r="J269" s="8">
+        <v>338515066</v>
+      </c>
+      <c r="K269" s="8">
+        <v>61</v>
+      </c>
+      <c r="L269" s="8">
+        <v>0</v>
+      </c>
+      <c r="M269" s="8">
+        <v>0</v>
+      </c>
+      <c r="N269" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A270" s="8">
+        <v>266</v>
+      </c>
+      <c r="B270" s="8">
+        <v>10266</v>
+      </c>
+      <c r="C270" s="8">
+        <v>266</v>
+      </c>
+      <c r="D270" s="8">
+        <v>27</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F270" s="8">
+        <v>2129845415</v>
+      </c>
+      <c r="G270" s="8">
+        <v>6544309944171</v>
+      </c>
+      <c r="H270" s="8">
+        <v>5</v>
+      </c>
+      <c r="I270" s="8">
+        <v>48262372716</v>
+      </c>
+      <c r="J270" s="8">
+        <v>372366567</v>
+      </c>
+      <c r="K270" s="8">
+        <v>67</v>
+      </c>
+      <c r="L270" s="8">
+        <v>0</v>
+      </c>
+      <c r="M270" s="8">
+        <v>0</v>
+      </c>
+      <c r="N270" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A271" s="8">
+        <v>267</v>
+      </c>
+      <c r="B271" s="8">
+        <v>10267</v>
+      </c>
+      <c r="C271" s="8">
+        <v>267</v>
+      </c>
+      <c r="D271" s="8">
+        <v>27</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F271" s="8">
+        <v>2289583875</v>
+      </c>
+      <c r="G271" s="8">
+        <v>7002411640460</v>
+      </c>
+      <c r="H271" s="8">
+        <v>5</v>
+      </c>
+      <c r="I271" s="8">
+        <v>53088609870</v>
+      </c>
+      <c r="J271" s="8">
+        <v>409603207</v>
+      </c>
+      <c r="K271" s="8">
+        <v>74</v>
+      </c>
+      <c r="L271" s="8">
+        <v>0</v>
+      </c>
+      <c r="M271" s="8">
+        <v>0</v>
+      </c>
+      <c r="N271" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A272" s="8">
+        <v>268</v>
+      </c>
+      <c r="B272" s="8">
+        <v>10268</v>
+      </c>
+      <c r="C272" s="8">
+        <v>268</v>
+      </c>
+      <c r="D272" s="8">
+        <v>27</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F272" s="8">
+        <v>2461302626</v>
+      </c>
+      <c r="G272" s="8">
+        <v>7492580455296</v>
+      </c>
+      <c r="H272" s="8">
+        <v>5</v>
+      </c>
+      <c r="I272" s="8">
+        <v>58397471108</v>
+      </c>
+      <c r="J272" s="8">
+        <v>450563644</v>
+      </c>
+      <c r="K272" s="8">
+        <v>81</v>
+      </c>
+      <c r="L272" s="8">
+        <v>0</v>
+      </c>
+      <c r="M272" s="8">
+        <v>0</v>
+      </c>
+      <c r="N272" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A273" s="8">
+        <v>269</v>
+      </c>
+      <c r="B273" s="8">
+        <v>10269</v>
+      </c>
+      <c r="C273" s="8">
+        <v>269</v>
+      </c>
+      <c r="D273" s="8">
+        <v>27</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F273" s="8">
+        <v>2645900366</v>
+      </c>
+      <c r="G273" s="8">
+        <v>8017061087520</v>
+      </c>
+      <c r="H273" s="8">
+        <v>5</v>
+      </c>
+      <c r="I273" s="8">
+        <v>64237217946</v>
+      </c>
+      <c r="J273" s="8">
+        <v>495619945</v>
+      </c>
+      <c r="K273" s="8">
+        <v>90</v>
+      </c>
+      <c r="L273" s="8">
+        <v>0</v>
+      </c>
+      <c r="M273" s="8">
+        <v>0</v>
+      </c>
+      <c r="N273" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A274" s="8">
+        <v>270</v>
+      </c>
+      <c r="B274" s="8">
+        <v>10270</v>
+      </c>
+      <c r="C274" s="8">
+        <v>270</v>
+      </c>
+      <c r="D274" s="8">
+        <v>27</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F274" s="8">
+        <v>14221714726</v>
+      </c>
+      <c r="G274" s="8">
+        <v>25878385080159</v>
+      </c>
+      <c r="H274" s="8">
+        <v>1</v>
+      </c>
+      <c r="I274" s="8">
+        <v>211982820630</v>
+      </c>
+      <c r="J274" s="8">
+        <v>1386572075</v>
+      </c>
+      <c r="K274" s="8">
+        <v>88</v>
+      </c>
+      <c r="L274" s="8">
+        <v>145</v>
+      </c>
+      <c r="M274" s="8">
+        <v>0</v>
+      </c>
+      <c r="N274" s="8">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A275" s="8">
+        <v>271</v>
+      </c>
+      <c r="B275" s="8">
+        <v>10271</v>
+      </c>
+      <c r="C275" s="8">
+        <v>271</v>
+      </c>
+      <c r="D275" s="8">
+        <v>28</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F275" s="8">
+        <v>2410304496</v>
+      </c>
+      <c r="G275" s="8">
+        <v>8664090881423</v>
+      </c>
+      <c r="H275" s="8">
+        <v>5</v>
+      </c>
+      <c r="I275" s="8">
+        <v>56895887871</v>
+      </c>
+      <c r="J275" s="8">
+        <v>398654256</v>
+      </c>
+      <c r="K275" s="8">
+        <v>42</v>
+      </c>
+      <c r="L275" s="8">
+        <v>0</v>
+      </c>
+      <c r="M275" s="8">
+        <v>0</v>
+      </c>
+      <c r="N275" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A276" s="8">
+        <v>272</v>
+      </c>
+      <c r="B276" s="8">
+        <v>10272</v>
+      </c>
+      <c r="C276" s="8">
+        <v>272</v>
+      </c>
+      <c r="D276" s="8">
+        <v>28</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F276" s="8">
+        <v>2591077354</v>
+      </c>
+      <c r="G276" s="8">
+        <v>9270577241869</v>
+      </c>
+      <c r="H276" s="8">
+        <v>5</v>
+      </c>
+      <c r="I276" s="8">
+        <v>62585476711</v>
+      </c>
+      <c r="J276" s="8">
+        <v>438519382</v>
+      </c>
+      <c r="K276" s="8">
+        <v>46</v>
+      </c>
+      <c r="L276" s="8">
+        <v>0</v>
+      </c>
+      <c r="M276" s="8">
+        <v>0</v>
+      </c>
+      <c r="N276" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" s="8">
+        <v>273</v>
+      </c>
+      <c r="B277" s="8">
+        <v>10273</v>
+      </c>
+      <c r="C277" s="8">
+        <v>273</v>
+      </c>
+      <c r="D277" s="8">
+        <v>28</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F277" s="8">
+        <v>2785408069</v>
+      </c>
+      <c r="G277" s="8">
+        <v>9919517649649</v>
+      </c>
+      <c r="H277" s="8">
+        <v>5</v>
+      </c>
+      <c r="I277" s="8">
+        <v>68844024511</v>
+      </c>
+      <c r="J277" s="8">
+        <v>482371422</v>
+      </c>
+      <c r="K277" s="8">
+        <v>50</v>
+      </c>
+      <c r="L277" s="8">
+        <v>0</v>
+      </c>
+      <c r="M277" s="8">
+        <v>0</v>
+      </c>
+      <c r="N277" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A278" s="8">
+        <v>274</v>
+      </c>
+      <c r="B278" s="8">
+        <v>10274</v>
+      </c>
+      <c r="C278" s="8">
+        <v>274</v>
+      </c>
+      <c r="D278" s="8">
+        <v>28</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F278" s="8">
+        <v>2994313697</v>
+      </c>
+      <c r="G278" s="8">
+        <v>10613883885386</v>
+      </c>
+      <c r="H278" s="8">
+        <v>5</v>
+      </c>
+      <c r="I278" s="8">
+        <v>75728427059</v>
+      </c>
+      <c r="J278" s="8">
+        <v>530608578</v>
+      </c>
+      <c r="K278" s="8">
+        <v>55</v>
+      </c>
+      <c r="L278" s="8">
+        <v>0</v>
+      </c>
+      <c r="M278" s="8">
+        <v>0</v>
+      </c>
+      <c r="N278" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" s="8">
+        <v>275</v>
+      </c>
+      <c r="B279" s="8">
+        <v>10275</v>
+      </c>
+      <c r="C279" s="8">
+        <v>275</v>
+      </c>
+      <c r="D279" s="8">
+        <v>28</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F279" s="8">
+        <v>3218887337</v>
+      </c>
+      <c r="G279" s="8">
+        <v>11356855756372</v>
+      </c>
+      <c r="H279" s="8">
+        <v>5</v>
+      </c>
+      <c r="I279" s="8">
+        <v>83301269633</v>
+      </c>
+      <c r="J279" s="8">
+        <v>583669542</v>
+      </c>
+      <c r="K279" s="8">
+        <v>61</v>
+      </c>
+      <c r="L279" s="8">
+        <v>0</v>
+      </c>
+      <c r="M279" s="8">
+        <v>0</v>
+      </c>
+      <c r="N279" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" s="8">
+        <v>276</v>
+      </c>
+      <c r="B280" s="8">
+        <v>10276</v>
+      </c>
+      <c r="C280" s="8">
+        <v>276</v>
+      </c>
+      <c r="D280" s="8">
+        <v>28</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F280" s="8">
+        <v>3460303807</v>
+      </c>
+      <c r="G280" s="8">
+        <v>12151835659387</v>
+      </c>
+      <c r="H280" s="8">
+        <v>5</v>
+      </c>
+      <c r="I280" s="8">
+        <v>91631396649</v>
+      </c>
+      <c r="J280" s="8">
+        <v>642036486</v>
+      </c>
+      <c r="K280" s="8">
+        <v>67</v>
+      </c>
+      <c r="L280" s="8">
+        <v>0</v>
+      </c>
+      <c r="M280" s="8">
+        <v>0</v>
+      </c>
+      <c r="N280" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A281" s="8">
+        <v>277</v>
+      </c>
+      <c r="B281" s="8">
+        <v>10277</v>
+      </c>
+      <c r="C281" s="8">
+        <v>277</v>
+      </c>
+      <c r="D281" s="8">
+        <v>28</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F281" s="8">
+        <v>3719826680</v>
+      </c>
+      <c r="G281" s="8">
+        <v>13002464155910</v>
+      </c>
+      <c r="H281" s="8">
+        <v>5</v>
+      </c>
+      <c r="I281" s="8">
+        <v>100794536091</v>
+      </c>
+      <c r="J281" s="8">
+        <v>706240106</v>
+      </c>
+      <c r="K281" s="8">
+        <v>74</v>
+      </c>
+      <c r="L281" s="8">
+        <v>0</v>
+      </c>
+      <c r="M281" s="8">
+        <v>0</v>
+      </c>
+      <c r="N281" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A282" s="8">
+        <v>278</v>
+      </c>
+      <c r="B282" s="8">
+        <v>10278</v>
+      </c>
+      <c r="C282" s="8">
+        <v>278</v>
+      </c>
+      <c r="D282" s="8">
+        <v>28</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F282" s="8">
+        <v>3998813616</v>
+      </c>
+      <c r="G282" s="8">
+        <v>13912636646831</v>
+      </c>
+      <c r="H282" s="8">
+        <v>5</v>
+      </c>
+      <c r="I282" s="8">
+        <v>110873990177</v>
+      </c>
+      <c r="J282" s="8">
+        <v>776864318</v>
+      </c>
+      <c r="K282" s="8">
+        <v>81</v>
+      </c>
+      <c r="L282" s="8">
+        <v>0</v>
+      </c>
+      <c r="M282" s="8">
+        <v>0</v>
+      </c>
+      <c r="N282" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A283" s="8">
+        <v>279</v>
+      </c>
+      <c r="B283" s="8">
+        <v>10279</v>
+      </c>
+      <c r="C283" s="8">
+        <v>279</v>
+      </c>
+      <c r="D283" s="8">
+        <v>28</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F283" s="8">
+        <v>4298724708</v>
+      </c>
+      <c r="G283" s="8">
+        <v>14886521212765</v>
+      </c>
+      <c r="H283" s="8">
+        <v>5</v>
+      </c>
+      <c r="I283" s="8">
+        <v>121961388677</v>
+      </c>
+      <c r="J283" s="8">
+        <v>854550640</v>
+      </c>
+      <c r="K283" s="8">
+        <v>90</v>
+      </c>
+      <c r="L283" s="8">
+        <v>0</v>
+      </c>
+      <c r="M283" s="8">
+        <v>0</v>
+      </c>
+      <c r="N283" s="8">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A284" s="8">
+        <v>280</v>
+      </c>
+      <c r="B284" s="8">
+        <v>10280</v>
+      </c>
+      <c r="C284" s="8">
+        <v>280</v>
+      </c>
+      <c r="D284" s="8">
+        <v>28</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F284" s="8">
+        <v>23105645726</v>
+      </c>
+      <c r="G284" s="8">
+        <v>48052412753545</v>
+      </c>
+      <c r="H284" s="8">
+        <v>1</v>
+      </c>
+      <c r="I284" s="8">
+        <v>402472585308</v>
+      </c>
+      <c r="J284" s="8">
+        <v>2390735213</v>
+      </c>
+      <c r="K284" s="8">
+        <v>88</v>
+      </c>
+      <c r="L284" s="8">
+        <v>150</v>
+      </c>
+      <c r="M284" s="8">
+        <v>0</v>
+      </c>
+      <c r="N284" s="8">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A285" s="8">
+        <v>281</v>
+      </c>
+      <c r="B285" s="8">
+        <v>10281</v>
+      </c>
+      <c r="C285" s="8">
+        <v>281</v>
+      </c>
+      <c r="D285" s="8">
+        <v>29</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F285" s="8">
+        <v>3765707520</v>
+      </c>
+      <c r="G285" s="8">
+        <v>14542049071753</v>
+      </c>
+      <c r="H285" s="8">
+        <v>5</v>
+      </c>
+      <c r="I285" s="8">
+        <v>102373039721</v>
+      </c>
+      <c r="J285" s="8">
+        <v>662604337</v>
+      </c>
+      <c r="K285" s="8">
+        <v>42</v>
+      </c>
+      <c r="L285" s="8">
+        <v>0</v>
+      </c>
+      <c r="M285" s="8">
+        <v>0</v>
+      </c>
+      <c r="N285" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A286" s="8">
+        <v>282</v>
+      </c>
+      <c r="B286" s="8">
+        <v>10282</v>
+      </c>
+      <c r="C286" s="8">
+        <v>282</v>
+      </c>
+      <c r="D286" s="8">
+        <v>29</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F286" s="8">
+        <v>4048135616</v>
+      </c>
+      <c r="G286" s="8">
+        <v>15559992504671</v>
+      </c>
+      <c r="H286" s="8">
+        <v>5</v>
+      </c>
+      <c r="I286" s="8">
+        <v>112610343788</v>
+      </c>
+      <c r="J286" s="8">
+        <v>728864273</v>
+      </c>
+      <c r="K286" s="8">
+        <v>46</v>
+      </c>
+      <c r="L286" s="8">
+        <v>0</v>
+      </c>
+      <c r="M286" s="8">
+        <v>0</v>
+      </c>
+      <c r="N286" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A287" s="8">
+        <v>283</v>
+      </c>
+      <c r="B287" s="8">
+        <v>10283</v>
+      </c>
+      <c r="C287" s="8">
+        <v>283</v>
+      </c>
+      <c r="D287" s="8">
+        <v>29</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F287" s="8">
+        <v>4351745653</v>
+      </c>
+      <c r="G287" s="8">
+        <v>16649191981424</v>
+      </c>
+      <c r="H287" s="8">
+        <v>5</v>
+      </c>
+      <c r="I287" s="8">
+        <v>123871378399</v>
+      </c>
+      <c r="J287" s="8">
+        <v>801750869</v>
+      </c>
+      <c r="K287" s="8">
+        <v>50</v>
+      </c>
+      <c r="L287" s="8">
+        <v>0</v>
+      </c>
+      <c r="M287" s="8">
+        <v>0</v>
+      </c>
+      <c r="N287" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A288" s="8">
+        <v>284</v>
+      </c>
+      <c r="B288" s="8">
+        <v>10284</v>
+      </c>
+      <c r="C288" s="8">
+        <v>284</v>
+      </c>
+      <c r="D288" s="8">
+        <v>29</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F288" s="8">
+        <v>4678126612</v>
+      </c>
+      <c r="G288" s="8">
+        <v>17814635420563</v>
+      </c>
+      <c r="H288" s="8">
+        <v>5</v>
+      </c>
+      <c r="I288" s="8">
+        <v>136258516413</v>
+      </c>
+      <c r="J288" s="8">
+        <v>881925979</v>
+      </c>
+      <c r="K288" s="8">
+        <v>55</v>
+      </c>
+      <c r="L288" s="8">
+        <v>0</v>
+      </c>
+      <c r="M288" s="8">
+        <v>0</v>
+      </c>
+      <c r="N288" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A289" s="8">
+        <v>285</v>
+      </c>
+      <c r="B289" s="8">
+        <v>10285</v>
+      </c>
+      <c r="C289" s="8">
+        <v>285</v>
+      </c>
+      <c r="D289" s="8">
+        <v>29</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F289" s="8">
+        <v>5028986284</v>
+      </c>
+      <c r="G289" s="8">
+        <v>19061659898339</v>
+      </c>
+      <c r="H289" s="8">
+        <v>5</v>
+      </c>
+      <c r="I289" s="8">
+        <v>149884367817</v>
+      </c>
+      <c r="J289" s="8">
+        <v>970118754</v>
+      </c>
+      <c r="K289" s="8">
+        <v>61</v>
+      </c>
+      <c r="L289" s="8">
+        <v>0</v>
+      </c>
+      <c r="M289" s="8">
+        <v>0</v>
+      </c>
+      <c r="N289" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A290" s="8">
+        <v>286</v>
+      </c>
+      <c r="B290" s="8">
+        <v>10286</v>
+      </c>
+      <c r="C290" s="8">
+        <v>286</v>
+      </c>
+      <c r="D290" s="8">
+        <v>29</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F290" s="8">
+        <v>5406160130</v>
+      </c>
+      <c r="G290" s="8">
+        <v>20395976091338</v>
+      </c>
+      <c r="H290" s="8">
+        <v>5</v>
+      </c>
+      <c r="I290" s="8">
+        <v>164872804694</v>
+      </c>
+      <c r="J290" s="8">
+        <v>1067130612</v>
+      </c>
+      <c r="K290" s="8">
+        <v>67</v>
+      </c>
+      <c r="L290" s="8">
+        <v>0</v>
+      </c>
+      <c r="M290" s="8">
+        <v>0</v>
+      </c>
+      <c r="N290" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A291" s="8">
+        <v>287</v>
+      </c>
+      <c r="B291" s="8">
+        <v>10287</v>
+      </c>
+      <c r="C291" s="8">
+        <v>287</v>
+      </c>
+      <c r="D291" s="8">
+        <v>29</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F291" s="8">
+        <v>5811622277</v>
+      </c>
+      <c r="G291" s="8">
+        <v>21823694418346</v>
+      </c>
+      <c r="H291" s="8">
+        <v>5</v>
+      </c>
+      <c r="I291" s="8">
+        <v>181360084762</v>
+      </c>
+      <c r="J291" s="8">
+        <v>1173843626</v>
+      </c>
+      <c r="K291" s="8">
+        <v>74</v>
+      </c>
+      <c r="L291" s="8">
+        <v>0</v>
+      </c>
+      <c r="M291" s="8">
+        <v>0</v>
+      </c>
+      <c r="N291" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A292" s="8">
+        <v>288</v>
+      </c>
+      <c r="B292" s="8">
+        <v>10288</v>
+      </c>
+      <c r="C292" s="8">
+        <v>288</v>
+      </c>
+      <c r="D292" s="8">
+        <v>29</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F292" s="8">
+        <v>6247493846</v>
+      </c>
+      <c r="G292" s="8">
+        <v>23351353027642</v>
+      </c>
+      <c r="H292" s="8">
+        <v>5</v>
+      </c>
+      <c r="I292" s="8">
+        <v>199496094097</v>
+      </c>
+      <c r="J292" s="8">
+        <v>1291228323</v>
+      </c>
+      <c r="K292" s="8">
+        <v>81</v>
+      </c>
+      <c r="L292" s="8">
+        <v>0</v>
+      </c>
+      <c r="M292" s="8">
+        <v>0</v>
+      </c>
+      <c r="N292" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A293" s="8">
+        <v>289</v>
+      </c>
+      <c r="B293" s="8">
+        <v>10289</v>
+      </c>
+      <c r="C293" s="8">
+        <v>289</v>
+      </c>
+      <c r="D293" s="8">
+        <v>29</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F293" s="8">
+        <v>6716055995</v>
+      </c>
+      <c r="G293" s="8">
+        <v>24985947740678</v>
+      </c>
+      <c r="H293" s="8">
+        <v>5</v>
+      </c>
+      <c r="I293" s="8">
+        <v>219445702575</v>
+      </c>
+      <c r="J293" s="8">
+        <v>1420350973</v>
+      </c>
+      <c r="K293" s="8">
+        <v>90</v>
+      </c>
+      <c r="L293" s="8">
+        <v>0</v>
+      </c>
+      <c r="M293" s="8">
+        <v>0</v>
+      </c>
+      <c r="N293" s="8">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A294" s="8">
+        <v>290</v>
+      </c>
+      <c r="B294" s="8">
+        <v>10290</v>
+      </c>
+      <c r="C294" s="8">
+        <v>290</v>
+      </c>
+      <c r="D294" s="8">
+        <v>29</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F294" s="8">
+        <v>36098801632</v>
+      </c>
+      <c r="G294" s="8">
+        <v>80652494744310</v>
+      </c>
+      <c r="H294" s="8">
+        <v>1</v>
+      </c>
+      <c r="I294" s="8">
+        <v>724170823309</v>
+      </c>
+      <c r="J294" s="8">
+        <v>3973647585</v>
+      </c>
+      <c r="K294" s="8">
+        <v>88</v>
+      </c>
+      <c r="L294" s="8">
+        <v>155</v>
+      </c>
+      <c r="M294" s="8">
+        <v>0</v>
+      </c>
+      <c r="N294" s="8">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A295" s="8">
+        <v>291</v>
+      </c>
+      <c r="B295" s="8">
+        <v>10291</v>
+      </c>
+      <c r="C295" s="8">
+        <v>291</v>
+      </c>
+      <c r="D295" s="8">
+        <v>30</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F295" s="8">
+        <v>5648561280</v>
+      </c>
+      <c r="G295" s="8">
+        <v>21813073607629</v>
+      </c>
+      <c r="H295" s="8">
+        <v>5</v>
+      </c>
+      <c r="I295" s="8">
+        <v>174034167525</v>
+      </c>
+      <c r="J295" s="8">
+        <v>1060166939</v>
+      </c>
+      <c r="K295" s="8">
+        <v>42</v>
+      </c>
+      <c r="L295" s="8">
+        <v>0</v>
+      </c>
+      <c r="M295" s="8">
+        <v>0</v>
+      </c>
+      <c r="N295" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A296" s="8">
+        <v>292</v>
+      </c>
+      <c r="B296" s="8">
+        <v>10292</v>
+      </c>
+      <c r="C296" s="8">
+        <v>292</v>
+      </c>
+      <c r="D296" s="8">
+        <v>30</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F296" s="8">
+        <v>6072203424</v>
+      </c>
+      <c r="G296" s="8">
+        <v>23339988757006</v>
+      </c>
+      <c r="H296" s="8">
+        <v>5</v>
+      </c>
+      <c r="I296" s="8">
+        <v>191437584439</v>
+      </c>
+      <c r="J296" s="8">
+        <v>1166182836</v>
+      </c>
+      <c r="K296" s="8">
+        <v>46</v>
+      </c>
+      <c r="L296" s="8">
+        <v>0</v>
+      </c>
+      <c r="M296" s="8">
+        <v>0</v>
+      </c>
+      <c r="N296" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A297" s="8">
+        <v>293</v>
+      </c>
+      <c r="B297" s="8">
+        <v>10293</v>
+      </c>
+      <c r="C297" s="8">
+        <v>293</v>
+      </c>
+      <c r="D297" s="8">
+        <v>30</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F297" s="8">
+        <v>6527618479</v>
+      </c>
+      <c r="G297" s="8">
+        <v>24973787972136</v>
+      </c>
+      <c r="H297" s="8">
+        <v>5</v>
+      </c>
+      <c r="I297" s="8">
+        <v>210581343278</v>
+      </c>
+      <c r="J297" s="8">
+        <v>1282801390</v>
+      </c>
+      <c r="K297" s="8">
+        <v>50</v>
+      </c>
+      <c r="L297" s="8">
+        <v>0</v>
+      </c>
+      <c r="M297" s="8">
+        <v>0</v>
+      </c>
+      <c r="N297" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A298" s="8">
+        <v>294</v>
+      </c>
+      <c r="B298" s="8">
+        <v>10294</v>
+      </c>
+      <c r="C298" s="8">
+        <v>294</v>
+      </c>
+      <c r="D298" s="8">
+        <v>30</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F298" s="8">
+        <v>7017189918</v>
+      </c>
+      <c r="G298" s="8">
+        <v>26721953130844</v>
+      </c>
+      <c r="H298" s="8">
+        <v>5</v>
+      </c>
+      <c r="I298" s="8">
+        <v>231639477902</v>
+      </c>
+      <c r="J298" s="8">
+        <v>1411081566</v>
+      </c>
+      <c r="K298" s="8">
+        <v>55</v>
+      </c>
+      <c r="L298" s="8">
+        <v>0</v>
+      </c>
+      <c r="M298" s="8">
+        <v>0</v>
+      </c>
+      <c r="N298" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A299" s="8">
+        <v>295</v>
+      </c>
+      <c r="B299" s="8">
+        <v>10295</v>
+      </c>
+      <c r="C299" s="8">
+        <v>295</v>
+      </c>
+      <c r="D299" s="8">
+        <v>30</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F299" s="8">
+        <v>7543479426</v>
+      </c>
+      <c r="G299" s="8">
+        <v>28592489847508</v>
+      </c>
+      <c r="H299" s="8">
+        <v>5</v>
+      </c>
+      <c r="I299" s="8">
+        <v>254803425288</v>
+      </c>
+      <c r="J299" s="8">
+        <v>1552190006</v>
+      </c>
+      <c r="K299" s="8">
+        <v>61</v>
+      </c>
+      <c r="L299" s="8">
+        <v>0</v>
+      </c>
+      <c r="M299" s="8">
+        <v>0</v>
+      </c>
+      <c r="N299" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A300" s="8">
+        <v>296</v>
+      </c>
+      <c r="B300" s="8">
+        <v>10296</v>
+      </c>
+      <c r="C300" s="8">
+        <v>296</v>
+      </c>
+      <c r="D300" s="8">
+        <v>30</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F300" s="8">
+        <v>8109240195</v>
+      </c>
+      <c r="G300" s="8">
+        <v>30593964137007</v>
+      </c>
+      <c r="H300" s="8">
+        <v>5</v>
+      </c>
+      <c r="I300" s="8">
+        <v>280283767979</v>
+      </c>
+      <c r="J300" s="8">
+        <v>1707408979</v>
+      </c>
+      <c r="K300" s="8">
+        <v>67</v>
+      </c>
+      <c r="L300" s="8">
+        <v>0</v>
+      </c>
+      <c r="M300" s="8">
+        <v>0</v>
+      </c>
+      <c r="N300" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A301" s="8">
+        <v>297</v>
+      </c>
+      <c r="B301" s="8">
+        <v>10297</v>
+      </c>
+      <c r="C301" s="8">
+        <v>297</v>
+      </c>
+      <c r="D301" s="8">
+        <v>30</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F301" s="8">
+        <v>8717433415</v>
+      </c>
+      <c r="G301" s="8">
+        <v>32735541627519</v>
+      </c>
+      <c r="H301" s="8">
+        <v>5</v>
+      </c>
+      <c r="I301" s="8">
+        <v>308312144095</v>
+      </c>
+      <c r="J301" s="8">
+        <v>1878149801</v>
+      </c>
+      <c r="K301" s="8">
+        <v>74</v>
+      </c>
+      <c r="L301" s="8">
+        <v>0</v>
+      </c>
+      <c r="M301" s="8">
+        <v>0</v>
+      </c>
+      <c r="N301" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A302" s="8">
+        <v>298</v>
+      </c>
+      <c r="B302" s="8">
+        <v>10298</v>
+      </c>
+      <c r="C302" s="8">
+        <v>298</v>
+      </c>
+      <c r="D302" s="8">
+        <v>30</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F302" s="8">
+        <v>9371240769</v>
+      </c>
+      <c r="G302" s="8">
+        <v>35027029541463</v>
+      </c>
+      <c r="H302" s="8">
+        <v>5</v>
+      </c>
+      <c r="I302" s="8">
+        <v>339143359964</v>
+      </c>
+      <c r="J302" s="8">
+        <v>2065965316</v>
+      </c>
+      <c r="K302" s="8">
+        <v>81</v>
+      </c>
+      <c r="L302" s="8">
+        <v>0</v>
+      </c>
+      <c r="M302" s="8">
+        <v>0</v>
+      </c>
+      <c r="N302" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A303" s="8">
+        <v>299</v>
+      </c>
+      <c r="B303" s="8">
+        <v>10299</v>
+      </c>
+      <c r="C303" s="8">
+        <v>299</v>
+      </c>
+      <c r="D303" s="8">
+        <v>30</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F303" s="8">
+        <v>10074083992</v>
+      </c>
+      <c r="G303" s="8">
+        <v>37478921611017</v>
+      </c>
+      <c r="H303" s="8">
+        <v>5</v>
+      </c>
+      <c r="I303" s="8">
+        <v>373057694377</v>
+      </c>
+      <c r="J303" s="8">
+        <v>2272561556</v>
+      </c>
+      <c r="K303" s="8">
+        <v>90</v>
+      </c>
+      <c r="L303" s="8">
+        <v>0</v>
+      </c>
+      <c r="M303" s="8">
+        <v>0</v>
+      </c>
+      <c r="N303" s="8">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A304" s="8">
+        <v>300</v>
+      </c>
+      <c r="B304" s="8">
+        <v>10300</v>
+      </c>
+      <c r="C304" s="8">
+        <v>300</v>
+      </c>
+      <c r="D304" s="8">
+        <v>30</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F304" s="8">
+        <v>54148202448</v>
+      </c>
+      <c r="G304" s="8">
+        <v>120978742116465</v>
+      </c>
+      <c r="H304" s="8">
+        <v>1</v>
+      </c>
+      <c r="I304" s="8">
+        <v>1231090399625</v>
+      </c>
+      <c r="J304" s="8">
+        <v>6357836136</v>
+      </c>
+      <c r="K304" s="8">
+        <v>88</v>
+      </c>
+      <c r="L304" s="8">
+        <v>160</v>
+      </c>
+      <c r="M304" s="8">
+        <v>0</v>
+      </c>
+      <c r="N304" s="8">
+        <v>2187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N204"/>
+  <autoFilter ref="A4:N304"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -31083,7 +35503,7 @@
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>104</v>
@@ -31091,7 +35511,7 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="H1" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
@@ -31107,22 +35527,22 @@
         <v>107</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>112</v>
@@ -31177,16 +35597,16 @@
         <v>119</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>122</v>
@@ -31215,13 +35635,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I5" s="8">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -31247,13 +35667,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I6" s="8">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -31279,13 +35699,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I7" s="8">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -31311,13 +35731,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I8" s="8">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -31343,13 +35763,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I9" s="8">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -31384,13 +35804,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -31403,7 +35823,7 @@
         <v>106</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>297</v>
@@ -31412,19 +35832,19 @@
         <v>109</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>301</v>
@@ -31473,25 +35893,25 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>298</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>167</v>
@@ -40057,13 +44477,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>112</v>
@@ -40100,16 +44520,16 @@
         <v>117</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>302</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>122</v>
@@ -40354,7 +44774,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I9"/>
+  <dimension ref="A2:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -40365,22 +44785,22 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I2" t="s">
         <v>112</v>
@@ -40423,22 +44843,22 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I4" t="s">
         <v>122</v>
@@ -40571,7 +44991,7 @@
         <v>200</v>
       </c>
       <c r="D9">
-        <v>999999</v>
+        <v>299</v>
       </c>
       <c r="E9">
         <v>5000</v>
@@ -40587,6 +45007,32 @@
       </c>
       <c r="I9" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>35106</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10">
+        <v>999999</v>
+      </c>
+      <c r="E10">
+        <v>9000</v>
+      </c>
+      <c r="F10">
+        <v>43200</v>
+      </c>
+      <c r="G10">
+        <v>86400</v>
+      </c>
+      <c r="H10">
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -40598,12 +45044,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F1" t="s">
         <v>104</v>
@@ -40617,19 +45063,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E2" t="s">
         <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -40663,19 +45109,19 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -40686,10 +45132,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D5" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -40709,10 +45155,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -40732,10 +45178,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D7" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -40755,10 +45201,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D8" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -40778,10 +45224,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -40801,10 +45247,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -40824,10 +45270,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D11" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -40847,10 +45293,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D12" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -40870,10 +45316,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D13" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -40893,10 +45339,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D14" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -40916,10 +45362,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D15" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -40939,10 +45385,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D16" t="s">
         <v>1084</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1083</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -40962,10 +45408,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D17" t="s">
         <v>1084</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1083</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -40985,10 +45431,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D18" t="s">
         <v>1084</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1083</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -41008,10 +45454,10 @@
         <v>33015</v>
       </c>
       <c r="C19" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D19" t="s">
         <v>1084</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1083</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -41031,10 +45477,10 @@
         <v>33016</v>
       </c>
       <c r="C20" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D20" t="s">
         <v>1084</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1083</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -41054,10 +45500,10 @@
         <v>33017</v>
       </c>
       <c r="C21" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D21" t="s">
         <v>1084</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1083</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
@@ -41077,10 +45523,10 @@
         <v>33018</v>
       </c>
       <c r="C22" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D22" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E22" t="s">
         <v>91</v>
@@ -41100,10 +45546,10 @@
         <v>33019</v>
       </c>
       <c r="C23" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D23" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E23" t="s">
         <v>94</v>
@@ -41123,10 +45569,10 @@
         <v>33020</v>
       </c>
       <c r="C24" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D24" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E24" t="s">
         <v>96</v>
@@ -41146,10 +45592,10 @@
         <v>33021</v>
       </c>
       <c r="C25" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D25" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
@@ -41159,6 +45605,29 @@
       </c>
       <c r="G25">
         <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26">
+        <v>33022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26">
+        <v>55028</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -16414,7 +16414,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -16464,7 +16464,7 @@
         <v>3</v>
       </c>
       <c r="P6" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -16514,7 +16514,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -16564,7 +16564,7 @@
         <v>8</v>
       </c>
       <c r="P8" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>12</v>
       </c>
       <c r="P9" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -16664,7 +16664,7 @@
         <v>16</v>
       </c>
       <c r="P10" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>22</v>
       </c>
       <c r="P11" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -16764,7 +16764,7 @@
         <v>30</v>
       </c>
       <c r="P12" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -53055,7 +53055,7 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>1190</v>
       </c>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -16414,7 +16414,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -16464,7 +16464,7 @@
         <v>3</v>
       </c>
       <c r="P6" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -16514,7 +16514,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -16564,7 +16564,7 @@
         <v>8</v>
       </c>
       <c r="P8" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>12</v>
       </c>
       <c r="P9" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -16664,7 +16664,7 @@
         <v>16</v>
       </c>
       <c r="P10" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>22</v>
       </c>
       <c r="P11" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -16764,7 +16764,7 @@
         <v>30</v>
       </c>
       <c r="P12" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -23,8 +23,8 @@
     <sheet sheetId="12" name="RelicTable" state="visible" r:id="rId17"/>
     <sheet sheetId="3" name="StageTable" state="visible" r:id="rId18"/>
     <sheet sheetId="9" name="PatchNoteTable" state="visible" r:id="rId19"/>
-    <sheet sheetId="13" name="GachaTable" state="visible" r:id="rId20"/>
-    <sheet sheetId="14" name="RelicSlotTable" state="visible" r:id="rId21"/>
+    <sheet sheetId="14" name="RelicSlotTable" state="visible" r:id="rId20"/>
+    <sheet sheetId="13" name="GachaTable" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">StringTable!$A$4:$E$131</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5704" uniqueCount="1395">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -3093,6 +3093,45 @@
     <t>Exist tree unlock gaps shortened</t>
   </si>
   <si>
+    <t>설정</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>ProfileUiLabel</t>
+  </si>
+  <si>
+    <t>배경음 볼륨</t>
+  </si>
+  <si>
+    <t>BGM Volume</t>
+  </si>
+  <si>
+    <t>효과음 볼륨</t>
+  </si>
+  <si>
+    <t>SFX Volume</t>
+  </si>
+  <si>
+    <t>전체 음소거</t>
+  </si>
+  <si>
+    <t>Mute All</t>
+  </si>
+  <si>
+    <t>사운드 추가 (BGM·효과음)</t>
+  </si>
+  <si>
+    <t>Sound added (BGM + SFX)</t>
+  </si>
+  <si>
+    <t>가챠 확률 표시 정밀도 개선</t>
+  </si>
+  <si>
+    <t>More precise gacha probability display</t>
+  </si>
+  <si>
     <t>EnumDefine/CurrencyType</t>
   </si>
   <si>
@@ -4167,6 +4206,9 @@
     <t>2026-09-12</t>
   </si>
   <si>
+    <t>해금 조건(존재력 트리 해금 수)</t>
+  </si>
+  <si>
     <t>요구 누적 뽑기</t>
   </si>
   <si>
@@ -4177,9 +4219,6 @@
   </si>
   <si>
     <t>MythicWeight</t>
-  </si>
-  <si>
-    <t>해금 조건(존재력 트리 해금 수)</t>
   </si>
 </sst>
 </file>
@@ -4685,27 +4724,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="B1" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="C1" t="s">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="D1" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="E1" t="s">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="F1" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B2" t="s">
         <v>117</v>
@@ -4725,7 +4764,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B3" t="s">
         <v>118</v>
@@ -4745,13 +4784,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B4" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="C4" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="D4" t="s">
         <v>125</v>
@@ -4765,13 +4804,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B5" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="C5" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="D5" t="s">
         <v>125</v>
@@ -4785,10 +4824,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B6" t="s">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -4800,18 +4839,18 @@
         <v>185</v>
       </c>
       <c r="F6" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B7" t="s">
         <v>382</v>
       </c>
       <c r="C7" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="D7" t="s">
         <v>125</v>
@@ -4825,13 +4864,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B8" t="s">
         <v>385</v>
       </c>
       <c r="C8" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -4845,13 +4884,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B9" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="C9" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -4865,13 +4904,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B10" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="C10" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4885,13 +4924,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B11" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="C11" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="D11" t="s">
         <v>125</v>
@@ -4905,13 +4944,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B12" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="C12" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -4925,13 +4964,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B13" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="C13" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4945,13 +4984,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B14" t="s">
         <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
@@ -4965,19 +5004,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B15" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="C15" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="D15" t="s">
         <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="F15" t="s">
         <v>185</v>
@@ -4985,7 +5024,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B16" t="s">
         <v>117</v>
@@ -5005,7 +5044,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B17" t="s">
         <v>118</v>
@@ -5025,13 +5064,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B18" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="C18" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="D18" t="s">
         <v>125</v>
@@ -5045,7 +5084,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B19" t="s">
         <v>279</v>
@@ -5065,13 +5104,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B20" t="s">
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D20" t="s">
         <v>125</v>
@@ -5085,13 +5124,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B21" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="C21" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="D21" t="s">
         <v>125</v>
@@ -5105,13 +5144,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B22" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="C22" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
@@ -5120,15 +5159,15 @@
         <v>185</v>
       </c>
       <c r="F22" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B23" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -5140,18 +5179,18 @@
         <v>185</v>
       </c>
       <c r="F23" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B24" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="C24" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="D24" t="s">
         <v>127</v>
@@ -5160,15 +5199,15 @@
         <v>185</v>
       </c>
       <c r="F24" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B25" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="C25" t="s">
         <v>149</v>
@@ -5185,7 +5224,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="B26" t="s">
         <v>283</v>
@@ -5205,7 +5244,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B27" t="s">
         <v>117</v>
@@ -5225,7 +5264,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B28" t="s">
         <v>118</v>
@@ -5245,7 +5284,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B29" t="s">
         <v>119</v>
@@ -5265,7 +5304,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B30" t="s">
         <v>120</v>
@@ -5285,7 +5324,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B31" t="s">
         <v>121</v>
@@ -5305,7 +5344,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B32" t="s">
         <v>122</v>
@@ -5325,7 +5364,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B33" t="s">
         <v>123</v>
@@ -5345,7 +5384,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B34" t="s">
         <v>124</v>
@@ -5365,7 +5404,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -5385,7 +5424,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B36" t="s">
         <v>118</v>
@@ -5405,7 +5444,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -5425,7 +5464,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B38" t="s">
         <v>139</v>
@@ -5445,7 +5484,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B39" t="s">
         <v>140</v>
@@ -5465,7 +5504,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B40" t="s">
         <v>124</v>
@@ -5485,7 +5524,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B41" t="s">
         <v>117</v>
@@ -5505,7 +5544,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B42" t="s">
         <v>118</v>
@@ -5525,19 +5564,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B43" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="C43" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="D43" t="s">
         <v>126</v>
       </c>
       <c r="E43" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="F43" t="s">
         <v>185</v>
@@ -5545,13 +5584,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B44" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="C44" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="D44" t="s">
         <v>127</v>
@@ -5560,32 +5599,32 @@
         <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B45" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="C45" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="D45" t="s">
         <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="F45" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B46" t="s">
         <v>343</v>
@@ -5600,24 +5639,24 @@
         <v>185</v>
       </c>
       <c r="F46" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B47" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="C47" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="D47" t="s">
         <v>125</v>
       </c>
       <c r="E47" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="F47" t="s">
         <v>116</v>
@@ -5625,19 +5664,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B48" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="C48" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="D48" t="s">
         <v>126</v>
       </c>
       <c r="E48" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="F48" t="s">
         <v>185</v>
@@ -5645,10 +5684,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B49" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="C49" t="s">
         <v>280</v>
@@ -5657,7 +5696,7 @@
         <v>125</v>
       </c>
       <c r="E49" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="F49" t="s">
         <v>185</v>
@@ -5665,19 +5704,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B50" t="s">
         <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D50" t="s">
         <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
@@ -5685,19 +5724,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B51" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="C51" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="D51" t="s">
         <v>125</v>
       </c>
       <c r="E51" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="F51" t="s">
         <v>116</v>
@@ -5705,13 +5744,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B52" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="C52" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="D52" t="s">
         <v>147</v>
@@ -5725,13 +5764,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B53" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="C53" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="D53" t="s">
         <v>147</v>
@@ -5745,13 +5784,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B54" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="C54" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="D54" t="s">
         <v>147</v>
@@ -5765,13 +5804,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B55" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="C55" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="D55" t="s">
         <v>126</v>
@@ -5780,12 +5819,12 @@
         <v>185</v>
       </c>
       <c r="F55" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B56" t="s">
         <v>124</v>
@@ -5805,7 +5844,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B57" t="s">
         <v>117</v>
@@ -5825,7 +5864,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B58" t="s">
         <v>118</v>
@@ -5845,13 +5884,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B59" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="C59" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="D59" t="s">
         <v>125</v>
@@ -5865,13 +5904,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B60" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="C60" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="D60" t="s">
         <v>125</v>
@@ -5885,13 +5924,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B61" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="C61" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="D61" t="s">
         <v>147</v>
@@ -5905,13 +5944,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B62" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="C62" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="D62" t="s">
         <v>147</v>
@@ -5925,13 +5964,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B63" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="C63" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -5945,13 +5984,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B64" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="C64" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="D64" t="s">
         <v>147</v>
@@ -5965,13 +6004,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B65" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="C65" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="D65" t="s">
         <v>147</v>
@@ -5985,13 +6024,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B66" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="C66" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="D66" t="s">
         <v>147</v>
@@ -6005,13 +6044,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B67" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="C67" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="D67" t="s">
         <v>147</v>
@@ -6025,13 +6064,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B68" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="C68" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="D68" t="s">
         <v>147</v>
@@ -6045,13 +6084,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B69" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="C69" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="D69" t="s">
         <v>147</v>
@@ -6065,13 +6104,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B70" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="C70" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="D70" t="s">
         <v>147</v>
@@ -6085,13 +6124,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B71" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="C71" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="D71" t="s">
         <v>125</v>
@@ -6105,7 +6144,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B72" t="s">
         <v>124</v>
@@ -6125,7 +6164,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B73" t="s">
         <v>117</v>
@@ -6145,7 +6184,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B74" t="s">
         <v>118</v>
@@ -6165,7 +6204,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B75" t="s">
         <v>343</v>
@@ -6180,12 +6219,12 @@
         <v>185</v>
       </c>
       <c r="F75" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B76" t="s">
         <v>121</v>
@@ -6205,19 +6244,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B77" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="C77" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="D77" t="s">
         <v>125</v>
       </c>
       <c r="E77" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="F77" t="s">
         <v>116</v>
@@ -6225,19 +6264,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B78" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="C78" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="D78" t="s">
         <v>125</v>
       </c>
       <c r="E78" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="F78" t="s">
         <v>116</v>
@@ -6245,19 +6284,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B79" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="C79" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="D79" t="s">
         <v>126</v>
       </c>
       <c r="E79" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="F79" t="s">
         <v>185</v>
@@ -6265,13 +6304,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B80" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="C80" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="D80" t="s">
         <v>127</v>
@@ -6280,18 +6319,18 @@
         <v>185</v>
       </c>
       <c r="F80" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B81" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="C81" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="D81" t="s">
         <v>147</v>
@@ -6305,13 +6344,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B82" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="C82" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="D82" t="s">
         <v>147</v>
@@ -6325,7 +6364,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
@@ -6345,10 +6384,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="B84" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -6360,12 +6399,12 @@
         <v>185</v>
       </c>
       <c r="F84" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B85" t="s">
         <v>117</v>
@@ -6385,7 +6424,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B86" t="s">
         <v>118</v>
@@ -6405,13 +6444,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B87" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="C87" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="D87" t="s">
         <v>125</v>
@@ -6425,13 +6464,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B88" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="C88" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="D88" t="s">
         <v>125</v>
@@ -6445,7 +6484,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B89" t="s">
         <v>124</v>
@@ -6465,7 +6504,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B90" t="s">
         <v>117</v>
@@ -6485,7 +6524,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B91" t="s">
         <v>118</v>
@@ -6505,19 +6544,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B92" t="s">
         <v>417</v>
       </c>
       <c r="C92" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="D92" t="s">
         <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="F92" t="s">
         <v>185</v>
@@ -6525,10 +6564,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B93" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="C93" t="s">
         <v>284</v>
@@ -6545,13 +6584,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B94" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="C94" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="D94" t="s">
         <v>147</v>
@@ -6565,13 +6604,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B95" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="C95" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="D95" t="s">
         <v>147</v>
@@ -6585,7 +6624,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B96" t="s">
         <v>124</v>
@@ -6605,7 +6644,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B97" t="s">
         <v>117</v>
@@ -6625,7 +6664,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B98" t="s">
         <v>118</v>
@@ -6645,13 +6684,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B99" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="C99" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="D99" t="s">
         <v>125</v>
@@ -6665,13 +6704,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B100" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="C100" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="D100" t="s">
         <v>125</v>
@@ -6685,13 +6724,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B101" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="C101" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="D101" t="s">
         <v>125</v>
@@ -6705,13 +6744,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B102" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="C102" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="D102" t="s">
         <v>125</v>
@@ -6725,13 +6764,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B103" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="C103" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="D103" t="s">
         <v>125</v>
@@ -6745,13 +6784,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B104" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="C104" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="D104" t="s">
         <v>125</v>
@@ -6765,7 +6804,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B105" t="s">
         <v>124</v>
@@ -6828,10 +6867,10 @@
         <v>782</v>
       </c>
       <c r="B108" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="C108" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="D108" t="s">
         <v>126</v>
@@ -6848,10 +6887,10 @@
         <v>782</v>
       </c>
       <c r="B109" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="C109" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="D109" t="s">
         <v>126</v>
@@ -6871,7 +6910,7 @@
         <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="D110" t="s">
         <v>127</v>
@@ -6880,7 +6919,7 @@
         <v>185</v>
       </c>
       <c r="F110" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -6888,10 +6927,10 @@
         <v>782</v>
       </c>
       <c r="B111" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="C111" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="D111" t="s">
         <v>125</v>
@@ -6908,10 +6947,10 @@
         <v>782</v>
       </c>
       <c r="B112" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="C112" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="D112" t="s">
         <v>125</v>
@@ -6925,7 +6964,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B113" t="s">
         <v>117</v>
@@ -6945,7 +6984,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B114" t="s">
         <v>118</v>
@@ -6965,7 +7004,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B115" t="s">
         <v>144</v>
@@ -6985,7 +7024,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B116" t="s">
         <v>119</v>
@@ -7005,7 +7044,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B117" t="s">
         <v>145</v>
@@ -7025,7 +7064,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B118" t="s">
         <v>146</v>
@@ -7045,7 +7084,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B119" t="s">
         <v>124</v>
@@ -7065,7 +7104,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B120" t="s">
         <v>117</v>
@@ -7085,7 +7124,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B121" t="s">
         <v>118</v>
@@ -7105,7 +7144,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B122" t="s">
         <v>214</v>
@@ -7125,7 +7164,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B123" t="s">
         <v>215</v>
@@ -7145,7 +7184,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="B124" t="s">
         <v>216</v>
@@ -7165,7 +7204,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B125" t="s">
         <v>117</v>
@@ -7185,7 +7224,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B126" t="s">
         <v>129</v>
@@ -7205,13 +7244,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B127" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="C127" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="D127" t="s">
         <v>126</v>
@@ -7225,13 +7264,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B128" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C128" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="D128" t="s">
         <v>147</v>
@@ -7245,13 +7284,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B129" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="C129" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="D129" t="s">
         <v>147</v>
@@ -7265,13 +7304,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B130" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="C130" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="D130" t="s">
         <v>147</v>
@@ -7285,13 +7324,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B131" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="C131" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="D131" t="s">
         <v>147</v>
@@ -7305,13 +7344,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B132" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="C132" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="D132" t="s">
         <v>125</v>
@@ -7325,10 +7364,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B133" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="C133" t="s">
         <v>128</v>
@@ -7345,7 +7384,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B134" t="s">
         <v>129</v>
@@ -7365,13 +7404,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B135" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="C135" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="D135" t="s">
         <v>127</v>
@@ -7380,18 +7419,18 @@
         <v>185</v>
       </c>
       <c r="F135" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B136" t="s">
         <v>119</v>
       </c>
       <c r="C136" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D136" t="s">
         <v>125</v>
@@ -7405,16 +7444,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B137" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="C137" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="D137" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="E137" t="s">
         <v>185</v>
@@ -7425,16 +7464,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B138" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="C138" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="D138" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="E138" t="s">
         <v>185</v>
@@ -7445,16 +7484,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B139" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="C139" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="D139" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="E139" t="s">
         <v>185</v>
@@ -7465,13 +7504,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B140" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="C140" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="D140" t="s">
         <v>125</v>
@@ -7485,7 +7524,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="B141" t="s">
         <v>124</v>
@@ -7505,7 +7544,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B142" t="s">
         <v>117</v>
@@ -7525,7 +7564,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B143" t="s">
         <v>118</v>
@@ -7545,7 +7584,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B144" t="s">
         <v>119</v>
@@ -7565,10 +7604,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B145" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -7580,12 +7619,12 @@
         <v>185</v>
       </c>
       <c r="F145" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B146" t="s">
         <v>121</v>
@@ -7605,13 +7644,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B147" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C147" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="D147" t="s">
         <v>147</v>
@@ -7625,13 +7664,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B148" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="C148" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="D148" t="s">
         <v>147</v>
@@ -7645,13 +7684,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B149" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="C149" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="D149" t="s">
         <v>126</v>
@@ -7660,18 +7699,18 @@
         <v>185</v>
       </c>
       <c r="F149" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B150" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="C150" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="D150" t="s">
         <v>125</v>
@@ -7685,7 +7724,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B151" t="s">
         <v>124</v>
@@ -7736,13 +7775,13 @@
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>116</v>
@@ -7759,7 +7798,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="P1" s="9"/>
     </row>
@@ -7771,43 +7810,43 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>343</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>121</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="P2" s="10" t="s">
         <v>124</v>
@@ -7871,43 +7910,43 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>344</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>280</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>134</v>
@@ -7921,7 +7960,7 @@
         <v>37201</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>48</v>
@@ -7936,7 +7975,7 @@
         <v>40058</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I5" s="8">
         <v>1</v>
@@ -7957,7 +7996,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>185</v>
@@ -7971,7 +8010,7 @@
         <v>37202</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -7986,7 +8025,7 @@
         <v>40058</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I6" s="8">
         <v>2</v>
@@ -8007,7 +8046,7 @@
         <v>5.5</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>185</v>
@@ -8021,7 +8060,7 @@
         <v>37203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -8036,7 +8075,7 @@
         <v>40058</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I7" s="8">
         <v>3</v>
@@ -8057,7 +8096,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>185</v>
@@ -8071,7 +8110,7 @@
         <v>37204</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
@@ -8086,7 +8125,7 @@
         <v>40058</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I8" s="8">
         <v>4</v>
@@ -8107,7 +8146,7 @@
         <v>6.5</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>185</v>
@@ -8121,7 +8160,7 @@
         <v>37205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
@@ -8136,7 +8175,7 @@
         <v>40058</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I9" s="8">
         <v>5</v>
@@ -8157,7 +8196,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>185</v>
@@ -8171,7 +8210,7 @@
         <v>37206</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>48</v>
@@ -8186,7 +8225,7 @@
         <v>40059</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I10" s="8">
         <v>1</v>
@@ -8207,7 +8246,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>185</v>
@@ -8221,7 +8260,7 @@
         <v>37207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
@@ -8236,7 +8275,7 @@
         <v>40059</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I11" s="8">
         <v>2</v>
@@ -8257,7 +8296,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>185</v>
@@ -8271,7 +8310,7 @@
         <v>37208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>48</v>
@@ -8286,7 +8325,7 @@
         <v>40059</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I12" s="8">
         <v>3</v>
@@ -8307,7 +8346,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>185</v>
@@ -8321,7 +8360,7 @@
         <v>37209</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
@@ -8336,7 +8375,7 @@
         <v>40059</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I13" s="8">
         <v>4</v>
@@ -8357,7 +8396,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>185</v>
@@ -8371,7 +8410,7 @@
         <v>37210</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>48</v>
@@ -8386,7 +8425,7 @@
         <v>40059</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I14" s="8">
         <v>5</v>
@@ -8407,7 +8446,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>185</v>
@@ -8421,7 +8460,7 @@
         <v>37211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>48</v>
@@ -8436,7 +8475,7 @@
         <v>40060</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I15" s="8">
         <v>1</v>
@@ -8457,7 +8496,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>185</v>
@@ -8471,7 +8510,7 @@
         <v>37212</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>48</v>
@@ -8486,7 +8525,7 @@
         <v>40060</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I16" s="8">
         <v>2</v>
@@ -8507,7 +8546,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>185</v>
@@ -8521,7 +8560,7 @@
         <v>37213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>48</v>
@@ -8536,7 +8575,7 @@
         <v>40060</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I17" s="8">
         <v>3</v>
@@ -8557,7 +8596,7 @@
         <v>24</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>185</v>
@@ -8571,7 +8610,7 @@
         <v>37214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>48</v>
@@ -8586,7 +8625,7 @@
         <v>40060</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I18" s="8">
         <v>4</v>
@@ -8607,7 +8646,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>185</v>
@@ -8621,7 +8660,7 @@
         <v>37215</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>48</v>
@@ -8636,7 +8675,7 @@
         <v>40060</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I19" s="8">
         <v>5</v>
@@ -8657,7 +8696,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>185</v>
@@ -8671,7 +8710,7 @@
         <v>37216</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>48</v>
@@ -8686,7 +8725,7 @@
         <v>40061</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I20" s="8">
         <v>1</v>
@@ -8707,7 +8746,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>185</v>
@@ -8721,7 +8760,7 @@
         <v>37217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -8736,7 +8775,7 @@
         <v>40061</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I21" s="8">
         <v>2</v>
@@ -8757,7 +8796,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>185</v>
@@ -8771,7 +8810,7 @@
         <v>37218</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>48</v>
@@ -8786,7 +8825,7 @@
         <v>40061</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I22" s="8">
         <v>3</v>
@@ -8807,7 +8846,7 @@
         <v>48</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>185</v>
@@ -8821,7 +8860,7 @@
         <v>37219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>48</v>
@@ -8836,7 +8875,7 @@
         <v>40061</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I23" s="8">
         <v>4</v>
@@ -8857,7 +8896,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>185</v>
@@ -8871,7 +8910,7 @@
         <v>37220</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>48</v>
@@ -8886,7 +8925,7 @@
         <v>40061</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I24" s="8">
         <v>5</v>
@@ -8907,7 +8946,7 @@
         <v>56</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>185</v>
@@ -8921,7 +8960,7 @@
         <v>37221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>48</v>
@@ -8936,7 +8975,7 @@
         <v>40062</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I25" s="8">
         <v>1</v>
@@ -8957,7 +8996,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>185</v>
@@ -8971,7 +9010,7 @@
         <v>37222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -8986,7 +9025,7 @@
         <v>40062</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I26" s="8">
         <v>2</v>
@@ -9007,7 +9046,7 @@
         <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>185</v>
@@ -9021,7 +9060,7 @@
         <v>37223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -9036,7 +9075,7 @@
         <v>40062</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I27" s="8">
         <v>3</v>
@@ -9057,7 +9096,7 @@
         <v>96</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>185</v>
@@ -9071,7 +9110,7 @@
         <v>37224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>48</v>
@@ -9086,7 +9125,7 @@
         <v>40062</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I28" s="8">
         <v>4</v>
@@ -9107,7 +9146,7 @@
         <v>104</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>185</v>
@@ -9121,7 +9160,7 @@
         <v>37225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>48</v>
@@ -9136,7 +9175,7 @@
         <v>40062</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I29" s="8">
         <v>5</v>
@@ -9157,7 +9196,7 @@
         <v>112</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>185</v>
@@ -9171,7 +9210,7 @@
         <v>37226</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>51</v>
@@ -9186,7 +9225,7 @@
         <v>40058</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I30" s="8">
         <v>1</v>
@@ -9207,7 +9246,7 @@
         <v>0.2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>185</v>
@@ -9221,7 +9260,7 @@
         <v>37227</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>51</v>
@@ -9236,7 +9275,7 @@
         <v>40058</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I31" s="8">
         <v>2</v>
@@ -9257,7 +9296,7 @@
         <v>0.22</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>185</v>
@@ -9271,7 +9310,7 @@
         <v>37228</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>51</v>
@@ -9286,7 +9325,7 @@
         <v>40058</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I32" s="8">
         <v>3</v>
@@ -9307,7 +9346,7 @@
         <v>0.24</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>185</v>
@@ -9321,7 +9360,7 @@
         <v>37229</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>51</v>
@@ -9336,7 +9375,7 @@
         <v>40058</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I33" s="8">
         <v>4</v>
@@ -9357,7 +9396,7 @@
         <v>0.26</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>185</v>
@@ -9371,7 +9410,7 @@
         <v>37230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>51</v>
@@ -9386,7 +9425,7 @@
         <v>40058</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I34" s="8">
         <v>5</v>
@@ -9407,7 +9446,7 @@
         <v>0.28</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>185</v>
@@ -9421,7 +9460,7 @@
         <v>37231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>51</v>
@@ -9436,7 +9475,7 @@
         <v>40059</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I35" s="8">
         <v>1</v>
@@ -9457,7 +9496,7 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>185</v>
@@ -9471,7 +9510,7 @@
         <v>37232</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>51</v>
@@ -9486,7 +9525,7 @@
         <v>40059</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I36" s="8">
         <v>2</v>
@@ -9507,7 +9546,7 @@
         <v>0.44</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>185</v>
@@ -9521,7 +9560,7 @@
         <v>37233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>51</v>
@@ -9536,7 +9575,7 @@
         <v>40059</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I37" s="8">
         <v>3</v>
@@ -9557,7 +9596,7 @@
         <v>0.48</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>185</v>
@@ -9571,7 +9610,7 @@
         <v>37234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>51</v>
@@ -9586,7 +9625,7 @@
         <v>40059</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I38" s="8">
         <v>4</v>
@@ -9607,7 +9646,7 @@
         <v>0.52</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>185</v>
@@ -9621,7 +9660,7 @@
         <v>37235</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>51</v>
@@ -9636,7 +9675,7 @@
         <v>40059</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
@@ -9657,7 +9696,7 @@
         <v>0.56</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>185</v>
@@ -9671,7 +9710,7 @@
         <v>37236</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>51</v>
@@ -9686,7 +9725,7 @@
         <v>40060</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I40" s="8">
         <v>1</v>
@@ -9707,7 +9746,7 @@
         <v>0.8</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>185</v>
@@ -9721,7 +9760,7 @@
         <v>37237</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -9736,7 +9775,7 @@
         <v>40060</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I41" s="8">
         <v>2</v>
@@ -9757,7 +9796,7 @@
         <v>0.88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>185</v>
@@ -9771,7 +9810,7 @@
         <v>37238</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
@@ -9786,7 +9825,7 @@
         <v>40060</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I42" s="8">
         <v>3</v>
@@ -9807,7 +9846,7 @@
         <v>0.96</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>185</v>
@@ -9821,7 +9860,7 @@
         <v>37239</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>51</v>
@@ -9836,7 +9875,7 @@
         <v>40060</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I43" s="8">
         <v>4</v>
@@ -9857,7 +9896,7 @@
         <v>1.04</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>185</v>
@@ -9871,7 +9910,7 @@
         <v>37240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>51</v>
@@ -9886,7 +9925,7 @@
         <v>40060</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I44" s="8">
         <v>5</v>
@@ -9907,7 +9946,7 @@
         <v>1.12</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>185</v>
@@ -9921,7 +9960,7 @@
         <v>37241</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>51</v>
@@ -9936,7 +9975,7 @@
         <v>40061</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I45" s="8">
         <v>1</v>
@@ -9957,7 +9996,7 @@
         <v>1.6</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>185</v>
@@ -9971,7 +10010,7 @@
         <v>37242</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -9986,7 +10025,7 @@
         <v>40061</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I46" s="8">
         <v>2</v>
@@ -10007,7 +10046,7 @@
         <v>1.76</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>185</v>
@@ -10021,7 +10060,7 @@
         <v>37243</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>51</v>
@@ -10036,7 +10075,7 @@
         <v>40061</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I47" s="8">
         <v>3</v>
@@ -10057,7 +10096,7 @@
         <v>1.92</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>185</v>
@@ -10071,7 +10110,7 @@
         <v>37244</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>51</v>
@@ -10086,7 +10125,7 @@
         <v>40061</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I48" s="8">
         <v>4</v>
@@ -10107,7 +10146,7 @@
         <v>2.08</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>185</v>
@@ -10121,7 +10160,7 @@
         <v>37245</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>51</v>
@@ -10136,7 +10175,7 @@
         <v>40061</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I49" s="8">
         <v>5</v>
@@ -10157,7 +10196,7 @@
         <v>2.24</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>185</v>
@@ -10171,7 +10210,7 @@
         <v>37246</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
@@ -10186,7 +10225,7 @@
         <v>40062</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I50" s="8">
         <v>1</v>
@@ -10207,7 +10246,7 @@
         <v>3.2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>185</v>
@@ -10221,7 +10260,7 @@
         <v>37247</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>51</v>
@@ -10236,7 +10275,7 @@
         <v>40062</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I51" s="8">
         <v>2</v>
@@ -10257,7 +10296,7 @@
         <v>3.52</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>185</v>
@@ -10271,7 +10310,7 @@
         <v>37248</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>51</v>
@@ -10286,7 +10325,7 @@
         <v>40062</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I52" s="8">
         <v>3</v>
@@ -10307,7 +10346,7 @@
         <v>3.84</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>185</v>
@@ -10321,7 +10360,7 @@
         <v>37249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -10336,7 +10375,7 @@
         <v>40062</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I53" s="8">
         <v>4</v>
@@ -10357,7 +10396,7 @@
         <v>4.16</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>185</v>
@@ -10371,7 +10410,7 @@
         <v>37250</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>51</v>
@@ -10386,7 +10425,7 @@
         <v>40062</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I54" s="8">
         <v>5</v>
@@ -10407,7 +10446,7 @@
         <v>4.48</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>185</v>
@@ -10421,7 +10460,7 @@
         <v>37251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>53</v>
@@ -10436,7 +10475,7 @@
         <v>40058</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I55" s="8">
         <v>1</v>
@@ -10457,7 +10496,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>185</v>
@@ -10471,7 +10510,7 @@
         <v>37252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -10486,7 +10525,7 @@
         <v>40058</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I56" s="8">
         <v>2</v>
@@ -10507,7 +10546,7 @@
         <v>3.3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>185</v>
@@ -10521,7 +10560,7 @@
         <v>37253</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>53</v>
@@ -10536,7 +10575,7 @@
         <v>40058</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I57" s="8">
         <v>3</v>
@@ -10557,7 +10596,7 @@
         <v>3.6</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>185</v>
@@ -10571,7 +10610,7 @@
         <v>37254</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>53</v>
@@ -10586,7 +10625,7 @@
         <v>40058</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I58" s="8">
         <v>4</v>
@@ -10607,7 +10646,7 @@
         <v>3.9</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>185</v>
@@ -10621,7 +10660,7 @@
         <v>37255</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>53</v>
@@ -10636,7 +10675,7 @@
         <v>40058</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I59" s="8">
         <v>5</v>
@@ -10657,7 +10696,7 @@
         <v>4.2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>185</v>
@@ -10671,7 +10710,7 @@
         <v>37256</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>53</v>
@@ -10686,7 +10725,7 @@
         <v>40059</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I60" s="8">
         <v>1</v>
@@ -10707,7 +10746,7 @@
         <v>6</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>185</v>
@@ -10721,7 +10760,7 @@
         <v>37257</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>53</v>
@@ -10736,7 +10775,7 @@
         <v>40059</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I61" s="8">
         <v>2</v>
@@ -10757,7 +10796,7 @@
         <v>6.6</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>185</v>
@@ -10771,7 +10810,7 @@
         <v>37258</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>53</v>
@@ -10786,7 +10825,7 @@
         <v>40059</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I62" s="8">
         <v>3</v>
@@ -10807,7 +10846,7 @@
         <v>7.2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>185</v>
@@ -10821,7 +10860,7 @@
         <v>37259</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>53</v>
@@ -10836,7 +10875,7 @@
         <v>40059</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I63" s="8">
         <v>4</v>
@@ -10857,7 +10896,7 @@
         <v>7.8</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>185</v>
@@ -10871,7 +10910,7 @@
         <v>37260</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>53</v>
@@ -10886,7 +10925,7 @@
         <v>40059</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I64" s="8">
         <v>5</v>
@@ -10907,7 +10946,7 @@
         <v>8.4</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>185</v>
@@ -10921,7 +10960,7 @@
         <v>37261</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>53</v>
@@ -10936,7 +10975,7 @@
         <v>40060</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I65" s="8">
         <v>1</v>
@@ -10957,7 +10996,7 @@
         <v>12</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>185</v>
@@ -10971,7 +11010,7 @@
         <v>37262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>53</v>
@@ -10986,7 +11025,7 @@
         <v>40060</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I66" s="8">
         <v>2</v>
@@ -11007,7 +11046,7 @@
         <v>13.2</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>185</v>
@@ -11021,7 +11060,7 @@
         <v>37263</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>53</v>
@@ -11036,7 +11075,7 @@
         <v>40060</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I67" s="8">
         <v>3</v>
@@ -11057,7 +11096,7 @@
         <v>14.4</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>185</v>
@@ -11071,7 +11110,7 @@
         <v>37264</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>53</v>
@@ -11086,7 +11125,7 @@
         <v>40060</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I68" s="8">
         <v>4</v>
@@ -11107,7 +11146,7 @@
         <v>15.6</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>185</v>
@@ -11121,7 +11160,7 @@
         <v>37265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>53</v>
@@ -11136,7 +11175,7 @@
         <v>40060</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I69" s="8">
         <v>5</v>
@@ -11157,7 +11196,7 @@
         <v>16.8</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>185</v>
@@ -11171,7 +11210,7 @@
         <v>37266</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>53</v>
@@ -11186,7 +11225,7 @@
         <v>40061</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I70" s="8">
         <v>1</v>
@@ -11207,7 +11246,7 @@
         <v>24</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>185</v>
@@ -11221,7 +11260,7 @@
         <v>37267</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>53</v>
@@ -11236,7 +11275,7 @@
         <v>40061</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I71" s="8">
         <v>2</v>
@@ -11257,7 +11296,7 @@
         <v>26.4</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>185</v>
@@ -11271,7 +11310,7 @@
         <v>37268</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>53</v>
@@ -11286,7 +11325,7 @@
         <v>40061</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I72" s="8">
         <v>3</v>
@@ -11307,7 +11346,7 @@
         <v>28.8</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>185</v>
@@ -11321,7 +11360,7 @@
         <v>37269</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>53</v>
@@ -11336,7 +11375,7 @@
         <v>40061</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I73" s="8">
         <v>4</v>
@@ -11357,7 +11396,7 @@
         <v>31.2</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>185</v>
@@ -11371,7 +11410,7 @@
         <v>37270</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1288</v>
+        <v>1301</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>53</v>
@@ -11386,7 +11425,7 @@
         <v>40061</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I74" s="8">
         <v>5</v>
@@ -11407,7 +11446,7 @@
         <v>33.6</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>185</v>
@@ -11421,7 +11460,7 @@
         <v>37271</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>53</v>
@@ -11436,7 +11475,7 @@
         <v>40062</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I75" s="8">
         <v>1</v>
@@ -11457,7 +11496,7 @@
         <v>48</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>185</v>
@@ -11471,7 +11510,7 @@
         <v>37272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>53</v>
@@ -11486,7 +11525,7 @@
         <v>40062</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I76" s="8">
         <v>2</v>
@@ -11507,7 +11546,7 @@
         <v>52.8</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>185</v>
@@ -11521,7 +11560,7 @@
         <v>37273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>53</v>
@@ -11536,7 +11575,7 @@
         <v>40062</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I77" s="8">
         <v>3</v>
@@ -11557,7 +11596,7 @@
         <v>57.6</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>185</v>
@@ -11571,7 +11610,7 @@
         <v>37274</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>53</v>
@@ -11586,7 +11625,7 @@
         <v>40062</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I78" s="8">
         <v>4</v>
@@ -11607,7 +11646,7 @@
         <v>62.4</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>185</v>
@@ -11621,7 +11660,7 @@
         <v>37275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>53</v>
@@ -11636,7 +11675,7 @@
         <v>40062</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I79" s="8">
         <v>5</v>
@@ -11657,7 +11696,7 @@
         <v>67.2</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>185</v>
@@ -11671,7 +11710,7 @@
         <v>37276</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>48</v>
@@ -11686,7 +11725,7 @@
         <v>40136</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I80" s="8">
         <v>1</v>
@@ -11707,7 +11746,7 @@
         <v>160</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P80" s="1"/>
     </row>
@@ -11719,7 +11758,7 @@
         <v>37277</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>48</v>
@@ -11734,7 +11773,7 @@
         <v>40136</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I81" s="8">
         <v>2</v>
@@ -11755,7 +11794,7 @@
         <v>176</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P81" s="1"/>
     </row>
@@ -11767,7 +11806,7 @@
         <v>37278</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>48</v>
@@ -11782,7 +11821,7 @@
         <v>40136</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I82" s="8">
         <v>3</v>
@@ -11803,7 +11842,7 @@
         <v>192</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P82" s="1"/>
     </row>
@@ -11815,7 +11854,7 @@
         <v>37279</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1298</v>
+        <v>1311</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>48</v>
@@ -11830,7 +11869,7 @@
         <v>40136</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I83" s="8">
         <v>4</v>
@@ -11851,7 +11890,7 @@
         <v>208</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P83" s="1"/>
     </row>
@@ -11863,7 +11902,7 @@
         <v>37280</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1299</v>
+        <v>1312</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>48</v>
@@ -11878,7 +11917,7 @@
         <v>40136</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I84" s="8">
         <v>5</v>
@@ -11899,7 +11938,7 @@
         <v>224</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P84" s="1"/>
     </row>
@@ -11911,7 +11950,7 @@
         <v>37281</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1300</v>
+        <v>1313</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>51</v>
@@ -11926,7 +11965,7 @@
         <v>40136</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I85" s="8">
         <v>1</v>
@@ -11947,7 +11986,7 @@
         <v>6.4</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P85" s="1"/>
     </row>
@@ -11959,7 +11998,7 @@
         <v>37282</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>51</v>
@@ -11974,7 +12013,7 @@
         <v>40136</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I86" s="8">
         <v>2</v>
@@ -11995,7 +12034,7 @@
         <v>7.04</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P86" s="1"/>
     </row>
@@ -12007,7 +12046,7 @@
         <v>37283</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1302</v>
+        <v>1315</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>51</v>
@@ -12022,7 +12061,7 @@
         <v>40136</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I87" s="8">
         <v>3</v>
@@ -12043,7 +12082,7 @@
         <v>7.68</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P87" s="1"/>
     </row>
@@ -12055,7 +12094,7 @@
         <v>37284</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1303</v>
+        <v>1316</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>51</v>
@@ -12070,7 +12109,7 @@
         <v>40136</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I88" s="8">
         <v>4</v>
@@ -12091,7 +12130,7 @@
         <v>8.32</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P88" s="1"/>
     </row>
@@ -12103,7 +12142,7 @@
         <v>37285</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1304</v>
+        <v>1317</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>51</v>
@@ -12118,7 +12157,7 @@
         <v>40136</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I89" s="8">
         <v>5</v>
@@ -12139,7 +12178,7 @@
         <v>8.96</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P89" s="1"/>
     </row>
@@ -12151,7 +12190,7 @@
         <v>37286</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>53</v>
@@ -12166,7 +12205,7 @@
         <v>40136</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I90" s="8">
         <v>1</v>
@@ -12187,7 +12226,7 @@
         <v>96</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P90" s="1"/>
     </row>
@@ -12199,7 +12238,7 @@
         <v>37287</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>53</v>
@@ -12214,7 +12253,7 @@
         <v>40136</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I91" s="8">
         <v>2</v>
@@ -12235,7 +12274,7 @@
         <v>105.6</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P91" s="1"/>
     </row>
@@ -12247,7 +12286,7 @@
         <v>37288</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>53</v>
@@ -12262,7 +12301,7 @@
         <v>40136</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I92" s="8">
         <v>3</v>
@@ -12283,7 +12322,7 @@
         <v>115.2</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P92" s="1"/>
     </row>
@@ -12295,7 +12334,7 @@
         <v>37289</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>53</v>
@@ -12310,7 +12349,7 @@
         <v>40136</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I93" s="8">
         <v>4</v>
@@ -12331,7 +12370,7 @@
         <v>124.8</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P93" s="1"/>
     </row>
@@ -12343,7 +12382,7 @@
         <v>37290</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>53</v>
@@ -12358,7 +12397,7 @@
         <v>40136</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I94" s="8">
         <v>5</v>
@@ -12379,7 +12418,7 @@
         <v>134.4</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P94" s="1"/>
     </row>
@@ -12391,7 +12430,7 @@
         <v>37291</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>104</v>
@@ -12406,7 +12445,7 @@
         <v>40058</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I95" s="8">
         <v>1</v>
@@ -12427,7 +12466,7 @@
         <v>10</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P95" s="1"/>
     </row>
@@ -12439,7 +12478,7 @@
         <v>37292</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>1311</v>
+        <v>1324</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>104</v>
@@ -12454,7 +12493,7 @@
         <v>40058</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I96" s="8">
         <v>2</v>
@@ -12475,7 +12514,7 @@
         <v>11</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P96" s="1"/>
     </row>
@@ -12487,7 +12526,7 @@
         <v>37293</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>104</v>
@@ -12502,7 +12541,7 @@
         <v>40058</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I97" s="8">
         <v>3</v>
@@ -12523,7 +12562,7 @@
         <v>12</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P97" s="1"/>
     </row>
@@ -12535,7 +12574,7 @@
         <v>37294</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>104</v>
@@ -12550,7 +12589,7 @@
         <v>40058</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I98" s="8">
         <v>4</v>
@@ -12571,7 +12610,7 @@
         <v>13</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P98" s="1"/>
     </row>
@@ -12583,7 +12622,7 @@
         <v>37295</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>104</v>
@@ -12598,7 +12637,7 @@
         <v>40058</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I99" s="8">
         <v>5</v>
@@ -12619,7 +12658,7 @@
         <v>14</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P99" s="1"/>
     </row>
@@ -12631,7 +12670,7 @@
         <v>37296</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>1315</v>
+        <v>1328</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>104</v>
@@ -12646,7 +12685,7 @@
         <v>40059</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I100" s="8">
         <v>1</v>
@@ -12667,7 +12706,7 @@
         <v>20</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P100" s="1"/>
     </row>
@@ -12679,7 +12718,7 @@
         <v>37297</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>104</v>
@@ -12694,7 +12733,7 @@
         <v>40059</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I101" s="8">
         <v>2</v>
@@ -12715,7 +12754,7 @@
         <v>22</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P101" s="1"/>
     </row>
@@ -12727,7 +12766,7 @@
         <v>37298</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>1317</v>
+        <v>1330</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>104</v>
@@ -12742,7 +12781,7 @@
         <v>40059</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I102" s="8">
         <v>3</v>
@@ -12763,7 +12802,7 @@
         <v>24</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P102" s="1"/>
     </row>
@@ -12775,7 +12814,7 @@
         <v>37299</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>1318</v>
+        <v>1331</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>104</v>
@@ -12790,7 +12829,7 @@
         <v>40059</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I103" s="8">
         <v>4</v>
@@ -12811,7 +12850,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P103" s="1"/>
     </row>
@@ -12823,7 +12862,7 @@
         <v>37300</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>104</v>
@@ -12838,7 +12877,7 @@
         <v>40059</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I104" s="8">
         <v>5</v>
@@ -12859,7 +12898,7 @@
         <v>28</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P104" s="1"/>
     </row>
@@ -12871,7 +12910,7 @@
         <v>37301</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>104</v>
@@ -12886,7 +12925,7 @@
         <v>40060</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I105" s="8">
         <v>1</v>
@@ -12907,7 +12946,7 @@
         <v>40</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P105" s="1"/>
     </row>
@@ -12919,7 +12958,7 @@
         <v>37302</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>104</v>
@@ -12934,7 +12973,7 @@
         <v>40060</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I106" s="8">
         <v>2</v>
@@ -12955,7 +12994,7 @@
         <v>44</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P106" s="1"/>
     </row>
@@ -12967,7 +13006,7 @@
         <v>37303</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>104</v>
@@ -12982,7 +13021,7 @@
         <v>40060</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I107" s="8">
         <v>3</v>
@@ -13003,7 +13042,7 @@
         <v>48</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P107" s="1"/>
     </row>
@@ -13015,7 +13054,7 @@
         <v>37304</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>104</v>
@@ -13030,7 +13069,7 @@
         <v>40060</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I108" s="8">
         <v>4</v>
@@ -13051,7 +13090,7 @@
         <v>52</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P108" s="1"/>
     </row>
@@ -13063,7 +13102,7 @@
         <v>37305</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>104</v>
@@ -13078,7 +13117,7 @@
         <v>40060</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I109" s="8">
         <v>5</v>
@@ -13099,7 +13138,7 @@
         <v>56</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P109" s="1"/>
     </row>
@@ -13111,7 +13150,7 @@
         <v>37306</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>104</v>
@@ -13126,7 +13165,7 @@
         <v>40061</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I110" s="8">
         <v>1</v>
@@ -13147,7 +13186,7 @@
         <v>80</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P110" s="1"/>
     </row>
@@ -13159,7 +13198,7 @@
         <v>37307</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>104</v>
@@ -13174,7 +13213,7 @@
         <v>40061</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I111" s="8">
         <v>2</v>
@@ -13195,7 +13234,7 @@
         <v>88</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P111" s="1"/>
     </row>
@@ -13207,7 +13246,7 @@
         <v>37308</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>104</v>
@@ -13222,7 +13261,7 @@
         <v>40061</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I112" s="8">
         <v>3</v>
@@ -13243,7 +13282,7 @@
         <v>96</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P112" s="1"/>
     </row>
@@ -13255,7 +13294,7 @@
         <v>37309</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>104</v>
@@ -13270,7 +13309,7 @@
         <v>40061</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I113" s="8">
         <v>4</v>
@@ -13291,7 +13330,7 @@
         <v>104</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P113" s="1"/>
     </row>
@@ -13303,7 +13342,7 @@
         <v>37310</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>104</v>
@@ -13318,7 +13357,7 @@
         <v>40061</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I114" s="8">
         <v>5</v>
@@ -13339,7 +13378,7 @@
         <v>112</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P114" s="1"/>
     </row>
@@ -13351,7 +13390,7 @@
         <v>37311</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1330</v>
+        <v>1343</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>104</v>
@@ -13366,7 +13405,7 @@
         <v>40062</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I115" s="8">
         <v>1</v>
@@ -13387,7 +13426,7 @@
         <v>160</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P115" s="1"/>
     </row>
@@ -13399,7 +13438,7 @@
         <v>37312</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>1331</v>
+        <v>1344</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>104</v>
@@ -13414,7 +13453,7 @@
         <v>40062</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I116" s="8">
         <v>2</v>
@@ -13435,7 +13474,7 @@
         <v>176</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P116" s="1"/>
     </row>
@@ -13447,7 +13486,7 @@
         <v>37313</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1332</v>
+        <v>1345</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>104</v>
@@ -13462,7 +13501,7 @@
         <v>40062</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I117" s="8">
         <v>3</v>
@@ -13483,7 +13522,7 @@
         <v>192</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P117" s="1"/>
     </row>
@@ -13495,7 +13534,7 @@
         <v>37314</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>104</v>
@@ -13510,7 +13549,7 @@
         <v>40062</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I118" s="8">
         <v>4</v>
@@ -13531,7 +13570,7 @@
         <v>208</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P118" s="1"/>
     </row>
@@ -13543,7 +13582,7 @@
         <v>37315</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>104</v>
@@ -13558,7 +13597,7 @@
         <v>40062</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I119" s="8">
         <v>5</v>
@@ -13579,7 +13618,7 @@
         <v>224</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P119" s="1"/>
     </row>
@@ -13591,7 +13630,7 @@
         <v>37316</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>104</v>
@@ -13606,7 +13645,7 @@
         <v>40136</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I120" s="8">
         <v>1</v>
@@ -13627,7 +13666,7 @@
         <v>320</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P120" s="1"/>
     </row>
@@ -13639,7 +13678,7 @@
         <v>37317</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>104</v>
@@ -13654,7 +13693,7 @@
         <v>40136</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I121" s="8">
         <v>2</v>
@@ -13675,7 +13714,7 @@
         <v>352</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P121" s="1"/>
     </row>
@@ -13687,7 +13726,7 @@
         <v>37318</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>104</v>
@@ -13702,7 +13741,7 @@
         <v>40136</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I122" s="8">
         <v>3</v>
@@ -13723,7 +13762,7 @@
         <v>384</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P122" s="1"/>
     </row>
@@ -13735,7 +13774,7 @@
         <v>37319</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1338</v>
+        <v>1351</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>104</v>
@@ -13750,7 +13789,7 @@
         <v>40136</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I123" s="8">
         <v>4</v>
@@ -13771,7 +13810,7 @@
         <v>416</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P123" s="1"/>
     </row>
@@ -13783,7 +13822,7 @@
         <v>37320</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>104</v>
@@ -13798,7 +13837,7 @@
         <v>40136</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I124" s="8">
         <v>5</v>
@@ -13819,7 +13858,7 @@
         <v>448</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P124" s="1"/>
     </row>
@@ -13831,7 +13870,7 @@
         <v>37321</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1340</v>
+        <v>1353</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>106</v>
@@ -13846,7 +13885,7 @@
         <v>40058</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I125" s="8">
         <v>1</v>
@@ -13867,7 +13906,7 @@
         <v>0.1</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P125" s="1"/>
     </row>
@@ -13879,7 +13918,7 @@
         <v>37322</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1341</v>
+        <v>1354</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>106</v>
@@ -13894,7 +13933,7 @@
         <v>40058</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I126" s="8">
         <v>2</v>
@@ -13915,7 +13954,7 @@
         <v>0.11</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P126" s="1"/>
     </row>
@@ -13927,7 +13966,7 @@
         <v>37323</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>1342</v>
+        <v>1355</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>106</v>
@@ -13942,7 +13981,7 @@
         <v>40058</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I127" s="8">
         <v>3</v>
@@ -13963,7 +14002,7 @@
         <v>0.12</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P127" s="1"/>
     </row>
@@ -13975,7 +14014,7 @@
         <v>37324</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>1343</v>
+        <v>1356</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>106</v>
@@ -13990,7 +14029,7 @@
         <v>40058</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I128" s="8">
         <v>4</v>
@@ -14011,7 +14050,7 @@
         <v>0.13</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P128" s="1"/>
     </row>
@@ -14023,7 +14062,7 @@
         <v>37325</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>106</v>
@@ -14038,7 +14077,7 @@
         <v>40058</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I129" s="8">
         <v>5</v>
@@ -14059,7 +14098,7 @@
         <v>0.14</v>
       </c>
       <c r="O129" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="P129" s="1"/>
     </row>
@@ -14071,7 +14110,7 @@
         <v>37326</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>1345</v>
+        <v>1358</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>106</v>
@@ -14086,7 +14125,7 @@
         <v>40059</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I130" s="8">
         <v>1</v>
@@ -14107,7 +14146,7 @@
         <v>0.2</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P130" s="1"/>
     </row>
@@ -14119,7 +14158,7 @@
         <v>37327</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>106</v>
@@ -14134,7 +14173,7 @@
         <v>40059</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I131" s="8">
         <v>2</v>
@@ -14155,7 +14194,7 @@
         <v>0.22</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P131" s="1"/>
     </row>
@@ -14167,7 +14206,7 @@
         <v>37328</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>1347</v>
+        <v>1360</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>106</v>
@@ -14182,7 +14221,7 @@
         <v>40059</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I132" s="8">
         <v>3</v>
@@ -14203,7 +14242,7 @@
         <v>0.24</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P132" s="1"/>
     </row>
@@ -14215,7 +14254,7 @@
         <v>37329</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1348</v>
+        <v>1361</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>106</v>
@@ -14230,7 +14269,7 @@
         <v>40059</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I133" s="8">
         <v>4</v>
@@ -14251,7 +14290,7 @@
         <v>0.26</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P133" s="1"/>
     </row>
@@ -14263,7 +14302,7 @@
         <v>37330</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>106</v>
@@ -14278,7 +14317,7 @@
         <v>40059</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I134" s="8">
         <v>5</v>
@@ -14299,7 +14338,7 @@
         <v>0.28</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="P134" s="1"/>
     </row>
@@ -14311,7 +14350,7 @@
         <v>37331</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>1350</v>
+        <v>1363</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>106</v>
@@ -14326,7 +14365,7 @@
         <v>40060</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I135" s="8">
         <v>1</v>
@@ -14347,7 +14386,7 @@
         <v>0.4</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P135" s="1"/>
     </row>
@@ -14359,7 +14398,7 @@
         <v>37332</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>106</v>
@@ -14374,7 +14413,7 @@
         <v>40060</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I136" s="8">
         <v>2</v>
@@ -14395,7 +14434,7 @@
         <v>0.44</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P136" s="1"/>
     </row>
@@ -14407,7 +14446,7 @@
         <v>37333</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1352</v>
+        <v>1365</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>106</v>
@@ -14422,7 +14461,7 @@
         <v>40060</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I137" s="8">
         <v>3</v>
@@ -14443,7 +14482,7 @@
         <v>0.48</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P137" s="1"/>
     </row>
@@ -14455,7 +14494,7 @@
         <v>37334</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1353</v>
+        <v>1366</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>106</v>
@@ -14470,7 +14509,7 @@
         <v>40060</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I138" s="8">
         <v>4</v>
@@ -14491,7 +14530,7 @@
         <v>0.52</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P138" s="1"/>
     </row>
@@ -14503,7 +14542,7 @@
         <v>37335</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>106</v>
@@ -14518,7 +14557,7 @@
         <v>40060</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I139" s="8">
         <v>5</v>
@@ -14539,7 +14578,7 @@
         <v>0.56</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="P139" s="1"/>
     </row>
@@ -14551,7 +14590,7 @@
         <v>37336</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1355</v>
+        <v>1368</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>106</v>
@@ -14566,7 +14605,7 @@
         <v>40061</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I140" s="8">
         <v>1</v>
@@ -14587,7 +14626,7 @@
         <v>0.8</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P140" s="1"/>
     </row>
@@ -14599,7 +14638,7 @@
         <v>37337</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>106</v>
@@ -14614,7 +14653,7 @@
         <v>40061</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I141" s="8">
         <v>2</v>
@@ -14635,7 +14674,7 @@
         <v>0.88</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P141" s="1"/>
     </row>
@@ -14647,7 +14686,7 @@
         <v>37338</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1357</v>
+        <v>1370</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>106</v>
@@ -14662,7 +14701,7 @@
         <v>40061</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I142" s="8">
         <v>3</v>
@@ -14683,7 +14722,7 @@
         <v>0.96</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P142" s="1"/>
     </row>
@@ -14695,7 +14734,7 @@
         <v>37339</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>106</v>
@@ -14710,7 +14749,7 @@
         <v>40061</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I143" s="8">
         <v>4</v>
@@ -14731,7 +14770,7 @@
         <v>1.04</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P143" s="1"/>
     </row>
@@ -14743,7 +14782,7 @@
         <v>37340</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>1359</v>
+        <v>1372</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>106</v>
@@ -14758,7 +14797,7 @@
         <v>40061</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I144" s="8">
         <v>5</v>
@@ -14779,7 +14818,7 @@
         <v>1.12</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="P144" s="1"/>
     </row>
@@ -14791,7 +14830,7 @@
         <v>37341</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>106</v>
@@ -14806,7 +14845,7 @@
         <v>40062</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I145" s="8">
         <v>1</v>
@@ -14827,7 +14866,7 @@
         <v>1.6</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P145" s="1"/>
     </row>
@@ -14839,7 +14878,7 @@
         <v>37342</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>106</v>
@@ -14854,7 +14893,7 @@
         <v>40062</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I146" s="8">
         <v>2</v>
@@ -14875,7 +14914,7 @@
         <v>1.76</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P146" s="1"/>
     </row>
@@ -14887,7 +14926,7 @@
         <v>37343</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>106</v>
@@ -14902,7 +14941,7 @@
         <v>40062</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I147" s="8">
         <v>3</v>
@@ -14923,7 +14962,7 @@
         <v>1.92</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P147" s="1"/>
     </row>
@@ -14935,7 +14974,7 @@
         <v>37344</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>106</v>
@@ -14950,7 +14989,7 @@
         <v>40062</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I148" s="8">
         <v>4</v>
@@ -14971,7 +15010,7 @@
         <v>2.08</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P148" s="1"/>
     </row>
@@ -14983,7 +15022,7 @@
         <v>37345</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>106</v>
@@ -14998,7 +15037,7 @@
         <v>40062</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I149" s="8">
         <v>5</v>
@@ -15019,7 +15058,7 @@
         <v>2.24</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="P149" s="1"/>
     </row>
@@ -15031,7 +15070,7 @@
         <v>37346</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>106</v>
@@ -15046,7 +15085,7 @@
         <v>40136</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I150" s="8">
         <v>1</v>
@@ -15067,7 +15106,7 @@
         <v>3.2</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P150" s="1"/>
     </row>
@@ -15079,7 +15118,7 @@
         <v>37347</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>106</v>
@@ -15094,7 +15133,7 @@
         <v>40136</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I151" s="8">
         <v>2</v>
@@ -15115,7 +15154,7 @@
         <v>3.52</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P151" s="1"/>
     </row>
@@ -15127,7 +15166,7 @@
         <v>37348</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>106</v>
@@ -15142,7 +15181,7 @@
         <v>40136</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I152" s="8">
         <v>3</v>
@@ -15163,7 +15202,7 @@
         <v>3.84</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P152" s="1"/>
     </row>
@@ -15175,7 +15214,7 @@
         <v>37349</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>106</v>
@@ -15190,7 +15229,7 @@
         <v>40136</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I153" s="8">
         <v>4</v>
@@ -15211,7 +15250,7 @@
         <v>4.16</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P153" s="1"/>
     </row>
@@ -15223,7 +15262,7 @@
         <v>37350</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>106</v>
@@ -15238,7 +15277,7 @@
         <v>40136</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I154" s="8">
         <v>5</v>
@@ -15259,7 +15298,7 @@
         <v>4.48</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="P154" s="1"/>
     </row>
@@ -15469,7 +15508,7 @@
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>116</v>
@@ -15482,13 +15521,13 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
       <c r="L1" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -15505,28 +15544,28 @@
         <v>121</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>124</v>
       </c>
       <c r="L2" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -15581,22 +15620,22 @@
         <v>131</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>134</v>
@@ -15625,7 +15664,7 @@
         <v>40058</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -15663,7 +15702,7 @@
         <v>40058</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>70</v>
@@ -15701,7 +15740,7 @@
         <v>40058</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
@@ -15739,7 +15778,7 @@
         <v>40059</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>70</v>
@@ -15777,7 +15816,7 @@
         <v>40059</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>72</v>
@@ -15815,7 +15854,7 @@
         <v>40059</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>75</v>
@@ -15853,7 +15892,7 @@
         <v>40060</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>73</v>
@@ -15891,7 +15930,7 @@
         <v>40060</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>77</v>
@@ -15929,7 +15968,7 @@
         <v>40060</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>68</v>
@@ -15967,7 +16006,7 @@
         <v>40058</v>
       </c>
       <c r="G14" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="H14" t="s">
         <v>110</v>
@@ -16005,7 +16044,7 @@
         <v>40059</v>
       </c>
       <c r="G15" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="H15" t="s">
         <v>112</v>
@@ -16043,7 +16082,7 @@
         <v>40060</v>
       </c>
       <c r="G16" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="H16" t="s">
         <v>72</v>
@@ -16081,7 +16120,7 @@
         <v>40060</v>
       </c>
       <c r="G17" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="H17" t="s">
         <v>114</v>
@@ -16119,7 +16158,7 @@
         <v>40062</v>
       </c>
       <c r="G18" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="H18" t="s">
         <v>114</v>
@@ -16157,7 +16196,7 @@
         <v>40062</v>
       </c>
       <c r="G19" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="H19" t="s">
         <v>77</v>
@@ -16225,46 +16264,46 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1377</v>
+        <v>1391</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1378</v>
+        <v>1392</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>1379</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -16325,46 +16364,46 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>1380</v>
+        <v>1394</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -16396,7 +16435,7 @@
         <v>0.2</v>
       </c>
       <c r="J5" s="8">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="K5" s="8">
         <v>60</v>
@@ -16446,7 +16485,7 @@
         <v>0.7</v>
       </c>
       <c r="J6" s="8">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="K6" s="8">
         <v>50</v>
@@ -16496,7 +16535,7 @@
         <v>1.5</v>
       </c>
       <c r="J7" s="8">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="8">
         <v>42</v>
@@ -16546,7 +16585,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="8">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="K8" s="8">
         <v>35</v>
@@ -16596,7 +16635,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="8">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="K9" s="8">
         <v>28</v>
@@ -16631,7 +16670,7 @@
         <v>1300</v>
       </c>
       <c r="E10" s="8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="8">
         <v>30</v>
@@ -16640,25 +16679,25 @@
         <v>24</v>
       </c>
       <c r="H10" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" s="8">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="8">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="K10" s="8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="8">
         <v>22</v>
       </c>
       <c r="M10" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O10" s="8">
         <v>16</v>
@@ -16681,37 +16720,37 @@
         <v>2300</v>
       </c>
       <c r="E11" s="8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="8">
+        <v>25</v>
+      </c>
+      <c r="H11" s="8">
+        <v>18</v>
+      </c>
+      <c r="I11" s="8">
+        <v>9</v>
+      </c>
+      <c r="J11" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="K11" s="8">
+        <v>19</v>
+      </c>
+      <c r="L11" s="8">
+        <v>20</v>
+      </c>
+      <c r="M11" s="8">
+        <v>19</v>
+      </c>
+      <c r="N11" s="8">
         <v>24</v>
       </c>
-      <c r="H11" s="8">
-        <v>19</v>
-      </c>
-      <c r="I11" s="8">
-        <v>10</v>
-      </c>
-      <c r="J11" s="8">
-        <v>7</v>
-      </c>
-      <c r="K11" s="8">
-        <v>17</v>
-      </c>
-      <c r="L11" s="8">
-        <v>19</v>
-      </c>
-      <c r="M11" s="8">
+      <c r="O11" s="8">
         <v>21</v>
-      </c>
-      <c r="N11" s="8">
-        <v>21</v>
-      </c>
-      <c r="O11" s="8">
-        <v>22</v>
       </c>
       <c r="P11" s="8">
         <v>50</v>
@@ -16731,37 +16770,37 @@
         <v>4000</v>
       </c>
       <c r="E12" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F12" s="8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G12" s="8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H12" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J12" s="8">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="K12" s="8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L12" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M12" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12" s="8">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O12" s="8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P12" s="8">
         <v>50</v>
@@ -16798,10 +16837,10 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1381</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -16826,10 +16865,10 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -18410,7 +18449,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E652"/>
+  <dimension ref="A1:E658"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -29490,6 +29529,108 @@
         <v>1018</v>
       </c>
       <c r="E652" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A653">
+        <v>649</v>
+      </c>
+      <c r="B653">
+        <v>52210</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D653" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E653" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A654">
+        <v>650</v>
+      </c>
+      <c r="B654">
+        <v>52211</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D654" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A655">
+        <v>651</v>
+      </c>
+      <c r="B655">
+        <v>52212</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A656">
+        <v>652</v>
+      </c>
+      <c r="B656">
+        <v>52213</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A657">
+        <v>653</v>
+      </c>
+      <c r="B657">
+        <v>55036</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D657" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E657" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A658">
+        <v>654</v>
+      </c>
+      <c r="B658">
+        <v>55037</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E658" t="s">
         <v>977</v>
       </c>
     </row>
@@ -29530,22 +29671,22 @@
         <v>129</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -29582,22 +29723,22 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -29608,7 +29749,7 @@
         <v>39001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="D5" s="8">
         <v>8</v>
@@ -29634,7 +29775,7 @@
         <v>39002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="D6" s="8">
         <v>10</v>
@@ -29660,7 +29801,7 @@
         <v>39003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
@@ -29686,7 +29827,7 @@
         <v>39004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="D8" s="8">
         <v>30</v>
@@ -29712,7 +29853,7 @@
         <v>39005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="D9" s="8">
         <v>60</v>
@@ -29738,7 +29879,7 @@
         <v>39006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="D10" s="8">
         <v>120</v>
@@ -29764,7 +29905,7 @@
         <v>39007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="D11" s="8">
         <v>240</v>
@@ -29790,7 +29931,7 @@
         <v>39008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="D12" s="8">
         <v>480</v>
@@ -29834,7 +29975,7 @@
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>116</v>
@@ -29847,28 +29988,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>129</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>119</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>124</v>
@@ -29888,13 +30029,13 @@
         <v>125</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>125</v>
@@ -29911,22 +30052,22 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>134</v>
@@ -29958,7 +30099,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -29987,7 +30128,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -30074,7 +30215,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -30103,7 +30244,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
     </row>
   </sheetData>
@@ -30139,7 +30280,7 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
@@ -30161,13 +30302,13 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>382</v>
@@ -30176,25 +30317,25 @@
         <v>385</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>121</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -30249,40 +30390,40 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -43511,7 +43652,7 @@
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>116</v>
@@ -43519,7 +43660,7 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="H1" s="9" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
@@ -43535,22 +43676,22 @@
         <v>119</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>121</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>124</v>
@@ -43605,16 +43746,16 @@
         <v>131</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>134</v>
@@ -43643,13 +43784,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I5" s="8">
         <v>9999</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -43675,13 +43816,13 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I6" s="8">
         <v>9999</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -43707,13 +43848,13 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I7" s="8">
         <v>9999</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1051</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -43739,13 +43880,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I8" s="8">
         <v>9999</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1052</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -43771,13 +43912,13 @@
         <v>0.02</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I9" s="8">
         <v>9999</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1053</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -43812,13 +43953,13 @@
         <v>116</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -43831,7 +43972,7 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>279</v>
@@ -43840,19 +43981,19 @@
         <v>121</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>283</v>
@@ -43901,25 +44042,25 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>280</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>149</v>
@@ -52485,13 +52626,13 @@
         <v>417</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>124</v>
@@ -52528,16 +52669,16 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>284</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>134</v>
@@ -52793,22 +52934,22 @@
         <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="D2" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="E2" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="F2" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="G2" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="H2" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="I2" t="s">
         <v>124</v>
@@ -52851,22 +52992,22 @@
         <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="D4" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="E4" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="F4" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="G4" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="H4" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="I4" t="s">
         <v>134</v>
@@ -53052,12 +53193,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="F1" t="s">
         <v>116</v>
@@ -53071,19 +53212,19 @@
         <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="D2" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="E2" t="s">
         <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="G2" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -53117,19 +53258,19 @@
         <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="D4" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="E4" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="G4" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -53140,10 +53281,10 @@
         <v>33001</v>
       </c>
       <c r="C5" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D5" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E5" t="s">
         <v>91</v>
@@ -53163,10 +53304,10 @@
         <v>33002</v>
       </c>
       <c r="C6" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D6" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -53186,10 +53327,10 @@
         <v>33003</v>
       </c>
       <c r="C7" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D7" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -53209,10 +53350,10 @@
         <v>33004</v>
       </c>
       <c r="C8" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D8" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -53232,10 +53373,10 @@
         <v>33005</v>
       </c>
       <c r="C9" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D9" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -53255,10 +53396,10 @@
         <v>33006</v>
       </c>
       <c r="C10" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D10" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -53278,10 +53419,10 @@
         <v>33007</v>
       </c>
       <c r="C11" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="D11" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -53301,10 +53442,10 @@
         <v>33008</v>
       </c>
       <c r="C12" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="D12" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -53324,10 +53465,10 @@
         <v>33009</v>
       </c>
       <c r="C13" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="D13" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -53347,10 +53488,10 @@
         <v>33010</v>
       </c>
       <c r="C14" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="D14" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E14" t="s">
         <v>94</v>
@@ -53370,10 +53511,10 @@
         <v>33011</v>
       </c>
       <c r="C15" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="D15" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E15" t="s">
         <v>94</v>
@@ -53393,10 +53534,10 @@
         <v>33012</v>
       </c>
       <c r="C16" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D16" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E16" t="s">
         <v>94</v>
@@ -53416,10 +53557,10 @@
         <v>33013</v>
       </c>
       <c r="C17" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D17" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
@@ -53439,10 +53580,10 @@
         <v>33014</v>
       </c>
       <c r="C18" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D18" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>
@@ -53462,10 +53603,10 @@
         <v>33015</v>
       </c>
       <c r="C19" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D19" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -53485,10 +53626,10 @@
         <v>33016</v>
       </c>
       <c r="C20" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D20" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -53508,10 +53649,10 @@
         <v>33017</v>
       </c>
       <c r="C21" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="D21" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
@@ -53531,10 +53672,10 @@
         <v>33018</v>
       </c>
       <c r="C22" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D22" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E22" t="s">
         <v>91</v>
@@ -53554,10 +53695,10 @@
         <v>33019</v>
       </c>
       <c r="C23" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D23" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E23" t="s">
         <v>94</v>
@@ -53577,10 +53718,10 @@
         <v>33020</v>
       </c>
       <c r="C24" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D24" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E24" t="s">
         <v>96</v>
@@ -53600,10 +53741,10 @@
         <v>33021</v>
       </c>
       <c r="C25" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D25" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
@@ -53623,10 +53764,10 @@
         <v>33022</v>
       </c>
       <c r="C26" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D26" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E26" t="s">
         <v>91</v>
@@ -53646,10 +53787,10 @@
         <v>33023</v>
       </c>
       <c r="C27" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D27" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E27" t="s">
         <v>91</v>
@@ -53669,10 +53810,10 @@
         <v>33024</v>
       </c>
       <c r="C28" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D28" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E28" t="s">
         <v>96</v>
@@ -53692,10 +53833,10 @@
         <v>33025</v>
       </c>
       <c r="C29" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D29" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E29" t="s">
         <v>94</v>
@@ -53715,10 +53856,10 @@
         <v>33026</v>
       </c>
       <c r="C30" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D30" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E30" t="s">
         <v>91</v>
@@ -53738,10 +53879,10 @@
         <v>33027</v>
       </c>
       <c r="C31" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D31" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E31" t="s">
         <v>91</v>
@@ -53761,10 +53902,10 @@
         <v>33028</v>
       </c>
       <c r="C32" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D32" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E32" t="s">
         <v>94</v>
@@ -53784,10 +53925,10 @@
         <v>33029</v>
       </c>
       <c r="C33" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="D33" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="E33" t="s">
         <v>94</v>
@@ -53797,6 +53938,52 @@
       </c>
       <c r="G33">
         <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34">
+        <v>33030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E34" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34">
+        <v>55036</v>
+      </c>
+      <c r="G34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35">
+        <v>33031</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35">
+        <v>55037</v>
+      </c>
+      <c r="G35">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5704" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5737" uniqueCount="1414">
   <si>
     <t>enum 그룹</t>
   </si>
@@ -3130,6 +3130,63 @@
   </si>
   <si>
     <t>More precise gacha probability display</t>
+  </si>
+  <si>
+    <t>일괄</t>
+  </si>
+  <si>
+    <t>Bulk</t>
+  </si>
+  <si>
+    <t>BulkUiLabel</t>
+  </si>
+  <si>
+    <t>실행 전 확인</t>
+  </si>
+  <si>
+    <t>Confirm before executing</t>
+  </si>
+  <si>
+    <t>처리 완료</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>연쇄 합성</t>
+  </si>
+  <si>
+    <t>Chain fusion</t>
+  </si>
+  <si>
+    <t>결과물로 또 합성할 수 있으면 계속 이어갑니다</t>
+  </si>
+  <si>
+    <t>Keeps fusing the result as long as it can</t>
+  </si>
+  <si>
+    <t>지금 처리할 수 있는 게 없습니다</t>
+  </si>
+  <si>
+    <t>Nothing to process right now</t>
+  </si>
+  <si>
+    <t>조건에 도달해 여기서 멈췄습니다</t>
+  </si>
+  <si>
+    <t>reached its unlock condition, stopping here</t>
+  </si>
+  <si>
+    <t>무기 일괄 돌파·합성 추가</t>
+  </si>
+  <si>
+    <t>Bulk breakthrough/fusion added</t>
+  </si>
+  <si>
+    <t>존재력 트리 일괄 해금 추가</t>
+  </si>
+  <si>
+    <t>Bulk exist tree unlock added</t>
   </si>
   <si>
     <t>EnumDefine/CurrencyType</t>
@@ -4724,27 +4781,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="B1" t="s">
-        <v>1068</v>
+        <v>1087</v>
       </c>
       <c r="C1" t="s">
-        <v>1069</v>
+        <v>1088</v>
       </c>
       <c r="D1" t="s">
-        <v>1070</v>
+        <v>1089</v>
       </c>
       <c r="E1" t="s">
-        <v>1071</v>
+        <v>1090</v>
       </c>
       <c r="F1" t="s">
-        <v>1072</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B2" t="s">
         <v>117</v>
@@ -4764,7 +4821,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B3" t="s">
         <v>118</v>
@@ -4784,13 +4841,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B4" t="s">
-        <v>1074</v>
+        <v>1093</v>
       </c>
       <c r="C4" t="s">
-        <v>1075</v>
+        <v>1094</v>
       </c>
       <c r="D4" t="s">
         <v>125</v>
@@ -4804,13 +4861,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B5" t="s">
-        <v>1076</v>
+        <v>1095</v>
       </c>
       <c r="C5" t="s">
-        <v>1077</v>
+        <v>1096</v>
       </c>
       <c r="D5" t="s">
         <v>125</v>
@@ -4824,10 +4881,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B6" t="s">
-        <v>1078</v>
+        <v>1097</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -4839,18 +4896,18 @@
         <v>185</v>
       </c>
       <c r="F6" t="s">
-        <v>1079</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B7" t="s">
         <v>382</v>
       </c>
       <c r="C7" t="s">
-        <v>1080</v>
+        <v>1099</v>
       </c>
       <c r="D7" t="s">
         <v>125</v>
@@ -4864,13 +4921,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B8" t="s">
         <v>385</v>
       </c>
       <c r="C8" t="s">
-        <v>1081</v>
+        <v>1100</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -4884,13 +4941,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B9" t="s">
-        <v>1082</v>
+        <v>1101</v>
       </c>
       <c r="C9" t="s">
-        <v>1083</v>
+        <v>1102</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -4904,13 +4961,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B10" t="s">
-        <v>1084</v>
+        <v>1103</v>
       </c>
       <c r="C10" t="s">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4924,13 +4981,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B11" t="s">
-        <v>1086</v>
+        <v>1105</v>
       </c>
       <c r="C11" t="s">
-        <v>1087</v>
+        <v>1106</v>
       </c>
       <c r="D11" t="s">
         <v>125</v>
@@ -4944,13 +5001,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B12" t="s">
-        <v>1088</v>
+        <v>1107</v>
       </c>
       <c r="C12" t="s">
-        <v>1089</v>
+        <v>1108</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -4964,13 +5021,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B13" t="s">
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="C13" t="s">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4984,13 +5041,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B14" t="s">
         <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
@@ -5004,19 +5061,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B15" t="s">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="C15" t="s">
-        <v>1093</v>
+        <v>1112</v>
       </c>
       <c r="D15" t="s">
         <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>1094</v>
+        <v>1113</v>
       </c>
       <c r="F15" t="s">
         <v>185</v>
@@ -5024,7 +5081,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B16" t="s">
         <v>117</v>
@@ -5044,7 +5101,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B17" t="s">
         <v>118</v>
@@ -5064,13 +5121,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B18" t="s">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="C18" t="s">
-        <v>1097</v>
+        <v>1116</v>
       </c>
       <c r="D18" t="s">
         <v>125</v>
@@ -5084,7 +5141,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B19" t="s">
         <v>279</v>
@@ -5104,13 +5161,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B20" t="s">
         <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="D20" t="s">
         <v>125</v>
@@ -5124,13 +5181,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B21" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="C21" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="D21" t="s">
         <v>125</v>
@@ -5144,13 +5201,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B22" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="C22" t="s">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
@@ -5159,15 +5216,15 @@
         <v>185</v>
       </c>
       <c r="F22" t="s">
-        <v>1102</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B23" t="s">
-        <v>1052</v>
+        <v>1071</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -5179,18 +5236,18 @@
         <v>185</v>
       </c>
       <c r="F23" t="s">
-        <v>1050</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B24" t="s">
-        <v>1103</v>
+        <v>1122</v>
       </c>
       <c r="C24" t="s">
-        <v>1104</v>
+        <v>1123</v>
       </c>
       <c r="D24" t="s">
         <v>127</v>
@@ -5199,15 +5256,15 @@
         <v>185</v>
       </c>
       <c r="F24" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B25" t="s">
-        <v>1105</v>
+        <v>1124</v>
       </c>
       <c r="C25" t="s">
         <v>149</v>
@@ -5224,7 +5281,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="B26" t="s">
         <v>283</v>
@@ -5244,7 +5301,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B27" t="s">
         <v>117</v>
@@ -5264,7 +5321,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B28" t="s">
         <v>118</v>
@@ -5284,7 +5341,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B29" t="s">
         <v>119</v>
@@ -5304,7 +5361,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B30" t="s">
         <v>120</v>
@@ -5324,7 +5381,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B31" t="s">
         <v>121</v>
@@ -5344,7 +5401,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B32" t="s">
         <v>122</v>
@@ -5364,7 +5421,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B33" t="s">
         <v>123</v>
@@ -5384,7 +5441,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B34" t="s">
         <v>124</v>
@@ -5404,7 +5461,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
@@ -5424,7 +5481,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B36" t="s">
         <v>118</v>
@@ -5444,7 +5501,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -5464,7 +5521,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B38" t="s">
         <v>139</v>
@@ -5484,7 +5541,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B39" t="s">
         <v>140</v>
@@ -5504,7 +5561,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="B40" t="s">
         <v>124</v>
@@ -5524,7 +5581,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B41" t="s">
         <v>117</v>
@@ -5544,7 +5601,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B42" t="s">
         <v>118</v>
@@ -5564,19 +5621,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B43" t="s">
-        <v>1109</v>
+        <v>1128</v>
       </c>
       <c r="C43" t="s">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="D43" t="s">
         <v>126</v>
       </c>
       <c r="E43" t="s">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="F43" t="s">
         <v>185</v>
@@ -5584,13 +5641,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B44" t="s">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="C44" t="s">
-        <v>1040</v>
+        <v>1059</v>
       </c>
       <c r="D44" t="s">
         <v>127</v>
@@ -5599,32 +5656,32 @@
         <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>1113</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B45" t="s">
-        <v>1114</v>
+        <v>1133</v>
       </c>
       <c r="C45" t="s">
-        <v>1115</v>
+        <v>1134</v>
       </c>
       <c r="D45" t="s">
         <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>1116</v>
+        <v>1135</v>
       </c>
       <c r="F45" t="s">
-        <v>1050</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B46" t="s">
         <v>343</v>
@@ -5639,24 +5696,24 @@
         <v>185</v>
       </c>
       <c r="F46" t="s">
-        <v>1117</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B47" t="s">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="C47" t="s">
-        <v>1119</v>
+        <v>1138</v>
       </c>
       <c r="D47" t="s">
         <v>125</v>
       </c>
       <c r="E47" t="s">
-        <v>1120</v>
+        <v>1139</v>
       </c>
       <c r="F47" t="s">
         <v>116</v>
@@ -5664,19 +5721,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B48" t="s">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="C48" t="s">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="D48" t="s">
         <v>126</v>
       </c>
       <c r="E48" t="s">
-        <v>1120</v>
+        <v>1139</v>
       </c>
       <c r="F48" t="s">
         <v>185</v>
@@ -5684,10 +5741,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B49" t="s">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="C49" t="s">
         <v>280</v>
@@ -5696,7 +5753,7 @@
         <v>125</v>
       </c>
       <c r="E49" t="s">
-        <v>1124</v>
+        <v>1143</v>
       </c>
       <c r="F49" t="s">
         <v>185</v>
@@ -5704,19 +5761,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B50" t="s">
         <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="D50" t="s">
         <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>1125</v>
+        <v>1144</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
@@ -5724,19 +5781,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B51" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="C51" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="D51" t="s">
         <v>125</v>
       </c>
       <c r="E51" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
       <c r="F51" t="s">
         <v>116</v>
@@ -5744,13 +5801,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B52" t="s">
-        <v>1127</v>
+        <v>1146</v>
       </c>
       <c r="C52" t="s">
-        <v>1128</v>
+        <v>1147</v>
       </c>
       <c r="D52" t="s">
         <v>147</v>
@@ -5764,13 +5821,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B53" t="s">
-        <v>1129</v>
+        <v>1148</v>
       </c>
       <c r="C53" t="s">
-        <v>1130</v>
+        <v>1149</v>
       </c>
       <c r="D53" t="s">
         <v>147</v>
@@ -5784,13 +5841,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B54" t="s">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="C54" t="s">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="D54" t="s">
         <v>147</v>
@@ -5804,13 +5861,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B55" t="s">
-        <v>1133</v>
+        <v>1152</v>
       </c>
       <c r="C55" t="s">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="D55" t="s">
         <v>126</v>
@@ -5819,12 +5876,12 @@
         <v>185</v>
       </c>
       <c r="F55" t="s">
-        <v>1051</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="B56" t="s">
         <v>124</v>
@@ -5844,7 +5901,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B57" t="s">
         <v>117</v>
@@ -5864,7 +5921,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B58" t="s">
         <v>118</v>
@@ -5884,13 +5941,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B59" t="s">
-        <v>1135</v>
+        <v>1154</v>
       </c>
       <c r="C59" t="s">
-        <v>1136</v>
+        <v>1155</v>
       </c>
       <c r="D59" t="s">
         <v>125</v>
@@ -5904,13 +5961,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B60" t="s">
-        <v>1137</v>
+        <v>1156</v>
       </c>
       <c r="C60" t="s">
-        <v>1138</v>
+        <v>1157</v>
       </c>
       <c r="D60" t="s">
         <v>125</v>
@@ -5924,13 +5981,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B61" t="s">
-        <v>1139</v>
+        <v>1158</v>
       </c>
       <c r="C61" t="s">
-        <v>1140</v>
+        <v>1159</v>
       </c>
       <c r="D61" t="s">
         <v>147</v>
@@ -5944,13 +6001,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B62" t="s">
-        <v>1141</v>
+        <v>1160</v>
       </c>
       <c r="C62" t="s">
-        <v>1142</v>
+        <v>1161</v>
       </c>
       <c r="D62" t="s">
         <v>147</v>
@@ -5964,13 +6021,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B63" t="s">
-        <v>1143</v>
+        <v>1162</v>
       </c>
       <c r="C63" t="s">
-        <v>1144</v>
+        <v>1163</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -5984,13 +6041,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B64" t="s">
-        <v>1145</v>
+        <v>1164</v>
       </c>
       <c r="C64" t="s">
-        <v>1146</v>
+        <v>1165</v>
       </c>
       <c r="D64" t="s">
         <v>147</v>
@@ -6004,13 +6061,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B65" t="s">
-        <v>1147</v>
+        <v>1166</v>
       </c>
       <c r="C65" t="s">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="D65" t="s">
         <v>147</v>
@@ -6024,13 +6081,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B66" t="s">
-        <v>1149</v>
+        <v>1168</v>
       </c>
       <c r="C66" t="s">
-        <v>1150</v>
+        <v>1169</v>
       </c>
       <c r="D66" t="s">
         <v>147</v>
@@ -6044,13 +6101,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B67" t="s">
-        <v>1151</v>
+        <v>1170</v>
       </c>
       <c r="C67" t="s">
-        <v>1152</v>
+        <v>1171</v>
       </c>
       <c r="D67" t="s">
         <v>147</v>
@@ -6064,13 +6121,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B68" t="s">
-        <v>1153</v>
+        <v>1172</v>
       </c>
       <c r="C68" t="s">
-        <v>1154</v>
+        <v>1173</v>
       </c>
       <c r="D68" t="s">
         <v>147</v>
@@ -6084,13 +6141,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B69" t="s">
-        <v>1155</v>
+        <v>1174</v>
       </c>
       <c r="C69" t="s">
-        <v>1156</v>
+        <v>1175</v>
       </c>
       <c r="D69" t="s">
         <v>147</v>
@@ -6104,13 +6161,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B70" t="s">
-        <v>1157</v>
+        <v>1176</v>
       </c>
       <c r="C70" t="s">
-        <v>1158</v>
+        <v>1177</v>
       </c>
       <c r="D70" t="s">
         <v>147</v>
@@ -6124,13 +6181,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B71" t="s">
-        <v>1159</v>
+        <v>1178</v>
       </c>
       <c r="C71" t="s">
-        <v>1160</v>
+        <v>1179</v>
       </c>
       <c r="D71" t="s">
         <v>125</v>
@@ -6144,7 +6201,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="B72" t="s">
         <v>124</v>
@@ -6164,7 +6221,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B73" t="s">
         <v>117</v>
@@ -6184,7 +6241,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B74" t="s">
         <v>118</v>
@@ -6204,7 +6261,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B75" t="s">
         <v>343</v>
@@ -6219,12 +6276,12 @@
         <v>185</v>
       </c>
       <c r="F75" t="s">
-        <v>1162</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B76" t="s">
         <v>121</v>
@@ -6244,19 +6301,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B77" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="C77" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="D77" t="s">
         <v>125</v>
       </c>
       <c r="E77" t="s">
-        <v>1163</v>
+        <v>1182</v>
       </c>
       <c r="F77" t="s">
         <v>116</v>
@@ -6264,19 +6321,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B78" t="s">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="C78" t="s">
-        <v>1119</v>
+        <v>1138</v>
       </c>
       <c r="D78" t="s">
         <v>125</v>
       </c>
       <c r="E78" t="s">
-        <v>1164</v>
+        <v>1183</v>
       </c>
       <c r="F78" t="s">
         <v>116</v>
@@ -6284,19 +6341,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B79" t="s">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="C79" t="s">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="D79" t="s">
         <v>126</v>
       </c>
       <c r="E79" t="s">
-        <v>1164</v>
+        <v>1183</v>
       </c>
       <c r="F79" t="s">
         <v>185</v>
@@ -6304,13 +6361,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B80" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="C80" t="s">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="D80" t="s">
         <v>127</v>
@@ -6319,18 +6376,18 @@
         <v>185</v>
       </c>
       <c r="F80" t="s">
-        <v>1165</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B81" t="s">
-        <v>1166</v>
+        <v>1185</v>
       </c>
       <c r="C81" t="s">
-        <v>1167</v>
+        <v>1186</v>
       </c>
       <c r="D81" t="s">
         <v>147</v>
@@ -6344,13 +6401,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B82" t="s">
-        <v>1168</v>
+        <v>1187</v>
       </c>
       <c r="C82" t="s">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="D82" t="s">
         <v>147</v>
@@ -6364,7 +6421,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
@@ -6384,10 +6441,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="B84" t="s">
-        <v>1170</v>
+        <v>1189</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -6399,12 +6456,12 @@
         <v>185</v>
       </c>
       <c r="F84" t="s">
-        <v>1171</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="B85" t="s">
         <v>117</v>
@@ -6424,7 +6481,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="B86" t="s">
         <v>118</v>
@@ -6444,13 +6501,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="B87" t="s">
-        <v>1173</v>
+        <v>1192</v>
       </c>
       <c r="C87" t="s">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="D87" t="s">
         <v>125</v>
@@ -6464,13 +6521,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="B88" t="s">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="C88" t="s">
-        <v>1176</v>
+        <v>1195</v>
       </c>
       <c r="D88" t="s">
         <v>125</v>
@@ -6484,7 +6541,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="B89" t="s">
         <v>124</v>
@@ -6504,7 +6561,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B90" t="s">
         <v>117</v>
@@ -6524,7 +6581,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B91" t="s">
         <v>118</v>
@@ -6544,19 +6601,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B92" t="s">
         <v>417</v>
       </c>
       <c r="C92" t="s">
-        <v>1178</v>
+        <v>1197</v>
       </c>
       <c r="D92" t="s">
         <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="F92" t="s">
         <v>185</v>
@@ -6564,10 +6621,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B93" t="s">
-        <v>1180</v>
+        <v>1199</v>
       </c>
       <c r="C93" t="s">
         <v>284</v>
@@ -6584,13 +6641,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B94" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="C94" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D94" t="s">
         <v>147</v>
@@ -6604,13 +6661,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B95" t="s">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="C95" t="s">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="D95" t="s">
         <v>147</v>
@@ -6624,7 +6681,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B96" t="s">
         <v>124</v>
@@ -6644,7 +6701,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B97" t="s">
         <v>117</v>
@@ -6664,7 +6721,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B98" t="s">
         <v>118</v>
@@ -6684,13 +6741,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B99" t="s">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="C99" t="s">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="D99" t="s">
         <v>125</v>
@@ -6704,13 +6761,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B100" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
       <c r="C100" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="D100" t="s">
         <v>125</v>
@@ -6724,13 +6781,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B101" t="s">
-        <v>1190</v>
+        <v>1209</v>
       </c>
       <c r="C101" t="s">
-        <v>1191</v>
+        <v>1210</v>
       </c>
       <c r="D101" t="s">
         <v>125</v>
@@ -6744,13 +6801,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B102" t="s">
-        <v>1192</v>
+        <v>1211</v>
       </c>
       <c r="C102" t="s">
-        <v>1193</v>
+        <v>1212</v>
       </c>
       <c r="D102" t="s">
         <v>125</v>
@@ -6764,13 +6821,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B103" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="C103" t="s">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="D103" t="s">
         <v>125</v>
@@ -6784,13 +6841,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B104" t="s">
-        <v>1196</v>
+        <v>1215</v>
       </c>
       <c r="C104" t="s">
-        <v>1197</v>
+        <v>1216</v>
       </c>
       <c r="D104" t="s">
         <v>125</v>
@@ -6804,7 +6861,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="B105" t="s">
         <v>124</v>
@@ -6867,10 +6924,10 @@
         <v>782</v>
       </c>
       <c r="B108" t="s">
-        <v>1198</v>
+        <v>1217</v>
       </c>
       <c r="C108" t="s">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="D108" t="s">
         <v>126</v>
@@ -6887,10 +6944,10 @@
         <v>782</v>
       </c>
       <c r="B109" t="s">
-        <v>1200</v>
+        <v>1219</v>
       </c>
       <c r="C109" t="s">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="D109" t="s">
         <v>126</v>
@@ -6910,7 +6967,7 @@
         <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>1202</v>
+        <v>1221</v>
       </c>
       <c r="D110" t="s">
         <v>127</v>
@@ -6919,7 +6976,7 @@
         <v>185</v>
       </c>
       <c r="F110" t="s">
-        <v>1203</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -6927,10 +6984,10 @@
         <v>782</v>
       </c>
       <c r="B111" t="s">
-        <v>1204</v>
+        <v>1223</v>
       </c>
       <c r="C111" t="s">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="D111" t="s">
         <v>125</v>
@@ -6947,10 +7004,10 @@
         <v>782</v>
       </c>
       <c r="B112" t="s">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="C112" t="s">
-        <v>1045</v>
+        <v>1064</v>
       </c>
       <c r="D112" t="s">
         <v>125</v>
@@ -6964,7 +7021,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B113" t="s">
         <v>117</v>
@@ -6984,7 +7041,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B114" t="s">
         <v>118</v>
@@ -7004,7 +7061,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B115" t="s">
         <v>144</v>
@@ -7024,7 +7081,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B116" t="s">
         <v>119</v>
@@ -7044,7 +7101,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B117" t="s">
         <v>145</v>
@@ -7064,7 +7121,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B118" t="s">
         <v>146</v>
@@ -7084,7 +7141,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B119" t="s">
         <v>124</v>
@@ -7104,7 +7161,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B120" t="s">
         <v>117</v>
@@ -7124,7 +7181,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B121" t="s">
         <v>118</v>
@@ -7144,7 +7201,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B122" t="s">
         <v>214</v>
@@ -7164,7 +7221,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B123" t="s">
         <v>215</v>
@@ -7184,7 +7241,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B124" t="s">
         <v>216</v>
@@ -7204,7 +7261,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B125" t="s">
         <v>117</v>
@@ -7224,7 +7281,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B126" t="s">
         <v>129</v>
@@ -7244,13 +7301,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B127" t="s">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="C127" t="s">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="D127" t="s">
         <v>126</v>
@@ -7264,13 +7321,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B128" t="s">
-        <v>1211</v>
+        <v>1230</v>
       </c>
       <c r="C128" t="s">
-        <v>1212</v>
+        <v>1231</v>
       </c>
       <c r="D128" t="s">
         <v>147</v>
@@ -7284,13 +7341,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B129" t="s">
-        <v>1213</v>
+        <v>1232</v>
       </c>
       <c r="C129" t="s">
-        <v>1214</v>
+        <v>1233</v>
       </c>
       <c r="D129" t="s">
         <v>147</v>
@@ -7304,13 +7361,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B130" t="s">
-        <v>1215</v>
+        <v>1234</v>
       </c>
       <c r="C130" t="s">
-        <v>1216</v>
+        <v>1235</v>
       </c>
       <c r="D130" t="s">
         <v>147</v>
@@ -7324,13 +7381,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B131" t="s">
-        <v>1217</v>
+        <v>1236</v>
       </c>
       <c r="C131" t="s">
-        <v>1058</v>
+        <v>1077</v>
       </c>
       <c r="D131" t="s">
         <v>147</v>
@@ -7344,13 +7401,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B132" t="s">
-        <v>1056</v>
+        <v>1075</v>
       </c>
       <c r="C132" t="s">
-        <v>1060</v>
+        <v>1079</v>
       </c>
       <c r="D132" t="s">
         <v>125</v>
@@ -7364,10 +7421,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B133" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="C133" t="s">
         <v>128</v>
@@ -7384,7 +7441,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B134" t="s">
         <v>129</v>
@@ -7404,13 +7461,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B135" t="s">
-        <v>1034</v>
+        <v>1053</v>
       </c>
       <c r="C135" t="s">
-        <v>1040</v>
+        <v>1059</v>
       </c>
       <c r="D135" t="s">
         <v>127</v>
@@ -7419,18 +7476,18 @@
         <v>185</v>
       </c>
       <c r="F135" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B136" t="s">
         <v>119</v>
       </c>
       <c r="C136" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="D136" t="s">
         <v>125</v>
@@ -7444,16 +7501,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B137" t="s">
-        <v>1035</v>
+        <v>1054</v>
       </c>
       <c r="C137" t="s">
-        <v>1042</v>
+        <v>1061</v>
       </c>
       <c r="D137" t="s">
-        <v>1039</v>
+        <v>1058</v>
       </c>
       <c r="E137" t="s">
         <v>185</v>
@@ -7464,16 +7521,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B138" t="s">
-        <v>1036</v>
+        <v>1055</v>
       </c>
       <c r="C138" t="s">
-        <v>1043</v>
+        <v>1062</v>
       </c>
       <c r="D138" t="s">
-        <v>1039</v>
+        <v>1058</v>
       </c>
       <c r="E138" t="s">
         <v>185</v>
@@ -7484,16 +7541,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B139" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="C139" t="s">
-        <v>1044</v>
+        <v>1063</v>
       </c>
       <c r="D139" t="s">
-        <v>1039</v>
+        <v>1058</v>
       </c>
       <c r="E139" t="s">
         <v>185</v>
@@ -7504,13 +7561,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B140" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
       <c r="C140" t="s">
-        <v>1045</v>
+        <v>1064</v>
       </c>
       <c r="D140" t="s">
         <v>125</v>
@@ -7524,7 +7581,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B141" t="s">
         <v>124</v>
@@ -7544,7 +7601,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B142" t="s">
         <v>117</v>
@@ -7564,7 +7621,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B143" t="s">
         <v>118</v>
@@ -7584,7 +7641,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B144" t="s">
         <v>119</v>
@@ -7604,10 +7661,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B145" t="s">
-        <v>1052</v>
+        <v>1071</v>
       </c>
       <c r="C145" t="s">
         <v>16</v>
@@ -7619,12 +7676,12 @@
         <v>185</v>
       </c>
       <c r="F145" t="s">
-        <v>1050</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B146" t="s">
         <v>121</v>
@@ -7644,13 +7701,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B147" t="s">
-        <v>1053</v>
+        <v>1072</v>
       </c>
       <c r="C147" t="s">
-        <v>1057</v>
+        <v>1076</v>
       </c>
       <c r="D147" t="s">
         <v>147</v>
@@ -7664,13 +7721,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B148" t="s">
-        <v>1054</v>
+        <v>1073</v>
       </c>
       <c r="C148" t="s">
-        <v>1058</v>
+        <v>1077</v>
       </c>
       <c r="D148" t="s">
         <v>147</v>
@@ -7684,13 +7741,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B149" t="s">
-        <v>1055</v>
+        <v>1074</v>
       </c>
       <c r="C149" t="s">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="D149" t="s">
         <v>126</v>
@@ -7699,18 +7756,18 @@
         <v>185</v>
       </c>
       <c r="F149" t="s">
-        <v>1051</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B150" t="s">
-        <v>1056</v>
+        <v>1075</v>
       </c>
       <c r="C150" t="s">
-        <v>1060</v>
+        <v>1079</v>
       </c>
       <c r="D150" t="s">
         <v>125</v>
@@ -7724,7 +7781,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="B151" t="s">
         <v>124</v>
@@ -7775,13 +7832,13 @@
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9" t="s">
-        <v>1113</v>
+        <v>1132</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1050</v>
+        <v>1069</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1117</v>
+        <v>1136</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>116</v>
@@ -7798,7 +7855,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
-        <v>1051</v>
+        <v>1070</v>
       </c>
       <c r="P1" s="9"/>
     </row>
@@ -7810,43 +7867,43 @@
         <v>118</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1109</v>
+        <v>1128</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1114</v>
+        <v>1133</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>343</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>121</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1127</v>
+        <v>1146</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>1129</v>
+        <v>1148</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>1133</v>
+        <v>1152</v>
       </c>
       <c r="P2" s="10" t="s">
         <v>124</v>
@@ -7910,43 +7967,43 @@
         <v>129</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1040</v>
+        <v>1059</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1115</v>
+        <v>1134</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>344</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1119</v>
+        <v>1138</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>280</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>1128</v>
+        <v>1147</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>1130</v>
+        <v>1149</v>
       </c>
       <c r="N4